--- a/2026/O HIGGINS 1157/Junio/Junio ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Junio/Junio ohiggins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8D2922-7A15-4BA9-A2AD-91B063F70847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA9D334-3521-4EA2-938C-1AF21387F432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="221">
   <si>
     <t>TOTAL</t>
   </si>
@@ -213,12 +213,6 @@
   </si>
   <si>
     <t>MOTIVO DE LA QUEJA:</t>
-  </si>
-  <si>
-    <t>VTO 18/06</t>
-  </si>
-  <si>
-    <t>PERÍODO: MAYO</t>
   </si>
   <si>
     <t>CUIT DEL EDIFICIO: 33-71743270-9</t>
@@ -488,12 +482,6 @@
     <t>Edesur - Cliente Nro. 04742252</t>
   </si>
   <si>
-    <t>Transf 04/05</t>
-  </si>
-  <si>
-    <t>Transf 05/05</t>
-  </si>
-  <si>
     <t>Transf 06/05</t>
   </si>
   <si>
@@ -515,27 +503,15 @@
     <t>Transf 13/05</t>
   </si>
   <si>
-    <t>Papeleria Corpa - Compra de caja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compra de bolsas </t>
-  </si>
-  <si>
     <t>Flores Lisandro - Revoque Gazeta de gas</t>
   </si>
   <si>
-    <t>Abono ascensor - ADS - Mantenimiento mes de abril</t>
-  </si>
-  <si>
     <t>Ferrateria La plaza - 6 dicroicas</t>
   </si>
   <si>
     <t>Transf 14/05</t>
   </si>
   <si>
-    <t>Honorarios administracion saliente - Del 01 al 15 de Mayo - Fc. 00585</t>
-  </si>
-  <si>
     <t>Traspaso administracion antigua - Honorarios cobrados por administracion saliente Fc- 000586</t>
   </si>
   <si>
@@ -557,18 +533,6 @@
     <t>Transf 29/04</t>
   </si>
   <si>
-    <t>Fernandez Carlos - Reparacion de postigones - Fc.  0009</t>
-  </si>
-  <si>
-    <t>Buenas Ondas - Articulos de limpieza - Fc 0002921</t>
-  </si>
-  <si>
-    <t>Matafuegos Protect Sur - Recarga de matafuegos - Fc. 0000195</t>
-  </si>
-  <si>
-    <t>Transf 08/05</t>
-  </si>
-  <si>
     <t>Casa Ruan - Compra de lamparas</t>
   </si>
   <si>
@@ -576,9 +540,6 @@
   </si>
   <si>
     <t>Orse Joathan Gabriel - Cambio de lampras en altura y medidores de gas</t>
-  </si>
-  <si>
-    <t>Honorarios administracion - Se adeuda Mitad de Mayo</t>
   </si>
   <si>
     <t xml:space="preserve">Gustavo Padron -  Sr. Contador </t>
@@ -704,6 +665,42 @@
   </si>
   <si>
     <t>Dice que este mes se equivoco y transfirio $183.820 de mas</t>
+  </si>
+  <si>
+    <t>VTO 17/07</t>
+  </si>
+  <si>
+    <t>PERÍODO: JUNIO</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Se adeuda Mitad de JUNIO</t>
+  </si>
+  <si>
+    <t>Honorarios administracion saliente - Del 01 al 15 de JUNIO - Fc. 00585</t>
+  </si>
+  <si>
+    <t>Abono ascensor - ADS - Mantenimiento mes de mayo</t>
+  </si>
+  <si>
+    <t>Romanatti Carlos - Certificacion de copias digitales</t>
+  </si>
+  <si>
+    <t>Transf 19/06</t>
+  </si>
+  <si>
+    <t>Citta Cerrajeria - Cambio de maquina cierrapuerta y cambio de herraje inferior</t>
+  </si>
+  <si>
+    <t>Doartero Julio - Colocacion de 4 visagras en puerta de aluminio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Servisur - cambio de lamparas y sensores </t>
+  </si>
+  <si>
+    <t>Transf 02/06</t>
+  </si>
+  <si>
+    <t>Transf 09/06</t>
   </si>
 </sst>
 </file>
@@ -1465,7 +1462,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1624,7 +1621,6 @@
     </xf>
     <xf numFmtId="44" fontId="11" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="8" fontId="20" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="11" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1758,174 +1754,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1933,6 +1761,176 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2320,12 +2318,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="187" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="188"/>
+      <c r="B1" s="186" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="187"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -2338,12 +2336,12 @@
     </row>
     <row r="3" spans="1:5" ht="56.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="189" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="189"/>
-      <c r="D3" s="189"/>
-      <c r="E3" s="190"/>
+      <c r="B3" s="190" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="191"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -2358,10 +2356,10 @@
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>63</v>
+        <v>210</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2381,49 +2379,49 @@
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="191" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="191"/>
+      <c r="B8" s="192" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="192"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="191"/>
-      <c r="C9" s="191"/>
+      <c r="B9" s="192"/>
+      <c r="C9" s="192"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="191"/>
-      <c r="C10" s="191"/>
+      <c r="B10" s="192"/>
+      <c r="C10" s="192"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="192" t="s">
-        <v>150</v>
-      </c>
-      <c r="B13" s="192"/>
-      <c r="C13" s="192"/>
-      <c r="D13" s="192"/>
-      <c r="E13" s="192"/>
+      <c r="A13" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="193"/>
+      <c r="C13" s="193"/>
+      <c r="D13" s="193"/>
+      <c r="E13" s="193"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="192"/>
-      <c r="B14" s="192"/>
-      <c r="C14" s="192"/>
-      <c r="D14" s="192"/>
-      <c r="E14" s="192"/>
+      <c r="A14" s="193"/>
+      <c r="B14" s="193"/>
+      <c r="C14" s="193"/>
+      <c r="D14" s="193"/>
+      <c r="E14" s="193"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="192"/>
-      <c r="B15" s="192"/>
-      <c r="C15" s="192"/>
-      <c r="D15" s="192"/>
-      <c r="E15" s="192"/>
+      <c r="A15" s="193"/>
+      <c r="B15" s="193"/>
+      <c r="C15" s="193"/>
+      <c r="D15" s="193"/>
+      <c r="E15" s="193"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="192"/>
-      <c r="B16" s="192"/>
-      <c r="C16" s="192"/>
-      <c r="D16" s="192"/>
-      <c r="E16" s="192"/>
+      <c r="A16" s="193"/>
+      <c r="B16" s="193"/>
+      <c r="C16" s="193"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2441,44 +2439,44 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
       <c r="D21" s="103"/>
-      <c r="E21" s="121"/>
+      <c r="E21" s="120"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="183" t="s">
+      <c r="A22" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="184"/>
+      <c r="B22" s="189"/>
       <c r="C22" s="20"/>
-      <c r="D22" s="163">
-        <v>1199023.2</v>
-      </c>
-      <c r="E22" s="122"/>
+      <c r="D22" s="162">
+        <v>1987270.86</v>
+      </c>
+      <c r="E22" s="121"/>
       <c r="H22" s="21"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="183" t="s">
+      <c r="A23" s="188" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="184"/>
+      <c r="B23" s="189"/>
       <c r="C23" s="20"/>
-      <c r="D23" s="163">
-        <v>-260787.54</v>
+      <c r="D23" s="162">
+        <v>-432231.42</v>
       </c>
       <c r="E23" s="22"/>
       <c r="H23" s="21"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="183" t="s">
+      <c r="A24" s="188" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="184"/>
+      <c r="B24" s="189"/>
       <c r="C24" s="20"/>
-      <c r="D24" s="164">
+      <c r="D24" s="163">
         <v>0.34</v>
       </c>
       <c r="E24" s="22"/>
@@ -2491,9 +2489,9 @@
       <c r="B25" s="23"/>
       <c r="C25" s="23"/>
       <c r="D25" s="24"/>
-      <c r="E25" s="123">
+      <c r="E25" s="122">
         <f>SUM(D22:D24)</f>
-        <v>938235.99999999988</v>
+        <v>1555039.7800000003</v>
       </c>
     </row>
     <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -2503,28 +2501,28 @@
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
       <c r="D26" s="24"/>
-      <c r="E26" s="124"/>
+      <c r="E26" s="123"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="20"/>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
       <c r="D27" s="36"/>
-      <c r="E27" s="136"/>
+      <c r="E27" s="135"/>
     </row>
     <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20"/>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
       <c r="D28" s="36"/>
-      <c r="E28" s="136"/>
+      <c r="E28" s="135"/>
     </row>
     <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20"/>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
       <c r="D29" s="36"/>
-      <c r="E29" s="136"/>
+      <c r="E29" s="135"/>
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
@@ -2533,7 +2531,7 @@
       <c r="B30" s="29"/>
       <c r="C30" s="29"/>
       <c r="D30" s="93"/>
-      <c r="E30" s="126">
+      <c r="E30" s="125">
         <f>SUM(D27:D29)</f>
         <v>0</v>
       </c>
@@ -2545,35 +2543,35 @@
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="24"/>
-      <c r="E31" s="124"/>
+      <c r="E31" s="123"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B32" s="85"/>
       <c r="C32" s="85"/>
       <c r="D32" s="36">
         <v>641302.6</v>
       </c>
-      <c r="E32" s="125" t="s">
-        <v>157</v>
+      <c r="E32" s="124" t="s">
+        <v>153</v>
       </c>
       <c r="G32" s="67"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="20" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C33" s="85"/>
       <c r="D33" s="36">
         <v>182823.01</v>
       </c>
-      <c r="E33" s="125" t="s">
-        <v>172</v>
+      <c r="E33" s="124" t="s">
+        <v>164</v>
       </c>
       <c r="G33" s="67"/>
     </row>
@@ -2583,11 +2581,11 @@
       </c>
       <c r="B34" s="85"/>
       <c r="C34" s="85"/>
-      <c r="D34" s="36">
-        <v>58593.37</v>
-      </c>
-      <c r="E34" s="125" t="s">
-        <v>156</v>
+      <c r="D34" s="243">
+        <v>53956.04</v>
+      </c>
+      <c r="E34" s="124" t="s">
+        <v>152</v>
       </c>
       <c r="G34" s="67"/>
     </row>
@@ -2597,10 +2595,10 @@
       </c>
       <c r="B35" s="85"/>
       <c r="C35" s="85"/>
-      <c r="D35" s="36">
-        <v>6510.37</v>
-      </c>
-      <c r="E35" s="125" t="str">
+      <c r="D35" s="243">
+        <v>5995.12</v>
+      </c>
+      <c r="E35" s="124" t="str">
         <f>E34</f>
         <v>Debito 12/05</v>
       </c>
@@ -2612,10 +2610,10 @@
       </c>
       <c r="B36" s="85"/>
       <c r="C36" s="85"/>
-      <c r="D36" s="36">
-        <v>102793.15</v>
-      </c>
-      <c r="E36" s="125" t="str">
+      <c r="D36" s="243">
+        <v>97494.97</v>
+      </c>
+      <c r="E36" s="124" t="str">
         <f>E34</f>
         <v>Debito 12/05</v>
       </c>
@@ -2629,7 +2627,7 @@
       <c r="D37" s="24"/>
       <c r="E37" s="42">
         <f>SUM(D32:D36)</f>
-        <v>992022.5</v>
+        <v>981571.74</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -2639,28 +2637,28 @@
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
       <c r="D38" s="25"/>
-      <c r="E38" s="126"/>
+      <c r="E38" s="125"/>
     </row>
     <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="180" t="s">
-        <v>72</v>
-      </c>
-      <c r="B39" s="181"/>
+      <c r="A39" s="194" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="195"/>
       <c r="C39" s="28"/>
-      <c r="D39" s="162">
+      <c r="D39" s="161">
         <v>205033.71</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="180" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" s="181"/>
+      <c r="A40" s="194" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="195"/>
       <c r="C40" s="28"/>
-      <c r="D40" s="162">
+      <c r="D40" s="161">
         <v>1282.32</v>
       </c>
       <c r="E40" s="22" t="str">
@@ -2669,12 +2667,12 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="180" t="s">
-        <v>74</v>
-      </c>
-      <c r="B41" s="181"/>
+      <c r="A41" s="194" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="195"/>
       <c r="C41" s="28"/>
-      <c r="D41" s="162">
+      <c r="D41" s="161">
         <v>12020</v>
       </c>
       <c r="E41" s="22" t="str">
@@ -2701,57 +2699,59 @@
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
       <c r="D43" s="30"/>
-      <c r="E43" s="127"/>
+      <c r="E43" s="126"/>
     </row>
     <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="31" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B44" s="31"/>
       <c r="C44" s="31"/>
-      <c r="D44" s="161">
-        <v>997677.51</v>
-      </c>
-      <c r="E44" s="22" t="s">
-        <v>152</v>
+      <c r="D44" s="242">
+        <v>1313151.8700000001</v>
+      </c>
+      <c r="E44" s="35" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="31" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B45" s="32"/>
       <c r="C45" s="31"/>
-      <c r="D45" s="161">
-        <v>6087.49</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>153</v>
+      <c r="D45" s="242">
+        <v>5910.35</v>
+      </c>
+      <c r="E45" s="35" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="180" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="181"/>
+      <c r="A46" s="194" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" s="195"/>
       <c r="C46" s="31"/>
-      <c r="D46" s="161">
-        <v>570397.97</v>
-      </c>
-      <c r="E46" s="104" t="s">
-        <v>160</v>
+      <c r="D46" s="242">
+        <v>511264.75</v>
+      </c>
+      <c r="E46" s="35" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="33" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B47" s="27"/>
       <c r="C47" s="31"/>
-      <c r="D47" s="161">
-        <v>0</v>
-      </c>
-      <c r="E47" s="22"/>
+      <c r="D47" s="242">
+        <v>62785.37</v>
+      </c>
+      <c r="E47" s="35" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="23" t="s">
@@ -2760,181 +2760,181 @@
       <c r="B48" s="23"/>
       <c r="C48" s="23"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="128">
+      <c r="E48" s="127">
         <f>SUM(D44:D47)</f>
-        <v>1574162.97</v>
+        <v>1893112.3400000003</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
       <c r="D49" s="24"/>
-      <c r="E49" s="129"/>
+      <c r="E49" s="128"/>
     </row>
     <row r="50" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="183" t="s">
-        <v>164</v>
-      </c>
-      <c r="B50" s="184"/>
+      <c r="A50" s="188" t="s">
+        <v>213</v>
+      </c>
+      <c r="B50" s="189"/>
       <c r="C50" s="31"/>
-      <c r="D50" s="161">
+      <c r="D50" s="160">
         <v>250600</v>
       </c>
       <c r="E50" s="35" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="188" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="183" t="s">
-        <v>158</v>
-      </c>
-      <c r="B51" s="184"/>
+      <c r="B51" s="189"/>
       <c r="C51" s="31"/>
-      <c r="D51" s="161">
+      <c r="D51" s="160">
         <v>367392.3</v>
       </c>
       <c r="E51" s="35" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="183" t="s">
-        <v>173</v>
-      </c>
-      <c r="B52" s="184"/>
+      <c r="A52" s="188" t="s">
+        <v>165</v>
+      </c>
+      <c r="B52" s="189"/>
       <c r="C52" s="31"/>
-      <c r="D52" s="161">
+      <c r="D52" s="160">
         <v>2130000</v>
       </c>
       <c r="E52" s="35" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="158" t="s">
-        <v>175</v>
+      <c r="A53" s="157" t="s">
+        <v>214</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="20"/>
-      <c r="D53" s="161">
-        <v>73000</v>
+      <c r="D53" s="242">
+        <v>332362.82</v>
       </c>
       <c r="E53" s="35" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="F53" s="51"/>
     </row>
     <row r="54" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="87" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="B54" s="19"/>
       <c r="C54" s="20"/>
-      <c r="D54" s="161">
-        <v>840000</v>
+      <c r="D54" s="242">
+        <v>810000</v>
       </c>
       <c r="E54" s="35" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="F54" s="51"/>
     </row>
     <row r="55" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="193" t="s">
-        <v>161</v>
-      </c>
-      <c r="B55" s="194"/>
+      <c r="A55" s="196" t="s">
+        <v>217</v>
+      </c>
+      <c r="B55" s="197"/>
       <c r="C55" s="20"/>
-      <c r="D55" s="161">
-        <v>4400</v>
+      <c r="D55" s="242">
+        <v>180000</v>
       </c>
       <c r="E55" s="35" t="s">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="F55" s="51"/>
     </row>
     <row r="56" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="87" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="B56" s="19"/>
       <c r="C56" s="20"/>
-      <c r="D56" s="161">
-        <v>60500</v>
+      <c r="D56" s="242">
+        <v>60000</v>
       </c>
       <c r="E56" s="35" t="s">
-        <v>154</v>
+        <v>219</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="87" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B57" s="19"/>
       <c r="C57" s="20"/>
-      <c r="D57" s="161">
-        <v>28000</v>
-      </c>
-      <c r="E57" s="135" t="s">
-        <v>160</v>
+      <c r="D57" s="242">
+        <v>31000</v>
+      </c>
+      <c r="E57" s="35" t="s">
+        <v>219</v>
       </c>
       <c r="F57" s="51"/>
     </row>
     <row r="58" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="87" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B58" s="19"/>
       <c r="C58" s="20"/>
-      <c r="D58" s="161">
+      <c r="D58" s="160">
         <v>10400</v>
       </c>
-      <c r="E58" s="135" t="s">
-        <v>180</v>
+      <c r="E58" s="134" t="s">
+        <v>168</v>
       </c>
       <c r="F58" s="51"/>
     </row>
     <row r="59" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="183" t="s">
-        <v>181</v>
-      </c>
-      <c r="B59" s="184"/>
+      <c r="A59" s="188" t="s">
+        <v>169</v>
+      </c>
+      <c r="B59" s="189"/>
       <c r="C59" s="20"/>
-      <c r="D59" s="161">
+      <c r="D59" s="160">
         <v>50000</v>
       </c>
-      <c r="E59" s="135" t="s">
-        <v>180</v>
+      <c r="E59" s="134" t="s">
+        <v>168</v>
       </c>
       <c r="F59" s="51"/>
     </row>
     <row r="60" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="183" t="s">
-        <v>163</v>
-      </c>
-      <c r="B60" s="184"/>
+      <c r="A60" s="188" t="s">
+        <v>157</v>
+      </c>
+      <c r="B60" s="189"/>
       <c r="C60" s="20"/>
-      <c r="D60" s="161">
+      <c r="D60" s="160">
         <v>127000</v>
       </c>
-      <c r="E60" s="135" t="s">
-        <v>160</v>
+      <c r="E60" s="134" t="s">
+        <v>156</v>
       </c>
       <c r="F60" s="51"/>
     </row>
     <row r="61" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="183" t="s">
-        <v>165</v>
-      </c>
-      <c r="B61" s="184"/>
+      <c r="A61" s="188" t="s">
+        <v>158</v>
+      </c>
+      <c r="B61" s="189"/>
       <c r="C61" s="20"/>
-      <c r="D61" s="161">
+      <c r="D61" s="160">
         <v>7200</v>
       </c>
-      <c r="E61" s="135" t="s">
-        <v>166</v>
+      <c r="E61" s="134" t="s">
+        <v>159</v>
       </c>
       <c r="F61" s="51"/>
     </row>
@@ -2947,7 +2947,7 @@
       <c r="D62" s="37"/>
       <c r="E62" s="42">
         <f>SUM(D50:D61)</f>
-        <v>3948492.3</v>
+        <v>4355955.1199999992</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2957,55 +2957,55 @@
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
       <c r="D63" s="18"/>
-      <c r="E63" s="121"/>
+      <c r="E63" s="120"/>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="183" t="s">
-        <v>182</v>
-      </c>
-      <c r="B64" s="184"/>
+      <c r="A64" s="188" t="s">
+        <v>211</v>
+      </c>
+      <c r="B64" s="189"/>
       <c r="C64" s="20"/>
-      <c r="D64" s="165">
-        <v>0</v>
-      </c>
-      <c r="E64" s="122"/>
+      <c r="D64" s="164">
+        <v>0</v>
+      </c>
+      <c r="E64" s="121"/>
     </row>
     <row r="65" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="183" t="s">
-        <v>167</v>
-      </c>
-      <c r="B65" s="184"/>
+      <c r="A65" s="188" t="s">
+        <v>212</v>
+      </c>
+      <c r="B65" s="189"/>
       <c r="C65" s="20"/>
-      <c r="D65" s="160">
+      <c r="D65" s="159">
         <v>230000</v>
       </c>
-      <c r="E65" s="122" t="s">
-        <v>169</v>
+      <c r="E65" s="121" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="183" t="s">
-        <v>168</v>
-      </c>
-      <c r="B66" s="184"/>
+      <c r="A66" s="188" t="s">
+        <v>160</v>
+      </c>
+      <c r="B66" s="189"/>
       <c r="C66" s="20"/>
-      <c r="D66" s="160">
+      <c r="D66" s="159">
         <v>460000</v>
       </c>
-      <c r="E66" s="122" t="s">
-        <v>169</v>
+      <c r="E66" s="121" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="87" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="B67" s="19"/>
       <c r="C67" s="20"/>
-      <c r="D67" s="160">
-        <v>0</v>
-      </c>
-      <c r="E67" s="122"/>
+      <c r="D67" s="159">
+        <v>0</v>
+      </c>
+      <c r="E67" s="121"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="23" t="s">
@@ -3014,7 +3014,7 @@
       <c r="B68" s="23"/>
       <c r="C68" s="23"/>
       <c r="D68" s="24"/>
-      <c r="E68" s="123">
+      <c r="E68" s="122">
         <f>SUM(D64:D67)</f>
         <v>690000</v>
       </c>
@@ -3030,26 +3030,26 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="31" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B70" s="86"/>
       <c r="C70" s="86"/>
-      <c r="D70" s="105">
+      <c r="D70" s="104">
         <v>69000</v>
       </c>
-      <c r="E70" s="130"/>
+      <c r="E70" s="129"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="31" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="B71" s="86"/>
       <c r="C71" s="86"/>
-      <c r="D71" s="105">
+      <c r="D71" s="104">
         <f>110434.89+15074+30455</f>
         <v>155963.89000000001</v>
       </c>
-      <c r="E71" s="130"/>
+      <c r="E71" s="129"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="40" t="s">
@@ -3094,7 +3094,7 @@
       <c r="D76" s="55"/>
       <c r="E76" s="56">
         <f>(SUM(E21:E74))</f>
-        <v>8586213.6899999995</v>
+        <v>9918978.9000000004</v>
       </c>
       <c r="F76" s="57"/>
       <c r="G76" s="51"/>
@@ -3118,11 +3118,11 @@
       <c r="E79" s="60"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="185"/>
-      <c r="B80" s="186"/>
+      <c r="A80" s="199"/>
+      <c r="B80" s="200"/>
       <c r="C80" s="31"/>
-      <c r="D80" s="145"/>
-      <c r="E80" s="146"/>
+      <c r="D80" s="144"/>
+      <c r="E80" s="145"/>
     </row>
     <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D81" s="43"/>
@@ -3142,7 +3142,7 @@
       <c r="B83" s="64"/>
       <c r="C83" s="64"/>
       <c r="D83" s="102"/>
-      <c r="E83" s="131">
+      <c r="E83" s="130">
         <f>SUM(D80:D82)</f>
         <v>0</v>
       </c>
@@ -3158,7 +3158,7 @@
       <c r="B85" s="45"/>
       <c r="C85" s="45"/>
       <c r="D85" s="46"/>
-      <c r="E85" s="134">
+      <c r="E85" s="133">
         <v>0</v>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B89" s="66">
         <f>E76</f>
-        <v>8586213.6899999995</v>
+        <v>9918978.9000000004</v>
       </c>
       <c r="D89" s="49"/>
       <c r="E89" s="49"/>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="B90" s="66">
         <f>E76-E74</f>
-        <v>8586213.6899999995</v>
+        <v>9918978.9000000004</v>
       </c>
       <c r="D90" s="49"/>
       <c r="E90" s="49"/>
@@ -3235,8 +3235,8 @@
       <c r="E94" s="49"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="137" t="s">
-        <v>195</v>
+      <c r="A95" s="136" t="s">
+        <v>182</v>
       </c>
       <c r="B95" s="70">
         <v>0</v>
@@ -3246,7 +3246,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="28" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B96" s="71">
         <v>2000000</v>
@@ -3256,13 +3256,13 @@
     </row>
     <row r="97" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="28"/>
-      <c r="B97" s="120"/>
+      <c r="B97" s="119"/>
       <c r="D97" s="49"/>
       <c r="E97" s="49"/>
     </row>
     <row r="98" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="73" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="B98" s="74">
         <v>2026301.37</v>
@@ -3271,20 +3271,20 @@
       <c r="E98" s="49"/>
     </row>
     <row r="99" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="166"/>
-      <c r="B99" s="167"/>
+      <c r="A99" s="165"/>
+      <c r="B99" s="166"/>
       <c r="D99" s="49"/>
       <c r="E99" s="49"/>
     </row>
     <row r="100" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="166"/>
-      <c r="B100" s="167"/>
+      <c r="A100" s="165"/>
+      <c r="B100" s="166"/>
       <c r="D100" s="49"/>
       <c r="E100" s="49"/>
     </row>
     <row r="101" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="137" t="s">
-        <v>201</v>
+      <c r="A101" s="136" t="s">
+        <v>188</v>
       </c>
       <c r="B101" s="70">
         <v>231400</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="102" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="28" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B102" s="71">
         <v>0</v>
@@ -3304,15 +3304,15 @@
     </row>
     <row r="103" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="B103" s="120"/>
+        <v>190</v>
+      </c>
+      <c r="B103" s="119"/>
       <c r="D103" s="49"/>
       <c r="E103" s="49"/>
     </row>
     <row r="104" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="73" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="B104" s="74">
         <f>SUM(B101:B103)</f>
@@ -3322,14 +3322,14 @@
       <c r="E104" s="49"/>
     </row>
     <row r="105" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="166"/>
-      <c r="B105" s="167"/>
+      <c r="A105" s="165"/>
+      <c r="B105" s="166"/>
       <c r="D105" s="49"/>
       <c r="E105" s="49"/>
     </row>
     <row r="106" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="137" t="s">
-        <v>204</v>
+      <c r="A106" s="136" t="s">
+        <v>191</v>
       </c>
       <c r="B106" s="70">
         <v>64328</v>
@@ -3339,7 +3339,7 @@
     </row>
     <row r="107" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="28" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B107" s="71">
         <v>0</v>
@@ -3349,15 +3349,15 @@
     </row>
     <row r="108" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="B108" s="120"/>
+        <v>190</v>
+      </c>
+      <c r="B108" s="119"/>
       <c r="D108" s="49"/>
       <c r="E108" s="49"/>
     </row>
     <row r="109" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="73" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="B109" s="74">
         <f>SUM(B106:B108)</f>
@@ -3370,27 +3370,27 @@
       <c r="A110"/>
       <c r="B110" s="67"/>
       <c r="C110" s="68"/>
-      <c r="D110" s="132"/>
-      <c r="E110" s="132"/>
+      <c r="D110" s="131"/>
+      <c r="E110" s="131"/>
     </row>
     <row r="111" spans="1:5" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="137" t="s">
-        <v>200</v>
+      <c r="A111" s="136" t="s">
+        <v>187</v>
       </c>
       <c r="B111" s="70">
         <v>4238170</v>
       </c>
       <c r="C111" s="68"/>
-      <c r="D111" s="133"/>
-      <c r="E111" s="133"/>
+      <c r="D111" s="132"/>
+      <c r="E111" s="132"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B112" s="170">
+      <c r="B112" s="169">
         <f>-B90-B91</f>
-        <v>-8586213.6899999995</v>
+        <v>-9918978.9000000004</v>
       </c>
       <c r="D112" s="49"/>
       <c r="E112" s="49"/>
@@ -3421,9 +3421,9 @@
     </row>
     <row r="115" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="28" t="s">
-        <v>205</v>
-      </c>
-      <c r="B115" s="169">
+        <v>192</v>
+      </c>
+      <c r="B115" s="168">
         <v>1576753.42</v>
       </c>
       <c r="D115" s="49"/>
@@ -3432,8 +3432,8 @@
     </row>
     <row r="116" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="28"/>
-      <c r="B116" s="120"/>
-      <c r="D116" s="168"/>
+      <c r="B116" s="119"/>
+      <c r="D116" s="167"/>
       <c r="E116" s="49"/>
       <c r="F116" s="67"/>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B117" s="74">
         <f>SUM(B111:C116)</f>
-        <v>3986543.7300000004</v>
+        <v>2653778.5199999996</v>
       </c>
       <c r="D117" s="67"/>
       <c r="E117" s="51"/>
@@ -3451,31 +3451,31 @@
     </row>
     <row r="118" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="119" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="171" t="s">
-        <v>206</v>
-      </c>
-      <c r="B119" s="172">
+      <c r="A119" s="170" t="s">
+        <v>193</v>
+      </c>
+      <c r="B119" s="171">
         <f>B117+B104</f>
-        <v>4217943.7300000004</v>
+        <v>2885178.5199999996</v>
       </c>
       <c r="E119" s="51"/>
     </row>
     <row r="120" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="182" t="s">
+      <c r="A121" s="198" t="s">
         <v>25</v>
       </c>
-      <c r="B121" s="182"/>
-      <c r="C121" s="182"/>
+      <c r="B121" s="198"/>
+      <c r="C121" s="198"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A122" s="182"/>
-      <c r="B122" s="182"/>
-      <c r="C122" s="182"/>
+      <c r="A122" s="198"/>
+      <c r="B122" s="198"/>
+      <c r="C122" s="198"/>
     </row>
     <row r="123" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="75" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="B123" s="101">
         <v>156782</v>
@@ -3498,6 +3498,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A121:C122"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A65:B65"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A64:B64"/>
@@ -3514,13 +3521,6 @@
     <mergeCell ref="A52:B52"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A121:C122"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A65:B65"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3554,50 +3554,50 @@
   <sheetData>
     <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="88"/>
-      <c r="B1" s="153"/>
+      <c r="B1" s="152"/>
       <c r="C1" s="89"/>
       <c r="D1" s="89"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="201" t="str">
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="227" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="201"/>
-      <c r="L1" s="201"/>
-      <c r="M1" s="201"/>
-      <c r="N1" s="201"/>
-      <c r="O1" s="201"/>
-      <c r="P1" s="202"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="227"/>
+      <c r="M1" s="227"/>
+      <c r="N1" s="227"/>
+      <c r="O1" s="227"/>
+      <c r="P1" s="228"/>
     </row>
     <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B2" s="154"/>
-      <c r="C2" s="174">
+        <v>195</v>
+      </c>
+      <c r="B2" s="153"/>
+      <c r="C2" s="173">
         <f>R3</f>
         <v>6319499.4800000004</v>
       </c>
       <c r="D2" s="90"/>
       <c r="E2" s="90"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="209"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="235"/>
       <c r="H2" s="90"/>
       <c r="I2" s="90"/>
-      <c r="J2" s="203"/>
-      <c r="K2" s="203"/>
-      <c r="L2" s="203"/>
-      <c r="M2" s="203"/>
-      <c r="N2" s="203"/>
-      <c r="O2" s="203"/>
-      <c r="P2" s="204"/>
+      <c r="J2" s="229"/>
+      <c r="K2" s="229"/>
+      <c r="L2" s="229"/>
+      <c r="M2" s="229"/>
+      <c r="N2" s="229"/>
+      <c r="O2" s="229"/>
+      <c r="P2" s="230"/>
       <c r="Q2" s="81"/>
       <c r="R2">
         <v>7500000</v>
@@ -3607,23 +3607,23 @@
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="154"/>
-      <c r="C3" s="174">
+      <c r="B3" s="153"/>
+      <c r="C3" s="173">
         <v>0</v>
       </c>
       <c r="D3" s="90"/>
       <c r="E3" s="90"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
       <c r="H3" s="90"/>
       <c r="I3" s="90"/>
-      <c r="J3" s="203"/>
-      <c r="K3" s="203"/>
-      <c r="L3" s="203"/>
-      <c r="M3" s="203"/>
-      <c r="N3" s="203"/>
-      <c r="O3" s="203"/>
-      <c r="P3" s="204"/>
+      <c r="J3" s="229"/>
+      <c r="K3" s="229"/>
+      <c r="L3" s="229"/>
+      <c r="M3" s="229"/>
+      <c r="N3" s="229"/>
+      <c r="O3" s="229"/>
+      <c r="P3" s="230"/>
       <c r="Q3" s="81"/>
       <c r="R3" s="51">
         <f>R2-C5-C4</f>
@@ -3632,34 +3632,34 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B4" s="154"/>
-      <c r="C4" s="174">
+        <v>201</v>
+      </c>
+      <c r="B4" s="153"/>
+      <c r="C4" s="173">
         <v>182823.01</v>
       </c>
       <c r="D4" s="90"/>
       <c r="E4" s="90"/>
-      <c r="F4" s="159"/>
-      <c r="G4" s="159"/>
+      <c r="F4" s="158"/>
+      <c r="G4" s="158"/>
       <c r="H4" s="90"/>
       <c r="I4" s="90"/>
-      <c r="J4" s="203"/>
-      <c r="K4" s="203"/>
-      <c r="L4" s="203"/>
-      <c r="M4" s="203"/>
-      <c r="N4" s="203"/>
-      <c r="O4" s="203"/>
-      <c r="P4" s="204"/>
+      <c r="J4" s="229"/>
+      <c r="K4" s="229"/>
+      <c r="L4" s="229"/>
+      <c r="M4" s="229"/>
+      <c r="N4" s="229"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="230"/>
       <c r="Q4" s="81"/>
       <c r="R4" s="51"/>
     </row>
     <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="173" t="s">
-        <v>209</v>
-      </c>
-      <c r="B5" s="155"/>
-      <c r="C5" s="175">
+      <c r="A5" s="172" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="154"/>
+      <c r="C5" s="174">
         <v>997677.51</v>
       </c>
       <c r="D5" s="91"/>
@@ -3668,211 +3668,211 @@
       <c r="G5" s="92"/>
       <c r="H5" s="91"/>
       <c r="I5" s="91"/>
-      <c r="J5" s="205"/>
-      <c r="K5" s="205"/>
-      <c r="L5" s="205"/>
-      <c r="M5" s="205"/>
-      <c r="N5" s="205"/>
-      <c r="O5" s="205"/>
-      <c r="P5" s="206"/>
+      <c r="J5" s="231"/>
+      <c r="K5" s="231"/>
+      <c r="L5" s="231"/>
+      <c r="M5" s="231"/>
+      <c r="N5" s="231"/>
+      <c r="O5" s="231"/>
+      <c r="P5" s="232"/>
       <c r="Q5" s="81"/>
     </row>
     <row r="6" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="211" t="s">
-        <v>211</v>
-      </c>
-      <c r="B6" s="212"/>
-      <c r="C6" s="213"/>
-      <c r="D6" s="213"/>
-      <c r="E6" s="213"/>
-      <c r="F6" s="213"/>
-      <c r="G6" s="213"/>
-      <c r="H6" s="213"/>
-      <c r="I6" s="213"/>
-      <c r="J6" s="213"/>
-      <c r="K6" s="213"/>
-      <c r="L6" s="213"/>
-      <c r="M6" s="213"/>
-      <c r="N6" s="213"/>
-      <c r="O6" s="213"/>
-      <c r="P6" s="214"/>
+      <c r="A6" s="202" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="203"/>
+      <c r="C6" s="204"/>
+      <c r="D6" s="204"/>
+      <c r="E6" s="204"/>
+      <c r="F6" s="204"/>
+      <c r="G6" s="204"/>
+      <c r="H6" s="204"/>
+      <c r="I6" s="204"/>
+      <c r="J6" s="204"/>
+      <c r="K6" s="204"/>
+      <c r="L6" s="204"/>
+      <c r="M6" s="204"/>
+      <c r="N6" s="204"/>
+      <c r="O6" s="204"/>
+      <c r="P6" s="205"/>
       <c r="Q6" s="81"/>
     </row>
     <row r="7" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="215"/>
-      <c r="B7" s="216"/>
-      <c r="C7" s="216"/>
-      <c r="D7" s="216"/>
-      <c r="E7" s="216"/>
-      <c r="F7" s="216"/>
-      <c r="G7" s="216"/>
-      <c r="H7" s="216"/>
-      <c r="I7" s="216"/>
-      <c r="J7" s="216"/>
-      <c r="K7" s="216"/>
-      <c r="L7" s="216"/>
-      <c r="M7" s="216"/>
-      <c r="N7" s="216"/>
-      <c r="O7" s="216"/>
-      <c r="P7" s="217"/>
+      <c r="A7" s="206"/>
+      <c r="B7" s="207"/>
+      <c r="C7" s="207"/>
+      <c r="D7" s="207"/>
+      <c r="E7" s="207"/>
+      <c r="F7" s="207"/>
+      <c r="G7" s="207"/>
+      <c r="H7" s="207"/>
+      <c r="I7" s="207"/>
+      <c r="J7" s="207"/>
+      <c r="K7" s="207"/>
+      <c r="L7" s="207"/>
+      <c r="M7" s="207"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="207"/>
+      <c r="P7" s="208"/>
       <c r="Q7" s="81"/>
     </row>
     <row r="8" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="215"/>
-      <c r="B8" s="216"/>
-      <c r="C8" s="216"/>
-      <c r="D8" s="216"/>
-      <c r="E8" s="216"/>
-      <c r="F8" s="216"/>
-      <c r="G8" s="216"/>
-      <c r="H8" s="216"/>
-      <c r="I8" s="216"/>
-      <c r="J8" s="216"/>
-      <c r="K8" s="216"/>
-      <c r="L8" s="216"/>
-      <c r="M8" s="216"/>
-      <c r="N8" s="216"/>
-      <c r="O8" s="216"/>
-      <c r="P8" s="217"/>
+      <c r="A8" s="206"/>
+      <c r="B8" s="207"/>
+      <c r="C8" s="207"/>
+      <c r="D8" s="207"/>
+      <c r="E8" s="207"/>
+      <c r="F8" s="207"/>
+      <c r="G8" s="207"/>
+      <c r="H8" s="207"/>
+      <c r="I8" s="207"/>
+      <c r="J8" s="207"/>
+      <c r="K8" s="207"/>
+      <c r="L8" s="207"/>
+      <c r="M8" s="207"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="207"/>
+      <c r="P8" s="208"/>
       <c r="Q8" s="81"/>
     </row>
     <row r="9" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="215"/>
-      <c r="B9" s="216"/>
-      <c r="C9" s="216"/>
-      <c r="D9" s="216"/>
-      <c r="E9" s="216"/>
-      <c r="F9" s="216"/>
-      <c r="G9" s="216"/>
-      <c r="H9" s="216"/>
-      <c r="I9" s="216"/>
-      <c r="J9" s="216"/>
-      <c r="K9" s="216"/>
-      <c r="L9" s="216"/>
-      <c r="M9" s="216"/>
-      <c r="N9" s="216"/>
-      <c r="O9" s="216"/>
-      <c r="P9" s="217"/>
+      <c r="A9" s="206"/>
+      <c r="B9" s="207"/>
+      <c r="C9" s="207"/>
+      <c r="D9" s="207"/>
+      <c r="E9" s="207"/>
+      <c r="F9" s="207"/>
+      <c r="G9" s="207"/>
+      <c r="H9" s="207"/>
+      <c r="I9" s="207"/>
+      <c r="J9" s="207"/>
+      <c r="K9" s="207"/>
+      <c r="L9" s="207"/>
+      <c r="M9" s="207"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="207"/>
+      <c r="P9" s="208"/>
       <c r="Q9" s="81"/>
     </row>
     <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="218"/>
-      <c r="B10" s="219"/>
-      <c r="C10" s="219"/>
-      <c r="D10" s="219"/>
-      <c r="E10" s="219"/>
-      <c r="F10" s="219"/>
-      <c r="G10" s="219"/>
-      <c r="H10" s="219"/>
-      <c r="I10" s="219"/>
-      <c r="J10" s="219"/>
-      <c r="K10" s="219"/>
-      <c r="L10" s="219"/>
-      <c r="M10" s="219"/>
-      <c r="N10" s="219"/>
-      <c r="O10" s="219"/>
-      <c r="P10" s="220"/>
+      <c r="A10" s="209"/>
+      <c r="B10" s="210"/>
+      <c r="C10" s="210"/>
+      <c r="D10" s="210"/>
+      <c r="E10" s="210"/>
+      <c r="F10" s="210"/>
+      <c r="G10" s="210"/>
+      <c r="H10" s="210"/>
+      <c r="I10" s="210"/>
+      <c r="J10" s="210"/>
+      <c r="K10" s="210"/>
+      <c r="L10" s="210"/>
+      <c r="M10" s="210"/>
+      <c r="N10" s="210"/>
+      <c r="O10" s="210"/>
+      <c r="P10" s="211"/>
     </row>
     <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="227" t="s">
+      <c r="A11" s="220" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="228"/>
-      <c r="C11" s="228"/>
-      <c r="D11" s="228"/>
-      <c r="E11" s="228"/>
-      <c r="F11" s="228"/>
-      <c r="G11" s="228"/>
-      <c r="H11" s="228"/>
-      <c r="I11" s="228"/>
-      <c r="J11" s="228"/>
-      <c r="K11" s="228"/>
-      <c r="L11" s="228"/>
-      <c r="M11" s="228"/>
-      <c r="N11" s="228"/>
-      <c r="O11" s="228"/>
-      <c r="P11" s="229"/>
+      <c r="B11" s="221"/>
+      <c r="C11" s="221"/>
+      <c r="D11" s="221"/>
+      <c r="E11" s="221"/>
+      <c r="F11" s="221"/>
+      <c r="G11" s="221"/>
+      <c r="H11" s="221"/>
+      <c r="I11" s="221"/>
+      <c r="J11" s="221"/>
+      <c r="K11" s="221"/>
+      <c r="L11" s="221"/>
+      <c r="M11" s="221"/>
+      <c r="N11" s="221"/>
+      <c r="O11" s="221"/>
+      <c r="P11" s="222"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="221" t="s">
+      <c r="A12" s="212" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="197" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="223" t="s">
+      <c r="B12" s="225" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="214" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="223" t="s">
+      <c r="D12" s="214" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="223" t="s">
+      <c r="E12" s="214" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="199" t="s">
+      <c r="F12" s="216" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="223" t="s">
+      <c r="G12" s="214" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="225" t="s">
+      <c r="H12" s="218" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="199" t="s">
+      <c r="I12" s="216" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="199" t="s">
+      <c r="J12" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="199" t="s">
+      <c r="K12" s="216" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="197" t="s">
-        <v>213</v>
-      </c>
-      <c r="M12" s="199" t="s">
-        <v>210</v>
-      </c>
-      <c r="N12" s="195" t="s">
+      <c r="L12" s="225" t="s">
+        <v>200</v>
+      </c>
+      <c r="M12" s="216" t="s">
+        <v>197</v>
+      </c>
+      <c r="N12" s="223" t="s">
         <v>52</v>
       </c>
-      <c r="O12" s="117" t="s">
+      <c r="O12" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="207" t="s">
+      <c r="P12" s="233" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="222"/>
-      <c r="B13" s="198"/>
-      <c r="C13" s="224"/>
-      <c r="D13" s="224"/>
-      <c r="E13" s="224"/>
-      <c r="F13" s="200"/>
-      <c r="G13" s="224"/>
-      <c r="H13" s="226"/>
-      <c r="I13" s="200"/>
-      <c r="J13" s="200"/>
-      <c r="K13" s="200"/>
-      <c r="L13" s="198"/>
-      <c r="M13" s="200"/>
-      <c r="N13" s="196"/>
-      <c r="O13" s="118" t="str">
+      <c r="A13" s="213"/>
+      <c r="B13" s="226"/>
+      <c r="C13" s="215"/>
+      <c r="D13" s="215"/>
+      <c r="E13" s="215"/>
+      <c r="F13" s="217"/>
+      <c r="G13" s="215"/>
+      <c r="H13" s="219"/>
+      <c r="I13" s="217"/>
+      <c r="J13" s="217"/>
+      <c r="K13" s="217"/>
+      <c r="L13" s="226"/>
+      <c r="M13" s="217"/>
+      <c r="N13" s="224"/>
+      <c r="O13" s="117" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 18/06</v>
-      </c>
-      <c r="P13" s="208"/>
+        <v>VTO 17/07</v>
+      </c>
+      <c r="P13" s="234"/>
     </row>
     <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="107">
+      <c r="A14" s="106">
         <v>1</v>
       </c>
-      <c r="B14" s="156" t="s">
-        <v>77</v>
+      <c r="B14" s="155" t="s">
+        <v>75</v>
       </c>
       <c r="C14" s="94" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D14" s="94"/>
       <c r="E14" s="96">
@@ -3893,28 +3893,28 @@
         <f>IF(H14&gt;0,H14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="106">
+      <c r="J14" s="105">
         <f>C$2*E14/100</f>
         <v>329877.87285599997</v>
       </c>
-      <c r="K14" s="106">
+      <c r="K14" s="105">
         <f t="shared" ref="K14:K45" si="1">F$2*E14/100</f>
         <v>0</v>
       </c>
-      <c r="L14" s="106">
+      <c r="L14" s="105">
         <f>C$4*E14/100</f>
         <v>9543.3611220000003</v>
       </c>
-      <c r="M14" s="106">
+      <c r="M14" s="105">
         <f>C$5*E14/100</f>
         <v>52078.766021999996</v>
       </c>
-      <c r="N14" s="106"/>
+      <c r="N14" s="105"/>
       <c r="O14" s="98">
         <f>ROUND(SUM(H14:N14),0) + Q14</f>
         <v>388500.01</v>
       </c>
-      <c r="P14" s="115">
+      <c r="P14" s="114">
         <f t="shared" ref="P14:P34" si="2">ROUND(O14*3%,0) + O14</f>
         <v>400155.01</v>
       </c>
@@ -3923,17 +3923,17 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="236">
+      <c r="A15" s="179">
         <v>2</v>
       </c>
-      <c r="B15" s="237" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="238" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" s="238" t="s">
-        <v>191</v>
+      <c r="B15" s="180" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="181" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="181" t="s">
+        <v>178</v>
       </c>
       <c r="E15" s="96">
         <v>3.4</v>
@@ -3952,28 +3952,28 @@
         <f t="shared" ref="I15:I59" si="3">IF(H15&gt;0,H15*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="106">
+      <c r="J15" s="105">
         <f t="shared" ref="J15:J59" si="4">C$2*E15/100</f>
         <v>214862.98232000001</v>
       </c>
-      <c r="K15" s="106">
+      <c r="K15" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L15" s="106">
+      <c r="L15" s="105">
         <f t="shared" ref="L15:L59" si="5">C$4*E15/100</f>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M15" s="106">
+      <c r="M15" s="105">
         <f t="shared" ref="M15:M59" si="6">C$5*E15/100</f>
         <v>33921.035340000002</v>
       </c>
-      <c r="N15" s="106"/>
+      <c r="N15" s="105"/>
       <c r="O15" s="98">
         <f t="shared" ref="O15:O59" si="7">ROUND(SUM(H15:N15),0) + Q15</f>
         <v>250394.02</v>
       </c>
-      <c r="P15" s="115">
+      <c r="P15" s="114">
         <f t="shared" si="2"/>
         <v>257906.02</v>
       </c>
@@ -3983,17 +3983,17 @@
       </c>
     </row>
     <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="107">
+      <c r="A16" s="106">
         <v>3</v>
       </c>
-      <c r="B16" s="156" t="s">
-        <v>81</v>
+      <c r="B16" s="155" t="s">
+        <v>79</v>
       </c>
       <c r="C16" s="94" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D16" s="94" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="E16" s="96">
         <v>2.54</v>
@@ -4012,28 +4012,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J16" s="106">
+      <c r="J16" s="105">
         <f t="shared" si="4"/>
         <v>160515.286792</v>
       </c>
-      <c r="K16" s="106">
+      <c r="K16" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L16" s="106">
+      <c r="L16" s="105">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M16" s="106">
+      <c r="M16" s="105">
         <f t="shared" si="6"/>
         <v>25341.008754000002</v>
       </c>
-      <c r="N16" s="106"/>
+      <c r="N16" s="105"/>
       <c r="O16" s="98">
         <f t="shared" si="7"/>
         <v>190304.03</v>
       </c>
-      <c r="P16" s="115">
+      <c r="P16" s="114">
         <f t="shared" si="2"/>
         <v>196013.03</v>
       </c>
@@ -4042,21 +4042,21 @@
         <v>0.03</v>
       </c>
       <c r="R16" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="176">
+      <c r="A17" s="175">
         <v>4</v>
       </c>
-      <c r="B17" s="177" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="179" t="s">
-        <v>126</v>
+      <c r="B17" s="176" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="178" t="s">
+        <v>124</v>
       </c>
       <c r="D17" s="99" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E17" s="96">
         <v>5.19</v>
@@ -4076,28 +4076,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="106">
+      <c r="J17" s="105">
         <f t="shared" si="4"/>
         <v>327982.02301200008</v>
       </c>
-      <c r="K17" s="106">
+      <c r="K17" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L17" s="106">
+      <c r="L17" s="105">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M17" s="106">
+      <c r="M17" s="105">
         <f t="shared" si="6"/>
         <v>51779.462769000005</v>
       </c>
-      <c r="N17" s="106"/>
+      <c r="N17" s="105"/>
       <c r="O17" s="98">
         <f t="shared" si="7"/>
         <v>384603.04</v>
       </c>
-      <c r="P17" s="115">
+      <c r="P17" s="114">
         <f t="shared" si="2"/>
         <v>396141.04</v>
       </c>
@@ -4106,21 +4106,21 @@
         <v>0.04</v>
       </c>
       <c r="R17" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="107">
+      <c r="A18" s="106">
         <v>5</v>
       </c>
-      <c r="B18" s="156" t="s">
-        <v>78</v>
+      <c r="B18" s="155" t="s">
+        <v>76</v>
       </c>
       <c r="C18" s="94" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D18" s="99" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="E18" s="96">
         <v>3.4</v>
@@ -4139,28 +4139,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J18" s="106">
+      <c r="J18" s="105">
         <f t="shared" si="4"/>
         <v>214862.98232000001</v>
       </c>
-      <c r="K18" s="106">
+      <c r="K18" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L18" s="106">
+      <c r="L18" s="105">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M18" s="106">
+      <c r="M18" s="105">
         <f t="shared" si="6"/>
         <v>33921.035340000002</v>
       </c>
-      <c r="N18" s="106"/>
+      <c r="N18" s="105"/>
       <c r="O18" s="98">
         <f t="shared" si="7"/>
         <v>255000.05</v>
       </c>
-      <c r="P18" s="115">
+      <c r="P18" s="114">
         <f t="shared" si="2"/>
         <v>262650.05</v>
       </c>
@@ -4170,14 +4170,14 @@
       </c>
     </row>
     <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="107">
+      <c r="A19" s="106">
         <v>6</v>
       </c>
-      <c r="B19" s="156" t="s">
-        <v>83</v>
+      <c r="B19" s="155" t="s">
+        <v>81</v>
       </c>
       <c r="C19" s="94" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D19" s="94"/>
       <c r="E19" s="96">
@@ -4197,28 +4197,28 @@
         <f t="shared" si="3"/>
         <v>4703.46</v>
       </c>
-      <c r="J19" s="106">
+      <c r="J19" s="105">
         <f t="shared" si="4"/>
         <v>160515.286792</v>
       </c>
-      <c r="K19" s="106">
+      <c r="K19" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L19" s="106">
+      <c r="L19" s="105">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M19" s="106">
+      <c r="M19" s="105">
         <f t="shared" si="6"/>
         <v>25341.008754000002</v>
       </c>
-      <c r="N19" s="106"/>
+      <c r="N19" s="105"/>
       <c r="O19" s="98">
         <f t="shared" si="7"/>
         <v>351985.06</v>
       </c>
-      <c r="P19" s="115">
+      <c r="P19" s="114">
         <f t="shared" si="2"/>
         <v>362545.06</v>
       </c>
@@ -4228,14 +4228,14 @@
       </c>
     </row>
     <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="107">
+      <c r="A20" s="106">
         <v>7</v>
       </c>
-      <c r="B20" s="156" t="s">
-        <v>84</v>
+      <c r="B20" s="155" t="s">
+        <v>82</v>
       </c>
       <c r="C20" s="94" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D20" s="94"/>
       <c r="E20" s="96">
@@ -4256,28 +4256,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J20" s="106">
+      <c r="J20" s="105">
         <f t="shared" si="4"/>
         <v>327982.02301200008</v>
       </c>
-      <c r="K20" s="106">
+      <c r="K20" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L20" s="106">
+      <c r="L20" s="105">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M20" s="106">
+      <c r="M20" s="105">
         <f t="shared" si="6"/>
         <v>51779.462769000005</v>
       </c>
-      <c r="N20" s="106"/>
+      <c r="N20" s="105"/>
       <c r="O20" s="98">
         <f t="shared" si="7"/>
         <v>389250.07</v>
       </c>
-      <c r="P20" s="115">
+      <c r="P20" s="114">
         <f t="shared" si="2"/>
         <v>400928.07</v>
       </c>
@@ -4287,14 +4287,14 @@
       </c>
     </row>
     <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="107">
+      <c r="A21" s="106">
         <v>8</v>
       </c>
-      <c r="B21" s="156" t="s">
-        <v>85</v>
+      <c r="B21" s="155" t="s">
+        <v>83</v>
       </c>
       <c r="C21" s="94" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D21" s="99"/>
       <c r="E21" s="96">
@@ -4314,28 +4314,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J21" s="106">
+      <c r="J21" s="105">
         <f t="shared" si="4"/>
         <v>214862.98232000001</v>
       </c>
-      <c r="K21" s="106">
+      <c r="K21" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L21" s="106">
+      <c r="L21" s="105">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M21" s="106">
+      <c r="M21" s="105">
         <f t="shared" si="6"/>
         <v>33921.035340000002</v>
       </c>
-      <c r="N21" s="106"/>
+      <c r="N21" s="105"/>
       <c r="O21" s="98">
         <f t="shared" si="7"/>
         <v>255000.08</v>
       </c>
-      <c r="P21" s="115">
+      <c r="P21" s="114">
         <f t="shared" si="2"/>
         <v>262650.07999999996</v>
       </c>
@@ -4345,17 +4345,17 @@
       </c>
     </row>
     <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="107">
+      <c r="A22" s="106">
         <v>9</v>
       </c>
-      <c r="B22" s="156" t="s">
-        <v>79</v>
+      <c r="B22" s="155" t="s">
+        <v>77</v>
       </c>
       <c r="C22" s="94" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D22" s="99" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="E22" s="96">
         <v>2.54</v>
@@ -4374,28 +4374,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J22" s="106">
+      <c r="J22" s="105">
         <f t="shared" si="4"/>
         <v>160515.286792</v>
       </c>
-      <c r="K22" s="106">
+      <c r="K22" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L22" s="106">
+      <c r="L22" s="105">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M22" s="106">
+      <c r="M22" s="105">
         <f t="shared" si="6"/>
         <v>25341.008754000002</v>
       </c>
-      <c r="N22" s="106"/>
+      <c r="N22" s="105"/>
       <c r="O22" s="98">
         <f t="shared" si="7"/>
         <v>190500.09</v>
       </c>
-      <c r="P22" s="115">
+      <c r="P22" s="114">
         <f t="shared" si="2"/>
         <v>196215.09</v>
       </c>
@@ -4405,14 +4405,14 @@
       </c>
     </row>
     <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="107">
+      <c r="A23" s="106">
         <v>10</v>
       </c>
-      <c r="B23" s="156" t="s">
-        <v>86</v>
+      <c r="B23" s="155" t="s">
+        <v>84</v>
       </c>
       <c r="C23" s="94" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D23" s="99"/>
       <c r="E23" s="96">
@@ -4433,28 +4433,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J23" s="106">
+      <c r="J23" s="105">
         <f t="shared" si="4"/>
         <v>327982.02301200008</v>
       </c>
-      <c r="K23" s="106">
+      <c r="K23" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L23" s="106">
+      <c r="L23" s="105">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M23" s="106">
+      <c r="M23" s="105">
         <f t="shared" si="6"/>
         <v>51779.462769000005</v>
       </c>
-      <c r="N23" s="106"/>
+      <c r="N23" s="105"/>
       <c r="O23" s="98">
         <f t="shared" si="7"/>
         <v>389250.1</v>
       </c>
-      <c r="P23" s="115">
+      <c r="P23" s="114">
         <f t="shared" si="2"/>
         <v>400928.1</v>
       </c>
@@ -4464,17 +4464,17 @@
       </c>
     </row>
     <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="107">
+      <c r="A24" s="106">
         <v>11</v>
       </c>
-      <c r="B24" s="156" t="s">
-        <v>87</v>
+      <c r="B24" s="155" t="s">
+        <v>85</v>
       </c>
       <c r="C24" s="94" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D24" s="99" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="E24" s="96">
         <v>3.4</v>
@@ -4493,28 +4493,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="106">
+      <c r="J24" s="105">
         <f t="shared" si="4"/>
         <v>214862.98232000001</v>
       </c>
-      <c r="K24" s="106">
+      <c r="K24" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L24" s="106">
+      <c r="L24" s="105">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M24" s="106">
+      <c r="M24" s="105">
         <f t="shared" si="6"/>
         <v>33921.035340000002</v>
       </c>
-      <c r="N24" s="106"/>
+      <c r="N24" s="105"/>
       <c r="O24" s="98">
         <f t="shared" si="7"/>
         <v>255000.11</v>
       </c>
-      <c r="P24" s="115">
+      <c r="P24" s="114">
         <f t="shared" si="2"/>
         <v>262650.11</v>
       </c>
@@ -4524,17 +4524,17 @@
       </c>
     </row>
     <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="107">
+      <c r="A25" s="106">
         <v>12</v>
       </c>
-      <c r="B25" s="156" t="s">
-        <v>88</v>
+      <c r="B25" s="155" t="s">
+        <v>86</v>
       </c>
       <c r="C25" s="94" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D25" s="99" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="E25" s="96">
         <v>2.54</v>
@@ -4554,28 +4554,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J25" s="106">
+      <c r="J25" s="105">
         <f t="shared" si="4"/>
         <v>160515.286792</v>
       </c>
-      <c r="K25" s="106">
+      <c r="K25" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L25" s="106">
+      <c r="L25" s="105">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M25" s="106">
+      <c r="M25" s="105">
         <f t="shared" si="6"/>
         <v>25341.008754000002</v>
       </c>
-      <c r="N25" s="106"/>
+      <c r="N25" s="105"/>
       <c r="O25" s="98">
         <f t="shared" si="7"/>
         <v>190500.12</v>
       </c>
-      <c r="P25" s="115">
+      <c r="P25" s="114">
         <f t="shared" si="2"/>
         <v>196215.12</v>
       </c>
@@ -4585,14 +4585,14 @@
       </c>
     </row>
     <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="107">
+      <c r="A26" s="106">
         <v>13</v>
       </c>
-      <c r="B26" s="156" t="s">
-        <v>89</v>
+      <c r="B26" s="155" t="s">
+        <v>87</v>
       </c>
       <c r="C26" s="94" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D26" s="99"/>
       <c r="E26" s="96">
@@ -4613,28 +4613,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="106">
+      <c r="J26" s="105">
         <f t="shared" si="4"/>
         <v>327982.02301200008</v>
       </c>
-      <c r="K26" s="106">
+      <c r="K26" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L26" s="106">
+      <c r="L26" s="105">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M26" s="106">
+      <c r="M26" s="105">
         <f t="shared" si="6"/>
         <v>51779.462769000005</v>
       </c>
-      <c r="N26" s="106"/>
+      <c r="N26" s="105"/>
       <c r="O26" s="98">
         <f t="shared" si="7"/>
         <v>389250.13</v>
       </c>
-      <c r="P26" s="115">
+      <c r="P26" s="114">
         <f t="shared" si="2"/>
         <v>400928.13</v>
       </c>
@@ -4644,14 +4644,14 @@
       </c>
     </row>
     <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="107">
+      <c r="A27" s="106">
         <v>14</v>
       </c>
-      <c r="B27" s="156" t="s">
-        <v>90</v>
+      <c r="B27" s="155" t="s">
+        <v>88</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D27" s="99"/>
       <c r="E27" s="96">
@@ -4672,28 +4672,28 @@
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="J27" s="106">
+      <c r="J27" s="105">
         <f t="shared" si="4"/>
         <v>214862.98232000001</v>
       </c>
-      <c r="K27" s="106">
+      <c r="K27" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L27" s="106">
+      <c r="L27" s="105">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M27" s="106">
+      <c r="M27" s="105">
         <f t="shared" si="6"/>
         <v>33921.035340000002</v>
       </c>
-      <c r="N27" s="106"/>
+      <c r="N27" s="105"/>
       <c r="O27" s="98">
         <f t="shared" si="7"/>
         <v>255618.14</v>
       </c>
-      <c r="P27" s="115">
+      <c r="P27" s="114">
         <f t="shared" si="2"/>
         <v>263287.14</v>
       </c>
@@ -4703,17 +4703,17 @@
       </c>
     </row>
     <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="107">
+      <c r="A28" s="106">
         <v>15</v>
       </c>
-      <c r="B28" s="156" t="s">
-        <v>91</v>
+      <c r="B28" s="155" t="s">
+        <v>89</v>
       </c>
       <c r="C28" s="94" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D28" s="94" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="E28" s="96">
         <v>2.54</v>
@@ -4732,28 +4732,28 @@
         <f t="shared" si="3"/>
         <v>1023.63</v>
       </c>
-      <c r="J28" s="106">
+      <c r="J28" s="105">
         <f t="shared" si="4"/>
         <v>160515.286792</v>
       </c>
-      <c r="K28" s="106">
+      <c r="K28" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L28" s="106">
+      <c r="L28" s="105">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M28" s="106">
+      <c r="M28" s="105">
         <f t="shared" si="6"/>
         <v>25341.008754000002</v>
       </c>
-      <c r="N28" s="106"/>
+      <c r="N28" s="105"/>
       <c r="O28" s="98">
         <f t="shared" si="7"/>
         <v>225645.15</v>
       </c>
-      <c r="P28" s="115">
+      <c r="P28" s="114">
         <f t="shared" si="2"/>
         <v>232414.15</v>
       </c>
@@ -4763,14 +4763,14 @@
       </c>
     </row>
     <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="107">
+      <c r="A29" s="106">
         <v>16</v>
       </c>
-      <c r="B29" s="156" t="s">
-        <v>92</v>
+      <c r="B29" s="155" t="s">
+        <v>90</v>
       </c>
       <c r="C29" s="94" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D29" s="94"/>
       <c r="E29" s="96">
@@ -4791,28 +4791,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="106">
+      <c r="J29" s="105">
         <f t="shared" si="4"/>
         <v>327982.02301200008</v>
       </c>
-      <c r="K29" s="106">
+      <c r="K29" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L29" s="106">
+      <c r="L29" s="105">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M29" s="106">
+      <c r="M29" s="105">
         <f t="shared" si="6"/>
         <v>51779.462769000005</v>
       </c>
-      <c r="N29" s="106"/>
+      <c r="N29" s="105"/>
       <c r="O29" s="98">
         <f t="shared" si="7"/>
         <v>389250.16</v>
       </c>
-      <c r="P29" s="115">
+      <c r="P29" s="114">
         <f t="shared" si="2"/>
         <v>400928.16</v>
       </c>
@@ -4822,17 +4822,17 @@
       </c>
     </row>
     <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="107">
+      <c r="A30" s="106">
         <v>17</v>
       </c>
-      <c r="B30" s="156" t="s">
-        <v>93</v>
+      <c r="B30" s="155" t="s">
+        <v>91</v>
       </c>
       <c r="C30" s="94" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D30" s="99" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="E30" s="96">
         <v>3.4</v>
@@ -4852,28 +4852,28 @@
         <f t="shared" si="3"/>
         <v>408</v>
       </c>
-      <c r="J30" s="106">
+      <c r="J30" s="105">
         <f t="shared" si="4"/>
         <v>214862.98232000001</v>
       </c>
-      <c r="K30" s="106">
+      <c r="K30" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L30" s="106">
+      <c r="L30" s="105">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M30" s="106">
+      <c r="M30" s="105">
         <f t="shared" si="6"/>
         <v>33921.035340000002</v>
       </c>
-      <c r="N30" s="106"/>
+      <c r="N30" s="105"/>
       <c r="O30" s="98">
         <f t="shared" si="7"/>
         <v>269008.17</v>
       </c>
-      <c r="P30" s="115">
+      <c r="P30" s="114">
         <f t="shared" si="2"/>
         <v>277078.17</v>
       </c>
@@ -4883,14 +4883,14 @@
       </c>
     </row>
     <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="107">
+      <c r="A31" s="106">
         <v>18</v>
       </c>
-      <c r="B31" s="156" t="s">
-        <v>94</v>
+      <c r="B31" s="155" t="s">
+        <v>92</v>
       </c>
       <c r="C31" s="94" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D31" s="95"/>
       <c r="E31" s="96">
@@ -4908,28 +4908,28 @@
         <f t="shared" si="3"/>
         <v>35538.57</v>
       </c>
-      <c r="J31" s="106">
+      <c r="J31" s="105">
         <f t="shared" si="4"/>
         <v>160515.286792</v>
       </c>
-      <c r="K31" s="106">
+      <c r="K31" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L31" s="106">
+      <c r="L31" s="105">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M31" s="106">
+      <c r="M31" s="105">
         <f t="shared" si="6"/>
         <v>25341.008754000002</v>
       </c>
-      <c r="N31" s="106"/>
+      <c r="N31" s="105"/>
       <c r="O31" s="98">
         <f t="shared" si="7"/>
         <v>1410658.18</v>
       </c>
-      <c r="P31" s="115">
+      <c r="P31" s="114">
         <f t="shared" si="2"/>
         <v>1452978.18</v>
       </c>
@@ -4939,14 +4939,14 @@
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" s="107">
+      <c r="A32" s="106">
         <v>19</v>
       </c>
-      <c r="B32" s="156" t="s">
-        <v>95</v>
+      <c r="B32" s="155" t="s">
+        <v>93</v>
       </c>
       <c r="C32" s="94" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D32" s="99"/>
       <c r="E32" s="96">
@@ -4966,28 +4966,28 @@
         <f t="shared" si="3"/>
         <v>10375.5</v>
       </c>
-      <c r="J32" s="106">
+      <c r="J32" s="105">
         <f t="shared" si="4"/>
         <v>327982.02301200008</v>
       </c>
-      <c r="K32" s="106">
+      <c r="K32" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L32" s="106">
+      <c r="L32" s="105">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M32" s="106">
+      <c r="M32" s="105">
         <f t="shared" si="6"/>
         <v>51779.462769000005</v>
       </c>
-      <c r="N32" s="106"/>
+      <c r="N32" s="105"/>
       <c r="O32" s="98">
         <f t="shared" si="7"/>
         <v>745476.19</v>
       </c>
-      <c r="P32" s="115">
+      <c r="P32" s="114">
         <f t="shared" si="2"/>
         <v>767840.19</v>
       </c>
@@ -4997,14 +4997,14 @@
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="107">
+      <c r="A33" s="106">
         <v>20</v>
       </c>
-      <c r="B33" s="156" t="s">
-        <v>96</v>
+      <c r="B33" s="155" t="s">
+        <v>94</v>
       </c>
       <c r="C33" s="94" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D33" s="99"/>
       <c r="E33" s="96">
@@ -5022,28 +5022,28 @@
         <v>0</v>
       </c>
       <c r="I33" s="97"/>
-      <c r="J33" s="106">
+      <c r="J33" s="105">
         <f t="shared" si="4"/>
         <v>214862.98232000001</v>
       </c>
-      <c r="K33" s="106">
+      <c r="K33" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L33" s="106">
+      <c r="L33" s="105">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M33" s="106">
+      <c r="M33" s="105">
         <f t="shared" si="6"/>
         <v>33921.035340000002</v>
       </c>
-      <c r="N33" s="106"/>
+      <c r="N33" s="105"/>
       <c r="O33" s="98">
         <f t="shared" si="7"/>
         <v>255000.2</v>
       </c>
-      <c r="P33" s="115">
+      <c r="P33" s="114">
         <f t="shared" si="2"/>
         <v>262650.2</v>
       </c>
@@ -5053,17 +5053,17 @@
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A34" s="107">
+      <c r="A34" s="106">
         <v>21</v>
       </c>
-      <c r="B34" s="156" t="s">
-        <v>97</v>
+      <c r="B34" s="155" t="s">
+        <v>95</v>
       </c>
       <c r="C34" s="100" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D34" s="99" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="E34" s="96">
         <v>2.54</v>
@@ -5082,28 +5082,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J34" s="106">
+      <c r="J34" s="105">
         <f t="shared" si="4"/>
         <v>160515.286792</v>
       </c>
-      <c r="K34" s="106">
+      <c r="K34" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L34" s="106">
+      <c r="L34" s="105">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M34" s="106">
+      <c r="M34" s="105">
         <f t="shared" si="6"/>
         <v>25341.008754000002</v>
       </c>
-      <c r="N34" s="106"/>
+      <c r="N34" s="105"/>
       <c r="O34" s="98">
         <f t="shared" si="7"/>
         <v>190500.21</v>
       </c>
-      <c r="P34" s="115">
+      <c r="P34" s="114">
         <f t="shared" si="2"/>
         <v>196215.21</v>
       </c>
@@ -5113,18 +5113,18 @@
       </c>
     </row>
     <row r="35" spans="1:18" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="107">
+      <c r="A35" s="106">
         <f>A34+1</f>
         <v>22</v>
       </c>
-      <c r="B35" s="156" t="s">
-        <v>98</v>
+      <c r="B35" s="155" t="s">
+        <v>96</v>
       </c>
       <c r="C35" s="100" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D35" s="99" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="E35" s="96">
         <v>4.9400000000000004</v>
@@ -5144,28 +5144,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="106">
+      <c r="J35" s="105">
         <f t="shared" si="4"/>
         <v>312183.27431200002</v>
       </c>
-      <c r="K35" s="106">
+      <c r="K35" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L35" s="106">
+      <c r="L35" s="105">
         <f t="shared" si="5"/>
         <v>9031.4566940000004</v>
       </c>
-      <c r="M35" s="106">
+      <c r="M35" s="105">
         <f t="shared" si="6"/>
         <v>49285.268994000005</v>
       </c>
-      <c r="N35" s="106"/>
+      <c r="N35" s="105"/>
       <c r="O35" s="98">
         <f t="shared" si="7"/>
         <v>370500.22</v>
       </c>
-      <c r="P35" s="115">
+      <c r="P35" s="114">
         <f t="shared" ref="P35:P59" si="10">ROUND(O35*3%,0) + O35</f>
         <v>381615.22</v>
       </c>
@@ -5175,18 +5175,18 @@
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" s="107">
+      <c r="A36" s="106">
         <f t="shared" ref="A36:A59" si="11">A35+1</f>
         <v>23</v>
       </c>
-      <c r="B36" s="156" t="s">
-        <v>99</v>
+      <c r="B36" s="155" t="s">
+        <v>97</v>
       </c>
       <c r="C36" s="100" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D36" s="99" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E36" s="96">
         <v>3.28</v>
@@ -5205,28 +5205,28 @@
         <f t="shared" si="3"/>
         <v>24.57</v>
       </c>
-      <c r="J36" s="106">
+      <c r="J36" s="105">
         <f t="shared" si="4"/>
         <v>207279.58294399999</v>
       </c>
-      <c r="K36" s="106">
+      <c r="K36" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L36" s="106">
+      <c r="L36" s="105">
         <f t="shared" si="5"/>
         <v>5996.594728</v>
       </c>
-      <c r="M36" s="106">
+      <c r="M36" s="105">
         <f t="shared" si="6"/>
         <v>32723.822327999998</v>
       </c>
-      <c r="N36" s="106"/>
+      <c r="N36" s="105"/>
       <c r="O36" s="98">
         <f t="shared" si="7"/>
         <v>246844.23</v>
       </c>
-      <c r="P36" s="115">
+      <c r="P36" s="114">
         <f t="shared" si="10"/>
         <v>254249.23</v>
       </c>
@@ -5236,15 +5236,15 @@
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" s="107">
+      <c r="A37" s="106">
         <f t="shared" si="11"/>
         <v>24</v>
       </c>
-      <c r="B37" s="156" t="s">
-        <v>100</v>
+      <c r="B37" s="155" t="s">
+        <v>98</v>
       </c>
       <c r="C37" s="100" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D37" s="99"/>
       <c r="E37" s="96">
@@ -5264,28 +5264,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="106">
+      <c r="J37" s="105">
         <f t="shared" si="4"/>
         <v>152299.93746800002</v>
       </c>
-      <c r="K37" s="106">
+      <c r="K37" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L37" s="106">
+      <c r="L37" s="105">
         <f t="shared" si="5"/>
         <v>4406.034541</v>
       </c>
-      <c r="M37" s="106">
+      <c r="M37" s="105">
         <f t="shared" si="6"/>
         <v>24044.027990999999</v>
       </c>
-      <c r="N37" s="106"/>
+      <c r="N37" s="105"/>
       <c r="O37" s="98">
         <f t="shared" si="7"/>
         <v>180750.24</v>
       </c>
-      <c r="P37" s="115">
+      <c r="P37" s="114">
         <f t="shared" si="10"/>
         <v>186173.24</v>
       </c>
@@ -5295,15 +5295,15 @@
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" s="107">
+      <c r="A38" s="106">
         <f t="shared" si="11"/>
         <v>25</v>
       </c>
-      <c r="B38" s="156" t="s">
-        <v>101</v>
+      <c r="B38" s="155" t="s">
+        <v>99</v>
       </c>
       <c r="C38" s="100" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D38" s="99"/>
       <c r="E38" s="96">
@@ -5324,28 +5324,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J38" s="106">
+      <c r="J38" s="105">
         <f t="shared" si="4"/>
         <v>27805.797712000003</v>
       </c>
-      <c r="K38" s="106">
+      <c r="K38" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L38" s="106">
+      <c r="L38" s="105">
         <f t="shared" si="5"/>
         <v>804.421244</v>
       </c>
-      <c r="M38" s="106">
+      <c r="M38" s="105">
         <f t="shared" si="6"/>
         <v>4389.7810440000003</v>
       </c>
-      <c r="N38" s="106"/>
+      <c r="N38" s="105"/>
       <c r="O38" s="98">
         <f t="shared" si="7"/>
         <v>24889.25</v>
       </c>
-      <c r="P38" s="115">
+      <c r="P38" s="114">
         <f t="shared" si="10"/>
         <v>25636.25</v>
       </c>
@@ -5354,19 +5354,19 @@
         <v>0.25000000000000006</v>
       </c>
       <c r="R38" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A39" s="107">
+      <c r="A39" s="106">
         <f t="shared" si="11"/>
         <v>26</v>
       </c>
-      <c r="B39" s="156" t="s">
-        <v>103</v>
+      <c r="B39" s="155" t="s">
+        <v>101</v>
       </c>
       <c r="C39" s="100" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D39" s="99"/>
       <c r="E39" s="96">
@@ -5386,28 +5386,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="106">
+      <c r="J39" s="105">
         <f t="shared" si="4"/>
         <v>34757.247140000007</v>
       </c>
-      <c r="K39" s="106">
+      <c r="K39" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L39" s="106">
+      <c r="L39" s="105">
         <f t="shared" si="5"/>
         <v>1005.526555</v>
       </c>
-      <c r="M39" s="106">
+      <c r="M39" s="105">
         <f t="shared" si="6"/>
         <v>5487.226305000001</v>
       </c>
-      <c r="N39" s="106"/>
+      <c r="N39" s="105"/>
       <c r="O39" s="98">
         <f t="shared" si="7"/>
         <v>41250.26</v>
       </c>
-      <c r="P39" s="115">
+      <c r="P39" s="114">
         <f t="shared" si="10"/>
         <v>42488.26</v>
       </c>
@@ -5417,15 +5417,15 @@
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A40" s="107">
+      <c r="A40" s="106">
         <f t="shared" si="11"/>
         <v>27</v>
       </c>
-      <c r="B40" s="156" t="s">
-        <v>102</v>
+      <c r="B40" s="155" t="s">
+        <v>100</v>
       </c>
       <c r="C40" s="100" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D40" s="99"/>
       <c r="E40" s="96">
@@ -5446,28 +5446,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J40" s="106">
+      <c r="J40" s="105">
         <f t="shared" si="4"/>
         <v>33493.347244000004</v>
       </c>
-      <c r="K40" s="106">
+      <c r="K40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L40" s="106">
+      <c r="L40" s="105">
         <f t="shared" si="5"/>
         <v>968.96195300000011</v>
       </c>
-      <c r="M40" s="106">
+      <c r="M40" s="105">
         <f t="shared" si="6"/>
         <v>5287.6908030000004</v>
       </c>
-      <c r="N40" s="106"/>
+      <c r="N40" s="105"/>
       <c r="O40" s="98">
         <f t="shared" si="7"/>
         <v>39750.269999999997</v>
       </c>
-      <c r="P40" s="115">
+      <c r="P40" s="114">
         <f t="shared" si="10"/>
         <v>40943.269999999997</v>
       </c>
@@ -5477,18 +5477,18 @@
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A41" s="107">
+      <c r="A41" s="106">
         <f t="shared" si="11"/>
         <v>28</v>
       </c>
-      <c r="B41" s="156" t="s">
-        <v>104</v>
+      <c r="B41" s="155" t="s">
+        <v>102</v>
       </c>
       <c r="C41" s="100" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D41" s="94" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E41" s="96">
         <v>0.28999999999999998</v>
@@ -5507,28 +5507,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J41" s="106">
+      <c r="J41" s="105">
         <f t="shared" si="4"/>
         <v>18326.548492000002</v>
       </c>
-      <c r="K41" s="106">
+      <c r="K41" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L41" s="106">
+      <c r="L41" s="105">
         <f t="shared" si="5"/>
         <v>530.18672900000001</v>
       </c>
-      <c r="M41" s="106">
+      <c r="M41" s="105">
         <f t="shared" si="6"/>
         <v>2893.2647790000001</v>
       </c>
-      <c r="N41" s="106"/>
+      <c r="N41" s="105"/>
       <c r="O41" s="98">
         <f t="shared" si="7"/>
         <v>19828.28</v>
       </c>
-      <c r="P41" s="115">
+      <c r="P41" s="114">
         <f t="shared" si="10"/>
         <v>20423.28</v>
       </c>
@@ -5538,18 +5538,18 @@
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A42" s="107">
+      <c r="A42" s="106">
         <f t="shared" si="11"/>
         <v>29</v>
       </c>
-      <c r="B42" s="156" t="s">
-        <v>105</v>
+      <c r="B42" s="155" t="s">
+        <v>103</v>
       </c>
       <c r="C42" s="100" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D42" s="99" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="E42" s="96">
         <v>0.08</v>
@@ -5569,28 +5569,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J42" s="106">
+      <c r="J42" s="105">
         <f t="shared" si="4"/>
         <v>5055.5995840000005</v>
       </c>
-      <c r="K42" s="106">
+      <c r="K42" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L42" s="106">
+      <c r="L42" s="105">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M42" s="106">
+      <c r="M42" s="105">
         <f t="shared" si="6"/>
         <v>798.14200800000003</v>
       </c>
-      <c r="N42" s="106"/>
+      <c r="N42" s="105"/>
       <c r="O42" s="98">
         <f t="shared" si="7"/>
         <v>6000.29</v>
       </c>
-      <c r="P42" s="115">
+      <c r="P42" s="114">
         <f t="shared" si="10"/>
         <v>6180.29</v>
       </c>
@@ -5600,15 +5600,15 @@
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A43" s="107">
+      <c r="A43" s="106">
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="B43" s="156" t="s">
-        <v>106</v>
+      <c r="B43" s="155" t="s">
+        <v>104</v>
       </c>
       <c r="C43" s="100" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D43" s="99"/>
       <c r="E43" s="96">
@@ -5628,28 +5628,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J43" s="106">
+      <c r="J43" s="105">
         <f t="shared" si="4"/>
         <v>5055.5995840000005</v>
       </c>
-      <c r="K43" s="106">
+      <c r="K43" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L43" s="106">
+      <c r="L43" s="105">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M43" s="106">
+      <c r="M43" s="105">
         <f t="shared" si="6"/>
         <v>798.14200800000003</v>
       </c>
-      <c r="N43" s="106"/>
+      <c r="N43" s="105"/>
       <c r="O43" s="98">
         <f t="shared" si="7"/>
         <v>6000.3</v>
       </c>
-      <c r="P43" s="115">
+      <c r="P43" s="114">
         <f t="shared" si="10"/>
         <v>6180.3</v>
       </c>
@@ -5659,15 +5659,15 @@
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A44" s="176">
+      <c r="A44" s="175">
         <f t="shared" si="11"/>
         <v>31</v>
       </c>
-      <c r="B44" s="177" t="s">
-        <v>107</v>
-      </c>
-      <c r="C44" s="178" t="s">
-        <v>126</v>
+      <c r="B44" s="176" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="177" t="s">
+        <v>124</v>
       </c>
       <c r="D44" s="99"/>
       <c r="E44" s="96">
@@ -5685,28 +5685,28 @@
         <f t="shared" si="3"/>
         <v>166.17</v>
       </c>
-      <c r="J44" s="106">
+      <c r="J44" s="105">
         <f t="shared" si="4"/>
         <v>5055.5995840000005</v>
       </c>
-      <c r="K44" s="106">
+      <c r="K44" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L44" s="106">
+      <c r="L44" s="105">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M44" s="106">
+      <c r="M44" s="105">
         <f t="shared" si="6"/>
         <v>798.14200800000003</v>
       </c>
-      <c r="N44" s="106"/>
+      <c r="N44" s="105"/>
       <c r="O44" s="98">
         <f t="shared" si="7"/>
         <v>11705.31</v>
       </c>
-      <c r="P44" s="115">
+      <c r="P44" s="114">
         <f t="shared" si="10"/>
         <v>12056.31</v>
       </c>
@@ -5715,19 +5715,19 @@
         <v>0.31000000000000011</v>
       </c>
       <c r="R44" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A45" s="107">
+      <c r="A45" s="106">
         <f t="shared" si="11"/>
         <v>32</v>
       </c>
-      <c r="B45" s="156" t="s">
-        <v>108</v>
+      <c r="B45" s="155" t="s">
+        <v>106</v>
       </c>
       <c r="C45" s="100" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D45" s="99"/>
       <c r="E45" s="96">
@@ -5747,28 +5747,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J45" s="106">
+      <c r="J45" s="105">
         <f t="shared" si="4"/>
         <v>5055.5995840000005</v>
       </c>
-      <c r="K45" s="106">
+      <c r="K45" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L45" s="106">
+      <c r="L45" s="105">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M45" s="106">
+      <c r="M45" s="105">
         <f t="shared" si="6"/>
         <v>798.14200800000003</v>
       </c>
-      <c r="N45" s="106"/>
+      <c r="N45" s="105"/>
       <c r="O45" s="98">
         <f t="shared" si="7"/>
         <v>6000.32</v>
       </c>
-      <c r="P45" s="115">
+      <c r="P45" s="114">
         <f t="shared" si="10"/>
         <v>6180.32</v>
       </c>
@@ -5778,15 +5778,15 @@
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A46" s="107">
+      <c r="A46" s="106">
         <f t="shared" si="11"/>
         <v>33</v>
       </c>
-      <c r="B46" s="156" t="s">
-        <v>109</v>
+      <c r="B46" s="155" t="s">
+        <v>107</v>
       </c>
       <c r="C46" s="100" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D46" s="99"/>
       <c r="E46" s="96">
@@ -5801,28 +5801,28 @@
         <v>12312</v>
       </c>
       <c r="I46" s="97"/>
-      <c r="J46" s="106">
+      <c r="J46" s="105">
         <f t="shared" si="4"/>
         <v>5055.5995840000005</v>
       </c>
-      <c r="K46" s="106">
+      <c r="K46" s="105">
         <f t="shared" ref="K46:K59" si="12">F$2*E46/100</f>
         <v>0</v>
       </c>
-      <c r="L46" s="106">
+      <c r="L46" s="105">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M46" s="106">
+      <c r="M46" s="105">
         <f t="shared" si="6"/>
         <v>798.14200800000003</v>
       </c>
-      <c r="N46" s="106"/>
+      <c r="N46" s="105"/>
       <c r="O46" s="98">
         <f t="shared" si="7"/>
         <v>18312.330000000002</v>
       </c>
-      <c r="P46" s="115">
+      <c r="P46" s="114">
         <f t="shared" si="10"/>
         <v>18861.330000000002</v>
       </c>
@@ -5832,15 +5832,15 @@
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A47" s="107">
+      <c r="A47" s="106">
         <f t="shared" si="11"/>
         <v>34</v>
       </c>
-      <c r="B47" s="156" t="s">
-        <v>110</v>
+      <c r="B47" s="155" t="s">
+        <v>108</v>
       </c>
       <c r="C47" s="100" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D47" s="99"/>
       <c r="E47" s="96">
@@ -5860,28 +5860,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J47" s="106">
+      <c r="J47" s="105">
         <f t="shared" si="4"/>
         <v>5055.5995840000005</v>
       </c>
-      <c r="K47" s="106">
+      <c r="K47" s="105">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L47" s="106">
+      <c r="L47" s="105">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M47" s="106">
+      <c r="M47" s="105">
         <f t="shared" si="6"/>
         <v>798.14200800000003</v>
       </c>
-      <c r="N47" s="106"/>
+      <c r="N47" s="105"/>
       <c r="O47" s="98">
         <f t="shared" si="7"/>
         <v>6000.34</v>
       </c>
-      <c r="P47" s="115">
+      <c r="P47" s="114">
         <f t="shared" si="10"/>
         <v>6180.34</v>
       </c>
@@ -5891,54 +5891,54 @@
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A48" s="147">
+      <c r="A48" s="146">
         <f t="shared" si="11"/>
         <v>35</v>
       </c>
-      <c r="B48" s="156" t="s">
-        <v>111</v>
-      </c>
-      <c r="C48" s="148" t="s">
-        <v>146</v>
-      </c>
-      <c r="D48" s="149"/>
-      <c r="E48" s="150">
+      <c r="B48" s="155" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" s="147" t="s">
+        <v>144</v>
+      </c>
+      <c r="D48" s="148"/>
+      <c r="E48" s="149">
         <v>0.09</v>
       </c>
       <c r="F48" s="82">
         <v>6231</v>
       </c>
       <c r="G48" s="82"/>
-      <c r="H48" s="151">
+      <c r="H48" s="150">
         <f t="shared" si="0"/>
         <v>6231</v>
       </c>
-      <c r="I48" s="151">
+      <c r="I48" s="150">
         <f t="shared" si="3"/>
         <v>186.93</v>
       </c>
-      <c r="J48" s="106">
+      <c r="J48" s="105">
         <f t="shared" si="4"/>
         <v>5687.549532</v>
       </c>
-      <c r="K48" s="152">
+      <c r="K48" s="151">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L48" s="106">
+      <c r="L48" s="105">
         <f t="shared" si="5"/>
         <v>164.54070899999999</v>
       </c>
-      <c r="M48" s="106">
+      <c r="M48" s="105">
         <f t="shared" si="6"/>
         <v>897.90975899999989</v>
       </c>
-      <c r="N48" s="152"/>
+      <c r="N48" s="151"/>
       <c r="O48" s="98">
         <f t="shared" si="7"/>
         <v>13168.35</v>
       </c>
-      <c r="P48" s="115">
+      <c r="P48" s="114">
         <f t="shared" si="10"/>
         <v>13563.35</v>
       </c>
@@ -5948,15 +5948,15 @@
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A49" s="107">
+      <c r="A49" s="106">
         <f t="shared" si="11"/>
         <v>36</v>
       </c>
-      <c r="B49" s="156" t="s">
-        <v>112</v>
+      <c r="B49" s="155" t="s">
+        <v>110</v>
       </c>
       <c r="C49" s="100" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D49" s="99"/>
       <c r="E49" s="96">
@@ -5976,28 +5976,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J49" s="106">
+      <c r="J49" s="105">
         <f t="shared" si="4"/>
         <v>49924.045892000002</v>
       </c>
-      <c r="K49" s="106">
+      <c r="K49" s="105">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L49" s="106">
+      <c r="L49" s="105">
         <f t="shared" si="5"/>
         <v>1444.3017790000001</v>
       </c>
-      <c r="M49" s="106">
+      <c r="M49" s="105">
         <f t="shared" si="6"/>
         <v>7881.6523290000005</v>
       </c>
-      <c r="N49" s="106"/>
+      <c r="N49" s="105"/>
       <c r="O49" s="98">
         <f t="shared" si="7"/>
         <v>59250.36</v>
       </c>
-      <c r="P49" s="115">
+      <c r="P49" s="114">
         <f t="shared" si="10"/>
         <v>61028.36</v>
       </c>
@@ -6007,15 +6007,15 @@
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A50" s="107">
+      <c r="A50" s="106">
         <f t="shared" si="11"/>
         <v>37</v>
       </c>
-      <c r="B50" s="156" t="s">
-        <v>113</v>
+      <c r="B50" s="155" t="s">
+        <v>111</v>
       </c>
       <c r="C50" s="100" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D50" s="99"/>
       <c r="E50" s="96">
@@ -6033,28 +6033,28 @@
         <f t="shared" si="3"/>
         <v>4616.76</v>
       </c>
-      <c r="J50" s="106">
+      <c r="J50" s="105">
         <f t="shared" si="4"/>
         <v>63194.994800000008</v>
       </c>
-      <c r="K50" s="106">
+      <c r="K50" s="105">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L50" s="106">
+      <c r="L50" s="105">
         <f t="shared" si="5"/>
         <v>1828.2301</v>
       </c>
-      <c r="M50" s="106">
+      <c r="M50" s="105">
         <f t="shared" si="6"/>
         <v>9976.7751000000007</v>
       </c>
-      <c r="N50" s="106"/>
+      <c r="N50" s="105"/>
       <c r="O50" s="98">
         <f t="shared" si="7"/>
         <v>233509.37</v>
       </c>
-      <c r="P50" s="115">
+      <c r="P50" s="114">
         <f t="shared" si="10"/>
         <v>240514.37</v>
       </c>
@@ -6064,15 +6064,15 @@
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A51" s="107">
+      <c r="A51" s="106">
         <f t="shared" si="11"/>
         <v>38</v>
       </c>
-      <c r="B51" s="156" t="s">
-        <v>114</v>
+      <c r="B51" s="155" t="s">
+        <v>112</v>
       </c>
       <c r="C51" s="100" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D51" s="99"/>
       <c r="E51" s="96">
@@ -6092,28 +6092,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J51" s="106">
+      <c r="J51" s="105">
         <f t="shared" si="4"/>
         <v>61299.144956000004</v>
       </c>
-      <c r="K51" s="106">
+      <c r="K51" s="105">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L51" s="106">
+      <c r="L51" s="105">
         <f t="shared" si="5"/>
         <v>1773.3831969999999</v>
       </c>
-      <c r="M51" s="106">
+      <c r="M51" s="105">
         <f t="shared" si="6"/>
         <v>9677.4718470000007</v>
       </c>
-      <c r="N51" s="106"/>
+      <c r="N51" s="105"/>
       <c r="O51" s="98">
         <f t="shared" si="7"/>
         <v>72750.38</v>
       </c>
-      <c r="P51" s="115">
+      <c r="P51" s="114">
         <f t="shared" si="10"/>
         <v>74933.38</v>
       </c>
@@ -6123,15 +6123,15 @@
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A52" s="107">
+      <c r="A52" s="106">
         <f t="shared" si="11"/>
         <v>39</v>
       </c>
-      <c r="B52" s="156" t="s">
-        <v>115</v>
+      <c r="B52" s="155" t="s">
+        <v>113</v>
       </c>
       <c r="C52" s="100" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D52" s="99"/>
       <c r="E52" s="96">
@@ -6151,28 +6151,28 @@
         <f t="shared" si="3"/>
         <v>14.01</v>
       </c>
-      <c r="J52" s="106">
+      <c r="J52" s="105">
         <f t="shared" si="4"/>
         <v>48660.145996000007</v>
       </c>
-      <c r="K52" s="106">
+      <c r="K52" s="105">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L52" s="106">
+      <c r="L52" s="105">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M52" s="106">
+      <c r="M52" s="105">
         <f t="shared" si="6"/>
         <v>7682.1168269999998</v>
       </c>
-      <c r="N52" s="106"/>
+      <c r="N52" s="105"/>
       <c r="O52" s="98">
         <f t="shared" si="7"/>
         <v>58231.39</v>
       </c>
-      <c r="P52" s="115">
+      <c r="P52" s="114">
         <f t="shared" si="10"/>
         <v>59978.39</v>
       </c>
@@ -6181,22 +6181,22 @@
         <v>0.39000000000000018</v>
       </c>
       <c r="R52" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A53" s="107">
+      <c r="A53" s="106">
         <f t="shared" si="11"/>
         <v>40</v>
       </c>
-      <c r="B53" s="156" t="s">
-        <v>116</v>
+      <c r="B53" s="155" t="s">
+        <v>114</v>
       </c>
       <c r="C53" s="100" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D53" s="99" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="E53" s="96">
         <v>0.77</v>
@@ -6216,28 +6216,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J53" s="106">
+      <c r="J53" s="105">
         <f t="shared" si="4"/>
         <v>48660.145996000007</v>
       </c>
-      <c r="K53" s="106">
+      <c r="K53" s="105">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L53" s="106">
+      <c r="L53" s="105">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M53" s="106">
+      <c r="M53" s="105">
         <f t="shared" si="6"/>
         <v>7682.1168269999998</v>
       </c>
-      <c r="N53" s="106"/>
+      <c r="N53" s="105"/>
       <c r="O53" s="98">
         <f t="shared" si="7"/>
         <v>57750.400000000001</v>
       </c>
-      <c r="P53" s="115">
+      <c r="P53" s="114">
         <f t="shared" si="10"/>
         <v>59483.4</v>
       </c>
@@ -6247,18 +6247,18 @@
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A54" s="107">
+      <c r="A54" s="106">
         <f t="shared" si="11"/>
         <v>41</v>
       </c>
-      <c r="B54" s="156" t="s">
-        <v>117</v>
+      <c r="B54" s="155" t="s">
+        <v>115</v>
       </c>
       <c r="C54" s="100" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D54" s="99" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="E54" s="96">
         <v>0.81</v>
@@ -6277,28 +6277,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J54" s="106">
+      <c r="J54" s="105">
         <f t="shared" si="4"/>
         <v>51187.945788000005</v>
       </c>
-      <c r="K54" s="106">
+      <c r="K54" s="105">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L54" s="106">
+      <c r="L54" s="105">
         <f t="shared" si="5"/>
         <v>1480.866381</v>
       </c>
-      <c r="M54" s="106">
+      <c r="M54" s="105">
         <f t="shared" si="6"/>
         <v>8081.1878310000011</v>
       </c>
-      <c r="N54" s="106"/>
+      <c r="N54" s="105"/>
       <c r="O54" s="98">
         <f t="shared" si="7"/>
         <v>60750.41</v>
       </c>
-      <c r="P54" s="115">
+      <c r="P54" s="114">
         <f t="shared" si="10"/>
         <v>62573.41</v>
       </c>
@@ -6308,18 +6308,18 @@
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A55" s="176">
+      <c r="A55" s="175">
         <f t="shared" si="11"/>
         <v>42</v>
       </c>
-      <c r="B55" s="177" t="s">
-        <v>118</v>
-      </c>
-      <c r="C55" s="178" t="s">
-        <v>148</v>
+      <c r="B55" s="176" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" s="177" t="s">
+        <v>146</v>
       </c>
       <c r="D55" s="99" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E55" s="96">
         <v>0.77</v>
@@ -6335,28 +6335,28 @@
         <v>0</v>
       </c>
       <c r="I55" s="97"/>
-      <c r="J55" s="106">
+      <c r="J55" s="105">
         <f t="shared" si="4"/>
         <v>48660.145996000007</v>
       </c>
-      <c r="K55" s="106">
+      <c r="K55" s="105">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L55" s="106">
+      <c r="L55" s="105">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M55" s="106">
+      <c r="M55" s="105">
         <f t="shared" si="6"/>
         <v>7682.1168269999998</v>
       </c>
-      <c r="N55" s="106"/>
+      <c r="N55" s="105"/>
       <c r="O55" s="98">
         <f t="shared" si="7"/>
         <v>57750.42</v>
       </c>
-      <c r="P55" s="115">
+      <c r="P55" s="114">
         <f t="shared" si="10"/>
         <v>59483.42</v>
       </c>
@@ -6365,19 +6365,19 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="R55" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A56" s="107">
+      <c r="A56" s="106">
         <f t="shared" si="11"/>
         <v>43</v>
       </c>
-      <c r="B56" s="156" t="s">
-        <v>119</v>
+      <c r="B56" s="155" t="s">
+        <v>117</v>
       </c>
       <c r="C56" s="100" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D56" s="99"/>
       <c r="E56" s="96">
@@ -6395,28 +6395,28 @@
         <f t="shared" si="3"/>
         <v>3497.91</v>
       </c>
-      <c r="J56" s="106">
+      <c r="J56" s="105">
         <f t="shared" si="4"/>
         <v>48660.145996000007</v>
       </c>
-      <c r="K56" s="106">
+      <c r="K56" s="105">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L56" s="106">
+      <c r="L56" s="105">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M56" s="106">
+      <c r="M56" s="105">
         <f t="shared" si="6"/>
         <v>7682.1168269999998</v>
       </c>
-      <c r="N56" s="106"/>
+      <c r="N56" s="105"/>
       <c r="O56" s="98">
         <f t="shared" si="7"/>
         <v>177845.43</v>
       </c>
-      <c r="P56" s="115">
+      <c r="P56" s="114">
         <f t="shared" si="10"/>
         <v>183180.43</v>
       </c>
@@ -6426,15 +6426,15 @@
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A57" s="107">
+      <c r="A57" s="106">
         <f t="shared" si="11"/>
         <v>44</v>
       </c>
-      <c r="B57" s="156" t="s">
-        <v>120</v>
+      <c r="B57" s="155" t="s">
+        <v>118</v>
       </c>
       <c r="C57" s="100" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D57" s="99"/>
       <c r="E57" s="96">
@@ -6452,28 +6452,28 @@
         <f t="shared" si="3"/>
         <v>1596.51</v>
       </c>
-      <c r="J57" s="106">
+      <c r="J57" s="105">
         <f t="shared" si="4"/>
         <v>48660.145996000007</v>
       </c>
-      <c r="K57" s="106">
+      <c r="K57" s="105">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L57" s="106">
+      <c r="L57" s="105">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M57" s="106">
+      <c r="M57" s="105">
         <f t="shared" si="6"/>
         <v>7682.1168269999998</v>
       </c>
-      <c r="N57" s="106"/>
+      <c r="N57" s="105"/>
       <c r="O57" s="98">
         <f t="shared" si="7"/>
         <v>112564.44</v>
       </c>
-      <c r="P57" s="115">
+      <c r="P57" s="114">
         <f t="shared" si="10"/>
         <v>115941.44</v>
       </c>
@@ -6483,18 +6483,18 @@
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A58" s="107">
+      <c r="A58" s="106">
         <f t="shared" si="11"/>
         <v>45</v>
       </c>
-      <c r="B58" s="156" t="s">
-        <v>121</v>
+      <c r="B58" s="155" t="s">
+        <v>119</v>
       </c>
       <c r="C58" s="100" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D58" s="99" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="E58" s="96">
         <v>0.77</v>
@@ -6514,28 +6514,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J58" s="106">
+      <c r="J58" s="105">
         <f t="shared" si="4"/>
         <v>48660.145996000007</v>
       </c>
-      <c r="K58" s="106">
+      <c r="K58" s="105">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L58" s="106">
+      <c r="L58" s="105">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M58" s="106">
+      <c r="M58" s="105">
         <f t="shared" si="6"/>
         <v>7682.1168269999998</v>
       </c>
-      <c r="N58" s="106"/>
+      <c r="N58" s="105"/>
       <c r="O58" s="98">
         <f t="shared" si="7"/>
         <v>57750.45</v>
       </c>
-      <c r="P58" s="115">
+      <c r="P58" s="114">
         <f t="shared" si="10"/>
         <v>59483.45</v>
       </c>
@@ -6545,15 +6545,15 @@
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A59" s="107">
+      <c r="A59" s="106">
         <f t="shared" si="11"/>
         <v>46</v>
       </c>
-      <c r="B59" s="156" t="s">
-        <v>122</v>
+      <c r="B59" s="155" t="s">
+        <v>120</v>
       </c>
       <c r="C59" s="100" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D59" s="99"/>
       <c r="E59" s="96">
@@ -6573,28 +6573,28 @@
         <f t="shared" si="3"/>
         <v>207.6</v>
       </c>
-      <c r="J59" s="106">
+      <c r="J59" s="105">
         <f t="shared" si="4"/>
         <v>54347.695528000004</v>
       </c>
-      <c r="K59" s="106">
+      <c r="K59" s="105">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L59" s="106">
+      <c r="L59" s="105">
         <f t="shared" si="5"/>
         <v>1572.2778860000001</v>
       </c>
-      <c r="M59" s="106">
+      <c r="M59" s="105">
         <f t="shared" si="6"/>
         <v>8580.026586</v>
       </c>
-      <c r="N59" s="106"/>
+      <c r="N59" s="105"/>
       <c r="O59" s="98">
         <f t="shared" si="7"/>
         <v>71628.460000000006</v>
       </c>
-      <c r="P59" s="115">
+      <c r="P59" s="114">
         <f t="shared" si="10"/>
         <v>73777.460000000006</v>
       </c>
@@ -6603,12 +6603,12 @@
         <v>0.46000000000000024</v>
       </c>
       <c r="R59" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A60" s="107"/>
-      <c r="B60" s="156"/>
+      <c r="A60" s="106"/>
+      <c r="B60" s="155"/>
       <c r="C60" s="94"/>
       <c r="D60" s="99"/>
       <c r="E60" s="96"/>
@@ -6616,62 +6616,62 @@
       <c r="G60" s="82"/>
       <c r="H60" s="97"/>
       <c r="I60" s="97"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="106"/>
-      <c r="L60" s="106"/>
-      <c r="M60" s="106"/>
-      <c r="N60" s="106"/>
+      <c r="J60" s="105"/>
+      <c r="K60" s="105"/>
+      <c r="L60" s="105"/>
+      <c r="M60" s="105"/>
+      <c r="N60" s="105"/>
       <c r="O60" s="98"/>
-      <c r="P60" s="115"/>
+      <c r="P60" s="114"/>
       <c r="Q60" s="51"/>
     </row>
     <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="108"/>
-      <c r="B61" s="157"/>
-      <c r="C61" s="109"/>
-      <c r="D61" s="109"/>
-      <c r="E61" s="110">
+      <c r="A61" s="107"/>
+      <c r="B61" s="156"/>
+      <c r="C61" s="108"/>
+      <c r="D61" s="108"/>
+      <c r="E61" s="109">
         <f t="shared" ref="E61:M61" si="13">SUM(E14:E60)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F61" s="111">
+      <c r="F61" s="110">
         <f t="shared" si="13"/>
         <v>8670136</v>
       </c>
-      <c r="G61" s="112">
+      <c r="G61" s="111">
         <f t="shared" si="13"/>
         <v>6601052</v>
       </c>
-      <c r="H61" s="112">
+      <c r="H61" s="111">
         <f t="shared" si="13"/>
         <v>2069084</v>
       </c>
-      <c r="I61" s="112">
+      <c r="I61" s="111">
         <f t="shared" si="13"/>
         <v>62377.62000000001</v>
       </c>
-      <c r="J61" s="113">
+      <c r="J61" s="112">
         <f t="shared" si="13"/>
         <v>6319499.4799999995</v>
       </c>
-      <c r="K61" s="113">
+      <c r="K61" s="112">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L61" s="113">
+      <c r="L61" s="112">
         <f t="shared" si="13"/>
         <v>182823.00999999992</v>
       </c>
-      <c r="M61" s="113">
+      <c r="M61" s="112">
         <f t="shared" si="13"/>
         <v>997677.51000000013</v>
       </c>
-      <c r="N61" s="114"/>
-      <c r="O61" s="119">
+      <c r="N61" s="113"/>
+      <c r="O61" s="118">
         <f>SUM(O14:O60)</f>
         <v>9631474.8099999987</v>
       </c>
-      <c r="P61" s="116">
+      <c r="P61" s="115">
         <f>SUM(P14:P60)</f>
         <v>9920424.8099999987</v>
       </c>
@@ -6682,99 +6682,103 @@
     </row>
     <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="210" t="s">
+      <c r="C64" s="201" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="210"/>
-      <c r="E64" s="210"/>
-      <c r="F64" s="210"/>
-      <c r="G64" s="210"/>
-      <c r="H64" s="210"/>
-      <c r="I64" s="210"/>
-      <c r="J64" s="210"/>
-      <c r="K64" s="210"/>
-      <c r="L64" s="210"/>
-      <c r="M64" s="210"/>
-      <c r="N64" s="210"/>
-      <c r="O64" s="210"/>
+      <c r="D64" s="201"/>
+      <c r="E64" s="201"/>
+      <c r="F64" s="201"/>
+      <c r="G64" s="201"/>
+      <c r="H64" s="201"/>
+      <c r="I64" s="201"/>
+      <c r="J64" s="201"/>
+      <c r="K64" s="201"/>
+      <c r="L64" s="201"/>
+      <c r="M64" s="201"/>
+      <c r="N64" s="201"/>
+      <c r="O64" s="201"/>
     </row>
     <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="210"/>
-      <c r="D65" s="210"/>
-      <c r="E65" s="210"/>
-      <c r="F65" s="210"/>
-      <c r="G65" s="210"/>
-      <c r="H65" s="210"/>
-      <c r="I65" s="210"/>
-      <c r="J65" s="210"/>
-      <c r="K65" s="210"/>
-      <c r="L65" s="210"/>
-      <c r="M65" s="210"/>
-      <c r="N65" s="210"/>
-      <c r="O65" s="210"/>
+      <c r="C65" s="201"/>
+      <c r="D65" s="201"/>
+      <c r="E65" s="201"/>
+      <c r="F65" s="201"/>
+      <c r="G65" s="201"/>
+      <c r="H65" s="201"/>
+      <c r="I65" s="201"/>
+      <c r="J65" s="201"/>
+      <c r="K65" s="201"/>
+      <c r="L65" s="201"/>
+      <c r="M65" s="201"/>
+      <c r="N65" s="201"/>
+      <c r="O65" s="201"/>
     </row>
     <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="210"/>
-      <c r="D66" s="210"/>
-      <c r="E66" s="210"/>
-      <c r="F66" s="210"/>
-      <c r="G66" s="210"/>
-      <c r="H66" s="210"/>
-      <c r="I66" s="210"/>
-      <c r="J66" s="210"/>
-      <c r="K66" s="210"/>
-      <c r="L66" s="210"/>
-      <c r="M66" s="210"/>
-      <c r="N66" s="210"/>
-      <c r="O66" s="210"/>
+      <c r="C66" s="201"/>
+      <c r="D66" s="201"/>
+      <c r="E66" s="201"/>
+      <c r="F66" s="201"/>
+      <c r="G66" s="201"/>
+      <c r="H66" s="201"/>
+      <c r="I66" s="201"/>
+      <c r="J66" s="201"/>
+      <c r="K66" s="201"/>
+      <c r="L66" s="201"/>
+      <c r="M66" s="201"/>
+      <c r="N66" s="201"/>
+      <c r="O66" s="201"/>
     </row>
     <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C67" s="210"/>
-      <c r="D67" s="210"/>
-      <c r="E67" s="210"/>
-      <c r="F67" s="210"/>
-      <c r="G67" s="210"/>
-      <c r="H67" s="210"/>
-      <c r="I67" s="210"/>
-      <c r="J67" s="210"/>
-      <c r="K67" s="210"/>
-      <c r="L67" s="210"/>
-      <c r="M67" s="210"/>
-      <c r="N67" s="210"/>
-      <c r="O67" s="210"/>
+      <c r="C67" s="201"/>
+      <c r="D67" s="201"/>
+      <c r="E67" s="201"/>
+      <c r="F67" s="201"/>
+      <c r="G67" s="201"/>
+      <c r="H67" s="201"/>
+      <c r="I67" s="201"/>
+      <c r="J67" s="201"/>
+      <c r="K67" s="201"/>
+      <c r="L67" s="201"/>
+      <c r="M67" s="201"/>
+      <c r="N67" s="201"/>
+      <c r="O67" s="201"/>
     </row>
     <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="210"/>
-      <c r="D68" s="210"/>
-      <c r="E68" s="210"/>
-      <c r="F68" s="210"/>
-      <c r="G68" s="210"/>
-      <c r="H68" s="210"/>
-      <c r="I68" s="210"/>
-      <c r="J68" s="210"/>
-      <c r="K68" s="210"/>
-      <c r="L68" s="210"/>
-      <c r="M68" s="210"/>
-      <c r="N68" s="210"/>
-      <c r="O68" s="210"/>
+      <c r="C68" s="201"/>
+      <c r="D68" s="201"/>
+      <c r="E68" s="201"/>
+      <c r="F68" s="201"/>
+      <c r="G68" s="201"/>
+      <c r="H68" s="201"/>
+      <c r="I68" s="201"/>
+      <c r="J68" s="201"/>
+      <c r="K68" s="201"/>
+      <c r="L68" s="201"/>
+      <c r="M68" s="201"/>
+      <c r="N68" s="201"/>
+      <c r="O68" s="201"/>
     </row>
     <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="210"/>
-      <c r="D69" s="210"/>
-      <c r="E69" s="210"/>
-      <c r="F69" s="210"/>
-      <c r="G69" s="210"/>
-      <c r="H69" s="210"/>
-      <c r="I69" s="210"/>
-      <c r="J69" s="210"/>
-      <c r="K69" s="210"/>
-      <c r="L69" s="210"/>
-      <c r="M69" s="210"/>
-      <c r="N69" s="210"/>
-      <c r="O69" s="210"/>
+      <c r="C69" s="201"/>
+      <c r="D69" s="201"/>
+      <c r="E69" s="201"/>
+      <c r="F69" s="201"/>
+      <c r="G69" s="201"/>
+      <c r="H69" s="201"/>
+      <c r="I69" s="201"/>
+      <c r="J69" s="201"/>
+      <c r="K69" s="201"/>
+      <c r="L69" s="201"/>
+      <c r="M69" s="201"/>
+      <c r="N69" s="201"/>
+      <c r="O69" s="201"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="J1:P5"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="C64:O69"/>
     <mergeCell ref="A6:P10"/>
     <mergeCell ref="A12:A13"/>
@@ -6791,10 +6795,6 @@
     <mergeCell ref="L12:L13"/>
     <mergeCell ref="K12:K13"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="J1:P5"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6815,26 +6815,26 @@
       <c r="C3" s="21"/>
     </row>
     <row r="4" spans="3:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="141" t="s">
+      <c r="C4" s="140" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="142">
+      <c r="D4" s="141">
         <v>1</v>
       </c>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="139"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="138"/>
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
     </row>
     <row r="5" spans="3:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="143" t="s">
+      <c r="C5" s="142" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="144"/>
+      <c r="D5" s="143"/>
       <c r="E5" t="s">
         <v>56</v>
       </c>
@@ -6842,17 +6842,17 @@
         <v>57</v>
       </c>
       <c r="H5" t="s">
-        <v>216</v>
-      </c>
-      <c r="J5" s="140"/>
+        <v>203</v>
+      </c>
+      <c r="J5" s="139"/>
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C6" s="143" t="s">
+      <c r="C6" s="142" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="144" t="s">
+      <c r="D6" s="143" t="s">
         <v>59</v>
       </c>
       <c r="E6" t="s">
@@ -6862,9 +6862,9 @@
         <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>215</v>
-      </c>
-      <c r="J6" s="140"/>
+        <v>202</v>
+      </c>
+      <c r="J6" s="139"/>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
     </row>
@@ -6872,54 +6872,54 @@
       <c r="C7" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="J7" s="140"/>
+      <c r="J7" s="139"/>
       <c r="K7" s="21"/>
       <c r="L7" s="21"/>
     </row>
     <row r="8" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C8" s="230" t="s">
-        <v>217</v>
-      </c>
-      <c r="D8" s="231"/>
-      <c r="E8" s="231"/>
-      <c r="F8" s="231"/>
-      <c r="G8" s="231"/>
-      <c r="H8" s="231"/>
-      <c r="I8" s="231"/>
-      <c r="J8" s="232"/>
+      <c r="C8" s="236" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" s="237"/>
+      <c r="E8" s="237"/>
+      <c r="F8" s="237"/>
+      <c r="G8" s="237"/>
+      <c r="H8" s="237"/>
+      <c r="I8" s="237"/>
+      <c r="J8" s="238"/>
       <c r="K8" s="21"/>
       <c r="L8" s="21"/>
     </row>
     <row r="9" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="233"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="234"/>
-      <c r="F9" s="234"/>
-      <c r="G9" s="234"/>
-      <c r="H9" s="234"/>
-      <c r="I9" s="234"/>
-      <c r="J9" s="235"/>
+      <c r="C9" s="239"/>
+      <c r="D9" s="240"/>
+      <c r="E9" s="240"/>
+      <c r="F9" s="240"/>
+      <c r="G9" s="240"/>
+      <c r="H9" s="240"/>
+      <c r="I9" s="240"/>
+      <c r="J9" s="241"/>
     </row>
     <row r="11" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C12" s="239" t="s">
+      <c r="C12" s="182" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="240">
+      <c r="D12" s="183">
         <v>1</v>
       </c>
-      <c r="E12" s="138"/>
-      <c r="F12" s="138"/>
-      <c r="G12" s="138"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="138"/>
-      <c r="J12" s="139"/>
+      <c r="E12" s="137"/>
+      <c r="F12" s="137"/>
+      <c r="G12" s="137"/>
+      <c r="H12" s="137"/>
+      <c r="I12" s="137"/>
+      <c r="J12" s="138"/>
     </row>
     <row r="13" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C13" s="241" t="s">
+      <c r="C13" s="184" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="242"/>
+      <c r="D13" s="185"/>
       <c r="E13" t="s">
         <v>56</v>
       </c>
@@ -6927,15 +6927,15 @@
         <v>57</v>
       </c>
       <c r="H13" t="s">
-        <v>219</v>
-      </c>
-      <c r="J13" s="140"/>
+        <v>206</v>
+      </c>
+      <c r="J13" s="139"/>
     </row>
     <row r="14" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C14" s="241" t="s">
+      <c r="C14" s="184" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="242" t="s">
+      <c r="D14" s="185" t="s">
         <v>59</v>
       </c>
       <c r="E14" t="s">
@@ -6945,37 +6945,37 @@
         <v>28</v>
       </c>
       <c r="H14" t="s">
-        <v>220</v>
-      </c>
-      <c r="J14" s="140"/>
+        <v>207</v>
+      </c>
+      <c r="J14" s="139"/>
     </row>
     <row r="15" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="140"/>
+      <c r="J15" s="139"/>
     </row>
     <row r="16" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C16" s="230" t="s">
-        <v>221</v>
-      </c>
-      <c r="D16" s="231"/>
-      <c r="E16" s="231"/>
-      <c r="F16" s="231"/>
-      <c r="G16" s="231"/>
-      <c r="H16" s="231"/>
-      <c r="I16" s="231"/>
-      <c r="J16" s="232"/>
+      <c r="C16" s="236" t="s">
+        <v>208</v>
+      </c>
+      <c r="D16" s="237"/>
+      <c r="E16" s="237"/>
+      <c r="F16" s="237"/>
+      <c r="G16" s="237"/>
+      <c r="H16" s="237"/>
+      <c r="I16" s="237"/>
+      <c r="J16" s="238"/>
     </row>
     <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="233"/>
-      <c r="D17" s="234"/>
-      <c r="E17" s="234"/>
-      <c r="F17" s="234"/>
-      <c r="G17" s="234"/>
-      <c r="H17" s="234"/>
-      <c r="I17" s="234"/>
-      <c r="J17" s="235"/>
+      <c r="C17" s="239"/>
+      <c r="D17" s="240"/>
+      <c r="E17" s="240"/>
+      <c r="F17" s="240"/>
+      <c r="G17" s="240"/>
+      <c r="H17" s="240"/>
+      <c r="I17" s="240"/>
+      <c r="J17" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/O HIGGINS 1157/Junio/Junio ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Junio/Junio ohiggins.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA9D334-3521-4EA2-938C-1AF21387F432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CC3C6F-B3EF-46CD-B51B-F194E2F036FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$69</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$118</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="216">
   <si>
     <t>TOTAL</t>
   </si>
@@ -176,9 +181,6 @@
     <t xml:space="preserve">CAJA DE BANCOS </t>
   </si>
   <si>
-    <t>Haberes</t>
-  </si>
-  <si>
     <t>Descuentos</t>
   </si>
   <si>
@@ -240,9 +242,6 @@
   </si>
   <si>
     <t>Allianz - Seguro integral de consorcio - Poliza Nro. 260230779515</t>
-  </si>
-  <si>
-    <t>Allianz - Seguro accidentes personales encargado</t>
   </si>
   <si>
     <t>Allianz - Seguro accidentes RCP encargado</t>
@@ -482,66 +481,15 @@
     <t>Edesur - Cliente Nro. 04742252</t>
   </si>
   <si>
-    <t>Transf 06/05</t>
-  </si>
-  <si>
     <t>Debito Autom.</t>
   </si>
   <si>
-    <t>Debito 12/05</t>
-  </si>
-  <si>
-    <t>Debito 06/05</t>
-  </si>
-  <si>
-    <t>ADS - Suministro y colocacion de dos nuevas baterias para alambas autonomas de cabina - 2 luces de emergencia</t>
-  </si>
-  <si>
-    <t>Transf 12/05</t>
-  </si>
-  <si>
-    <t>Transf 13/05</t>
-  </si>
-  <si>
-    <t>Flores Lisandro - Revoque Gazeta de gas</t>
-  </si>
-  <si>
-    <t>Ferrateria La plaza - 6 dicroicas</t>
-  </si>
-  <si>
-    <t>Transf 14/05</t>
-  </si>
-  <si>
-    <t>Traspaso administracion antigua - Honorarios cobrados por administracion saliente Fc- 000586</t>
-  </si>
-  <si>
-    <t>Transf 15/05</t>
-  </si>
-  <si>
     <t>Plan de Pago ARCA</t>
   </si>
   <si>
-    <t>Cuota 14/24</t>
-  </si>
-  <si>
-    <t>Debito 18/05</t>
-  </si>
-  <si>
-    <t>Arguello Alejandro - Estado de situaicon diagnositico en sala de medidores, reparacion de perdidas y cambio de llave de paso - Reparacion de brida de regulador principal, corte de servicios y habilitacion de unidades. Encendido de artefactos - Fc. 0000384</t>
-  </si>
-  <si>
-    <t>Transf 29/04</t>
-  </si>
-  <si>
     <t>Casa Ruan - Compra de lamparas</t>
   </si>
   <si>
-    <t>Transf 30/04</t>
-  </si>
-  <si>
-    <t>Orse Joathan Gabriel - Cambio de lampras en altura y medidores de gas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gustavo Padron -  Sr. Contador </t>
   </si>
   <si>
@@ -572,30 +520,15 @@
     <t>Gimenez Gisele</t>
   </si>
   <si>
-    <t>Inicio 06/05/2026</t>
-  </si>
-  <si>
-    <t>Dinero al 29/05</t>
-  </si>
-  <si>
-    <t>Plazo Fijo (Vto. 05/06)</t>
-  </si>
-  <si>
     <t>Martinez Blanca Myriam</t>
   </si>
   <si>
-    <t>Transferencia Agüero Villanueva Brisa - 08/05</t>
-  </si>
-  <si>
     <t>Monica Bratuz y Federico Paez</t>
   </si>
   <si>
     <t>Deposita - Paga Cocheras 1, 15 y 22 - Lanzilotto</t>
   </si>
   <si>
-    <t>Saldo inicial - Al 30/04</t>
-  </si>
-  <si>
     <t xml:space="preserve">Caja SUM </t>
   </si>
   <si>
@@ -608,13 +541,7 @@
     <t xml:space="preserve">Caja Efectivo </t>
   </si>
   <si>
-    <t>Liquidacion Plazo Fijo colocado por administracion anterior (06/05)</t>
-  </si>
-  <si>
     <t>Caja Real en banco (Caja Bancaria + SUM)</t>
-  </si>
-  <si>
-    <t>Gastos bancarios - Desde el 25 del mes 4</t>
   </si>
   <si>
     <t>Gastos A:</t>
@@ -673,15 +600,6 @@
     <t>PERÍODO: JUNIO</t>
   </si>
   <si>
-    <t>Honorarios administracion - Se adeuda Mitad de JUNIO</t>
-  </si>
-  <si>
-    <t>Honorarios administracion saliente - Del 01 al 15 de JUNIO - Fc. 00585</t>
-  </si>
-  <si>
-    <t>Abono ascensor - ADS - Mantenimiento mes de mayo</t>
-  </si>
-  <si>
     <t>Romanatti Carlos - Certificacion de copias digitales</t>
   </si>
   <si>
@@ -701,6 +619,78 @@
   </si>
   <si>
     <t>Transf 09/06</t>
+  </si>
+  <si>
+    <t>Abono de 2 meses</t>
+  </si>
+  <si>
+    <t>Debito 12/06</t>
+  </si>
+  <si>
+    <t>Cuota 15/24</t>
+  </si>
+  <si>
+    <t>Debito 16/06</t>
+  </si>
+  <si>
+    <t>Debito 30/06</t>
+  </si>
+  <si>
+    <t>Haberes + SAC</t>
+  </si>
+  <si>
+    <t>Abono ascensor - ADS - No enviaron la factura</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Se adeuda Mitad de MAYO Y JUNIO</t>
+  </si>
+  <si>
+    <t>Se adeuda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gastos bancarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo inicial </t>
+  </si>
+  <si>
+    <t>Saldo final</t>
+  </si>
+  <si>
+    <t>Gombach Paula / Romero Miguel</t>
+  </si>
+  <si>
+    <t>Brisa Agüero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencia ya identificada mes anterior </t>
+  </si>
+  <si>
+    <t>Punitorios mal cobrados</t>
+  </si>
+  <si>
+    <t>Deposito 29/06</t>
+  </si>
+  <si>
+    <t>Ingreso correspondiente a finalizacion de P. Fijo 05/06</t>
+  </si>
+  <si>
+    <t>Egreso a FCI super ahorro plus inversion - 19/06</t>
+  </si>
+  <si>
+    <t>FCI Super ahorro plus</t>
+  </si>
+  <si>
+    <t>Inicio 19/06/2026</t>
+  </si>
+  <si>
+    <t>Egreso pago de metrogas</t>
+  </si>
+  <si>
+    <t>Servisur - Correccion de secuencia de fases alimentacion de bomba de agua</t>
+  </si>
+  <si>
+    <t>Transf 30/06</t>
   </si>
 </sst>
 </file>
@@ -717,7 +707,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -873,8 +863,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -959,6 +956,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="40">
     <border>
@@ -1462,7 +1465,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1621,7 +1624,6 @@
     </xf>
     <xf numFmtId="44" fontId="11" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="8" fontId="20" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="17" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1667,9 +1669,6 @@
     <xf numFmtId="44" fontId="15" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="8" fontId="14" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1714,7 +1713,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="11" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="8" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1748,31 +1746,38 @@
     <xf numFmtId="44" fontId="1" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1786,25 +1791,43 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1851,12 +1874,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1884,33 +1901,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1929,8 +1919,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="21" fillId="12" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="15" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="15" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="15" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="15" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="12" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="7" fillId="12" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="12" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="12" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2014,9 +2022,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2054,9 +2062,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2089,9 +2097,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2124,9 +2149,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2300,32 +2342,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M119"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="186" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="186"/>
-      <c r="D1" s="186"/>
-      <c r="E1" s="187"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="184" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="185"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="10" t="s">
         <v>46</v>
@@ -2334,16 +2376,16 @@
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" ht="56.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="190" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="191"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="186"/>
+      <c r="D3" s="186"/>
+      <c r="E3" s="187"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
@@ -2354,12 +2396,12 @@
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2367,68 +2409,68 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="84" t="s">
         <v>38</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E6" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="192" t="s">
-        <v>209</v>
-      </c>
-      <c r="C8" s="192"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="192"/>
-      <c r="C9" s="192"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="192"/>
-      <c r="C10" s="192"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="193" t="s">
-        <v>148</v>
-      </c>
-      <c r="B13" s="193"/>
-      <c r="C13" s="193"/>
-      <c r="D13" s="193"/>
-      <c r="E13" s="193"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="193"/>
-      <c r="B14" s="193"/>
-      <c r="C14" s="193"/>
-      <c r="D14" s="193"/>
-      <c r="E14" s="193"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="193"/>
-      <c r="B15" s="193"/>
-      <c r="C15" s="193"/>
-      <c r="D15" s="193"/>
-      <c r="E15" s="193"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="193"/>
-      <c r="B16" s="193"/>
-      <c r="C16" s="193"/>
-      <c r="D16" s="193"/>
-      <c r="E16" s="193"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="188" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="188"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="188"/>
+      <c r="C9" s="188"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="188"/>
+      <c r="C10" s="188"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="189" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="189"/>
+      <c r="C13" s="189"/>
+      <c r="D13" s="189"/>
+      <c r="E13" s="189"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="189"/>
+      <c r="B14" s="189"/>
+      <c r="C14" s="189"/>
+      <c r="D14" s="189"/>
+      <c r="E14" s="189"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="189"/>
+      <c r="B15" s="189"/>
+      <c r="C15" s="189"/>
+      <c r="D15" s="189"/>
+      <c r="E15" s="189"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="189"/>
+      <c r="B16" s="189"/>
+      <c r="C16" s="189"/>
+      <c r="D16" s="189"/>
+      <c r="E16" s="189"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>7</v>
       </c>
@@ -2437,188 +2479,188 @@
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
       <c r="D21" s="103"/>
-      <c r="E21" s="120"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="188" t="s">
+      <c r="E21" s="119"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="180" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="181"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="159">
+        <v>1987270.86</v>
+      </c>
+      <c r="E22" s="120"/>
+      <c r="H22" s="21"/>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="189"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="162">
-        <v>1987270.86</v>
-      </c>
-      <c r="E22" s="121"/>
-      <c r="H22" s="21"/>
-    </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="188" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="189"/>
+      <c r="B23" s="181"/>
       <c r="C23" s="20"/>
-      <c r="D23" s="162">
+      <c r="D23" s="159">
         <v>-432231.42</v>
       </c>
       <c r="E23" s="22"/>
       <c r="H23" s="21"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="188" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="189"/>
+      <c r="B24" s="181"/>
       <c r="C24" s="20"/>
-      <c r="D24" s="163">
+      <c r="D24" s="160">
         <v>0.34</v>
       </c>
       <c r="E24" s="22"/>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="23" t="s">
         <v>8</v>
       </c>
       <c r="B25" s="23"/>
       <c r="C25" s="23"/>
       <c r="D25" s="24"/>
-      <c r="E25" s="122">
+      <c r="E25" s="121">
         <f>SUM(D22:D24)</f>
         <v>1555039.7800000003</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
       <c r="D26" s="24"/>
-      <c r="E26" s="123"/>
-    </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E26" s="122"/>
+    </row>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="20"/>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
       <c r="D27" s="36"/>
-      <c r="E27" s="135"/>
-    </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E27" s="133"/>
+    </row>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20"/>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
       <c r="D28" s="36"/>
-      <c r="E28" s="135"/>
-    </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E28" s="133"/>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="20"/>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
       <c r="D29" s="36"/>
-      <c r="E29" s="135"/>
-    </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E29" s="133"/>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
         <v>8</v>
       </c>
       <c r="B30" s="29"/>
       <c r="C30" s="29"/>
       <c r="D30" s="93"/>
-      <c r="E30" s="125">
+      <c r="E30" s="124">
         <f>SUM(D27:D29)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>39</v>
       </c>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="24"/>
-      <c r="E31" s="123"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E31" s="122"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B32" s="85"/>
       <c r="C32" s="85"/>
-      <c r="D32" s="36">
-        <v>641302.6</v>
-      </c>
-      <c r="E32" s="124" t="s">
-        <v>153</v>
+      <c r="D32" s="247">
+        <v>589558.79</v>
+      </c>
+      <c r="E32" s="123" t="s">
+        <v>196</v>
       </c>
       <c r="G32" s="67"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="C33" s="85"/>
-      <c r="D33" s="36">
+      <c r="D33" s="247">
         <v>182823.01</v>
       </c>
-      <c r="E33" s="124" t="s">
-        <v>164</v>
+      <c r="E33" s="123" t="s">
+        <v>195</v>
       </c>
       <c r="G33" s="67"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
         <v>41</v>
       </c>
       <c r="B34" s="85"/>
       <c r="C34" s="85"/>
-      <c r="D34" s="243">
+      <c r="D34" s="247">
         <v>53956.04</v>
       </c>
-      <c r="E34" s="124" t="s">
-        <v>152</v>
+      <c r="E34" s="123" t="s">
+        <v>193</v>
       </c>
       <c r="G34" s="67"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
         <v>43</v>
       </c>
       <c r="B35" s="85"/>
       <c r="C35" s="85"/>
-      <c r="D35" s="243">
+      <c r="D35" s="247">
         <v>5995.12</v>
       </c>
-      <c r="E35" s="124" t="str">
+      <c r="E35" s="123" t="str">
         <f>E34</f>
-        <v>Debito 12/05</v>
+        <v>Debito 12/06</v>
       </c>
       <c r="G35" s="51"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="20" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="85"/>
       <c r="C36" s="85"/>
-      <c r="D36" s="243">
+      <c r="D36" s="247">
         <v>97494.97</v>
       </c>
-      <c r="E36" s="124" t="str">
+      <c r="E36" s="123" t="str">
         <f>E34</f>
-        <v>Debito 12/05</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>Debito 12/06</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="23" t="s">
         <v>40</v>
       </c>
@@ -2627,900 +2669,814 @@
       <c r="D37" s="24"/>
       <c r="E37" s="42">
         <f>SUM(D32:D36)</f>
-        <v>981571.74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>929827.93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
       <c r="D38" s="25"/>
-      <c r="E38" s="125"/>
-    </row>
-    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="194" t="s">
+      <c r="E38" s="124"/>
+    </row>
+    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="177" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" s="178"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="245">
+        <v>205033.71</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="177" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="195"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="161">
-        <v>205033.71</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="194" t="s">
-        <v>71</v>
-      </c>
-      <c r="B40" s="195"/>
+      <c r="B40" s="178"/>
       <c r="C40" s="28"/>
-      <c r="D40" s="161">
-        <v>1282.32</v>
+      <c r="D40" s="245">
+        <v>12020</v>
       </c>
       <c r="E40" s="22" t="str">
         <f>E39</f>
         <v>Debito Autom.</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="194" t="s">
-        <v>72</v>
-      </c>
-      <c r="B41" s="195"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="161">
-        <v>12020</v>
-      </c>
-      <c r="E41" s="22" t="str">
-        <f>E40</f>
-        <v>Debito Autom.</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="23" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="42">
-        <f>SUM(D39:D41)</f>
-        <v>218336.03</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="17" t="s">
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="42">
+        <f>SUM(D39:D40)</f>
+        <v>217053.71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="126"/>
-    </row>
-    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="125"/>
+    </row>
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="246">
+        <v>1313151.8700000001</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="B44" s="31"/>
+        <v>67</v>
+      </c>
+      <c r="B44" s="32"/>
       <c r="C44" s="31"/>
-      <c r="D44" s="242">
-        <v>1313151.8700000001</v>
-      </c>
-      <c r="E44" s="35" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="31" t="s">
+      <c r="D44" s="176">
+        <v>0</v>
+      </c>
+      <c r="E44" s="35"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="177" t="s">
         <v>68</v>
       </c>
-      <c r="B45" s="32"/>
+      <c r="B45" s="178"/>
       <c r="C45" s="31"/>
-      <c r="D45" s="242">
-        <v>5910.35</v>
+      <c r="D45" s="246">
+        <v>511264.75</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="194" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" s="195"/>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="27" t="s">
+        <v>192</v>
+      </c>
       <c r="C46" s="31"/>
-      <c r="D46" s="242">
-        <v>511264.75</v>
+      <c r="D46" s="246">
+        <v>62785.37</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="242">
-        <v>62785.37</v>
-      </c>
-      <c r="E47" s="35" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="23" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="23" t="s">
         <v>12</v>
+      </c>
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="126">
+        <f>SUM(D43:D46)</f>
+        <v>1887201.9900000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="17" t="s">
+        <v>65</v>
       </c>
       <c r="B48" s="23"/>
       <c r="C48" s="23"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="127">
-        <f>SUM(D44:D47)</f>
-        <v>1893112.3400000003</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="128"/>
-    </row>
-    <row r="50" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="188" t="s">
-        <v>213</v>
-      </c>
-      <c r="B50" s="189"/>
-      <c r="C50" s="31"/>
-      <c r="D50" s="160">
-        <v>250600</v>
+      <c r="D48" s="24"/>
+      <c r="E48" s="127"/>
+    </row>
+    <row r="49" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="180" t="s">
+        <v>198</v>
+      </c>
+      <c r="B49" s="181"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="158">
+        <v>0</v>
+      </c>
+      <c r="E49" s="35"/>
+    </row>
+    <row r="50" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="155" t="s">
+        <v>185</v>
+      </c>
+      <c r="B50" s="19"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="246">
+        <v>332362.82</v>
       </c>
       <c r="E50" s="35" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="188" t="s">
-        <v>154</v>
-      </c>
-      <c r="B51" s="189"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="160">
-        <v>367392.3</v>
+        <v>186</v>
+      </c>
+      <c r="F50" s="51"/>
+    </row>
+    <row r="51" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="87" t="s">
+        <v>187</v>
+      </c>
+      <c r="B51" s="19"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="246">
+        <v>810000</v>
       </c>
       <c r="E51" s="35" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="188" t="s">
-        <v>165</v>
-      </c>
-      <c r="B52" s="189"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="160">
-        <v>2130000</v>
+        <v>186</v>
+      </c>
+      <c r="F51" s="51"/>
+    </row>
+    <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="190" t="s">
+        <v>188</v>
+      </c>
+      <c r="B52" s="191"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="246">
+        <v>180000</v>
       </c>
       <c r="E52" s="35" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="157" t="s">
-        <v>214</v>
+        <v>186</v>
+      </c>
+      <c r="F52" s="51"/>
+    </row>
+    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="87" t="s">
+        <v>189</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="20"/>
-      <c r="D53" s="242">
-        <v>332362.82</v>
+      <c r="D53" s="246">
+        <v>60000</v>
       </c>
       <c r="E53" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="F53" s="51"/>
-    </row>
-    <row r="54" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="87" t="s">
-        <v>216</v>
-      </c>
-      <c r="B54" s="19"/>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="180" t="s">
+        <v>214</v>
+      </c>
+      <c r="B54" s="181"/>
       <c r="C54" s="20"/>
-      <c r="D54" s="242">
-        <v>810000</v>
+      <c r="D54" s="246">
+        <v>40000</v>
       </c>
       <c r="E54" s="35" t="s">
         <v>215</v>
       </c>
-      <c r="F54" s="51"/>
-    </row>
-    <row r="55" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="196" t="s">
-        <v>217</v>
-      </c>
-      <c r="B55" s="197"/>
+    </row>
+    <row r="55" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="87" t="s">
+        <v>150</v>
+      </c>
+      <c r="B55" s="19"/>
       <c r="C55" s="20"/>
-      <c r="D55" s="242">
-        <v>180000</v>
+      <c r="D55" s="246">
+        <v>31000</v>
       </c>
       <c r="E55" s="35" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="F55" s="51"/>
     </row>
-    <row r="56" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="87" t="s">
-        <v>218</v>
-      </c>
-      <c r="B56" s="19"/>
-      <c r="C56" s="20"/>
-      <c r="D56" s="242">
-        <v>60000</v>
-      </c>
-      <c r="E56" s="35" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="87" t="s">
-        <v>167</v>
-      </c>
-      <c r="B57" s="19"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="242">
-        <v>31000</v>
-      </c>
-      <c r="E57" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="F57" s="51"/>
-    </row>
-    <row r="58" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="87" t="s">
-        <v>167</v>
-      </c>
-      <c r="B58" s="19"/>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="42">
+        <f>SUM(D49:D55)</f>
+        <v>1453362.82</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B57" s="17"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="119"/>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="180" t="s">
+        <v>199</v>
+      </c>
+      <c r="B58" s="181"/>
       <c r="C58" s="20"/>
-      <c r="D58" s="160">
-        <v>10400</v>
-      </c>
-      <c r="E58" s="134" t="s">
-        <v>168</v>
-      </c>
-      <c r="F58" s="51"/>
-    </row>
-    <row r="59" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="188" t="s">
-        <v>169</v>
-      </c>
-      <c r="B59" s="189"/>
+      <c r="D58" s="161">
+        <v>0</v>
+      </c>
+      <c r="E58" s="120"/>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="87" t="s">
+        <v>151</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>200</v>
+      </c>
       <c r="C59" s="20"/>
-      <c r="D59" s="160">
-        <v>50000</v>
-      </c>
-      <c r="E59" s="134" t="s">
-        <v>168</v>
-      </c>
-      <c r="F59" s="51"/>
-    </row>
-    <row r="60" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="188" t="s">
-        <v>157</v>
-      </c>
-      <c r="B60" s="189"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="160">
-        <v>127000</v>
-      </c>
-      <c r="E60" s="134" t="s">
-        <v>156</v>
-      </c>
-      <c r="F60" s="51"/>
-    </row>
-    <row r="61" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="188" t="s">
-        <v>158</v>
-      </c>
-      <c r="B61" s="189"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="160">
-        <v>7200</v>
-      </c>
-      <c r="E61" s="134" t="s">
-        <v>159</v>
-      </c>
-      <c r="F61" s="51"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="42">
-        <f>SUM(D50:D61)</f>
-        <v>4355955.1199999992</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="120"/>
-    </row>
-    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="188" t="s">
-        <v>211</v>
-      </c>
-      <c r="B64" s="189"/>
-      <c r="C64" s="20"/>
-      <c r="D64" s="164">
-        <v>0</v>
-      </c>
-      <c r="E64" s="121"/>
-    </row>
-    <row r="65" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="188" t="s">
-        <v>212</v>
-      </c>
-      <c r="B65" s="189"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="159">
-        <v>230000</v>
-      </c>
-      <c r="E65" s="121" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="188" t="s">
-        <v>160</v>
-      </c>
-      <c r="B66" s="189"/>
-      <c r="C66" s="20"/>
-      <c r="D66" s="159">
-        <v>460000</v>
-      </c>
-      <c r="E66" s="121" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="87" t="s">
-        <v>170</v>
-      </c>
-      <c r="B67" s="19"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="159">
-        <v>0</v>
-      </c>
-      <c r="E67" s="121"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="23" t="s">
+      <c r="D59" s="157">
+        <v>0</v>
+      </c>
+      <c r="E59" s="120"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B68" s="23"/>
-      <c r="C68" s="23"/>
-      <c r="D68" s="24"/>
-      <c r="E68" s="122">
-        <f>SUM(D64:D67)</f>
-        <v>690000</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="17" t="s">
+      <c r="B60" s="23"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="121">
+        <f>SUM(D58:D59)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B69" s="38"/>
-      <c r="C69" s="23"/>
-      <c r="D69" s="39"/>
-      <c r="E69" s="42"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="B70" s="86"/>
-      <c r="C70" s="86"/>
-      <c r="D70" s="104">
+      <c r="B61" s="38"/>
+      <c r="C61" s="23"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="42"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62" s="86"/>
+      <c r="C62" s="86"/>
+      <c r="D62" s="248">
         <v>69000</v>
       </c>
-      <c r="E70" s="129"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="B71" s="86"/>
-      <c r="C71" s="86"/>
-      <c r="D71" s="104">
-        <f>110434.89+15074+30455</f>
-        <v>155963.89000000001</v>
-      </c>
-      <c r="E71" s="129"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="40" t="s">
+      <c r="E62" s="128"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="B63" s="86"/>
+      <c r="C63" s="86"/>
+      <c r="D63" s="248">
+        <f>102445.07+3388</f>
+        <v>105833.07</v>
+      </c>
+      <c r="E63" s="128"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B72" s="40"/>
-      <c r="C72" s="40"/>
-      <c r="D72" s="41"/>
-      <c r="E72" s="42">
-        <f>SUM(D70:D71)</f>
-        <v>224963.89</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="31"/>
-      <c r="B73" s="31"/>
-      <c r="C73" s="31"/>
+      <c r="B64" s="40"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="42">
+        <f>SUM(D62:D63)</f>
+        <v>174833.07</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="31"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="43"/>
+      <c r="E65" s="44"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" s="45"/>
+      <c r="C66" s="45"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="47"/>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="48"/>
+      <c r="D67" s="49"/>
+      <c r="E67" s="50"/>
+      <c r="F67" s="51"/>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="B68" s="53"/>
+      <c r="C68" s="54"/>
+      <c r="D68" s="55"/>
+      <c r="E68" s="56">
+        <f>(SUM(E21:E66))</f>
+        <v>6217319.3000000007</v>
+      </c>
+      <c r="F68" s="57"/>
+      <c r="G68" s="51"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D70" s="49"/>
+      <c r="E70" s="49"/>
+      <c r="H70" s="58"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B71" s="13"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="59"/>
+      <c r="E71" s="60"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="182"/>
+      <c r="B72" s="183"/>
+      <c r="C72" s="31"/>
+      <c r="D72" s="142"/>
+      <c r="E72" s="143"/>
+    </row>
+    <row r="73" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D73" s="43"/>
-      <c r="E73" s="44"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" s="45"/>
-      <c r="C74" s="45"/>
-      <c r="D74" s="46"/>
-      <c r="E74" s="47"/>
-    </row>
-    <row r="75" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="48"/>
-      <c r="D75" s="49"/>
-      <c r="E75" s="50"/>
-      <c r="F75" s="51"/>
-    </row>
-    <row r="76" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="B76" s="53"/>
-      <c r="C76" s="54"/>
-      <c r="D76" s="55"/>
-      <c r="E76" s="56">
-        <f>(SUM(E21:E74))</f>
-        <v>9918978.9000000004</v>
-      </c>
-      <c r="F76" s="57"/>
-      <c r="G76" s="51"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D77" s="49"/>
-      <c r="E77" s="49"/>
-    </row>
-    <row r="78" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E73" s="43"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="26"/>
+      <c r="B74" s="62"/>
+      <c r="C74" s="31"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="61"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="B75" s="64"/>
+      <c r="C75" s="64"/>
+      <c r="D75" s="102"/>
+      <c r="E75" s="129">
+        <f>SUM(D72:D74)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D76" s="49"/>
+      <c r="E76" s="49"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B77" s="45"/>
+      <c r="C77" s="45"/>
+      <c r="D77" s="46"/>
+      <c r="E77" s="132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D78" s="49"/>
       <c r="E78" s="49"/>
-      <c r="H78" s="58"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B79" s="13"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="59"/>
-      <c r="E79" s="60"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="199"/>
-      <c r="B80" s="200"/>
-      <c r="C80" s="31"/>
-      <c r="D80" s="144"/>
-      <c r="E80" s="145"/>
-    </row>
-    <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D81" s="43"/>
-      <c r="E81" s="43"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="26"/>
-      <c r="B82" s="62"/>
-      <c r="C82" s="31"/>
-      <c r="D82" s="36"/>
-      <c r="E82" s="61"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="64"/>
-      <c r="C83" s="64"/>
-      <c r="D83" s="102"/>
-      <c r="E83" s="130">
-        <f>SUM(D80:D82)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79" s="53"/>
+      <c r="C79" s="54"/>
+      <c r="D79" s="55"/>
+      <c r="E79" s="56">
+        <f>E75+E77</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="B81" s="66">
+        <f>E68</f>
+        <v>6217319.3000000007</v>
+      </c>
+      <c r="D81" s="49"/>
+      <c r="E81" s="49"/>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="65" t="s">
+        <v>21</v>
+      </c>
+      <c r="B82" s="66">
+        <f>E68-E66</f>
+        <v>6217319.3000000007</v>
+      </c>
+      <c r="D82" s="49"/>
+      <c r="E82" s="49"/>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="66">
+        <f>E79-E77</f>
+        <v>0</v>
+      </c>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="B84" s="66">
+        <f>E79</f>
+        <v>0</v>
+      </c>
       <c r="D84" s="49"/>
       <c r="E84" s="49"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="B85" s="45"/>
-      <c r="C85" s="45"/>
-      <c r="D85" s="46"/>
-      <c r="E85" s="133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D85" s="49"/>
+      <c r="E85" s="49"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D86" s="49"/>
       <c r="E86" s="49"/>
     </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B87" s="53"/>
-      <c r="C87" s="54"/>
-      <c r="D87" s="55"/>
-      <c r="E87" s="56">
-        <f>E83+E85</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="134" t="s">
+        <v>211</v>
+      </c>
+      <c r="B87" s="70">
+        <v>0</v>
+      </c>
+      <c r="D87" s="49"/>
+      <c r="E87" s="49"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="B88" s="71">
+        <v>6500000</v>
+      </c>
       <c r="D88" s="49"/>
       <c r="E88" s="49"/>
     </row>
-    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="65" t="s">
-        <v>20</v>
-      </c>
-      <c r="B89" s="66">
-        <f>E76</f>
-        <v>9918978.9000000004</v>
-      </c>
+    <row r="89" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="28"/>
+      <c r="B89" s="118"/>
       <c r="D89" s="49"/>
       <c r="E89" s="49"/>
     </row>
-    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="65" t="s">
-        <v>21</v>
-      </c>
-      <c r="B90" s="66">
-        <f>E76-E74</f>
-        <v>9918978.9000000004</v>
+    <row r="90" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="73" t="s">
+        <v>203</v>
+      </c>
+      <c r="B90" s="74">
+        <f>B88</f>
+        <v>6500000</v>
       </c>
       <c r="D90" s="49"/>
       <c r="E90" s="49"/>
     </row>
-    <row r="91" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="B91" s="66">
-        <f>E87-E85</f>
-        <v>0</v>
-      </c>
+    <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="162"/>
+      <c r="B91" s="163"/>
       <c r="D91" s="49"/>
       <c r="E91" s="49"/>
     </row>
-    <row r="92" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="65" t="s">
-        <v>23</v>
-      </c>
-      <c r="B92" s="66">
-        <f>E87</f>
-        <v>0</v>
-      </c>
+    <row r="92" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="162"/>
+      <c r="B92" s="163"/>
       <c r="D92" s="49"/>
       <c r="E92" s="49"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="134" t="s">
+        <v>164</v>
+      </c>
+      <c r="B93" s="70">
+        <v>231400</v>
+      </c>
       <c r="D93" s="49"/>
       <c r="E93" s="49"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B94" s="71">
+        <v>0</v>
+      </c>
       <c r="D94" s="49"/>
       <c r="E94" s="49"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="136" t="s">
-        <v>182</v>
-      </c>
-      <c r="B95" s="70">
-        <v>0</v>
-      </c>
+    <row r="95" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="B95" s="118"/>
       <c r="D95" s="49"/>
       <c r="E95" s="49"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="B96" s="71">
-        <v>2000000</v>
+    <row r="96" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="73" t="s">
+        <v>203</v>
+      </c>
+      <c r="B96" s="74">
+        <f>SUM(B93:B95)</f>
+        <v>231400</v>
       </c>
       <c r="D96" s="49"/>
       <c r="E96" s="49"/>
     </row>
-    <row r="97" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="28"/>
-      <c r="B97" s="119"/>
+    <row r="97" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="162"/>
+      <c r="B97" s="163"/>
       <c r="D97" s="49"/>
       <c r="E97" s="49"/>
     </row>
-    <row r="98" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="73" t="s">
-        <v>181</v>
-      </c>
-      <c r="B98" s="74">
-        <v>2026301.37</v>
+    <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="134" t="s">
+        <v>167</v>
+      </c>
+      <c r="B98" s="70">
+        <v>64328</v>
       </c>
       <c r="D98" s="49"/>
       <c r="E98" s="49"/>
     </row>
-    <row r="99" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="165"/>
-      <c r="B99" s="166"/>
+    <row r="99" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B99" s="71">
+        <v>0</v>
+      </c>
       <c r="D99" s="49"/>
       <c r="E99" s="49"/>
     </row>
-    <row r="100" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="165"/>
-      <c r="B100" s="166"/>
+    <row r="100" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="B100" s="118">
+        <v>-5910</v>
+      </c>
       <c r="D100" s="49"/>
       <c r="E100" s="49"/>
     </row>
-    <row r="101" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="136" t="s">
-        <v>188</v>
-      </c>
-      <c r="B101" s="70">
-        <v>231400</v>
+    <row r="101" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="73" t="s">
+        <v>203</v>
+      </c>
+      <c r="B101" s="74">
+        <f>SUM(B98:B100)</f>
+        <v>58418</v>
       </c>
       <c r="D101" s="49"/>
       <c r="E101" s="49"/>
     </row>
-    <row r="102" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="B102" s="71">
-        <v>0</v>
-      </c>
-      <c r="D102" s="49"/>
-      <c r="E102" s="49"/>
-    </row>
-    <row r="103" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="B103" s="119"/>
-      <c r="D103" s="49"/>
-      <c r="E103" s="49"/>
-    </row>
-    <row r="104" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="73" t="s">
-        <v>181</v>
-      </c>
-      <c r="B104" s="74">
-        <f>SUM(B101:B103)</f>
-        <v>231400</v>
+    <row r="102" spans="1:6" s="69" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102"/>
+      <c r="B102" s="67"/>
+      <c r="C102" s="68"/>
+      <c r="D102" s="130"/>
+      <c r="E102" s="130"/>
+    </row>
+    <row r="103" spans="1:6" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="134" t="s">
+        <v>202</v>
+      </c>
+      <c r="B103" s="70">
+        <v>3986543.73</v>
+      </c>
+      <c r="C103" s="68"/>
+      <c r="D103" s="131"/>
+      <c r="E103" s="131"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B104" s="166">
+        <f>-B82-B83</f>
+        <v>-6217319.3000000007</v>
       </c>
       <c r="D104" s="49"/>
       <c r="E104" s="49"/>
     </row>
-    <row r="105" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="165"/>
-      <c r="B105" s="166"/>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B105" s="71">
+        <f>B118</f>
+        <v>160000</v>
+      </c>
       <c r="D105" s="49"/>
       <c r="E105" s="49"/>
-    </row>
-    <row r="106" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="136" t="s">
-        <v>191</v>
-      </c>
-      <c r="B106" s="70">
-        <v>64328</v>
+      <c r="F105" s="67"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B106" s="72">
+        <f>PRORRATEO!G61</f>
+        <v>6991775.4199999999</v>
       </c>
       <c r="D106" s="49"/>
       <c r="E106" s="49"/>
-    </row>
-    <row r="107" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F106" s="67"/>
+    </row>
+    <row r="107" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="B107" s="71">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="B107" s="118">
+        <v>-6500000</v>
       </c>
       <c r="D107" s="49"/>
       <c r="E107" s="49"/>
-    </row>
-    <row r="108" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F107" s="67"/>
+    </row>
+    <row r="108" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="B108" s="119"/>
+        <v>209</v>
+      </c>
+      <c r="B108" s="165">
+        <v>2026301.37</v>
+      </c>
       <c r="D108" s="49"/>
       <c r="E108" s="49"/>
-    </row>
-    <row r="109" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="73" t="s">
-        <v>181</v>
-      </c>
-      <c r="B109" s="74">
-        <f>SUM(B106:B108)</f>
-        <v>64328</v>
+      <c r="F108" s="67"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B109" s="118">
+        <v>-4703</v>
       </c>
       <c r="D109" s="49"/>
       <c r="E109" s="49"/>
-    </row>
-    <row r="110" spans="1:5" s="69" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A110"/>
-      <c r="B110" s="67"/>
-      <c r="C110" s="68"/>
-      <c r="D110" s="131"/>
-      <c r="E110" s="131"/>
-    </row>
-    <row r="111" spans="1:5" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="136" t="s">
-        <v>187</v>
-      </c>
-      <c r="B111" s="70">
-        <v>4238170</v>
-      </c>
-      <c r="C111" s="68"/>
-      <c r="D111" s="132"/>
-      <c r="E111" s="132"/>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="B112" s="169">
-        <f>-B90-B91</f>
-        <v>-9918978.9000000004</v>
-      </c>
-      <c r="D112" s="49"/>
-      <c r="E112" s="49"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B113" s="71">
-        <f>B124</f>
-        <v>156782</v>
-      </c>
-      <c r="D113" s="49"/>
-      <c r="E113" s="49"/>
-      <c r="F113" s="67"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B114" s="72">
-        <f>PRORRATEO!G61</f>
-        <v>6601052</v>
-      </c>
-      <c r="D114" s="49"/>
-      <c r="E114" s="49"/>
-      <c r="F114" s="67"/>
-    </row>
-    <row r="115" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A115" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="B115" s="168">
-        <v>1576753.42</v>
-      </c>
-      <c r="D115" s="49"/>
-      <c r="E115" s="49"/>
-      <c r="F115" s="67"/>
-    </row>
-    <row r="116" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="28"/>
-      <c r="B116" s="119"/>
-      <c r="D116" s="167"/>
-      <c r="E116" s="49"/>
-      <c r="F116" s="67"/>
-    </row>
-    <row r="117" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="73" t="s">
+      <c r="F109" s="67"/>
+    </row>
+    <row r="110" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="B110" s="118">
+        <v>-156782</v>
+      </c>
+      <c r="D110" s="164"/>
+      <c r="E110" s="49"/>
+      <c r="F110" s="67"/>
+    </row>
+    <row r="111" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="B117" s="74">
-        <f>SUM(B111:C116)</f>
-        <v>2653778.5199999996</v>
-      </c>
-      <c r="D117" s="67"/>
-      <c r="E117" s="51"/>
-      <c r="F117" s="51"/>
-    </row>
-    <row r="118" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="119" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="170" t="s">
-        <v>193</v>
-      </c>
-      <c r="B119" s="171">
-        <f>B117+B104</f>
-        <v>2885178.5199999996</v>
-      </c>
-      <c r="E119" s="51"/>
-    </row>
-    <row r="120" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="198" t="s">
+      <c r="B111" s="74">
+        <f>SUM(B103:C110)</f>
+        <v>285816.21999999974</v>
+      </c>
+      <c r="D111" s="67"/>
+      <c r="E111" s="51"/>
+      <c r="F111" s="51"/>
+    </row>
+    <row r="112" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="113" spans="1:13" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="167" t="s">
+        <v>168</v>
+      </c>
+      <c r="B113" s="168">
+        <f>B111+B96</f>
+        <v>517216.21999999974</v>
+      </c>
+      <c r="D113" s="51"/>
+      <c r="E113" s="51"/>
+    </row>
+    <row r="114" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="179" t="s">
         <v>25</v>
       </c>
-      <c r="B121" s="198"/>
-      <c r="C121" s="198"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A122" s="198"/>
-      <c r="B122" s="198"/>
-      <c r="C122" s="198"/>
-    </row>
-    <row r="123" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="75" t="s">
-        <v>184</v>
-      </c>
-      <c r="B123" s="101">
-        <v>156782</v>
-      </c>
-      <c r="C123" s="76"/>
-      <c r="D123" s="57"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B124" s="78">
-        <f>SUM(B123:B123)</f>
-        <v>156782</v>
-      </c>
-      <c r="C124" s="79"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M125" s="80"/>
+      <c r="B115" s="179"/>
+      <c r="C115" s="179"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="179"/>
+      <c r="B116" s="179"/>
+      <c r="C116" s="179"/>
+    </row>
+    <row r="117" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="75" t="s">
+        <v>208</v>
+      </c>
+      <c r="B117" s="101">
+        <v>160000</v>
+      </c>
+      <c r="C117" s="76"/>
+      <c r="D117" s="57"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B118" s="78">
+        <f>SUM(B117:B117)</f>
+        <v>160000</v>
+      </c>
+      <c r="C118" s="79"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M119" s="80"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A121:C122"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A65:B65"/>
+  <mergeCells count="16">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A58:B58"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A45:B45"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A40:B40"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A115:C116"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A54:B54"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3531,136 +3487,130 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:R69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="13" width="14.44140625" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" customWidth="1"/>
-    <col min="16" max="16" width="14.33203125" customWidth="1"/>
-    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="13" width="14.42578125" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" customWidth="1"/>
+    <col min="17" max="17" width="8.5703125" customWidth="1"/>
     <col min="18" max="18" width="19" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="88"/>
-      <c r="B1" s="152"/>
+      <c r="B1" s="150"/>
       <c r="C1" s="89"/>
       <c r="D1" s="89"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="227" t="str">
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="192" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
-      <c r="M1" s="227"/>
-      <c r="N1" s="227"/>
-      <c r="O1" s="227"/>
-      <c r="P1" s="228"/>
-    </row>
-    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="192"/>
+      <c r="L1" s="192"/>
+      <c r="M1" s="192"/>
+      <c r="N1" s="192"/>
+      <c r="O1" s="192"/>
+      <c r="P1" s="193"/>
+    </row>
+    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="173">
-        <f>R3</f>
-        <v>6319499.4800000004</v>
+        <v>169</v>
+      </c>
+      <c r="B2" s="151"/>
+      <c r="C2" s="170">
+        <f>6219841.65-C5</f>
+        <v>4906689.78</v>
       </c>
       <c r="D2" s="90"/>
       <c r="E2" s="90"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="235"/>
+      <c r="F2" s="202"/>
+      <c r="G2" s="202"/>
       <c r="H2" s="90"/>
       <c r="I2" s="90"/>
-      <c r="J2" s="229"/>
-      <c r="K2" s="229"/>
-      <c r="L2" s="229"/>
-      <c r="M2" s="229"/>
-      <c r="N2" s="229"/>
-      <c r="O2" s="229"/>
-      <c r="P2" s="230"/>
+      <c r="J2" s="194"/>
+      <c r="K2" s="194"/>
+      <c r="L2" s="194"/>
+      <c r="M2" s="194"/>
+      <c r="N2" s="194"/>
+      <c r="O2" s="194"/>
+      <c r="P2" s="195"/>
       <c r="Q2" s="81"/>
-      <c r="R2">
-        <v>7500000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="153"/>
-      <c r="C3" s="173">
+      <c r="B3" s="151"/>
+      <c r="C3" s="170">
         <v>0</v>
       </c>
       <c r="D3" s="90"/>
       <c r="E3" s="90"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
       <c r="H3" s="90"/>
       <c r="I3" s="90"/>
-      <c r="J3" s="229"/>
-      <c r="K3" s="229"/>
-      <c r="L3" s="229"/>
-      <c r="M3" s="229"/>
-      <c r="N3" s="229"/>
-      <c r="O3" s="229"/>
-      <c r="P3" s="230"/>
+      <c r="J3" s="194"/>
+      <c r="K3" s="194"/>
+      <c r="L3" s="194"/>
+      <c r="M3" s="194"/>
+      <c r="N3" s="194"/>
+      <c r="O3" s="194"/>
+      <c r="P3" s="195"/>
       <c r="Q3" s="81"/>
-      <c r="R3" s="51">
-        <f>R2-C5-C4</f>
-        <v>6319499.4800000004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R3" s="51"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B4" s="153"/>
-      <c r="C4" s="173">
+        <v>175</v>
+      </c>
+      <c r="B4" s="151"/>
+      <c r="C4" s="170">
         <v>182823.01</v>
       </c>
       <c r="D4" s="90"/>
       <c r="E4" s="90"/>
-      <c r="F4" s="158"/>
-      <c r="G4" s="158"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
       <c r="H4" s="90"/>
       <c r="I4" s="90"/>
-      <c r="J4" s="229"/>
-      <c r="K4" s="229"/>
-      <c r="L4" s="229"/>
-      <c r="M4" s="229"/>
-      <c r="N4" s="229"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="230"/>
+      <c r="J4" s="194"/>
+      <c r="K4" s="194"/>
+      <c r="L4" s="194"/>
+      <c r="M4" s="194"/>
+      <c r="N4" s="194"/>
+      <c r="O4" s="194"/>
+      <c r="P4" s="195"/>
       <c r="Q4" s="81"/>
       <c r="R4" s="51"/>
     </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="172" t="s">
-        <v>196</v>
-      </c>
-      <c r="B5" s="154"/>
-      <c r="C5" s="174">
-        <v>997677.51</v>
+    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="169" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="152"/>
+      <c r="C5" s="171">
+        <v>1313151.8700000001</v>
       </c>
       <c r="D5" s="91"/>
       <c r="E5" s="91"/>
@@ -3668,112 +3618,112 @@
       <c r="G5" s="92"/>
       <c r="H5" s="91"/>
       <c r="I5" s="91"/>
-      <c r="J5" s="231"/>
-      <c r="K5" s="231"/>
-      <c r="L5" s="231"/>
-      <c r="M5" s="231"/>
-      <c r="N5" s="231"/>
-      <c r="O5" s="231"/>
-      <c r="P5" s="232"/>
+      <c r="J5" s="196"/>
+      <c r="K5" s="196"/>
+      <c r="L5" s="196"/>
+      <c r="M5" s="196"/>
+      <c r="N5" s="196"/>
+      <c r="O5" s="196"/>
+      <c r="P5" s="197"/>
       <c r="Q5" s="81"/>
     </row>
-    <row r="6" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="202" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="203"/>
-      <c r="C6" s="204"/>
-      <c r="D6" s="204"/>
-      <c r="E6" s="204"/>
-      <c r="F6" s="204"/>
-      <c r="G6" s="204"/>
-      <c r="H6" s="204"/>
-      <c r="I6" s="204"/>
-      <c r="J6" s="204"/>
-      <c r="K6" s="204"/>
-      <c r="L6" s="204"/>
-      <c r="M6" s="204"/>
-      <c r="N6" s="204"/>
-      <c r="O6" s="204"/>
-      <c r="P6" s="205"/>
+    <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="204" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="205"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
+      <c r="J6" s="206"/>
+      <c r="K6" s="206"/>
+      <c r="L6" s="206"/>
+      <c r="M6" s="206"/>
+      <c r="N6" s="206"/>
+      <c r="O6" s="206"/>
+      <c r="P6" s="207"/>
       <c r="Q6" s="81"/>
     </row>
-    <row r="7" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="206"/>
-      <c r="B7" s="207"/>
-      <c r="C7" s="207"/>
-      <c r="D7" s="207"/>
-      <c r="E7" s="207"/>
-      <c r="F7" s="207"/>
-      <c r="G7" s="207"/>
-      <c r="H7" s="207"/>
-      <c r="I7" s="207"/>
-      <c r="J7" s="207"/>
-      <c r="K7" s="207"/>
-      <c r="L7" s="207"/>
-      <c r="M7" s="207"/>
-      <c r="N7" s="207"/>
-      <c r="O7" s="207"/>
-      <c r="P7" s="208"/>
+    <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="208"/>
+      <c r="B7" s="209"/>
+      <c r="C7" s="209"/>
+      <c r="D7" s="209"/>
+      <c r="E7" s="209"/>
+      <c r="F7" s="209"/>
+      <c r="G7" s="209"/>
+      <c r="H7" s="209"/>
+      <c r="I7" s="209"/>
+      <c r="J7" s="209"/>
+      <c r="K7" s="209"/>
+      <c r="L7" s="209"/>
+      <c r="M7" s="209"/>
+      <c r="N7" s="209"/>
+      <c r="O7" s="209"/>
+      <c r="P7" s="210"/>
       <c r="Q7" s="81"/>
     </row>
-    <row r="8" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="206"/>
-      <c r="B8" s="207"/>
-      <c r="C8" s="207"/>
-      <c r="D8" s="207"/>
-      <c r="E8" s="207"/>
-      <c r="F8" s="207"/>
-      <c r="G8" s="207"/>
-      <c r="H8" s="207"/>
-      <c r="I8" s="207"/>
-      <c r="J8" s="207"/>
-      <c r="K8" s="207"/>
-      <c r="L8" s="207"/>
-      <c r="M8" s="207"/>
-      <c r="N8" s="207"/>
-      <c r="O8" s="207"/>
-      <c r="P8" s="208"/>
+    <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="208"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
+      <c r="E8" s="209"/>
+      <c r="F8" s="209"/>
+      <c r="G8" s="209"/>
+      <c r="H8" s="209"/>
+      <c r="I8" s="209"/>
+      <c r="J8" s="209"/>
+      <c r="K8" s="209"/>
+      <c r="L8" s="209"/>
+      <c r="M8" s="209"/>
+      <c r="N8" s="209"/>
+      <c r="O8" s="209"/>
+      <c r="P8" s="210"/>
       <c r="Q8" s="81"/>
     </row>
-    <row r="9" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="206"/>
-      <c r="B9" s="207"/>
-      <c r="C9" s="207"/>
-      <c r="D9" s="207"/>
-      <c r="E9" s="207"/>
-      <c r="F9" s="207"/>
-      <c r="G9" s="207"/>
-      <c r="H9" s="207"/>
-      <c r="I9" s="207"/>
-      <c r="J9" s="207"/>
-      <c r="K9" s="207"/>
-      <c r="L9" s="207"/>
-      <c r="M9" s="207"/>
-      <c r="N9" s="207"/>
-      <c r="O9" s="207"/>
-      <c r="P9" s="208"/>
+    <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="208"/>
+      <c r="B9" s="209"/>
+      <c r="C9" s="209"/>
+      <c r="D9" s="209"/>
+      <c r="E9" s="209"/>
+      <c r="F9" s="209"/>
+      <c r="G9" s="209"/>
+      <c r="H9" s="209"/>
+      <c r="I9" s="209"/>
+      <c r="J9" s="209"/>
+      <c r="K9" s="209"/>
+      <c r="L9" s="209"/>
+      <c r="M9" s="209"/>
+      <c r="N9" s="209"/>
+      <c r="O9" s="209"/>
+      <c r="P9" s="210"/>
       <c r="Q9" s="81"/>
     </row>
-    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="209"/>
-      <c r="B10" s="210"/>
-      <c r="C10" s="210"/>
-      <c r="D10" s="210"/>
-      <c r="E10" s="210"/>
-      <c r="F10" s="210"/>
-      <c r="G10" s="210"/>
-      <c r="H10" s="210"/>
-      <c r="I10" s="210"/>
-      <c r="J10" s="210"/>
-      <c r="K10" s="210"/>
-      <c r="L10" s="210"/>
-      <c r="M10" s="210"/>
-      <c r="N10" s="210"/>
-      <c r="O10" s="210"/>
-      <c r="P10" s="211"/>
-    </row>
-    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="211"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="212"/>
+      <c r="D10" s="212"/>
+      <c r="E10" s="212"/>
+      <c r="F10" s="212"/>
+      <c r="G10" s="212"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="212"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="212"/>
+      <c r="L10" s="212"/>
+      <c r="M10" s="212"/>
+      <c r="N10" s="212"/>
+      <c r="O10" s="212"/>
+      <c r="P10" s="213"/>
+    </row>
+    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="220" t="s">
         <v>47</v>
       </c>
@@ -3793,343 +3743,345 @@
       <c r="O11" s="221"/>
       <c r="P11" s="222"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="212" t="s">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="214" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="225" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="214" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="216" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="214" t="s">
+      <c r="D12" s="216" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="214" t="s">
+      <c r="E12" s="216" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="216" t="s">
+      <c r="F12" s="198" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="214" t="s">
+      <c r="G12" s="216" t="s">
         <v>33</v>
       </c>
       <c r="H12" s="218" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="216" t="s">
+      <c r="I12" s="198" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="216" t="s">
+      <c r="J12" s="198" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="216" t="s">
+      <c r="K12" s="198" t="s">
         <v>26</v>
       </c>
       <c r="L12" s="225" t="s">
-        <v>200</v>
-      </c>
-      <c r="M12" s="216" t="s">
-        <v>197</v>
+        <v>174</v>
+      </c>
+      <c r="M12" s="198" t="s">
+        <v>171</v>
       </c>
       <c r="N12" s="223" t="s">
-        <v>52</v>
-      </c>
-      <c r="O12" s="116" t="s">
+        <v>51</v>
+      </c>
+      <c r="O12" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="233" t="s">
+      <c r="P12" s="200" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="213"/>
+    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="215"/>
       <c r="B13" s="226"/>
-      <c r="C13" s="215"/>
-      <c r="D13" s="215"/>
-      <c r="E13" s="215"/>
-      <c r="F13" s="217"/>
-      <c r="G13" s="215"/>
+      <c r="C13" s="217"/>
+      <c r="D13" s="217"/>
+      <c r="E13" s="217"/>
+      <c r="F13" s="199"/>
+      <c r="G13" s="217"/>
       <c r="H13" s="219"/>
-      <c r="I13" s="217"/>
-      <c r="J13" s="217"/>
-      <c r="K13" s="217"/>
+      <c r="I13" s="199"/>
+      <c r="J13" s="199"/>
+      <c r="K13" s="199"/>
       <c r="L13" s="226"/>
-      <c r="M13" s="217"/>
+      <c r="M13" s="199"/>
       <c r="N13" s="224"/>
-      <c r="O13" s="117" t="str">
+      <c r="O13" s="116" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="P13" s="234"/>
-    </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="106">
+      <c r="P13" s="201"/>
+    </row>
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="105">
         <v>1</v>
       </c>
-      <c r="B14" s="155" t="s">
-        <v>75</v>
+      <c r="B14" s="153" t="s">
+        <v>73</v>
       </c>
       <c r="C14" s="94" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D14" s="94"/>
       <c r="E14" s="96">
         <v>5.22</v>
       </c>
       <c r="F14" s="82">
-        <v>361399</v>
-      </c>
-      <c r="G14" s="82">
-        <f>406632-G43-G40</f>
-        <v>364399</v>
+        <v>388500.01</v>
+      </c>
+      <c r="G14" s="234">
+        <f>400155.01</f>
+        <v>400155.01</v>
       </c>
       <c r="H14" s="97">
         <f t="shared" ref="H14:H59" si="0">F14-G14</f>
-        <v>-3000</v>
+        <v>-11655</v>
       </c>
       <c r="I14" s="97">
         <f>IF(H14&gt;0,H14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="105">
+      <c r="J14" s="104">
         <f>C$2*E14/100</f>
-        <v>329877.87285599997</v>
-      </c>
-      <c r="K14" s="105">
+        <v>256129.20651600001</v>
+      </c>
+      <c r="K14" s="104">
         <f t="shared" ref="K14:K45" si="1">F$2*E14/100</f>
         <v>0</v>
       </c>
-      <c r="L14" s="105">
+      <c r="L14" s="104">
         <f>C$4*E14/100</f>
         <v>9543.3611220000003</v>
       </c>
-      <c r="M14" s="105">
+      <c r="M14" s="104">
         <f>C$5*E14/100</f>
-        <v>52078.766021999996</v>
-      </c>
-      <c r="N14" s="105"/>
+        <v>68546.527614000006</v>
+      </c>
+      <c r="N14" s="104"/>
       <c r="O14" s="98">
         <f>ROUND(SUM(H14:N14),0) + Q14</f>
-        <v>388500.01</v>
-      </c>
-      <c r="P14" s="114">
+        <v>322564.01</v>
+      </c>
+      <c r="P14" s="113">
         <f t="shared" ref="P14:P34" si="2">ROUND(O14*3%,0) + O14</f>
-        <v>400155.01</v>
+        <v>332241.01</v>
       </c>
       <c r="Q14" s="51">
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="179">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="105">
         <v>2</v>
       </c>
-      <c r="B15" s="180" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="181" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" s="181" t="s">
-        <v>178</v>
+      <c r="B15" s="153" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="94" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" s="94" t="s">
+        <v>159</v>
       </c>
       <c r="E15" s="96">
         <v>3.4</v>
       </c>
       <c r="F15" s="82">
-        <v>235394</v>
-      </c>
-      <c r="G15" s="82">
-        <v>240000</v>
+        <v>257906.02</v>
+      </c>
+      <c r="G15" s="234">
+        <f>F15+204243.28-F41</f>
+        <v>442321.02</v>
       </c>
       <c r="H15" s="97">
         <f t="shared" si="0"/>
-        <v>-4606</v>
+        <v>-184415.00000000003</v>
       </c>
       <c r="I15" s="97">
         <f t="shared" ref="I15:I59" si="3">IF(H15&gt;0,H15*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="105">
+      <c r="J15" s="104">
         <f t="shared" ref="J15:J59" si="4">C$2*E15/100</f>
-        <v>214862.98232000001</v>
-      </c>
-      <c r="K15" s="105">
+        <v>166827.45251999999</v>
+      </c>
+      <c r="K15" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L15" s="105">
+      <c r="L15" s="104">
         <f t="shared" ref="L15:L59" si="5">C$4*E15/100</f>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M15" s="105">
+      <c r="M15" s="104">
         <f t="shared" ref="M15:M59" si="6">C$5*E15/100</f>
-        <v>33921.035340000002</v>
-      </c>
-      <c r="N15" s="105"/>
+        <v>44647.16358</v>
+      </c>
+      <c r="N15" s="104"/>
       <c r="O15" s="98">
         <f t="shared" ref="O15:O59" si="7">ROUND(SUM(H15:N15),0) + Q15</f>
-        <v>250394.02</v>
-      </c>
-      <c r="P15" s="114">
+        <v>33276.019999999997</v>
+      </c>
+      <c r="P15" s="113">
         <f t="shared" si="2"/>
-        <v>257906.02</v>
+        <v>34274.019999999997</v>
       </c>
       <c r="Q15" s="51">
         <f>Q14+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="106">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="105">
         <v>3</v>
       </c>
-      <c r="B16" s="155" t="s">
-        <v>79</v>
+      <c r="B16" s="153" t="s">
+        <v>77</v>
       </c>
       <c r="C16" s="94" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D16" s="94" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="E16" s="96">
         <v>2.54</v>
       </c>
       <c r="F16" s="82">
-        <v>178804</v>
-      </c>
-      <c r="G16" s="82">
-        <v>179000</v>
+        <v>190304.03</v>
+      </c>
+      <c r="G16" s="234">
+        <v>192000</v>
       </c>
       <c r="H16" s="97">
         <f t="shared" si="0"/>
-        <v>-196</v>
+        <v>-1695.9700000000012</v>
       </c>
       <c r="I16" s="97">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J16" s="105">
+      <c r="J16" s="104">
         <f t="shared" si="4"/>
-        <v>160515.286792</v>
-      </c>
-      <c r="K16" s="105">
+        <v>124629.92041200001</v>
+      </c>
+      <c r="K16" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L16" s="105">
+      <c r="L16" s="104">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M16" s="105">
+      <c r="M16" s="104">
         <f t="shared" si="6"/>
-        <v>25341.008754000002</v>
-      </c>
-      <c r="N16" s="105"/>
+        <v>33354.057498000002</v>
+      </c>
+      <c r="N16" s="104"/>
       <c r="O16" s="98">
         <f t="shared" si="7"/>
-        <v>190304.03</v>
-      </c>
-      <c r="P16" s="114">
+        <v>160932.03</v>
+      </c>
+      <c r="P16" s="113">
         <f t="shared" si="2"/>
-        <v>196013.03</v>
+        <v>165760.03</v>
       </c>
       <c r="Q16" s="51">
         <f t="shared" ref="Q16:Q31" si="8">Q15+0.01</f>
         <v>0.03</v>
       </c>
       <c r="R16" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="175">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="105">
         <v>4</v>
       </c>
-      <c r="B17" s="176" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="178" t="s">
-        <v>124</v>
+      <c r="B17" s="153" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="94" t="s">
+        <v>122</v>
       </c>
       <c r="D17" s="99" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="E17" s="96">
         <v>5.19</v>
       </c>
       <c r="F17" s="82">
-        <v>358430</v>
-      </c>
-      <c r="G17" s="82">
-        <f>416387-G55</f>
-        <v>363077</v>
+        <v>384603.04</v>
+      </c>
+      <c r="G17" s="234">
+        <f>449413-G55-G44</f>
+        <v>379957.27</v>
       </c>
       <c r="H17" s="97">
         <f t="shared" si="0"/>
-        <v>-4647</v>
+        <v>4645.7699999999604</v>
       </c>
       <c r="I17" s="97">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="105">
+        <v>139.3730999999988</v>
+      </c>
+      <c r="J17" s="104">
         <f t="shared" si="4"/>
-        <v>327982.02301200008</v>
-      </c>
-      <c r="K17" s="105">
+        <v>254657.19958200003</v>
+      </c>
+      <c r="K17" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L17" s="105">
+      <c r="L17" s="104">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M17" s="105">
+      <c r="M17" s="104">
         <f t="shared" si="6"/>
-        <v>51779.462769000005</v>
-      </c>
-      <c r="N17" s="105"/>
+        <v>68152.58205300002</v>
+      </c>
+      <c r="N17" s="104"/>
       <c r="O17" s="98">
         <f t="shared" si="7"/>
-        <v>384603.04</v>
-      </c>
-      <c r="P17" s="114">
+        <v>337083.04</v>
+      </c>
+      <c r="P17" s="113">
         <f t="shared" si="2"/>
-        <v>396141.04</v>
+        <v>347195.04</v>
       </c>
       <c r="Q17" s="51">
         <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
       <c r="R17" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="106">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="105">
         <v>5</v>
       </c>
-      <c r="B18" s="155" t="s">
-        <v>76</v>
+      <c r="B18" s="153" t="s">
+        <v>74</v>
       </c>
       <c r="C18" s="94" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D18" s="99" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="E18" s="96">
         <v>3.4</v>
       </c>
       <c r="F18" s="82">
-        <v>235394</v>
-      </c>
-      <c r="G18" s="82">
-        <v>235394</v>
+        <v>255000.05</v>
+      </c>
+      <c r="G18" s="234">
+        <f>F18</f>
+        <v>255000.05</v>
       </c>
       <c r="H18" s="97">
         <f t="shared" si="0"/>
@@ -4139,114 +4091,117 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J18" s="105">
+      <c r="J18" s="104">
         <f t="shared" si="4"/>
-        <v>214862.98232000001</v>
-      </c>
-      <c r="K18" s="105">
+        <v>166827.45251999999</v>
+      </c>
+      <c r="K18" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L18" s="105">
+      <c r="L18" s="104">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M18" s="105">
+      <c r="M18" s="104">
         <f t="shared" si="6"/>
-        <v>33921.035340000002</v>
-      </c>
-      <c r="N18" s="105"/>
+        <v>44647.16358</v>
+      </c>
+      <c r="N18" s="104"/>
       <c r="O18" s="98">
         <f t="shared" si="7"/>
-        <v>255000.05</v>
-      </c>
-      <c r="P18" s="114">
+        <v>217691.05</v>
+      </c>
+      <c r="P18" s="113">
         <f t="shared" si="2"/>
-        <v>262650.05</v>
+        <v>224222.05</v>
       </c>
       <c r="Q18" s="51">
         <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="106">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="105">
         <v>6</v>
       </c>
-      <c r="B19" s="155" t="s">
-        <v>81</v>
+      <c r="B19" s="153" t="s">
+        <v>79</v>
       </c>
       <c r="C19" s="94" t="s">
-        <v>122</v>
-      </c>
-      <c r="D19" s="94"/>
+        <v>120</v>
+      </c>
+      <c r="D19" s="94" t="s">
+        <v>205</v>
+      </c>
       <c r="E19" s="96">
         <v>2.54</v>
       </c>
       <c r="F19" s="82">
-        <v>343733</v>
-      </c>
-      <c r="G19" s="82">
-        <v>186951</v>
+        <v>351985.06</v>
+      </c>
+      <c r="G19" s="234">
+        <f>156782+190500.06+4703</f>
+        <v>351985.06</v>
       </c>
       <c r="H19" s="97">
         <f t="shared" si="0"/>
-        <v>156782</v>
+        <v>0</v>
       </c>
       <c r="I19" s="97">
         <f t="shared" si="3"/>
-        <v>4703.46</v>
-      </c>
-      <c r="J19" s="105">
+        <v>0</v>
+      </c>
+      <c r="J19" s="104">
         <f t="shared" si="4"/>
-        <v>160515.286792</v>
-      </c>
-      <c r="K19" s="105">
+        <v>124629.92041200001</v>
+      </c>
+      <c r="K19" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L19" s="105">
+      <c r="L19" s="104">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M19" s="105">
+      <c r="M19" s="104">
         <f t="shared" si="6"/>
-        <v>25341.008754000002</v>
-      </c>
-      <c r="N19" s="105"/>
+        <v>33354.057498000002</v>
+      </c>
+      <c r="N19" s="104"/>
       <c r="O19" s="98">
         <f t="shared" si="7"/>
-        <v>351985.06</v>
-      </c>
-      <c r="P19" s="114">
+        <v>162628.06</v>
+      </c>
+      <c r="P19" s="113">
         <f t="shared" si="2"/>
-        <v>362545.06</v>
+        <v>167507.06</v>
       </c>
       <c r="Q19" s="51">
         <f t="shared" si="8"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="106">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="105">
         <v>7</v>
       </c>
-      <c r="B20" s="155" t="s">
-        <v>82</v>
+      <c r="B20" s="153" t="s">
+        <v>80</v>
       </c>
       <c r="C20" s="94" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D20" s="94"/>
       <c r="E20" s="96">
         <v>5.19</v>
       </c>
       <c r="F20" s="82">
-        <v>359322</v>
-      </c>
-      <c r="G20" s="82">
+        <v>389250.07</v>
+      </c>
+      <c r="G20" s="234">
         <f>F20</f>
-        <v>359322</v>
+        <v>389250.07</v>
       </c>
       <c r="H20" s="97">
         <f t="shared" si="0"/>
@@ -4256,55 +4211,56 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J20" s="105">
+      <c r="J20" s="104">
         <f t="shared" si="4"/>
-        <v>327982.02301200008</v>
-      </c>
-      <c r="K20" s="105">
+        <v>254657.19958200003</v>
+      </c>
+      <c r="K20" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L20" s="105">
+      <c r="L20" s="104">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M20" s="105">
+      <c r="M20" s="104">
         <f t="shared" si="6"/>
-        <v>51779.462769000005</v>
-      </c>
-      <c r="N20" s="105"/>
+        <v>68152.58205300002</v>
+      </c>
+      <c r="N20" s="104"/>
       <c r="O20" s="98">
         <f t="shared" si="7"/>
-        <v>389250.07</v>
-      </c>
-      <c r="P20" s="114">
+        <v>332298.07</v>
+      </c>
+      <c r="P20" s="113">
         <f t="shared" si="2"/>
-        <v>400928.07</v>
+        <v>342267.07</v>
       </c>
       <c r="Q20" s="51">
         <f t="shared" si="8"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="106">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="105">
         <v>8</v>
       </c>
-      <c r="B21" s="155" t="s">
-        <v>83</v>
+      <c r="B21" s="153" t="s">
+        <v>81</v>
       </c>
       <c r="C21" s="94" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D21" s="99"/>
       <c r="E21" s="96">
         <v>3.4</v>
       </c>
       <c r="F21" s="82">
-        <v>235394</v>
-      </c>
-      <c r="G21" s="82">
-        <v>235394</v>
+        <v>255000.08</v>
+      </c>
+      <c r="G21" s="234">
+        <f>F21</f>
+        <v>255000.08</v>
       </c>
       <c r="H21" s="97">
         <f t="shared" si="0"/>
@@ -4314,57 +4270,58 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J21" s="105">
+      <c r="J21" s="104">
         <f t="shared" si="4"/>
-        <v>214862.98232000001</v>
-      </c>
-      <c r="K21" s="105">
+        <v>166827.45251999999</v>
+      </c>
+      <c r="K21" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L21" s="105">
+      <c r="L21" s="104">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M21" s="105">
+      <c r="M21" s="104">
         <f t="shared" si="6"/>
-        <v>33921.035340000002</v>
-      </c>
-      <c r="N21" s="105"/>
+        <v>44647.16358</v>
+      </c>
+      <c r="N21" s="104"/>
       <c r="O21" s="98">
         <f t="shared" si="7"/>
-        <v>255000.08</v>
-      </c>
-      <c r="P21" s="114">
+        <v>217691.08</v>
+      </c>
+      <c r="P21" s="113">
         <f t="shared" si="2"/>
-        <v>262650.07999999996</v>
+        <v>224222.07999999999</v>
       </c>
       <c r="Q21" s="51">
         <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="106">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="105">
         <v>9</v>
       </c>
-      <c r="B22" s="155" t="s">
-        <v>77</v>
+      <c r="B22" s="153" t="s">
+        <v>75</v>
       </c>
       <c r="C22" s="94" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D22" s="99" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="E22" s="96">
         <v>2.54</v>
       </c>
       <c r="F22" s="82">
-        <v>180600</v>
-      </c>
-      <c r="G22" s="82">
-        <v>180600</v>
+        <v>190500.09</v>
+      </c>
+      <c r="G22" s="234">
+        <f>F22</f>
+        <v>190500.09</v>
       </c>
       <c r="H22" s="97">
         <f t="shared" si="0"/>
@@ -4374,56 +4331,56 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J22" s="105">
+      <c r="J22" s="104">
         <f t="shared" si="4"/>
-        <v>160515.286792</v>
-      </c>
-      <c r="K22" s="105">
+        <v>124629.92041200001</v>
+      </c>
+      <c r="K22" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L22" s="105">
+      <c r="L22" s="104">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M22" s="105">
+      <c r="M22" s="104">
         <f t="shared" si="6"/>
-        <v>25341.008754000002</v>
-      </c>
-      <c r="N22" s="105"/>
+        <v>33354.057498000002</v>
+      </c>
+      <c r="N22" s="104"/>
       <c r="O22" s="98">
         <f t="shared" si="7"/>
-        <v>190500.09</v>
-      </c>
-      <c r="P22" s="114">
+        <v>162628.09</v>
+      </c>
+      <c r="P22" s="113">
         <f t="shared" si="2"/>
-        <v>196215.09</v>
+        <v>167507.09</v>
       </c>
       <c r="Q22" s="51">
         <f t="shared" si="8"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="106">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="105">
         <v>10</v>
       </c>
-      <c r="B23" s="155" t="s">
-        <v>84</v>
+      <c r="B23" s="153" t="s">
+        <v>82</v>
       </c>
       <c r="C23" s="94" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D23" s="99"/>
       <c r="E23" s="96">
         <v>5.19</v>
       </c>
       <c r="F23" s="82">
-        <v>359322</v>
-      </c>
-      <c r="G23" s="82">
-        <f>397400-G39</f>
-        <v>359322</v>
+        <v>389250.1</v>
+      </c>
+      <c r="G23" s="234">
+        <f>F23</f>
+        <v>389250.1</v>
       </c>
       <c r="H23" s="97">
         <f t="shared" si="0"/>
@@ -4433,57 +4390,58 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J23" s="105">
+      <c r="J23" s="104">
         <f t="shared" si="4"/>
-        <v>327982.02301200008</v>
-      </c>
-      <c r="K23" s="105">
+        <v>254657.19958200003</v>
+      </c>
+      <c r="K23" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L23" s="105">
+      <c r="L23" s="104">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M23" s="105">
+      <c r="M23" s="104">
         <f t="shared" si="6"/>
-        <v>51779.462769000005</v>
-      </c>
-      <c r="N23" s="105"/>
+        <v>68152.58205300002</v>
+      </c>
+      <c r="N23" s="104"/>
       <c r="O23" s="98">
         <f t="shared" si="7"/>
-        <v>389250.1</v>
-      </c>
-      <c r="P23" s="114">
+        <v>332298.09999999998</v>
+      </c>
+      <c r="P23" s="113">
         <f t="shared" si="2"/>
-        <v>400928.1</v>
+        <v>342267.1</v>
       </c>
       <c r="Q23" s="51">
         <f t="shared" si="8"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="106">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="105">
         <v>11</v>
       </c>
-      <c r="B24" s="155" t="s">
-        <v>85</v>
+      <c r="B24" s="153" t="s">
+        <v>83</v>
       </c>
       <c r="C24" s="94" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D24" s="99" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="E24" s="96">
         <v>3.4</v>
       </c>
       <c r="F24" s="82">
-        <v>241955</v>
-      </c>
-      <c r="G24" s="82">
-        <v>241955</v>
+        <v>255000.11</v>
+      </c>
+      <c r="G24" s="234">
+        <f>F24</f>
+        <v>255000.11</v>
       </c>
       <c r="H24" s="97">
         <f t="shared" si="0"/>
@@ -4493,58 +4451,58 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="105">
+      <c r="J24" s="104">
         <f t="shared" si="4"/>
-        <v>214862.98232000001</v>
-      </c>
-      <c r="K24" s="105">
+        <v>166827.45251999999</v>
+      </c>
+      <c r="K24" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L24" s="105">
+      <c r="L24" s="104">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M24" s="105">
+      <c r="M24" s="104">
         <f t="shared" si="6"/>
-        <v>33921.035340000002</v>
-      </c>
-      <c r="N24" s="105"/>
+        <v>44647.16358</v>
+      </c>
+      <c r="N24" s="104"/>
       <c r="O24" s="98">
         <f t="shared" si="7"/>
-        <v>255000.11</v>
-      </c>
-      <c r="P24" s="114">
+        <v>217691.11</v>
+      </c>
+      <c r="P24" s="113">
         <f t="shared" si="2"/>
-        <v>262650.11</v>
+        <v>224222.11</v>
       </c>
       <c r="Q24" s="51">
         <f t="shared" si="8"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="106">
+    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="105">
         <v>12</v>
       </c>
-      <c r="B25" s="155" t="s">
-        <v>86</v>
+      <c r="B25" s="153" t="s">
+        <v>84</v>
       </c>
       <c r="C25" s="94" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D25" s="99" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="E25" s="96">
         <v>2.54</v>
       </c>
       <c r="F25" s="82">
-        <v>175853</v>
-      </c>
-      <c r="G25" s="82">
+        <v>190500.12</v>
+      </c>
+      <c r="G25" s="234">
         <f>F25</f>
-        <v>175853</v>
+        <v>190500.12</v>
       </c>
       <c r="H25" s="97">
         <f t="shared" si="0"/>
@@ -4554,234 +4512,235 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J25" s="105">
+      <c r="J25" s="104">
         <f t="shared" si="4"/>
-        <v>160515.286792</v>
-      </c>
-      <c r="K25" s="105">
+        <v>124629.92041200001</v>
+      </c>
+      <c r="K25" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L25" s="105">
+      <c r="L25" s="104">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M25" s="105">
+      <c r="M25" s="104">
         <f t="shared" si="6"/>
-        <v>25341.008754000002</v>
-      </c>
-      <c r="N25" s="105"/>
+        <v>33354.057498000002</v>
+      </c>
+      <c r="N25" s="104"/>
       <c r="O25" s="98">
         <f t="shared" si="7"/>
-        <v>190500.12</v>
-      </c>
-      <c r="P25" s="114">
+        <v>162628.12</v>
+      </c>
+      <c r="P25" s="113">
         <f t="shared" si="2"/>
-        <v>196215.12</v>
+        <v>167507.12</v>
       </c>
       <c r="Q25" s="51">
         <f t="shared" si="8"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="106">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="235">
         <v>13</v>
       </c>
-      <c r="B26" s="155" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="94" t="s">
-        <v>131</v>
-      </c>
-      <c r="D26" s="99"/>
-      <c r="E26" s="96">
+      <c r="B26" s="236" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="237" t="s">
+        <v>204</v>
+      </c>
+      <c r="D26" s="238"/>
+      <c r="E26" s="239">
         <v>5.19</v>
       </c>
-      <c r="F26" s="82">
-        <v>359322</v>
-      </c>
-      <c r="G26" s="82">
-        <f>364861-G45</f>
-        <v>359322</v>
-      </c>
-      <c r="H26" s="97">
+      <c r="F26" s="240">
+        <v>389250.13</v>
+      </c>
+      <c r="G26" s="234">
+        <f>407108-G45</f>
+        <v>401107.68</v>
+      </c>
+      <c r="H26" s="241">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="97">
+        <v>-11857.549999999988</v>
+      </c>
+      <c r="I26" s="241">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="105">
+      <c r="J26" s="242">
         <f t="shared" si="4"/>
-        <v>327982.02301200008</v>
-      </c>
-      <c r="K26" s="105">
+        <v>254657.19958200003</v>
+      </c>
+      <c r="K26" s="242">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L26" s="105">
+      <c r="L26" s="242">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M26" s="105">
+      <c r="M26" s="242">
         <f t="shared" si="6"/>
-        <v>51779.462769000005</v>
-      </c>
-      <c r="N26" s="105"/>
-      <c r="O26" s="98">
+        <v>68152.58205300002</v>
+      </c>
+      <c r="N26" s="242"/>
+      <c r="O26" s="243">
         <f t="shared" si="7"/>
-        <v>389250.13</v>
-      </c>
-      <c r="P26" s="114">
+        <v>320441.13</v>
+      </c>
+      <c r="P26" s="244">
         <f t="shared" si="2"/>
-        <v>400928.13</v>
+        <v>330054.13</v>
       </c>
       <c r="Q26" s="51">
         <f t="shared" si="8"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="106">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="235">
         <v>14</v>
       </c>
-      <c r="B27" s="155" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="94" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="99"/>
-      <c r="E27" s="96">
+      <c r="B27" s="236" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="237" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="238"/>
+      <c r="E27" s="239">
         <v>3.4</v>
       </c>
-      <c r="F27" s="82">
-        <v>234610</v>
-      </c>
-      <c r="G27" s="82">
-        <f>301167-G51</f>
-        <v>234010</v>
-      </c>
-      <c r="H27" s="97">
+      <c r="F27" s="240">
+        <v>255618.14</v>
+      </c>
+      <c r="G27" s="234">
+        <f>328368.22-G51</f>
+        <v>255617.83999999997</v>
+      </c>
+      <c r="H27" s="241">
         <f t="shared" si="0"/>
-        <v>600</v>
-      </c>
-      <c r="I27" s="97">
+        <v>0.30000000004656613</v>
+      </c>
+      <c r="I27" s="241">
         <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-      <c r="J27" s="105">
+        <v>9.0000000013969843E-3</v>
+      </c>
+      <c r="J27" s="242">
         <f t="shared" si="4"/>
-        <v>214862.98232000001</v>
-      </c>
-      <c r="K27" s="105">
+        <v>166827.45251999999</v>
+      </c>
+      <c r="K27" s="242">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L27" s="105">
+      <c r="L27" s="242">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M27" s="105">
+      <c r="M27" s="242">
         <f t="shared" si="6"/>
-        <v>33921.035340000002</v>
-      </c>
-      <c r="N27" s="105"/>
-      <c r="O27" s="98">
+        <v>44647.16358</v>
+      </c>
+      <c r="N27" s="242"/>
+      <c r="O27" s="243">
         <f t="shared" si="7"/>
-        <v>255618.14</v>
-      </c>
-      <c r="P27" s="114">
+        <v>217691.14</v>
+      </c>
+      <c r="P27" s="244">
         <f t="shared" si="2"/>
-        <v>263287.14</v>
+        <v>224222.14</v>
       </c>
       <c r="Q27" s="51">
         <f t="shared" si="8"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="106">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="105">
         <v>15</v>
       </c>
-      <c r="B28" s="155" t="s">
-        <v>89</v>
+      <c r="B28" s="153" t="s">
+        <v>87</v>
       </c>
       <c r="C28" s="94" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D28" s="94" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="E28" s="96">
         <v>2.54</v>
       </c>
       <c r="F28" s="82">
-        <v>175853</v>
-      </c>
-      <c r="G28" s="82">
-        <v>141732</v>
+        <v>225645.15</v>
+      </c>
+      <c r="G28" s="234">
+        <f>F28</f>
+        <v>225645.15</v>
       </c>
       <c r="H28" s="97">
         <f t="shared" si="0"/>
-        <v>34121</v>
+        <v>0</v>
       </c>
       <c r="I28" s="97">
         <f t="shared" si="3"/>
-        <v>1023.63</v>
-      </c>
-      <c r="J28" s="105">
+        <v>0</v>
+      </c>
+      <c r="J28" s="104">
         <f t="shared" si="4"/>
-        <v>160515.286792</v>
-      </c>
-      <c r="K28" s="105">
+        <v>124629.92041200001</v>
+      </c>
+      <c r="K28" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L28" s="105">
+      <c r="L28" s="104">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M28" s="105">
+      <c r="M28" s="104">
         <f t="shared" si="6"/>
-        <v>25341.008754000002</v>
-      </c>
-      <c r="N28" s="105"/>
+        <v>33354.057498000002</v>
+      </c>
+      <c r="N28" s="104"/>
       <c r="O28" s="98">
         <f t="shared" si="7"/>
-        <v>225645.15</v>
-      </c>
-      <c r="P28" s="114">
+        <v>162628.15</v>
+      </c>
+      <c r="P28" s="113">
         <f t="shared" si="2"/>
-        <v>232414.15</v>
+        <v>167507.15</v>
       </c>
       <c r="Q28" s="51">
         <f t="shared" si="8"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="106">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="105">
         <v>16</v>
       </c>
-      <c r="B29" s="155" t="s">
-        <v>90</v>
+      <c r="B29" s="153" t="s">
+        <v>88</v>
       </c>
       <c r="C29" s="94" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D29" s="94"/>
       <c r="E29" s="96">
         <v>5.19</v>
       </c>
       <c r="F29" s="82">
-        <v>359322</v>
-      </c>
-      <c r="G29" s="82">
-        <f>414017-G49</f>
-        <v>359322</v>
+        <v>389250.16</v>
+      </c>
+      <c r="G29" s="234">
+        <f>F29</f>
+        <v>389250.16</v>
       </c>
       <c r="H29" s="97">
         <f t="shared" si="0"/>
@@ -4791,288 +4750,289 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="105">
+      <c r="J29" s="104">
         <f t="shared" si="4"/>
-        <v>327982.02301200008</v>
-      </c>
-      <c r="K29" s="105">
+        <v>254657.19958200003</v>
+      </c>
+      <c r="K29" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L29" s="105">
+      <c r="L29" s="104">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M29" s="105">
+      <c r="M29" s="104">
         <f t="shared" si="6"/>
-        <v>51779.462769000005</v>
-      </c>
-      <c r="N29" s="105"/>
+        <v>68152.58205300002</v>
+      </c>
+      <c r="N29" s="104"/>
       <c r="O29" s="98">
         <f t="shared" si="7"/>
-        <v>389250.16</v>
-      </c>
-      <c r="P29" s="114">
+        <v>332298.15999999997</v>
+      </c>
+      <c r="P29" s="113">
         <f t="shared" si="2"/>
-        <v>400928.16</v>
+        <v>342267.16</v>
       </c>
       <c r="Q29" s="51">
         <f t="shared" si="8"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="106">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="105">
         <v>17</v>
       </c>
-      <c r="B30" s="155" t="s">
-        <v>91</v>
+      <c r="B30" s="153" t="s">
+        <v>89</v>
       </c>
       <c r="C30" s="94" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D30" s="99" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="E30" s="96">
         <v>3.4</v>
       </c>
       <c r="F30" s="82">
-        <v>235394</v>
-      </c>
-      <c r="G30" s="82">
-        <f>275104-G53</f>
-        <v>221794</v>
+        <v>269008.17</v>
+      </c>
+      <c r="G30" s="234">
+        <f>326761-G53</f>
+        <v>269010.59999999998</v>
       </c>
       <c r="H30" s="97">
         <f t="shared" si="0"/>
-        <v>13600</v>
+        <v>-2.4299999999930151</v>
       </c>
       <c r="I30" s="97">
         <f t="shared" si="3"/>
-        <v>408</v>
-      </c>
-      <c r="J30" s="105">
+        <v>0</v>
+      </c>
+      <c r="J30" s="104">
         <f t="shared" si="4"/>
-        <v>214862.98232000001</v>
-      </c>
-      <c r="K30" s="105">
+        <v>166827.45251999999</v>
+      </c>
+      <c r="K30" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L30" s="105">
+      <c r="L30" s="104">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M30" s="105">
+      <c r="M30" s="104">
         <f t="shared" si="6"/>
-        <v>33921.035340000002</v>
-      </c>
-      <c r="N30" s="105"/>
+        <v>44647.16358</v>
+      </c>
+      <c r="N30" s="104"/>
       <c r="O30" s="98">
         <f t="shared" si="7"/>
-        <v>269008.17</v>
-      </c>
-      <c r="P30" s="114">
+        <v>217688.17</v>
+      </c>
+      <c r="P30" s="113">
         <f t="shared" si="2"/>
-        <v>277078.17</v>
+        <v>224219.17</v>
       </c>
       <c r="Q30" s="51">
         <f t="shared" si="8"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="106">
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="105">
         <v>18</v>
       </c>
-      <c r="B31" s="155" t="s">
-        <v>92</v>
+      <c r="B31" s="153" t="s">
+        <v>90</v>
       </c>
       <c r="C31" s="94" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D31" s="95"/>
       <c r="E31" s="96">
         <v>2.54</v>
       </c>
       <c r="F31" s="82">
-        <v>1184619</v>
+        <v>1410658.18</v>
       </c>
       <c r="G31" s="82"/>
       <c r="H31" s="97">
         <f t="shared" si="0"/>
-        <v>1184619</v>
+        <v>1410658.18</v>
       </c>
       <c r="I31" s="97">
         <f t="shared" si="3"/>
-        <v>35538.57</v>
-      </c>
-      <c r="J31" s="105">
+        <v>42319.7454</v>
+      </c>
+      <c r="J31" s="104">
         <f t="shared" si="4"/>
-        <v>160515.286792</v>
-      </c>
-      <c r="K31" s="105">
+        <v>124629.92041200001</v>
+      </c>
+      <c r="K31" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L31" s="105">
+      <c r="L31" s="104">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M31" s="105">
+      <c r="M31" s="104">
         <f t="shared" si="6"/>
-        <v>25341.008754000002</v>
-      </c>
-      <c r="N31" s="105"/>
+        <v>33354.057498000002</v>
+      </c>
+      <c r="N31" s="104"/>
       <c r="O31" s="98">
         <f t="shared" si="7"/>
-        <v>1410658.18</v>
-      </c>
-      <c r="P31" s="114">
+        <v>1615606.18</v>
+      </c>
+      <c r="P31" s="113">
         <f t="shared" si="2"/>
-        <v>1452978.18</v>
+        <v>1664074.18</v>
       </c>
       <c r="Q31" s="51">
         <f t="shared" si="8"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" s="106">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="105">
         <v>19</v>
       </c>
-      <c r="B32" s="155" t="s">
-        <v>93</v>
+      <c r="B32" s="153" t="s">
+        <v>91</v>
       </c>
       <c r="C32" s="94" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D32" s="99"/>
       <c r="E32" s="96">
         <v>5.19</v>
       </c>
       <c r="F32" s="82">
-        <v>745850</v>
+        <v>745476.19</v>
       </c>
       <c r="G32" s="82">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="H32" s="97">
         <f t="shared" si="0"/>
-        <v>345850</v>
+        <v>745476.19</v>
       </c>
       <c r="I32" s="97">
         <f t="shared" si="3"/>
-        <v>10375.5</v>
-      </c>
-      <c r="J32" s="105">
+        <v>22364.285699999997</v>
+      </c>
+      <c r="J32" s="104">
         <f t="shared" si="4"/>
-        <v>327982.02301200008</v>
-      </c>
-      <c r="K32" s="105">
+        <v>254657.19958200003</v>
+      </c>
+      <c r="K32" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L32" s="105">
+      <c r="L32" s="104">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M32" s="105">
+      <c r="M32" s="104">
         <f t="shared" si="6"/>
-        <v>51779.462769000005</v>
-      </c>
-      <c r="N32" s="105"/>
+        <v>68152.58205300002</v>
+      </c>
+      <c r="N32" s="104"/>
       <c r="O32" s="98">
         <f t="shared" si="7"/>
-        <v>745476.19</v>
-      </c>
-      <c r="P32" s="114">
+        <v>1100139.19</v>
+      </c>
+      <c r="P32" s="113">
         <f t="shared" si="2"/>
-        <v>767840.19</v>
+        <v>1133143.19</v>
       </c>
       <c r="Q32" s="51">
         <f>Q31+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="106">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="105">
         <v>20</v>
       </c>
-      <c r="B33" s="155" t="s">
-        <v>94</v>
+      <c r="B33" s="153" t="s">
+        <v>92</v>
       </c>
       <c r="C33" s="94" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D33" s="99"/>
       <c r="E33" s="96">
         <v>3.4</v>
       </c>
       <c r="F33" s="82">
-        <v>235394</v>
-      </c>
-      <c r="G33" s="82">
-        <f>240933-G47</f>
-        <v>235394</v>
+        <v>255000.2</v>
+      </c>
+      <c r="G33" s="234">
+        <f>261000.54-G47</f>
+        <v>255000.2</v>
       </c>
       <c r="H33" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I33" s="97"/>
-      <c r="J33" s="105">
+      <c r="J33" s="104">
         <f t="shared" si="4"/>
-        <v>214862.98232000001</v>
-      </c>
-      <c r="K33" s="105">
+        <v>166827.45251999999</v>
+      </c>
+      <c r="K33" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L33" s="105">
+      <c r="L33" s="104">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M33" s="105">
+      <c r="M33" s="104">
         <f t="shared" si="6"/>
-        <v>33921.035340000002</v>
-      </c>
-      <c r="N33" s="105"/>
+        <v>44647.16358</v>
+      </c>
+      <c r="N33" s="104"/>
       <c r="O33" s="98">
         <f t="shared" si="7"/>
-        <v>255000.2</v>
-      </c>
-      <c r="P33" s="114">
+        <v>217691.2</v>
+      </c>
+      <c r="P33" s="113">
         <f t="shared" si="2"/>
-        <v>262650.2</v>
+        <v>224222.2</v>
       </c>
       <c r="Q33" s="51">
         <f t="shared" ref="Q33:Q59" si="9">Q32+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A34" s="106">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="105">
         <v>21</v>
       </c>
-      <c r="B34" s="155" t="s">
-        <v>95</v>
+      <c r="B34" s="153" t="s">
+        <v>93</v>
       </c>
       <c r="C34" s="100" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D34" s="99" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="E34" s="96">
         <v>2.54</v>
       </c>
       <c r="F34" s="82">
-        <v>175853</v>
-      </c>
-      <c r="G34" s="82">
-        <v>175853</v>
+        <v>190500.21</v>
+      </c>
+      <c r="G34" s="234">
+        <f>F34</f>
+        <v>190500.21</v>
       </c>
       <c r="H34" s="97">
         <f t="shared" si="0"/>
@@ -5082,59 +5042,59 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J34" s="105">
+      <c r="J34" s="104">
         <f t="shared" si="4"/>
-        <v>160515.286792</v>
-      </c>
-      <c r="K34" s="105">
+        <v>124629.92041200001</v>
+      </c>
+      <c r="K34" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L34" s="105">
+      <c r="L34" s="104">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M34" s="105">
+      <c r="M34" s="104">
         <f t="shared" si="6"/>
-        <v>25341.008754000002</v>
-      </c>
-      <c r="N34" s="105"/>
+        <v>33354.057498000002</v>
+      </c>
+      <c r="N34" s="104"/>
       <c r="O34" s="98">
         <f t="shared" si="7"/>
-        <v>190500.21</v>
-      </c>
-      <c r="P34" s="114">
+        <v>162628.21</v>
+      </c>
+      <c r="P34" s="113">
         <f t="shared" si="2"/>
-        <v>196215.21</v>
+        <v>167507.21</v>
       </c>
       <c r="Q34" s="51">
         <f t="shared" si="9"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="106">
+    <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="105">
         <f>A34+1</f>
         <v>22</v>
       </c>
-      <c r="B35" s="155" t="s">
-        <v>96</v>
+      <c r="B35" s="153" t="s">
+        <v>94</v>
       </c>
       <c r="C35" s="100" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D35" s="99" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="E35" s="96">
         <v>4.9400000000000004</v>
       </c>
       <c r="F35" s="82">
-        <v>342014</v>
-      </c>
-      <c r="G35" s="82">
-        <f>342014</f>
-        <v>342014</v>
+        <v>370500.22</v>
+      </c>
+      <c r="G35" s="234">
+        <f>F35</f>
+        <v>370500.22</v>
       </c>
       <c r="H35" s="97">
         <f t="shared" si="0"/>
@@ -5144,117 +5104,118 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="105">
+      <c r="J35" s="104">
         <f t="shared" si="4"/>
-        <v>312183.27431200002</v>
-      </c>
-      <c r="K35" s="105">
+        <v>242390.47513200005</v>
+      </c>
+      <c r="K35" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L35" s="105">
+      <c r="L35" s="104">
         <f t="shared" si="5"/>
         <v>9031.4566940000004</v>
       </c>
-      <c r="M35" s="105">
+      <c r="M35" s="104">
         <f t="shared" si="6"/>
-        <v>49285.268994000005</v>
-      </c>
-      <c r="N35" s="105"/>
+        <v>64869.702378000009</v>
+      </c>
+      <c r="N35" s="104"/>
       <c r="O35" s="98">
         <f t="shared" si="7"/>
-        <v>370500.22</v>
-      </c>
-      <c r="P35" s="114">
+        <v>316292.21999999997</v>
+      </c>
+      <c r="P35" s="113">
         <f t="shared" ref="P35:P59" si="10">ROUND(O35*3%,0) + O35</f>
-        <v>381615.22</v>
+        <v>325781.21999999997</v>
       </c>
       <c r="Q35" s="51">
         <f t="shared" si="9"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" s="106">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="105">
         <f t="shared" ref="A36:A59" si="11">A35+1</f>
         <v>23</v>
       </c>
-      <c r="B36" s="155" t="s">
-        <v>97</v>
+      <c r="B36" s="153" t="s">
+        <v>95</v>
       </c>
       <c r="C36" s="100" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D36" s="99" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="E36" s="96">
         <v>3.28</v>
       </c>
       <c r="F36" s="82">
-        <v>233819</v>
-      </c>
-      <c r="G36" s="82">
-        <v>233000</v>
+        <v>246844.23</v>
+      </c>
+      <c r="G36" s="234">
+        <v>246000</v>
       </c>
       <c r="H36" s="97">
         <f t="shared" si="0"/>
-        <v>819</v>
+        <v>844.23000000001048</v>
       </c>
       <c r="I36" s="97">
         <f t="shared" si="3"/>
-        <v>24.57</v>
-      </c>
-      <c r="J36" s="105">
+        <v>25.326900000000315</v>
+      </c>
+      <c r="J36" s="104">
         <f t="shared" si="4"/>
-        <v>207279.58294399999</v>
-      </c>
-      <c r="K36" s="105">
+        <v>160939.424784</v>
+      </c>
+      <c r="K36" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L36" s="105">
+      <c r="L36" s="104">
         <f t="shared" si="5"/>
         <v>5996.594728</v>
       </c>
-      <c r="M36" s="105">
+      <c r="M36" s="104">
         <f t="shared" si="6"/>
-        <v>32723.822327999998</v>
-      </c>
-      <c r="N36" s="105"/>
+        <v>43071.381336000006</v>
+      </c>
+      <c r="N36" s="104"/>
       <c r="O36" s="98">
         <f t="shared" si="7"/>
-        <v>246844.23</v>
-      </c>
-      <c r="P36" s="114">
+        <v>210877.23</v>
+      </c>
+      <c r="P36" s="113">
         <f t="shared" si="10"/>
-        <v>254249.23</v>
+        <v>217203.23</v>
       </c>
       <c r="Q36" s="51">
         <f t="shared" si="9"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" s="106">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" s="105">
         <f t="shared" si="11"/>
         <v>24</v>
       </c>
-      <c r="B37" s="155" t="s">
-        <v>98</v>
+      <c r="B37" s="153" t="s">
+        <v>96</v>
       </c>
       <c r="C37" s="100" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D37" s="99"/>
       <c r="E37" s="96">
         <v>2.41</v>
       </c>
       <c r="F37" s="82">
-        <v>171357</v>
-      </c>
-      <c r="G37" s="82">
-        <v>171357</v>
+        <v>180750.24</v>
+      </c>
+      <c r="G37" s="234">
+        <f>F37</f>
+        <v>180750.24</v>
       </c>
       <c r="H37" s="97">
         <f t="shared" si="0"/>
@@ -5264,119 +5225,119 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="105">
+      <c r="J37" s="104">
         <f t="shared" si="4"/>
-        <v>152299.93746800002</v>
-      </c>
-      <c r="K37" s="105">
+        <v>118251.22369800002</v>
+      </c>
+      <c r="K37" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L37" s="105">
+      <c r="L37" s="104">
         <f t="shared" si="5"/>
         <v>4406.034541</v>
       </c>
-      <c r="M37" s="105">
+      <c r="M37" s="104">
         <f t="shared" si="6"/>
-        <v>24044.027990999999</v>
-      </c>
-      <c r="N37" s="105"/>
+        <v>31646.960067000004</v>
+      </c>
+      <c r="N37" s="104"/>
       <c r="O37" s="98">
         <f t="shared" si="7"/>
-        <v>180750.24</v>
-      </c>
-      <c r="P37" s="114">
+        <v>154304.24</v>
+      </c>
+      <c r="P37" s="113">
         <f t="shared" si="10"/>
-        <v>186173.24</v>
+        <v>158933.24</v>
       </c>
       <c r="Q37" s="51">
         <f t="shared" si="9"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" s="106">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" s="105">
         <f t="shared" si="11"/>
         <v>25</v>
       </c>
-      <c r="B38" s="155" t="s">
-        <v>99</v>
+      <c r="B38" s="153" t="s">
+        <v>97</v>
       </c>
       <c r="C38" s="100" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D38" s="99"/>
       <c r="E38" s="96">
         <v>0.44</v>
       </c>
       <c r="F38" s="82">
-        <v>31499</v>
+        <v>24889.25</v>
       </c>
       <c r="G38" s="82">
-        <f>149000-G52-G59</f>
-        <v>39610</v>
+        <v>0</v>
       </c>
       <c r="H38" s="97">
         <f t="shared" si="0"/>
-        <v>-8111</v>
+        <v>24889.25</v>
       </c>
       <c r="I38" s="97">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J38" s="105">
+        <v>746.67750000000001</v>
+      </c>
+      <c r="J38" s="104">
         <f t="shared" si="4"/>
-        <v>27805.797712000003</v>
-      </c>
-      <c r="K38" s="105">
+        <v>21589.435032000001</v>
+      </c>
+      <c r="K38" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L38" s="105">
+      <c r="L38" s="104">
         <f t="shared" si="5"/>
         <v>804.421244</v>
       </c>
-      <c r="M38" s="105">
+      <c r="M38" s="104">
         <f t="shared" si="6"/>
-        <v>4389.7810440000003</v>
-      </c>
-      <c r="N38" s="105"/>
+        <v>5777.8682280000012</v>
+      </c>
+      <c r="N38" s="104"/>
       <c r="O38" s="98">
         <f t="shared" si="7"/>
-        <v>24889.25</v>
-      </c>
-      <c r="P38" s="114">
+        <v>53808.25</v>
+      </c>
+      <c r="P38" s="113">
         <f t="shared" si="10"/>
-        <v>25636.25</v>
+        <v>55422.25</v>
       </c>
       <c r="Q38" s="51">
         <f t="shared" si="9"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="R38" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A39" s="106">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="105">
         <f t="shared" si="11"/>
         <v>26</v>
       </c>
-      <c r="B39" s="155" t="s">
-        <v>101</v>
+      <c r="B39" s="153" t="s">
+        <v>99</v>
       </c>
       <c r="C39" s="100" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D39" s="99"/>
       <c r="E39" s="96">
         <v>0.55000000000000004</v>
       </c>
       <c r="F39" s="82">
-        <v>38078</v>
-      </c>
-      <c r="G39" s="82">
-        <v>38078</v>
+        <v>41250.26</v>
+      </c>
+      <c r="G39" s="234">
+        <f>F39</f>
+        <v>41250.26</v>
       </c>
       <c r="H39" s="97">
         <f t="shared" si="0"/>
@@ -5386,180 +5347,180 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="105">
+      <c r="J39" s="104">
         <f t="shared" si="4"/>
-        <v>34757.247140000007</v>
-      </c>
-      <c r="K39" s="105">
+        <v>26986.793790000003</v>
+      </c>
+      <c r="K39" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L39" s="105">
+      <c r="L39" s="104">
         <f t="shared" si="5"/>
         <v>1005.526555</v>
       </c>
-      <c r="M39" s="105">
+      <c r="M39" s="104">
         <f t="shared" si="6"/>
-        <v>5487.226305000001</v>
-      </c>
-      <c r="N39" s="105"/>
+        <v>7222.335285000001</v>
+      </c>
+      <c r="N39" s="104"/>
       <c r="O39" s="98">
         <f t="shared" si="7"/>
-        <v>41250.26</v>
-      </c>
-      <c r="P39" s="114">
+        <v>35215.26</v>
+      </c>
+      <c r="P39" s="113">
         <f t="shared" si="10"/>
-        <v>42488.26</v>
+        <v>36271.26</v>
       </c>
       <c r="Q39" s="51">
         <f t="shared" si="9"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A40" s="106">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" s="105">
         <f t="shared" si="11"/>
         <v>27</v>
       </c>
-      <c r="B40" s="155" t="s">
-        <v>100</v>
+      <c r="B40" s="153" t="s">
+        <v>98</v>
       </c>
       <c r="C40" s="100" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D40" s="99"/>
       <c r="E40" s="96">
         <v>0.53</v>
       </c>
       <c r="F40" s="82">
-        <v>36694</v>
-      </c>
-      <c r="G40" s="82">
-        <f>F40</f>
-        <v>36694</v>
+        <v>39750.269999999997</v>
+      </c>
+      <c r="G40" s="234">
+        <v>40943.269999999997</v>
       </c>
       <c r="H40" s="97">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1193</v>
       </c>
       <c r="I40" s="97">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J40" s="105">
+      <c r="J40" s="104">
         <f t="shared" si="4"/>
-        <v>33493.347244000004</v>
-      </c>
-      <c r="K40" s="105">
+        <v>26005.455834000004</v>
+      </c>
+      <c r="K40" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L40" s="105">
+      <c r="L40" s="104">
         <f t="shared" si="5"/>
         <v>968.96195300000011</v>
       </c>
-      <c r="M40" s="105">
+      <c r="M40" s="104">
         <f t="shared" si="6"/>
-        <v>5287.6908030000004</v>
-      </c>
-      <c r="N40" s="105"/>
+        <v>6959.7049110000007</v>
+      </c>
+      <c r="N40" s="104"/>
       <c r="O40" s="98">
         <f t="shared" si="7"/>
-        <v>39750.269999999997</v>
-      </c>
-      <c r="P40" s="114">
+        <v>32741.27</v>
+      </c>
+      <c r="P40" s="113">
         <f t="shared" si="10"/>
-        <v>40943.269999999997</v>
+        <v>33723.270000000004</v>
       </c>
       <c r="Q40" s="51">
         <f t="shared" si="9"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A41" s="106">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" s="105">
         <f t="shared" si="11"/>
         <v>28</v>
       </c>
-      <c r="B41" s="155" t="s">
-        <v>102</v>
+      <c r="B41" s="153" t="s">
+        <v>100</v>
       </c>
       <c r="C41" s="100" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D41" s="94" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="E41" s="96">
         <v>0.28999999999999998</v>
       </c>
       <c r="F41" s="82">
-        <v>20078</v>
-      </c>
-      <c r="G41" s="82">
-        <v>22000</v>
+        <v>19828.28</v>
+      </c>
+      <c r="G41" s="234">
+        <f>F41</f>
+        <v>19828.28</v>
       </c>
       <c r="H41" s="97">
         <f t="shared" si="0"/>
-        <v>-1922</v>
+        <v>0</v>
       </c>
       <c r="I41" s="97">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J41" s="105">
+      <c r="J41" s="104">
         <f t="shared" si="4"/>
-        <v>18326.548492000002</v>
-      </c>
-      <c r="K41" s="105">
+        <v>14229.400362</v>
+      </c>
+      <c r="K41" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L41" s="105">
+      <c r="L41" s="104">
         <f t="shared" si="5"/>
         <v>530.18672900000001</v>
       </c>
-      <c r="M41" s="105">
+      <c r="M41" s="104">
         <f t="shared" si="6"/>
-        <v>2893.2647790000001</v>
-      </c>
-      <c r="N41" s="105"/>
+        <v>3808.1404230000003</v>
+      </c>
+      <c r="N41" s="104"/>
       <c r="O41" s="98">
         <f t="shared" si="7"/>
-        <v>19828.28</v>
-      </c>
-      <c r="P41" s="114">
+        <v>18568.28</v>
+      </c>
+      <c r="P41" s="113">
         <f t="shared" si="10"/>
-        <v>20423.28</v>
+        <v>19125.28</v>
       </c>
       <c r="Q41" s="51">
         <f t="shared" si="9"/>
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A42" s="106">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="105">
         <f t="shared" si="11"/>
         <v>29</v>
       </c>
-      <c r="B42" s="155" t="s">
-        <v>103</v>
+      <c r="B42" s="153" t="s">
+        <v>101</v>
       </c>
       <c r="C42" s="100" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D42" s="99" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="E42" s="96">
         <v>0.08</v>
       </c>
       <c r="F42" s="82">
-        <v>5737</v>
-      </c>
-      <c r="G42" s="82">
+        <v>6000.29</v>
+      </c>
+      <c r="G42" s="234">
         <f>F42</f>
-        <v>5737</v>
+        <v>6000.29</v>
       </c>
       <c r="H42" s="97">
         <f t="shared" si="0"/>
@@ -5569,175 +5530,181 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J42" s="105">
+      <c r="J42" s="104">
         <f t="shared" si="4"/>
-        <v>5055.5995840000005</v>
-      </c>
-      <c r="K42" s="105">
+        <v>3925.3518240000003</v>
+      </c>
+      <c r="K42" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L42" s="105">
+      <c r="L42" s="104">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M42" s="105">
+      <c r="M42" s="104">
         <f t="shared" si="6"/>
-        <v>798.14200800000003</v>
-      </c>
-      <c r="N42" s="105"/>
+        <v>1050.5214960000001</v>
+      </c>
+      <c r="N42" s="104"/>
       <c r="O42" s="98">
         <f t="shared" si="7"/>
-        <v>6000.29</v>
-      </c>
-      <c r="P42" s="114">
+        <v>5122.29</v>
+      </c>
+      <c r="P42" s="113">
         <f t="shared" si="10"/>
-        <v>6180.29</v>
+        <v>5276.29</v>
       </c>
       <c r="Q42" s="51">
         <f t="shared" si="9"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A43" s="106">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="105">
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="B43" s="155" t="s">
-        <v>104</v>
+      <c r="B43" s="153" t="s">
+        <v>102</v>
       </c>
       <c r="C43" s="100" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D43" s="99"/>
       <c r="E43" s="96">
         <v>0.08</v>
       </c>
       <c r="F43" s="82">
-        <v>5539</v>
-      </c>
-      <c r="G43" s="82">
-        <v>5539</v>
+        <v>6000.3</v>
+      </c>
+      <c r="G43" s="234">
+        <v>6180.3</v>
       </c>
       <c r="H43" s="97">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="I43" s="97">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J43" s="105">
+      <c r="J43" s="104">
         <f t="shared" si="4"/>
-        <v>5055.5995840000005</v>
-      </c>
-      <c r="K43" s="105">
+        <v>3925.3518240000003</v>
+      </c>
+      <c r="K43" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L43" s="105">
+      <c r="L43" s="104">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M43" s="105">
+      <c r="M43" s="104">
         <f t="shared" si="6"/>
-        <v>798.14200800000003</v>
-      </c>
-      <c r="N43" s="105"/>
+        <v>1050.5214960000001</v>
+      </c>
+      <c r="N43" s="104"/>
       <c r="O43" s="98">
         <f t="shared" si="7"/>
-        <v>6000.3</v>
-      </c>
-      <c r="P43" s="114">
+        <v>4942.3</v>
+      </c>
+      <c r="P43" s="113">
         <f t="shared" si="10"/>
-        <v>6180.3</v>
+        <v>5090.3</v>
       </c>
       <c r="Q43" s="51">
         <f t="shared" si="9"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A44" s="175">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" s="105">
         <f t="shared" si="11"/>
         <v>31</v>
       </c>
-      <c r="B44" s="176" t="s">
-        <v>105</v>
-      </c>
-      <c r="C44" s="177" t="s">
-        <v>124</v>
-      </c>
-      <c r="D44" s="99"/>
+      <c r="B44" s="153" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="D44" s="99" t="s">
+        <v>157</v>
+      </c>
       <c r="E44" s="96">
         <v>0.08</v>
       </c>
       <c r="F44" s="82">
-        <v>5539</v>
-      </c>
-      <c r="G44" s="82"/>
+        <v>11705.31</v>
+      </c>
+      <c r="G44" s="234">
+        <f>F44</f>
+        <v>11705.31</v>
+      </c>
       <c r="H44" s="97">
         <f t="shared" si="0"/>
-        <v>5539</v>
+        <v>0</v>
       </c>
       <c r="I44" s="97">
         <f t="shared" si="3"/>
-        <v>166.17</v>
-      </c>
-      <c r="J44" s="105">
+        <v>0</v>
+      </c>
+      <c r="J44" s="104">
         <f t="shared" si="4"/>
-        <v>5055.5995840000005</v>
-      </c>
-      <c r="K44" s="105">
+        <v>3925.3518240000003</v>
+      </c>
+      <c r="K44" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L44" s="105">
+      <c r="L44" s="104">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M44" s="105">
+      <c r="M44" s="104">
         <f t="shared" si="6"/>
-        <v>798.14200800000003</v>
-      </c>
-      <c r="N44" s="105"/>
+        <v>1050.5214960000001</v>
+      </c>
+      <c r="N44" s="104"/>
       <c r="O44" s="98">
         <f t="shared" si="7"/>
-        <v>11705.31</v>
-      </c>
-      <c r="P44" s="114">
+        <v>5122.3100000000004</v>
+      </c>
+      <c r="P44" s="113">
         <f t="shared" si="10"/>
-        <v>12056.31</v>
+        <v>5276.31</v>
       </c>
       <c r="Q44" s="51">
         <f t="shared" si="9"/>
         <v>0.31000000000000011</v>
       </c>
       <c r="R44" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A45" s="106">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" s="105">
         <f t="shared" si="11"/>
         <v>32</v>
       </c>
-      <c r="B45" s="155" t="s">
-        <v>106</v>
+      <c r="B45" s="153" t="s">
+        <v>104</v>
       </c>
       <c r="C45" s="100" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D45" s="99"/>
       <c r="E45" s="96">
         <v>0.08</v>
       </c>
       <c r="F45" s="82">
-        <v>5539</v>
-      </c>
-      <c r="G45" s="82">
-        <v>5539</v>
+        <v>6000.32</v>
+      </c>
+      <c r="G45" s="234">
+        <f>F45</f>
+        <v>6000.32</v>
       </c>
       <c r="H45" s="97">
         <f t="shared" si="0"/>
@@ -5747,110 +5714,111 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J45" s="105">
+      <c r="J45" s="104">
         <f t="shared" si="4"/>
-        <v>5055.5995840000005</v>
-      </c>
-      <c r="K45" s="105">
+        <v>3925.3518240000003</v>
+      </c>
+      <c r="K45" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L45" s="105">
+      <c r="L45" s="104">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M45" s="105">
+      <c r="M45" s="104">
         <f t="shared" si="6"/>
-        <v>798.14200800000003</v>
-      </c>
-      <c r="N45" s="105"/>
+        <v>1050.5214960000001</v>
+      </c>
+      <c r="N45" s="104"/>
       <c r="O45" s="98">
         <f t="shared" si="7"/>
-        <v>6000.32</v>
-      </c>
-      <c r="P45" s="114">
+        <v>5122.32</v>
+      </c>
+      <c r="P45" s="113">
         <f t="shared" si="10"/>
-        <v>6180.32</v>
+        <v>5276.32</v>
       </c>
       <c r="Q45" s="51">
         <f t="shared" si="9"/>
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A46" s="106">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46" s="105">
         <f t="shared" si="11"/>
         <v>33</v>
       </c>
-      <c r="B46" s="155" t="s">
-        <v>107</v>
+      <c r="B46" s="153" t="s">
+        <v>105</v>
       </c>
       <c r="C46" s="100" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D46" s="99"/>
       <c r="E46" s="96">
         <v>0.08</v>
       </c>
       <c r="F46" s="82">
-        <v>12312</v>
+        <v>18312.330000000002</v>
       </c>
       <c r="G46" s="82"/>
       <c r="H46" s="97">
         <f t="shared" si="0"/>
-        <v>12312</v>
+        <v>18312.330000000002</v>
       </c>
       <c r="I46" s="97"/>
-      <c r="J46" s="105">
+      <c r="J46" s="104">
         <f t="shared" si="4"/>
-        <v>5055.5995840000005</v>
-      </c>
-      <c r="K46" s="105">
+        <v>3925.3518240000003</v>
+      </c>
+      <c r="K46" s="104">
         <f t="shared" ref="K46:K59" si="12">F$2*E46/100</f>
         <v>0</v>
       </c>
-      <c r="L46" s="105">
+      <c r="L46" s="104">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M46" s="105">
+      <c r="M46" s="104">
         <f t="shared" si="6"/>
-        <v>798.14200800000003</v>
-      </c>
-      <c r="N46" s="105"/>
+        <v>1050.5214960000001</v>
+      </c>
+      <c r="N46" s="104"/>
       <c r="O46" s="98">
         <f t="shared" si="7"/>
-        <v>18312.330000000002</v>
-      </c>
-      <c r="P46" s="114">
+        <v>23434.33</v>
+      </c>
+      <c r="P46" s="113">
         <f t="shared" si="10"/>
-        <v>18861.330000000002</v>
+        <v>24137.33</v>
       </c>
       <c r="Q46" s="51">
         <f t="shared" si="9"/>
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A47" s="106">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" s="105">
         <f t="shared" si="11"/>
         <v>34</v>
       </c>
-      <c r="B47" s="155" t="s">
-        <v>108</v>
+      <c r="B47" s="153" t="s">
+        <v>106</v>
       </c>
       <c r="C47" s="100" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D47" s="99"/>
       <c r="E47" s="96">
         <v>0.08</v>
       </c>
       <c r="F47" s="82">
-        <v>5539</v>
-      </c>
-      <c r="G47" s="82">
-        <v>5539</v>
+        <v>6000.34</v>
+      </c>
+      <c r="G47" s="234">
+        <f>F47</f>
+        <v>6000.34</v>
       </c>
       <c r="H47" s="97">
         <f t="shared" si="0"/>
@@ -5860,113 +5828,116 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J47" s="105">
+      <c r="J47" s="104">
         <f t="shared" si="4"/>
-        <v>5055.5995840000005</v>
-      </c>
-      <c r="K47" s="105">
+        <v>3925.3518240000003</v>
+      </c>
+      <c r="K47" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L47" s="105">
+      <c r="L47" s="104">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M47" s="105">
+      <c r="M47" s="104">
         <f t="shared" si="6"/>
-        <v>798.14200800000003</v>
-      </c>
-      <c r="N47" s="105"/>
+        <v>1050.5214960000001</v>
+      </c>
+      <c r="N47" s="104"/>
       <c r="O47" s="98">
         <f t="shared" si="7"/>
-        <v>6000.34</v>
-      </c>
-      <c r="P47" s="114">
+        <v>5122.34</v>
+      </c>
+      <c r="P47" s="113">
         <f t="shared" si="10"/>
-        <v>6180.34</v>
+        <v>5276.34</v>
       </c>
       <c r="Q47" s="51">
         <f t="shared" si="9"/>
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A48" s="146">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="144">
         <f t="shared" si="11"/>
         <v>35</v>
       </c>
-      <c r="B48" s="155" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" s="147" t="s">
-        <v>144</v>
-      </c>
-      <c r="D48" s="148"/>
-      <c r="E48" s="149">
+      <c r="B48" s="153" t="s">
+        <v>107</v>
+      </c>
+      <c r="C48" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="D48" s="146"/>
+      <c r="E48" s="147">
         <v>0.09</v>
       </c>
       <c r="F48" s="82">
-        <v>6231</v>
-      </c>
-      <c r="G48" s="82"/>
-      <c r="H48" s="150">
+        <v>13563.35</v>
+      </c>
+      <c r="G48" s="234">
+        <v>13563.35</v>
+      </c>
+      <c r="H48" s="148">
         <f t="shared" si="0"/>
-        <v>6231</v>
-      </c>
-      <c r="I48" s="150">
+        <v>0</v>
+      </c>
+      <c r="I48" s="148">
         <f t="shared" si="3"/>
-        <v>186.93</v>
-      </c>
-      <c r="J48" s="105">
+        <v>0</v>
+      </c>
+      <c r="J48" s="104">
         <f t="shared" si="4"/>
-        <v>5687.549532</v>
-      </c>
-      <c r="K48" s="151">
+        <v>4416.020802</v>
+      </c>
+      <c r="K48" s="149">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L48" s="105">
+      <c r="L48" s="104">
         <f t="shared" si="5"/>
         <v>164.54070899999999</v>
       </c>
-      <c r="M48" s="105">
+      <c r="M48" s="104">
         <f t="shared" si="6"/>
-        <v>897.90975899999989</v>
-      </c>
-      <c r="N48" s="151"/>
+        <v>1181.836683</v>
+      </c>
+      <c r="N48" s="149"/>
       <c r="O48" s="98">
         <f t="shared" si="7"/>
-        <v>13168.35</v>
-      </c>
-      <c r="P48" s="114">
+        <v>5762.35</v>
+      </c>
+      <c r="P48" s="113">
         <f t="shared" si="10"/>
-        <v>13563.35</v>
+        <v>5935.35</v>
       </c>
       <c r="Q48" s="51">
         <f t="shared" si="9"/>
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A49" s="106">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" s="105">
         <f t="shared" si="11"/>
         <v>36</v>
       </c>
-      <c r="B49" s="155" t="s">
-        <v>110</v>
+      <c r="B49" s="153" t="s">
+        <v>108</v>
       </c>
       <c r="C49" s="100" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D49" s="99"/>
       <c r="E49" s="96">
         <v>0.79</v>
       </c>
       <c r="F49" s="82">
-        <v>54695</v>
-      </c>
-      <c r="G49" s="82">
-        <v>54695</v>
+        <v>59250.36</v>
+      </c>
+      <c r="G49" s="234">
+        <f>F49</f>
+        <v>59250.36</v>
       </c>
       <c r="H49" s="97">
         <f t="shared" si="0"/>
@@ -5976,113 +5947,114 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J49" s="105">
+      <c r="J49" s="104">
         <f t="shared" si="4"/>
-        <v>49924.045892000002</v>
-      </c>
-      <c r="K49" s="105">
+        <v>38762.849262000003</v>
+      </c>
+      <c r="K49" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L49" s="105">
+      <c r="L49" s="104">
         <f t="shared" si="5"/>
         <v>1444.3017790000001</v>
       </c>
-      <c r="M49" s="105">
+      <c r="M49" s="104">
         <f t="shared" si="6"/>
-        <v>7881.6523290000005</v>
-      </c>
-      <c r="N49" s="105"/>
+        <v>10373.899773000001</v>
+      </c>
+      <c r="N49" s="104"/>
       <c r="O49" s="98">
         <f t="shared" si="7"/>
-        <v>59250.36</v>
-      </c>
-      <c r="P49" s="114">
+        <v>50581.36</v>
+      </c>
+      <c r="P49" s="113">
         <f t="shared" si="10"/>
-        <v>61028.36</v>
+        <v>52098.36</v>
       </c>
       <c r="Q49" s="51">
         <f t="shared" si="9"/>
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A50" s="106">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="105">
         <f t="shared" si="11"/>
         <v>37</v>
       </c>
-      <c r="B50" s="155" t="s">
-        <v>111</v>
+      <c r="B50" s="153" t="s">
+        <v>109</v>
       </c>
       <c r="C50" s="100" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D50" s="99"/>
       <c r="E50" s="96">
         <v>1</v>
       </c>
       <c r="F50" s="82">
-        <v>153892</v>
+        <v>233509.37</v>
       </c>
       <c r="G50" s="82"/>
       <c r="H50" s="97">
         <f t="shared" si="0"/>
-        <v>153892</v>
+        <v>233509.37</v>
       </c>
       <c r="I50" s="97">
         <f t="shared" si="3"/>
-        <v>4616.76</v>
-      </c>
-      <c r="J50" s="105">
+        <v>7005.2810999999992</v>
+      </c>
+      <c r="J50" s="104">
         <f t="shared" si="4"/>
-        <v>63194.994800000008</v>
-      </c>
-      <c r="K50" s="105">
+        <v>49066.897800000006</v>
+      </c>
+      <c r="K50" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L50" s="105">
+      <c r="L50" s="104">
         <f t="shared" si="5"/>
         <v>1828.2301</v>
       </c>
-      <c r="M50" s="105">
+      <c r="M50" s="104">
         <f t="shared" si="6"/>
-        <v>9976.7751000000007</v>
-      </c>
-      <c r="N50" s="105"/>
+        <v>13131.518700000001</v>
+      </c>
+      <c r="N50" s="104"/>
       <c r="O50" s="98">
         <f t="shared" si="7"/>
-        <v>233509.37</v>
-      </c>
-      <c r="P50" s="114">
+        <v>304541.37</v>
+      </c>
+      <c r="P50" s="113">
         <f t="shared" si="10"/>
-        <v>240514.37</v>
+        <v>313677.37</v>
       </c>
       <c r="Q50" s="51">
         <f t="shared" si="9"/>
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A51" s="106">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" s="105">
         <f t="shared" si="11"/>
         <v>38</v>
       </c>
-      <c r="B51" s="155" t="s">
-        <v>112</v>
+      <c r="B51" s="153" t="s">
+        <v>110</v>
       </c>
       <c r="C51" s="100" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D51" s="99"/>
       <c r="E51" s="96">
         <v>0.97</v>
       </c>
       <c r="F51" s="82">
-        <v>67157</v>
-      </c>
-      <c r="G51" s="82">
-        <v>67157</v>
+        <v>72750.38</v>
+      </c>
+      <c r="G51" s="234">
+        <f>F51</f>
+        <v>72750.38</v>
       </c>
       <c r="H51" s="97">
         <f t="shared" si="0"/>
@@ -6092,121 +6064,121 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J51" s="105">
+      <c r="J51" s="104">
         <f t="shared" si="4"/>
-        <v>61299.144956000004</v>
-      </c>
-      <c r="K51" s="105">
+        <v>47594.890866000002</v>
+      </c>
+      <c r="K51" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L51" s="105">
+      <c r="L51" s="104">
         <f t="shared" si="5"/>
         <v>1773.3831969999999</v>
       </c>
-      <c r="M51" s="105">
+      <c r="M51" s="104">
         <f t="shared" si="6"/>
-        <v>9677.4718470000007</v>
-      </c>
-      <c r="N51" s="105"/>
+        <v>12737.573139000002</v>
+      </c>
+      <c r="N51" s="104"/>
       <c r="O51" s="98">
         <f t="shared" si="7"/>
-        <v>72750.38</v>
-      </c>
-      <c r="P51" s="114">
+        <v>62106.38</v>
+      </c>
+      <c r="P51" s="113">
         <f t="shared" si="10"/>
-        <v>74933.38</v>
+        <v>63969.38</v>
       </c>
       <c r="Q51" s="51">
         <f t="shared" si="9"/>
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A52" s="106">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="105">
         <f t="shared" si="11"/>
         <v>39</v>
       </c>
-      <c r="B52" s="155" t="s">
-        <v>113</v>
+      <c r="B52" s="153" t="s">
+        <v>111</v>
       </c>
       <c r="C52" s="100" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D52" s="99"/>
       <c r="E52" s="96">
         <v>0.77</v>
       </c>
       <c r="F52" s="82">
-        <v>55162</v>
+        <v>58231.39</v>
       </c>
       <c r="G52" s="82">
-        <v>54695</v>
+        <v>0</v>
       </c>
       <c r="H52" s="97">
         <f t="shared" si="0"/>
-        <v>467</v>
+        <v>58231.39</v>
       </c>
       <c r="I52" s="97">
         <f t="shared" si="3"/>
-        <v>14.01</v>
-      </c>
-      <c r="J52" s="105">
+        <v>1746.9416999999999</v>
+      </c>
+      <c r="J52" s="104">
         <f t="shared" si="4"/>
-        <v>48660.145996000007</v>
-      </c>
-      <c r="K52" s="105">
+        <v>37781.511306</v>
+      </c>
+      <c r="K52" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L52" s="105">
+      <c r="L52" s="104">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M52" s="105">
+      <c r="M52" s="104">
         <f t="shared" si="6"/>
-        <v>7682.1168269999998</v>
-      </c>
-      <c r="N52" s="105"/>
+        <v>10111.269399000001</v>
+      </c>
+      <c r="N52" s="104"/>
       <c r="O52" s="98">
         <f t="shared" si="7"/>
-        <v>58231.39</v>
-      </c>
-      <c r="P52" s="114">
+        <v>109279.39</v>
+      </c>
+      <c r="P52" s="113">
         <f t="shared" si="10"/>
-        <v>59978.39</v>
+        <v>112557.39</v>
       </c>
       <c r="Q52" s="51">
         <f t="shared" si="9"/>
         <v>0.39000000000000018</v>
       </c>
       <c r="R52" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A53" s="106">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="105">
         <f t="shared" si="11"/>
         <v>40</v>
       </c>
-      <c r="B53" s="155" t="s">
-        <v>114</v>
+      <c r="B53" s="153" t="s">
+        <v>112</v>
       </c>
       <c r="C53" s="100" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D53" s="99" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="E53" s="96">
         <v>0.77</v>
       </c>
       <c r="F53" s="82">
-        <v>53310</v>
-      </c>
-      <c r="G53" s="82">
+        <v>57750.400000000001</v>
+      </c>
+      <c r="G53" s="234">
         <f>F53</f>
-        <v>53310</v>
+        <v>57750.400000000001</v>
       </c>
       <c r="H53" s="97">
         <f t="shared" si="0"/>
@@ -6216,58 +6188,59 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J53" s="105">
+      <c r="J53" s="104">
         <f t="shared" si="4"/>
-        <v>48660.145996000007</v>
-      </c>
-      <c r="K53" s="105">
+        <v>37781.511306</v>
+      </c>
+      <c r="K53" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L53" s="105">
+      <c r="L53" s="104">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M53" s="105">
+      <c r="M53" s="104">
         <f t="shared" si="6"/>
-        <v>7682.1168269999998</v>
-      </c>
-      <c r="N53" s="105"/>
+        <v>10111.269399000001</v>
+      </c>
+      <c r="N53" s="104"/>
       <c r="O53" s="98">
         <f t="shared" si="7"/>
-        <v>57750.400000000001</v>
-      </c>
-      <c r="P53" s="114">
+        <v>49301.4</v>
+      </c>
+      <c r="P53" s="113">
         <f t="shared" si="10"/>
-        <v>59483.4</v>
+        <v>50780.4</v>
       </c>
       <c r="Q53" s="51">
         <f t="shared" si="9"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A54" s="106">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54" s="105">
         <f t="shared" si="11"/>
         <v>41</v>
       </c>
-      <c r="B54" s="155" t="s">
-        <v>115</v>
+      <c r="B54" s="153" t="s">
+        <v>113</v>
       </c>
       <c r="C54" s="100" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D54" s="99" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="E54" s="96">
         <v>0.81</v>
       </c>
       <c r="F54" s="82">
-        <v>56079</v>
-      </c>
-      <c r="G54" s="82">
-        <v>56079</v>
+        <v>60750.41</v>
+      </c>
+      <c r="G54" s="234">
+        <f>F54</f>
+        <v>60750.41</v>
       </c>
       <c r="H54" s="97">
         <f t="shared" si="0"/>
@@ -6277,234 +6250,235 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J54" s="105">
+      <c r="J54" s="104">
         <f t="shared" si="4"/>
-        <v>51187.945788000005</v>
-      </c>
-      <c r="K54" s="105">
+        <v>39744.187218000006</v>
+      </c>
+      <c r="K54" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L54" s="105">
+      <c r="L54" s="104">
         <f t="shared" si="5"/>
         <v>1480.866381</v>
       </c>
-      <c r="M54" s="105">
+      <c r="M54" s="104">
         <f t="shared" si="6"/>
-        <v>8081.1878310000011</v>
-      </c>
-      <c r="N54" s="105"/>
+        <v>10636.530147000001</v>
+      </c>
+      <c r="N54" s="104"/>
       <c r="O54" s="98">
         <f t="shared" si="7"/>
-        <v>60750.41</v>
-      </c>
-      <c r="P54" s="114">
+        <v>51862.41</v>
+      </c>
+      <c r="P54" s="113">
         <f t="shared" si="10"/>
-        <v>62573.41</v>
+        <v>53418.41</v>
       </c>
       <c r="Q54" s="51">
         <f t="shared" si="9"/>
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A55" s="175">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55" s="105">
         <f t="shared" si="11"/>
         <v>42</v>
       </c>
-      <c r="B55" s="176" t="s">
-        <v>116</v>
-      </c>
-      <c r="C55" s="177" t="s">
-        <v>146</v>
+      <c r="B55" s="153" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" s="100" t="s">
+        <v>144</v>
       </c>
       <c r="D55" s="99" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="E55" s="96">
         <v>0.77</v>
       </c>
       <c r="F55" s="82">
-        <v>53310</v>
-      </c>
-      <c r="G55" s="82">
-        <v>53310</v>
+        <v>57750.42</v>
+      </c>
+      <c r="G55" s="234">
+        <f>F55</f>
+        <v>57750.42</v>
       </c>
       <c r="H55" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I55" s="97"/>
-      <c r="J55" s="105">
+      <c r="J55" s="104">
         <f t="shared" si="4"/>
-        <v>48660.145996000007</v>
-      </c>
-      <c r="K55" s="105">
+        <v>37781.511306</v>
+      </c>
+      <c r="K55" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L55" s="105">
+      <c r="L55" s="104">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M55" s="105">
+      <c r="M55" s="104">
         <f t="shared" si="6"/>
-        <v>7682.1168269999998</v>
-      </c>
-      <c r="N55" s="105"/>
+        <v>10111.269399000001</v>
+      </c>
+      <c r="N55" s="104"/>
       <c r="O55" s="98">
         <f t="shared" si="7"/>
-        <v>57750.42</v>
-      </c>
-      <c r="P55" s="114">
+        <v>49301.42</v>
+      </c>
+      <c r="P55" s="113">
         <f t="shared" si="10"/>
-        <v>59483.42</v>
+        <v>50780.42</v>
       </c>
       <c r="Q55" s="51">
         <f t="shared" si="9"/>
         <v>0.42000000000000021</v>
       </c>
       <c r="R55" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A56" s="106">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" s="105">
         <f t="shared" si="11"/>
         <v>43</v>
       </c>
-      <c r="B56" s="155" t="s">
-        <v>117</v>
+      <c r="B56" s="153" t="s">
+        <v>115</v>
       </c>
       <c r="C56" s="100" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D56" s="99"/>
       <c r="E56" s="96">
         <v>0.77</v>
       </c>
       <c r="F56" s="82">
-        <v>116597</v>
+        <v>177845.43</v>
       </c>
       <c r="G56" s="82"/>
       <c r="H56" s="97">
         <f t="shared" si="0"/>
-        <v>116597</v>
+        <v>177845.43</v>
       </c>
       <c r="I56" s="97">
         <f t="shared" si="3"/>
-        <v>3497.91</v>
-      </c>
-      <c r="J56" s="105">
+        <v>5335.3628999999992</v>
+      </c>
+      <c r="J56" s="104">
         <f t="shared" si="4"/>
-        <v>48660.145996000007</v>
-      </c>
-      <c r="K56" s="105">
+        <v>37781.511306</v>
+      </c>
+      <c r="K56" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L56" s="105">
+      <c r="L56" s="104">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M56" s="105">
+      <c r="M56" s="104">
         <f t="shared" si="6"/>
-        <v>7682.1168269999998</v>
-      </c>
-      <c r="N56" s="105"/>
+        <v>10111.269399000001</v>
+      </c>
+      <c r="N56" s="104"/>
       <c r="O56" s="98">
         <f t="shared" si="7"/>
-        <v>177845.43</v>
-      </c>
-      <c r="P56" s="114">
+        <v>232481.43</v>
+      </c>
+      <c r="P56" s="113">
         <f t="shared" si="10"/>
-        <v>183180.43</v>
+        <v>239455.43</v>
       </c>
       <c r="Q56" s="51">
         <f t="shared" si="9"/>
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A57" s="106">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A57" s="105">
         <f t="shared" si="11"/>
         <v>44</v>
       </c>
-      <c r="B57" s="155" t="s">
-        <v>118</v>
+      <c r="B57" s="153" t="s">
+        <v>116</v>
       </c>
       <c r="C57" s="100" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D57" s="99"/>
       <c r="E57" s="96">
         <v>0.77</v>
       </c>
       <c r="F57" s="82">
-        <v>53217</v>
+        <v>112564.44</v>
       </c>
       <c r="G57" s="82"/>
       <c r="H57" s="97">
         <f t="shared" si="0"/>
-        <v>53217</v>
+        <v>112564.44</v>
       </c>
       <c r="I57" s="97">
         <f t="shared" si="3"/>
-        <v>1596.51</v>
-      </c>
-      <c r="J57" s="105">
+        <v>3376.9331999999999</v>
+      </c>
+      <c r="J57" s="104">
         <f t="shared" si="4"/>
-        <v>48660.145996000007</v>
-      </c>
-      <c r="K57" s="105">
+        <v>37781.511306</v>
+      </c>
+      <c r="K57" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L57" s="105">
+      <c r="L57" s="104">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M57" s="105">
+      <c r="M57" s="104">
         <f t="shared" si="6"/>
-        <v>7682.1168269999998</v>
-      </c>
-      <c r="N57" s="105"/>
+        <v>10111.269399000001</v>
+      </c>
+      <c r="N57" s="104"/>
       <c r="O57" s="98">
         <f t="shared" si="7"/>
-        <v>112564.44</v>
-      </c>
-      <c r="P57" s="114">
+        <v>165242.44</v>
+      </c>
+      <c r="P57" s="113">
         <f t="shared" si="10"/>
-        <v>115941.44</v>
+        <v>170199.44</v>
       </c>
       <c r="Q57" s="51">
         <f t="shared" si="9"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A58" s="106">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" s="105">
         <f t="shared" si="11"/>
         <v>45</v>
       </c>
-      <c r="B58" s="155" t="s">
-        <v>119</v>
+      <c r="B58" s="153" t="s">
+        <v>117</v>
       </c>
       <c r="C58" s="100" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D58" s="99" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="E58" s="96">
         <v>0.77</v>
       </c>
       <c r="F58" s="82">
-        <v>53310</v>
-      </c>
-      <c r="G58" s="82">
+        <v>57750.45</v>
+      </c>
+      <c r="G58" s="234">
         <f>F58</f>
-        <v>53310</v>
+        <v>57750.45</v>
       </c>
       <c r="H58" s="97">
         <f t="shared" si="0"/>
@@ -6514,101 +6488,101 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J58" s="105">
+      <c r="J58" s="104">
         <f t="shared" si="4"/>
-        <v>48660.145996000007</v>
-      </c>
-      <c r="K58" s="105">
+        <v>37781.511306</v>
+      </c>
+      <c r="K58" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L58" s="105">
+      <c r="L58" s="104">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M58" s="105">
+      <c r="M58" s="104">
         <f t="shared" si="6"/>
-        <v>7682.1168269999998</v>
-      </c>
-      <c r="N58" s="105"/>
+        <v>10111.269399000001</v>
+      </c>
+      <c r="N58" s="104"/>
       <c r="O58" s="98">
         <f t="shared" si="7"/>
-        <v>57750.45</v>
-      </c>
-      <c r="P58" s="114">
+        <v>49301.45</v>
+      </c>
+      <c r="P58" s="113">
         <f t="shared" si="10"/>
-        <v>59483.45</v>
+        <v>50780.45</v>
       </c>
       <c r="Q58" s="51">
         <f t="shared" si="9"/>
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A59" s="106">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" s="105">
         <f t="shared" si="11"/>
         <v>46</v>
       </c>
-      <c r="B59" s="155" t="s">
-        <v>120</v>
+      <c r="B59" s="153" t="s">
+        <v>118</v>
       </c>
       <c r="C59" s="100" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D59" s="99"/>
       <c r="E59" s="96">
         <v>0.86</v>
       </c>
       <c r="F59" s="82">
-        <v>61615</v>
+        <v>71628.460000000006</v>
       </c>
       <c r="G59" s="82">
-        <v>54695</v>
+        <v>0</v>
       </c>
       <c r="H59" s="97">
         <f t="shared" si="0"/>
-        <v>6920</v>
+        <v>71628.460000000006</v>
       </c>
       <c r="I59" s="97">
         <f t="shared" si="3"/>
-        <v>207.6</v>
-      </c>
-      <c r="J59" s="105">
+        <v>2148.8538000000003</v>
+      </c>
+      <c r="J59" s="104">
         <f t="shared" si="4"/>
-        <v>54347.695528000004</v>
-      </c>
-      <c r="K59" s="105">
+        <v>42197.532108000007</v>
+      </c>
+      <c r="K59" s="104">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L59" s="105">
+      <c r="L59" s="104">
         <f t="shared" si="5"/>
         <v>1572.2778860000001</v>
       </c>
-      <c r="M59" s="105">
+      <c r="M59" s="104">
         <f t="shared" si="6"/>
-        <v>8580.026586</v>
-      </c>
-      <c r="N59" s="105"/>
+        <v>11293.106082000002</v>
+      </c>
+      <c r="N59" s="104"/>
       <c r="O59" s="98">
         <f t="shared" si="7"/>
-        <v>71628.460000000006</v>
-      </c>
-      <c r="P59" s="114">
+        <v>128840.46</v>
+      </c>
+      <c r="P59" s="113">
         <f t="shared" si="10"/>
-        <v>73777.460000000006</v>
+        <v>132705.46000000002</v>
       </c>
       <c r="Q59" s="51">
         <f t="shared" si="9"/>
         <v>0.46000000000000024</v>
       </c>
       <c r="R59" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A60" s="106"/>
-      <c r="B60" s="155"/>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="105"/>
+      <c r="B60" s="153"/>
       <c r="C60" s="94"/>
       <c r="D60" s="99"/>
       <c r="E60" s="96"/>
@@ -6616,165 +6590,169 @@
       <c r="G60" s="82"/>
       <c r="H60" s="97"/>
       <c r="I60" s="97"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="105"/>
-      <c r="L60" s="105"/>
-      <c r="M60" s="105"/>
-      <c r="N60" s="105"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="104"/>
+      <c r="L60" s="104"/>
+      <c r="M60" s="104"/>
+      <c r="N60" s="104"/>
       <c r="O60" s="98"/>
-      <c r="P60" s="114"/>
+      <c r="P60" s="113"/>
       <c r="Q60" s="51"/>
     </row>
-    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="107"/>
-      <c r="B61" s="156"/>
-      <c r="C61" s="108"/>
-      <c r="D61" s="108"/>
-      <c r="E61" s="109">
+    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="106"/>
+      <c r="B61" s="154"/>
+      <c r="C61" s="107"/>
+      <c r="D61" s="107"/>
+      <c r="E61" s="108">
         <f t="shared" ref="E61:M61" si="13">SUM(E14:E60)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F61" s="110">
+      <c r="F61" s="109">
         <f t="shared" si="13"/>
-        <v>8670136</v>
-      </c>
-      <c r="G61" s="111">
+        <v>9639381.8099999987</v>
+      </c>
+      <c r="G61" s="110">
+        <f>SUM(G14:G60)</f>
+        <v>6991775.4199999999</v>
+      </c>
+      <c r="H61" s="110">
         <f t="shared" si="13"/>
-        <v>6601052</v>
-      </c>
-      <c r="H61" s="111">
+        <v>2647606.39</v>
+      </c>
+      <c r="I61" s="110">
         <f t="shared" si="13"/>
-        <v>2069084</v>
-      </c>
-      <c r="I61" s="111">
+        <v>85208.790299999979</v>
+      </c>
+      <c r="J61" s="111">
         <f t="shared" si="13"/>
-        <v>62377.62000000001</v>
-      </c>
-      <c r="J61" s="112">
+        <v>4906689.7799999956</v>
+      </c>
+      <c r="K61" s="111">
         <f t="shared" si="13"/>
-        <v>6319499.4799999995</v>
-      </c>
-      <c r="K61" s="112">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="L61" s="112">
+        <v>0</v>
+      </c>
+      <c r="L61" s="111">
         <f t="shared" si="13"/>
         <v>182823.00999999992</v>
       </c>
-      <c r="M61" s="112">
+      <c r="M61" s="111">
         <f t="shared" si="13"/>
-        <v>997677.51000000013</v>
-      </c>
-      <c r="N61" s="113"/>
-      <c r="O61" s="118">
+        <v>1313151.8700000008</v>
+      </c>
+      <c r="N61" s="112"/>
+      <c r="O61" s="117">
         <f>SUM(O14:O60)</f>
-        <v>9631474.8099999987</v>
-      </c>
-      <c r="P61" s="115">
+        <v>9135494.8100000005</v>
+      </c>
+      <c r="P61" s="114">
         <f>SUM(P14:P60)</f>
-        <v>9920424.8099999987</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9409558.8100000005</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="83"/>
       <c r="D62" s="83"/>
     </row>
-    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="201" t="s">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="201"/>
-      <c r="E64" s="201"/>
-      <c r="F64" s="201"/>
-      <c r="G64" s="201"/>
-      <c r="H64" s="201"/>
-      <c r="I64" s="201"/>
-      <c r="J64" s="201"/>
-      <c r="K64" s="201"/>
-      <c r="L64" s="201"/>
-      <c r="M64" s="201"/>
-      <c r="N64" s="201"/>
-      <c r="O64" s="201"/>
-    </row>
-    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="201"/>
-      <c r="D65" s="201"/>
-      <c r="E65" s="201"/>
-      <c r="F65" s="201"/>
-      <c r="G65" s="201"/>
-      <c r="H65" s="201"/>
-      <c r="I65" s="201"/>
-      <c r="J65" s="201"/>
-      <c r="K65" s="201"/>
-      <c r="L65" s="201"/>
-      <c r="M65" s="201"/>
-      <c r="N65" s="201"/>
-      <c r="O65" s="201"/>
-    </row>
-    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="201"/>
-      <c r="D66" s="201"/>
-      <c r="E66" s="201"/>
-      <c r="F66" s="201"/>
-      <c r="G66" s="201"/>
-      <c r="H66" s="201"/>
-      <c r="I66" s="201"/>
-      <c r="J66" s="201"/>
-      <c r="K66" s="201"/>
-      <c r="L66" s="201"/>
-      <c r="M66" s="201"/>
-      <c r="N66" s="201"/>
-      <c r="O66" s="201"/>
-    </row>
-    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C67" s="201"/>
-      <c r="D67" s="201"/>
-      <c r="E67" s="201"/>
-      <c r="F67" s="201"/>
-      <c r="G67" s="201"/>
-      <c r="H67" s="201"/>
-      <c r="I67" s="201"/>
-      <c r="J67" s="201"/>
-      <c r="K67" s="201"/>
-      <c r="L67" s="201"/>
-      <c r="M67" s="201"/>
-      <c r="N67" s="201"/>
-      <c r="O67" s="201"/>
-    </row>
-    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="201"/>
-      <c r="D68" s="201"/>
-      <c r="E68" s="201"/>
-      <c r="F68" s="201"/>
-      <c r="G68" s="201"/>
-      <c r="H68" s="201"/>
-      <c r="I68" s="201"/>
-      <c r="J68" s="201"/>
-      <c r="K68" s="201"/>
-      <c r="L68" s="201"/>
-      <c r="M68" s="201"/>
-      <c r="N68" s="201"/>
-      <c r="O68" s="201"/>
-    </row>
-    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="201"/>
-      <c r="D69" s="201"/>
-      <c r="E69" s="201"/>
-      <c r="F69" s="201"/>
-      <c r="G69" s="201"/>
-      <c r="H69" s="201"/>
-      <c r="I69" s="201"/>
-      <c r="J69" s="201"/>
-      <c r="K69" s="201"/>
-      <c r="L69" s="201"/>
-      <c r="M69" s="201"/>
-      <c r="N69" s="201"/>
-      <c r="O69" s="201"/>
+      <c r="D64" s="203"/>
+      <c r="E64" s="203"/>
+      <c r="F64" s="203"/>
+      <c r="G64" s="203"/>
+      <c r="H64" s="203"/>
+      <c r="I64" s="203"/>
+      <c r="J64" s="203"/>
+      <c r="K64" s="203"/>
+      <c r="L64" s="203"/>
+      <c r="M64" s="203"/>
+      <c r="N64" s="203"/>
+      <c r="O64" s="203"/>
+    </row>
+    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="203"/>
+      <c r="D65" s="203"/>
+      <c r="E65" s="203"/>
+      <c r="F65" s="203"/>
+      <c r="G65" s="203"/>
+      <c r="H65" s="203"/>
+      <c r="I65" s="203"/>
+      <c r="J65" s="203"/>
+      <c r="K65" s="203"/>
+      <c r="L65" s="203"/>
+      <c r="M65" s="203"/>
+      <c r="N65" s="203"/>
+      <c r="O65" s="203"/>
+    </row>
+    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="203"/>
+      <c r="D66" s="203"/>
+      <c r="E66" s="203"/>
+      <c r="F66" s="203"/>
+      <c r="G66" s="203"/>
+      <c r="H66" s="203"/>
+      <c r="I66" s="203"/>
+      <c r="J66" s="203"/>
+      <c r="K66" s="203"/>
+      <c r="L66" s="203"/>
+      <c r="M66" s="203"/>
+      <c r="N66" s="203"/>
+      <c r="O66" s="203"/>
+    </row>
+    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="203"/>
+      <c r="D67" s="203"/>
+      <c r="E67" s="203"/>
+      <c r="F67" s="203"/>
+      <c r="G67" s="203"/>
+      <c r="H67" s="203"/>
+      <c r="I67" s="203"/>
+      <c r="J67" s="203"/>
+      <c r="K67" s="203"/>
+      <c r="L67" s="203"/>
+      <c r="M67" s="203"/>
+      <c r="N67" s="203"/>
+      <c r="O67" s="203"/>
+    </row>
+    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="203"/>
+      <c r="D68" s="203"/>
+      <c r="E68" s="203"/>
+      <c r="F68" s="203"/>
+      <c r="G68" s="203"/>
+      <c r="H68" s="203"/>
+      <c r="I68" s="203"/>
+      <c r="J68" s="203"/>
+      <c r="K68" s="203"/>
+      <c r="L68" s="203"/>
+      <c r="M68" s="203"/>
+      <c r="N68" s="203"/>
+      <c r="O68" s="203"/>
+    </row>
+    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="203"/>
+      <c r="D69" s="203"/>
+      <c r="E69" s="203"/>
+      <c r="F69" s="203"/>
+      <c r="G69" s="203"/>
+      <c r="H69" s="203"/>
+      <c r="I69" s="203"/>
+      <c r="J69" s="203"/>
+      <c r="K69" s="203"/>
+      <c r="L69" s="203"/>
+      <c r="M69" s="203"/>
+      <c r="N69" s="203"/>
+      <c r="O69" s="203"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="J1:P5"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="P12:P13"/>
@@ -6791,10 +6769,6 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6804,178 +6778,190 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="C3:L17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="C3:M17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="21"/>
     </row>
-    <row r="4" spans="3:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="140" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="141">
+    <row r="4" spans="3:13" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="138" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="139">
         <v>1</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137"/>
-      <c r="I4" s="137"/>
-      <c r="J4" s="138"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="136"/>
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
     </row>
-    <row r="5" spans="3:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="142" t="s">
+    <row r="5" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="140" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="141"/>
+      <c r="E5" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="143"/>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>56</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J5" s="137"/>
+      <c r="K5" s="233"/>
+      <c r="L5" s="21"/>
+    </row>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C6" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="H5" t="s">
-        <v>203</v>
-      </c>
-      <c r="J5" s="139"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C6" s="142" t="s">
+      <c r="D6" s="141" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="143" t="s">
+      <c r="E6" t="s">
         <v>59</v>
-      </c>
-      <c r="E6" t="s">
-        <v>60</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>202</v>
-      </c>
-      <c r="J6" s="139"/>
-      <c r="K6" s="21"/>
+        <v>176</v>
+      </c>
+      <c r="J6" s="137"/>
+      <c r="K6" s="233"/>
       <c r="L6" s="21"/>
     </row>
-    <row r="7" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="J7" s="139"/>
-      <c r="K7" s="21"/>
+        <v>60</v>
+      </c>
+      <c r="J7" s="137"/>
+      <c r="K7" s="233"/>
       <c r="L7" s="21"/>
     </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C8" s="236" t="s">
-        <v>204</v>
-      </c>
-      <c r="D8" s="237"/>
-      <c r="E8" s="237"/>
-      <c r="F8" s="237"/>
-      <c r="G8" s="237"/>
-      <c r="H8" s="237"/>
-      <c r="I8" s="237"/>
-      <c r="J8" s="238"/>
+    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C8" s="227" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="228"/>
+      <c r="E8" s="228"/>
+      <c r="F8" s="228"/>
+      <c r="G8" s="228"/>
+      <c r="H8" s="228"/>
+      <c r="I8" s="228"/>
+      <c r="J8" s="229"/>
       <c r="K8" s="21"/>
       <c r="L8" s="21"/>
     </row>
-    <row r="9" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="239"/>
-      <c r="D9" s="240"/>
-      <c r="E9" s="240"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="240"/>
-      <c r="I9" s="240"/>
-      <c r="J9" s="241"/>
-    </row>
-    <row r="11" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C12" s="182" t="s">
+    <row r="9" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="230"/>
+      <c r="D9" s="231"/>
+      <c r="E9" s="231"/>
+      <c r="F9" s="231"/>
+      <c r="G9" s="231"/>
+      <c r="H9" s="231"/>
+      <c r="I9" s="231"/>
+      <c r="J9" s="232"/>
+    </row>
+    <row r="11" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C12" s="172" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="173">
+        <v>1</v>
+      </c>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="136"/>
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C13" s="174" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="183">
-        <v>1</v>
-      </c>
-      <c r="E12" s="137"/>
-      <c r="F12" s="137"/>
-      <c r="G12" s="137"/>
-      <c r="H12" s="137"/>
-      <c r="I12" s="137"/>
-      <c r="J12" s="138"/>
-    </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C13" s="184" t="s">
+      <c r="D13" s="175"/>
+      <c r="E13" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="185"/>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>56</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
+        <v>180</v>
+      </c>
+      <c r="J13" s="137"/>
+      <c r="K13" s="233"/>
+      <c r="L13" s="233"/>
+      <c r="M13" s="233"/>
+    </row>
+    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C14" s="174" t="s">
         <v>57</v>
       </c>
-      <c r="H13" t="s">
-        <v>206</v>
-      </c>
-      <c r="J13" s="139"/>
-    </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C14" s="184" t="s">
+      <c r="D14" s="175" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="185" t="s">
+      <c r="E14" t="s">
         <v>59</v>
-      </c>
-      <c r="E14" t="s">
-        <v>60</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
       </c>
       <c r="H14" t="s">
-        <v>207</v>
-      </c>
-      <c r="J14" s="139"/>
-    </row>
-    <row r="15" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>181</v>
+      </c>
+      <c r="J14" s="137"/>
+      <c r="K14" s="233"/>
+      <c r="L14" s="233"/>
+      <c r="M14" s="233"/>
+    </row>
+    <row r="15" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="J15" s="139"/>
-    </row>
-    <row r="16" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C16" s="236" t="s">
-        <v>208</v>
-      </c>
-      <c r="D16" s="237"/>
-      <c r="E16" s="237"/>
-      <c r="F16" s="237"/>
-      <c r="G16" s="237"/>
-      <c r="H16" s="237"/>
-      <c r="I16" s="237"/>
-      <c r="J16" s="238"/>
-    </row>
-    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="239"/>
-      <c r="D17" s="240"/>
-      <c r="E17" s="240"/>
-      <c r="F17" s="240"/>
-      <c r="G17" s="240"/>
-      <c r="H17" s="240"/>
-      <c r="I17" s="240"/>
-      <c r="J17" s="241"/>
+        <v>60</v>
+      </c>
+      <c r="J15" s="137"/>
+      <c r="K15" s="233"/>
+      <c r="L15" s="233"/>
+      <c r="M15" s="233"/>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C16" s="227" t="s">
+        <v>182</v>
+      </c>
+      <c r="D16" s="228"/>
+      <c r="E16" s="228"/>
+      <c r="F16" s="228"/>
+      <c r="G16" s="228"/>
+      <c r="H16" s="228"/>
+      <c r="I16" s="228"/>
+      <c r="J16" s="229"/>
+      <c r="K16" s="233"/>
+      <c r="L16" s="233"/>
+      <c r="M16" s="233"/>
+    </row>
+    <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="230"/>
+      <c r="D17" s="231"/>
+      <c r="E17" s="231"/>
+      <c r="F17" s="231"/>
+      <c r="G17" s="231"/>
+      <c r="H17" s="231"/>
+      <c r="I17" s="231"/>
+      <c r="J17" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/O HIGGINS 1157/Junio/Junio ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Junio/Junio ohiggins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CC3C6F-B3EF-46CD-B51B-F194E2F036FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3745DE5-2287-4812-AD76-97BD6F8CF30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -187,9 +187,6 @@
     <t>10 A 15HS - EMERGENCIAS 24HS</t>
   </si>
   <si>
-    <t>Gasto particular</t>
-  </si>
-  <si>
     <t>REEMPLAZOS</t>
   </si>
   <si>
@@ -691,6 +688,9 @@
   </si>
   <si>
     <t>Transf 30/06</t>
+  </si>
+  <si>
+    <t>Gasto particular / SUM</t>
   </si>
 </sst>
 </file>
@@ -707,7 +707,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -863,13 +863,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -1465,7 +1458,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1487,56 +1480,32 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="10" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="13" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="13" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="11" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="13" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="11" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="8" fontId="13" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="13" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="15" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="15" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="1" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="15" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1546,13 +1515,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1586,11 +1548,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1680,9 +1637,6 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1703,9 +1657,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1721,12 +1672,6 @@
     </xf>
     <xf numFmtId="8" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1750,177 +1695,7 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="21" fillId="12" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1935,10 +1710,250 @@
     <xf numFmtId="167" fontId="17" fillId="15" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="18" fillId="15" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="18" fillId="15" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="12" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="7" fillId="12" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="12" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="12" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="13" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="13" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="10" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2360,12 +2375,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="184" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="185"/>
+      <c r="B1" s="204" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="205"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -2378,12 +2393,12 @@
     </row>
     <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="186" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="186"/>
-      <c r="D3" s="186"/>
-      <c r="E3" s="187"/>
+      <c r="B3" s="206" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="206"/>
+      <c r="D3" s="206"/>
+      <c r="E3" s="207"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
@@ -2398,10 +2413,10 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2410,7 +2425,7 @@
       <c r="E5" s="11"/>
     </row>
     <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="65" t="s">
         <v>38</v>
       </c>
       <c r="B6" s="8"/>
@@ -2421,49 +2436,49 @@
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="188" t="s">
-        <v>183</v>
-      </c>
-      <c r="C8" s="188"/>
+      <c r="B8" s="208" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="208"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="188"/>
-      <c r="C9" s="188"/>
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="188"/>
-      <c r="C10" s="188"/>
+      <c r="B10" s="208"/>
+      <c r="C10" s="208"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="189" t="s">
-        <v>146</v>
-      </c>
-      <c r="B13" s="189"/>
-      <c r="C13" s="189"/>
-      <c r="D13" s="189"/>
-      <c r="E13" s="189"/>
+      <c r="A13" s="209" t="s">
+        <v>145</v>
+      </c>
+      <c r="B13" s="209"/>
+      <c r="C13" s="209"/>
+      <c r="D13" s="209"/>
+      <c r="E13" s="209"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="189"/>
-      <c r="B14" s="189"/>
-      <c r="C14" s="189"/>
-      <c r="D14" s="189"/>
-      <c r="E14" s="189"/>
+      <c r="A14" s="209"/>
+      <c r="B14" s="209"/>
+      <c r="C14" s="209"/>
+      <c r="D14" s="209"/>
+      <c r="E14" s="209"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="189"/>
-      <c r="B15" s="189"/>
-      <c r="C15" s="189"/>
-      <c r="D15" s="189"/>
-      <c r="E15" s="189"/>
+      <c r="A15" s="209"/>
+      <c r="B15" s="209"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="209"/>
+      <c r="E15" s="209"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="189"/>
-      <c r="B16" s="189"/>
-      <c r="C16" s="189"/>
-      <c r="D16" s="189"/>
-      <c r="E16" s="189"/>
+      <c r="A16" s="209"/>
+      <c r="B16" s="209"/>
+      <c r="C16" s="209"/>
+      <c r="D16" s="209"/>
+      <c r="E16" s="209"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2481,986 +2496,1107 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="119"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="97"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="180" t="s">
-        <v>197</v>
-      </c>
-      <c r="B22" s="181"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="159">
+      <c r="A22" s="210" t="s">
+        <v>196</v>
+      </c>
+      <c r="B22" s="211"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="135">
         <v>1987270.86</v>
       </c>
-      <c r="E22" s="120"/>
-      <c r="H22" s="21"/>
+      <c r="E22" s="98"/>
+      <c r="H22" s="20"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="180" t="s">
+      <c r="A23" s="200" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="181"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="159">
+      <c r="B23" s="201"/>
+      <c r="C23" s="161"/>
+      <c r="D23" s="135">
         <v>-432231.42</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="H23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="38"/>
+      <c r="H23" s="20"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="180" t="s">
+      <c r="A24" s="200" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="181"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="160">
+      <c r="B24" s="201"/>
+      <c r="C24" s="161"/>
+      <c r="D24" s="136">
         <v>0.34</v>
       </c>
-      <c r="E24" s="22"/>
-      <c r="H24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="38"/>
+      <c r="H24" s="20"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="121">
+      <c r="B25" s="162"/>
+      <c r="C25" s="162"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="99">
         <f>SUM(D22:D24)</f>
         <v>1555039.7800000003</v>
       </c>
+      <c r="F25" s="38"/>
     </row>
     <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="122"/>
+      <c r="A26" s="162" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="162"/>
+      <c r="C26" s="162"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="100"/>
+      <c r="F26" s="38"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="133"/>
+      <c r="A27" s="161"/>
+      <c r="B27" s="161"/>
+      <c r="C27" s="161"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="111"/>
+      <c r="F27" s="38"/>
     </row>
     <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="133"/>
+      <c r="A28" s="161"/>
+      <c r="B28" s="161"/>
+      <c r="C28" s="161"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="38"/>
     </row>
     <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="133"/>
+      <c r="A29" s="161"/>
+      <c r="B29" s="161"/>
+      <c r="C29" s="161"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="111"/>
+      <c r="F29" s="38"/>
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="162" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="93"/>
-      <c r="E30" s="124">
+      <c r="B30" s="163"/>
+      <c r="C30" s="163"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="102">
         <f>SUM(D27:D29)</f>
         <v>0</v>
       </c>
+      <c r="F30" s="38"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="122"/>
+      <c r="B31" s="162"/>
+      <c r="C31" s="162"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="38"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" s="85"/>
-      <c r="C32" s="85"/>
-      <c r="D32" s="247">
+      <c r="A32" s="161" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="164"/>
+      <c r="C32" s="164"/>
+      <c r="D32" s="28">
         <v>589558.79</v>
       </c>
-      <c r="E32" s="123" t="s">
-        <v>196</v>
-      </c>
-      <c r="G32" s="67"/>
+      <c r="E32" s="101" t="s">
+        <v>195</v>
+      </c>
+      <c r="F32" s="38"/>
+      <c r="G32" s="48"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="B33" s="20" t="s">
+      <c r="A33" s="161" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" s="161" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" s="164"/>
+      <c r="D33" s="28">
+        <v>182823.01</v>
+      </c>
+      <c r="E33" s="101" t="s">
         <v>194</v>
       </c>
-      <c r="C33" s="85"/>
-      <c r="D33" s="247">
-        <v>182823.01</v>
-      </c>
-      <c r="E33" s="123" t="s">
-        <v>195</v>
-      </c>
-      <c r="G33" s="67"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="48"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="161" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="85"/>
-      <c r="C34" s="85"/>
-      <c r="D34" s="247">
+      <c r="B34" s="164"/>
+      <c r="C34" s="164"/>
+      <c r="D34" s="28">
         <v>53956.04</v>
       </c>
-      <c r="E34" s="123" t="s">
-        <v>193</v>
-      </c>
-      <c r="G34" s="67"/>
+      <c r="E34" s="101" t="s">
+        <v>192</v>
+      </c>
+      <c r="F34" s="38"/>
+      <c r="G34" s="48"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="161" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="85"/>
-      <c r="C35" s="85"/>
-      <c r="D35" s="247">
+      <c r="B35" s="164"/>
+      <c r="C35" s="164"/>
+      <c r="D35" s="28">
         <v>5995.12</v>
       </c>
-      <c r="E35" s="123" t="str">
+      <c r="E35" s="101" t="str">
         <f>E34</f>
         <v>Debito 12/06</v>
       </c>
-      <c r="G35" s="51"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="40"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="161" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="85"/>
-      <c r="C36" s="85"/>
-      <c r="D36" s="247">
+      <c r="B36" s="164"/>
+      <c r="C36" s="164"/>
+      <c r="D36" s="28">
         <v>97494.97</v>
       </c>
-      <c r="E36" s="123" t="str">
+      <c r="E36" s="101" t="str">
         <f>E34</f>
         <v>Debito 12/06</v>
       </c>
+      <c r="F36" s="38"/>
     </row>
     <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="162" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="42">
+      <c r="B37" s="162"/>
+      <c r="C37" s="162"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="32">
         <f>SUM(D32:D36)</f>
         <v>929827.93</v>
       </c>
+      <c r="F37" s="38"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="124"/>
+      <c r="B38" s="162"/>
+      <c r="C38" s="162"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="102"/>
+      <c r="F38" s="38"/>
     </row>
     <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="177" t="s">
+      <c r="A39" s="212" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="213"/>
+      <c r="C39" s="165"/>
+      <c r="D39" s="166">
+        <v>205033.71</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="F39" s="38"/>
+    </row>
+    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="212" t="s">
         <v>69</v>
       </c>
-      <c r="B39" s="178"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="245">
-        <v>205033.71</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="177" t="s">
-        <v>70</v>
-      </c>
-      <c r="B40" s="178"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="245">
+      <c r="B40" s="213"/>
+      <c r="C40" s="165"/>
+      <c r="D40" s="166">
         <v>12020</v>
       </c>
-      <c r="E40" s="22" t="str">
+      <c r="E40" s="21" t="str">
         <f>E39</f>
         <v>Debito Autom.</v>
       </c>
+      <c r="F40" s="38"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="162" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="42">
+      <c r="B41" s="162"/>
+      <c r="C41" s="162"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="32">
         <f>SUM(D39:D40)</f>
         <v>217053.71</v>
       </c>
+      <c r="F41" s="38"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="125"/>
+      <c r="B42" s="163"/>
+      <c r="C42" s="163"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="103"/>
+      <c r="F42" s="38"/>
     </row>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="246">
+      <c r="A43" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="B43" s="33"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="134">
         <v>1313151.8700000001</v>
       </c>
-      <c r="E43" s="35" t="s">
+      <c r="E43" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="F43" s="38"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="167"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="134">
+        <v>0</v>
+      </c>
+      <c r="E44" s="27"/>
+      <c r="F44" s="38"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="212" t="s">
+        <v>67</v>
+      </c>
+      <c r="B45" s="213"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="134">
+        <v>511264.75</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="F45" s="38"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="168" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" s="169" t="s">
+        <v>191</v>
+      </c>
+      <c r="C46" s="33"/>
+      <c r="D46" s="134">
+        <v>62785.37</v>
+      </c>
+      <c r="E46" s="27" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="B44" s="32"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="176">
-        <v>0</v>
-      </c>
-      <c r="E44" s="35"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="177" t="s">
-        <v>68</v>
-      </c>
-      <c r="B45" s="178"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="246">
-        <v>511264.75</v>
-      </c>
-      <c r="E45" s="35" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B46" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="C46" s="31"/>
-      <c r="D46" s="246">
-        <v>62785.37</v>
-      </c>
-      <c r="E46" s="35" t="s">
-        <v>191</v>
-      </c>
+      <c r="F46" s="38"/>
     </row>
     <row r="47" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="162" t="s">
         <v>12</v>
       </c>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="126">
+      <c r="B47" s="162"/>
+      <c r="C47" s="162"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="104">
         <f>SUM(D43:D46)</f>
         <v>1887201.9900000002</v>
       </c>
+      <c r="F47" s="38"/>
     </row>
     <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="127"/>
+      <c r="A48" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B48" s="162"/>
+      <c r="C48" s="162"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="105"/>
+      <c r="F48" s="38"/>
     </row>
     <row r="49" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="180" t="s">
-        <v>198</v>
-      </c>
-      <c r="B49" s="181"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="158">
-        <v>0</v>
-      </c>
-      <c r="E49" s="35"/>
+      <c r="A49" s="200" t="s">
+        <v>197</v>
+      </c>
+      <c r="B49" s="201"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="134">
+        <v>0</v>
+      </c>
+      <c r="E49" s="27"/>
+      <c r="F49" s="38"/>
     </row>
     <row r="50" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="155" t="s">
+      <c r="A50" s="170" t="s">
+        <v>184</v>
+      </c>
+      <c r="B50" s="171"/>
+      <c r="C50" s="161"/>
+      <c r="D50" s="134">
+        <v>332362.82</v>
+      </c>
+      <c r="E50" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="B50" s="19"/>
-      <c r="C50" s="20"/>
-      <c r="D50" s="246">
-        <v>332362.82</v>
-      </c>
-      <c r="E50" s="35" t="s">
+      <c r="F50" s="138"/>
+    </row>
+    <row r="51" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="172" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="51"/>
-    </row>
-    <row r="51" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="87" t="s">
+      <c r="B51" s="171"/>
+      <c r="C51" s="161"/>
+      <c r="D51" s="134">
+        <v>810000</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="F51" s="138"/>
+    </row>
+    <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="214" t="s">
         <v>187</v>
       </c>
-      <c r="B51" s="19"/>
-      <c r="C51" s="20"/>
-      <c r="D51" s="246">
-        <v>810000</v>
-      </c>
-      <c r="E51" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="F51" s="51"/>
-    </row>
-    <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="190" t="s">
+      <c r="B52" s="215"/>
+      <c r="C52" s="161"/>
+      <c r="D52" s="134">
+        <v>180000</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="F52" s="138"/>
+    </row>
+    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="172" t="s">
         <v>188</v>
       </c>
-      <c r="B52" s="191"/>
-      <c r="C52" s="20"/>
-      <c r="D52" s="246">
-        <v>180000</v>
-      </c>
-      <c r="E52" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="F52" s="51"/>
-    </row>
-    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="87" t="s">
+      <c r="B53" s="171"/>
+      <c r="C53" s="161"/>
+      <c r="D53" s="134">
+        <v>60000</v>
+      </c>
+      <c r="E53" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="B53" s="19"/>
-      <c r="C53" s="20"/>
-      <c r="D53" s="246">
-        <v>60000</v>
-      </c>
-      <c r="E53" s="35" t="s">
-        <v>190</v>
-      </c>
+      <c r="F53" s="38"/>
     </row>
     <row r="54" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="180" t="s">
+      <c r="A54" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="B54" s="201"/>
+      <c r="C54" s="161"/>
+      <c r="D54" s="134">
+        <v>40000</v>
+      </c>
+      <c r="E54" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="B54" s="181"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="246">
-        <v>40000</v>
-      </c>
-      <c r="E54" s="35" t="s">
-        <v>215</v>
-      </c>
+      <c r="F54" s="38"/>
     </row>
     <row r="55" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="87" t="s">
-        <v>150</v>
-      </c>
-      <c r="B55" s="19"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="246">
+      <c r="A55" s="172" t="s">
+        <v>149</v>
+      </c>
+      <c r="B55" s="171"/>
+      <c r="C55" s="161"/>
+      <c r="D55" s="134">
         <v>31000</v>
       </c>
-      <c r="E55" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="F55" s="51"/>
+      <c r="E55" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="F55" s="138"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="42">
+      <c r="A56" s="162" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="32">
         <f>SUM(D49:D55)</f>
         <v>1453362.82</v>
       </c>
+      <c r="F56" s="38"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
       <c r="D57" s="18"/>
-      <c r="E57" s="119"/>
+      <c r="E57" s="97"/>
+      <c r="F57" s="38"/>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="180" t="s">
+      <c r="A58" s="200" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" s="201"/>
+      <c r="C58" s="161"/>
+      <c r="D58" s="137">
+        <v>0</v>
+      </c>
+      <c r="E58" s="98"/>
+      <c r="F58" s="38"/>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="172" t="s">
+        <v>150</v>
+      </c>
+      <c r="B59" s="171" t="s">
         <v>199</v>
       </c>
-      <c r="B58" s="181"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="161">
-        <v>0</v>
-      </c>
-      <c r="E58" s="120"/>
-    </row>
-    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="87" t="s">
-        <v>151</v>
-      </c>
-      <c r="B59" s="19" t="s">
+      <c r="C59" s="161"/>
+      <c r="D59" s="133">
+        <v>0</v>
+      </c>
+      <c r="E59" s="98"/>
+      <c r="F59" s="38"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="162" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" s="162"/>
+      <c r="C60" s="162"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="99">
+        <f>SUM(D58:D59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="38"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" s="173"/>
+      <c r="C61" s="162"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="38"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="174"/>
+      <c r="C62" s="174"/>
+      <c r="D62" s="175">
+        <v>69000</v>
+      </c>
+      <c r="E62" s="106"/>
+      <c r="F62" s="38"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="C59" s="20"/>
-      <c r="D59" s="157">
-        <v>0</v>
-      </c>
-      <c r="E59" s="120"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="23" t="s">
+      <c r="B63" s="174"/>
+      <c r="C63" s="174"/>
+      <c r="D63" s="175">
+        <v>109681.94</v>
+      </c>
+      <c r="E63" s="106"/>
+      <c r="F63" s="38"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="176" t="s">
         <v>8</v>
       </c>
-      <c r="B60" s="23"/>
-      <c r="C60" s="23"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="121">
-        <f>SUM(D58:D59)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B61" s="38"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="39"/>
-      <c r="E61" s="42"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="B62" s="86"/>
-      <c r="C62" s="86"/>
-      <c r="D62" s="248">
-        <v>69000</v>
-      </c>
-      <c r="E62" s="128"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="31" t="s">
-        <v>201</v>
-      </c>
-      <c r="B63" s="86"/>
-      <c r="C63" s="86"/>
-      <c r="D63" s="248">
-        <f>102445.07+3388</f>
-        <v>105833.07</v>
-      </c>
-      <c r="E63" s="128"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="B64" s="40"/>
-      <c r="C64" s="40"/>
-      <c r="D64" s="41"/>
-      <c r="E64" s="42">
+      <c r="B64" s="176"/>
+      <c r="C64" s="176"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="32">
         <f>SUM(D62:D63)</f>
-        <v>174833.07</v>
-      </c>
+        <v>178681.94</v>
+      </c>
+      <c r="F64" s="38"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="31"/>
-      <c r="B65" s="31"/>
-      <c r="C65" s="31"/>
-      <c r="D65" s="43"/>
-      <c r="E65" s="44"/>
+      <c r="A65" s="33"/>
+      <c r="B65" s="33"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="33"/>
+      <c r="E65" s="34"/>
+      <c r="F65" s="38"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="45" t="s">
+      <c r="A66" s="177" t="s">
         <v>15</v>
       </c>
-      <c r="B66" s="45"/>
-      <c r="C66" s="45"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="47"/>
+      <c r="B66" s="177"/>
+      <c r="C66" s="177"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="38"/>
     </row>
     <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="48"/>
-      <c r="D67" s="49"/>
-      <c r="E67" s="50"/>
-      <c r="F67" s="51"/>
+      <c r="A67" s="178"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="38"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="138"/>
     </row>
     <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="52" t="s">
+      <c r="A68" s="179" t="s">
         <v>16</v>
       </c>
-      <c r="B68" s="53"/>
-      <c r="C68" s="54"/>
-      <c r="D68" s="55"/>
-      <c r="E68" s="56">
+      <c r="B68" s="180"/>
+      <c r="C68" s="41"/>
+      <c r="D68" s="41"/>
+      <c r="E68" s="42">
         <f>(SUM(E21:E66))</f>
-        <v>6217319.3000000007</v>
-      </c>
-      <c r="F68" s="57"/>
-      <c r="G68" s="51"/>
+        <v>6221168.1700000009</v>
+      </c>
+      <c r="F68" s="181"/>
+      <c r="G68" s="40"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D69" s="49"/>
-      <c r="E69" s="49"/>
+      <c r="A69" s="38"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="38"/>
     </row>
     <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D70" s="49"/>
-      <c r="E70" s="49"/>
-      <c r="H70" s="58"/>
+      <c r="A70" s="38"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="H70" s="44"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
+      <c r="A71" s="182" t="s">
         <v>17</v>
       </c>
-      <c r="B71" s="13"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="59"/>
-      <c r="E71" s="60"/>
+      <c r="B71" s="183"/>
+      <c r="C71" s="184"/>
+      <c r="D71" s="45"/>
+      <c r="E71" s="46"/>
+      <c r="F71" s="38"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="182"/>
-      <c r="B72" s="183"/>
-      <c r="C72" s="31"/>
-      <c r="D72" s="142"/>
-      <c r="E72" s="143"/>
+      <c r="A72" s="202"/>
+      <c r="B72" s="203"/>
+      <c r="C72" s="33"/>
+      <c r="D72" s="185"/>
+      <c r="E72" s="120"/>
+      <c r="F72" s="38"/>
     </row>
     <row r="73" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D73" s="43"/>
-      <c r="E73" s="43"/>
+      <c r="A73" s="38"/>
+      <c r="B73" s="38"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="33"/>
+      <c r="E73" s="33"/>
+      <c r="F73" s="38"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="26"/>
-      <c r="B74" s="62"/>
-      <c r="C74" s="31"/>
-      <c r="D74" s="36"/>
-      <c r="E74" s="61"/>
+      <c r="A74" s="186"/>
+      <c r="B74" s="187"/>
+      <c r="C74" s="33"/>
+      <c r="D74" s="28"/>
+      <c r="E74" s="47"/>
+      <c r="F74" s="38"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="63" t="s">
+      <c r="A75" s="188" t="s">
         <v>45</v>
       </c>
-      <c r="B75" s="64"/>
-      <c r="C75" s="64"/>
-      <c r="D75" s="102"/>
-      <c r="E75" s="129">
+      <c r="B75" s="189"/>
+      <c r="C75" s="189"/>
+      <c r="D75" s="80"/>
+      <c r="E75" s="107">
         <f>SUM(D72:D74)</f>
         <v>0</v>
       </c>
+      <c r="F75" s="38"/>
     </row>
     <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D76" s="49"/>
-      <c r="E76" s="49"/>
+      <c r="A76" s="38"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="38"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="38"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="45" t="s">
+      <c r="A77" s="177" t="s">
         <v>18</v>
       </c>
-      <c r="B77" s="45"/>
-      <c r="C77" s="45"/>
-      <c r="D77" s="46"/>
-      <c r="E77" s="132">
-        <v>0</v>
-      </c>
+      <c r="B77" s="177"/>
+      <c r="C77" s="177"/>
+      <c r="D77" s="35"/>
+      <c r="E77" s="110">
+        <v>0</v>
+      </c>
+      <c r="F77" s="38"/>
     </row>
     <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D78" s="49"/>
-      <c r="E78" s="49"/>
+      <c r="A78" s="38"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
     </row>
     <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="52" t="s">
+      <c r="A79" s="179" t="s">
         <v>19</v>
       </c>
-      <c r="B79" s="53"/>
-      <c r="C79" s="54"/>
-      <c r="D79" s="55"/>
-      <c r="E79" s="56">
+      <c r="B79" s="180"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="42">
         <f>E75+E77</f>
         <v>0</v>
       </c>
+      <c r="F79" s="38"/>
     </row>
     <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-    </row>
-    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="65" t="s">
+      <c r="A80" s="38"/>
+      <c r="B80" s="38"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="38"/>
+    </row>
+    <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="190" t="s">
         <v>20</v>
       </c>
-      <c r="B81" s="66">
+      <c r="B81" s="191">
         <f>E68</f>
-        <v>6217319.3000000007</v>
-      </c>
-      <c r="D81" s="49"/>
-      <c r="E81" s="49"/>
-    </row>
-    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="65" t="s">
+        <v>6221168.1700000009</v>
+      </c>
+      <c r="C81" s="38"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="38"/>
+    </row>
+    <row r="82" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="190" t="s">
         <v>21</v>
       </c>
-      <c r="B82" s="66">
+      <c r="B82" s="191">
         <f>E68-E66</f>
-        <v>6217319.3000000007</v>
-      </c>
-      <c r="D82" s="49"/>
-      <c r="E82" s="49"/>
-    </row>
-    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="65" t="s">
+        <v>6221168.1700000009</v>
+      </c>
+      <c r="C82" s="38"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="38"/>
+    </row>
+    <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="190" t="s">
         <v>22</v>
       </c>
-      <c r="B83" s="66">
+      <c r="B83" s="191">
         <f>E79-E77</f>
         <v>0</v>
       </c>
-      <c r="D83" s="49"/>
-      <c r="E83" s="49"/>
-    </row>
-    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="65" t="s">
+      <c r="C83" s="38"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="38"/>
+      <c r="F83" s="38"/>
+    </row>
+    <row r="84" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="190" t="s">
         <v>23</v>
       </c>
-      <c r="B84" s="66">
+      <c r="B84" s="191">
         <f>E79</f>
         <v>0</v>
       </c>
-      <c r="D84" s="49"/>
-      <c r="E84" s="49"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D85" s="49"/>
-      <c r="E85" s="49"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D86" s="49"/>
-      <c r="E86" s="49"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="134" t="s">
+      <c r="C84" s="38"/>
+      <c r="D84" s="38"/>
+      <c r="E84" s="38"/>
+      <c r="F84" s="38"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="38"/>
+      <c r="B85" s="38"/>
+      <c r="C85" s="38"/>
+      <c r="D85" s="38"/>
+      <c r="E85" s="38"/>
+      <c r="F85" s="38"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="38"/>
+      <c r="B86" s="38"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="38"/>
+      <c r="F86" s="38"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="192" t="s">
+        <v>210</v>
+      </c>
+      <c r="B87" s="193">
+        <v>0</v>
+      </c>
+      <c r="C87" s="38"/>
+      <c r="D87" s="38"/>
+      <c r="E87" s="38"/>
+      <c r="F87" s="38"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="165" t="s">
         <v>211</v>
       </c>
-      <c r="B87" s="70">
-        <v>0</v>
-      </c>
-      <c r="D87" s="49"/>
-      <c r="E87" s="49"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="B88" s="71">
+      <c r="B88" s="194">
         <v>6500000</v>
       </c>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-    </row>
-    <row r="89" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="28"/>
-      <c r="B89" s="118"/>
-      <c r="D89" s="49"/>
-      <c r="E89" s="49"/>
-    </row>
-    <row r="90" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="73" t="s">
-        <v>203</v>
-      </c>
-      <c r="B90" s="74">
+      <c r="C88" s="38"/>
+      <c r="D88" s="38"/>
+      <c r="E88" s="38"/>
+      <c r="F88" s="38"/>
+    </row>
+    <row r="89" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="165"/>
+      <c r="B89" s="139"/>
+      <c r="C89" s="38"/>
+      <c r="D89" s="38"/>
+      <c r="E89" s="38"/>
+      <c r="F89" s="38"/>
+    </row>
+    <row r="90" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="195" t="s">
+        <v>202</v>
+      </c>
+      <c r="B90" s="196">
         <f>B88</f>
         <v>6500000</v>
       </c>
-      <c r="D90" s="49"/>
-      <c r="E90" s="49"/>
-    </row>
-    <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="162"/>
-      <c r="B91" s="163"/>
-      <c r="D91" s="49"/>
-      <c r="E91" s="49"/>
-    </row>
-    <row r="92" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="162"/>
-      <c r="B92" s="163"/>
-      <c r="D92" s="49"/>
-      <c r="E92" s="49"/>
-    </row>
-    <row r="93" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="134" t="s">
+      <c r="C90" s="38"/>
+      <c r="D90" s="38"/>
+      <c r="E90" s="38"/>
+      <c r="F90" s="38"/>
+    </row>
+    <row r="91" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="197"/>
+      <c r="B91" s="198"/>
+      <c r="C91" s="38"/>
+      <c r="D91" s="38"/>
+      <c r="E91" s="38"/>
+      <c r="F91" s="38"/>
+    </row>
+    <row r="92" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="197"/>
+      <c r="B92" s="198"/>
+      <c r="C92" s="38"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="38"/>
+      <c r="F92" s="38"/>
+    </row>
+    <row r="93" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="192" t="s">
+        <v>163</v>
+      </c>
+      <c r="B93" s="193">
+        <v>231400</v>
+      </c>
+      <c r="C93" s="38"/>
+      <c r="D93" s="38"/>
+      <c r="E93" s="38"/>
+      <c r="F93" s="38"/>
+    </row>
+    <row r="94" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="165" t="s">
         <v>164</v>
       </c>
-      <c r="B93" s="70">
-        <v>231400</v>
-      </c>
-      <c r="D93" s="49"/>
-      <c r="E93" s="49"/>
-    </row>
-    <row r="94" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="28" t="s">
+      <c r="B94" s="194">
+        <v>0</v>
+      </c>
+      <c r="C94" s="38"/>
+      <c r="D94" s="38"/>
+      <c r="E94" s="38"/>
+      <c r="F94" s="38"/>
+    </row>
+    <row r="95" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="165" t="s">
         <v>165</v>
       </c>
-      <c r="B94" s="71">
-        <v>0</v>
-      </c>
-      <c r="D94" s="49"/>
-      <c r="E94" s="49"/>
-    </row>
-    <row r="95" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="B95" s="118"/>
-      <c r="D95" s="49"/>
-      <c r="E95" s="49"/>
-    </row>
-    <row r="96" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="73" t="s">
-        <v>203</v>
-      </c>
-      <c r="B96" s="74">
+      <c r="B95" s="139"/>
+      <c r="C95" s="38"/>
+      <c r="D95" s="38"/>
+      <c r="E95" s="38"/>
+      <c r="F95" s="38"/>
+    </row>
+    <row r="96" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="195" t="s">
+        <v>202</v>
+      </c>
+      <c r="B96" s="196">
         <f>SUM(B93:B95)</f>
         <v>231400</v>
       </c>
-      <c r="D96" s="49"/>
-      <c r="E96" s="49"/>
+      <c r="C96" s="38"/>
+      <c r="D96" s="38"/>
+      <c r="E96" s="38"/>
+      <c r="F96" s="38"/>
     </row>
     <row r="97" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="162"/>
-      <c r="B97" s="163"/>
-      <c r="D97" s="49"/>
-      <c r="E97" s="49"/>
+      <c r="A97" s="197"/>
+      <c r="B97" s="198"/>
+      <c r="C97" s="38"/>
+      <c r="D97" s="38"/>
+      <c r="E97" s="38"/>
+      <c r="F97" s="38"/>
     </row>
     <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="134" t="s">
-        <v>167</v>
-      </c>
-      <c r="B98" s="70">
+      <c r="A98" s="192" t="s">
+        <v>166</v>
+      </c>
+      <c r="B98" s="193">
         <v>64328</v>
       </c>
-      <c r="D98" s="49"/>
-      <c r="E98" s="49"/>
+      <c r="C98" s="38"/>
+      <c r="D98" s="38"/>
+      <c r="E98" s="38"/>
+      <c r="F98" s="38"/>
     </row>
     <row r="99" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="B99" s="71">
-        <v>0</v>
-      </c>
-      <c r="D99" s="49"/>
-      <c r="E99" s="49"/>
+      <c r="A99" s="165" t="s">
+        <v>164</v>
+      </c>
+      <c r="B99" s="194">
+        <v>0</v>
+      </c>
+      <c r="C99" s="38"/>
+      <c r="D99" s="38"/>
+      <c r="E99" s="38"/>
+      <c r="F99" s="38"/>
     </row>
     <row r="100" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="B100" s="118">
+      <c r="A100" s="165" t="s">
+        <v>212</v>
+      </c>
+      <c r="B100" s="139">
         <v>-5910</v>
       </c>
-      <c r="D100" s="49"/>
-      <c r="E100" s="49"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
     </row>
     <row r="101" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="73" t="s">
-        <v>203</v>
-      </c>
-      <c r="B101" s="74">
+      <c r="A101" s="195" t="s">
+        <v>202</v>
+      </c>
+      <c r="B101" s="196">
         <f>SUM(B98:B100)</f>
         <v>58418</v>
       </c>
-      <c r="D101" s="49"/>
-      <c r="E101" s="49"/>
-    </row>
-    <row r="102" spans="1:6" s="69" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="38"/>
+    </row>
+    <row r="102" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
-      <c r="B102" s="67"/>
-      <c r="C102" s="68"/>
-      <c r="D102" s="130"/>
-      <c r="E102" s="130"/>
-    </row>
-    <row r="103" spans="1:6" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="134" t="s">
-        <v>202</v>
-      </c>
-      <c r="B103" s="70">
+      <c r="B102" s="48"/>
+      <c r="C102" s="49"/>
+      <c r="D102" s="108"/>
+      <c r="E102" s="108"/>
+    </row>
+    <row r="103" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="112" t="s">
+        <v>201</v>
+      </c>
+      <c r="B103" s="51">
         <v>3986543.73</v>
       </c>
-      <c r="C103" s="68"/>
-      <c r="D103" s="131"/>
-      <c r="E103" s="131"/>
+      <c r="C103" s="49"/>
+      <c r="D103" s="109"/>
+      <c r="E103" s="109"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="28" t="s">
+      <c r="A104" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B104" s="166">
+      <c r="B104" s="140">
         <f>-B82-B83</f>
-        <v>-6217319.3000000007</v>
-      </c>
-      <c r="D104" s="49"/>
-      <c r="E104" s="49"/>
+        <v>-6221168.1700000009</v>
+      </c>
+      <c r="D104" s="38"/>
+      <c r="E104" s="38"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="28" t="s">
+      <c r="A105" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B105" s="71">
+      <c r="B105" s="52">
         <f>B118</f>
         <v>160000</v>
       </c>
-      <c r="D105" s="49"/>
-      <c r="E105" s="49"/>
-      <c r="F105" s="67"/>
+      <c r="D105" s="38"/>
+      <c r="E105" s="38"/>
+      <c r="F105" s="48"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="28" t="s">
+      <c r="A106" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B106" s="72">
+      <c r="B106" s="53">
         <f>PRORRATEO!G61</f>
         <v>6991775.4199999999</v>
       </c>
-      <c r="D106" s="49"/>
-      <c r="E106" s="49"/>
-      <c r="F106" s="67"/>
+      <c r="D106" s="38"/>
+      <c r="E106" s="38"/>
+      <c r="F106" s="48"/>
     </row>
     <row r="107" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A107" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="B107" s="118">
+      <c r="A107" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="B107" s="96">
         <v>-6500000</v>
       </c>
-      <c r="D107" s="49"/>
-      <c r="E107" s="49"/>
-      <c r="F107" s="67"/>
+      <c r="D107" s="38"/>
+      <c r="E107" s="38"/>
+      <c r="F107" s="48"/>
     </row>
     <row r="108" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A108" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="B108" s="165">
+      <c r="A108" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="B108" s="139">
         <v>2026301.37</v>
       </c>
-      <c r="D108" s="49"/>
-      <c r="E108" s="49"/>
-      <c r="F108" s="67"/>
+      <c r="D108" s="38"/>
+      <c r="E108" s="38"/>
+      <c r="F108" s="48"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="B109" s="118">
+      <c r="A109" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="B109" s="96">
         <v>-4703</v>
       </c>
-      <c r="D109" s="49"/>
-      <c r="E109" s="49"/>
-      <c r="F109" s="67"/>
+      <c r="D109" s="38"/>
+      <c r="E109" s="38"/>
+      <c r="F109" s="48"/>
     </row>
     <row r="110" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="B110" s="118">
+      <c r="A110" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="B110" s="96">
         <v>-156782</v>
       </c>
-      <c r="D110" s="164"/>
-      <c r="E110" s="49"/>
-      <c r="F110" s="67"/>
+      <c r="D110" s="138"/>
+      <c r="E110" s="38"/>
+      <c r="F110" s="48"/>
     </row>
     <row r="111" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="73" t="s">
+      <c r="A111" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="B111" s="74">
+      <c r="B111" s="55">
         <f>SUM(B103:C110)</f>
-        <v>285816.21999999974</v>
-      </c>
-      <c r="D111" s="67"/>
-      <c r="E111" s="51"/>
-      <c r="F111" s="51"/>
+        <v>281967.3499999987</v>
+      </c>
+      <c r="D111" s="48"/>
+      <c r="E111" s="40"/>
+      <c r="F111" s="40"/>
     </row>
     <row r="112" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="113" spans="1:13" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="167" t="s">
-        <v>168</v>
-      </c>
-      <c r="B113" s="168">
+      <c r="A113" s="141" t="s">
+        <v>167</v>
+      </c>
+      <c r="B113" s="142">
         <f>B111+B96</f>
-        <v>517216.21999999974</v>
-      </c>
-      <c r="D113" s="51"/>
-      <c r="E113" s="51"/>
+        <v>513367.3499999987</v>
+      </c>
+      <c r="D113" s="40"/>
+      <c r="E113" s="40"/>
     </row>
     <row r="114" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="179" t="s">
+      <c r="A115" s="199" t="s">
         <v>25</v>
       </c>
-      <c r="B115" s="179"/>
-      <c r="C115" s="179"/>
+      <c r="B115" s="199"/>
+      <c r="C115" s="199"/>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="179"/>
-      <c r="B116" s="179"/>
-      <c r="C116" s="179"/>
+      <c r="A116" s="199"/>
+      <c r="B116" s="199"/>
+      <c r="C116" s="199"/>
     </row>
     <row r="117" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="75" t="s">
-        <v>208</v>
-      </c>
-      <c r="B117" s="101">
+      <c r="A117" s="56" t="s">
+        <v>207</v>
+      </c>
+      <c r="B117" s="79">
         <v>160000</v>
       </c>
-      <c r="C117" s="76"/>
-      <c r="D117" s="57"/>
+      <c r="C117" s="57"/>
+      <c r="D117" s="43"/>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B118" s="78">
+      <c r="A118" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B118" s="59">
         <f>SUM(B117:B117)</f>
         <v>160000</v>
       </c>
-      <c r="C118" s="79"/>
+      <c r="C118" s="60"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M119" s="80"/>
+      <c r="M119" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A115:C116"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A54:B54"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A58:B58"/>
@@ -3473,10 +3609,6 @@
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A115:C116"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A54:B54"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3509,3250 +3641,3248 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88"/>
-      <c r="B1" s="150"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="192" t="str">
+      <c r="A1" s="66"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="242" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="193"/>
+      <c r="K1" s="242"/>
+      <c r="L1" s="242"/>
+      <c r="M1" s="242"/>
+      <c r="N1" s="242"/>
+      <c r="O1" s="242"/>
+      <c r="P1" s="243"/>
     </row>
     <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B2" s="151"/>
-      <c r="C2" s="170">
+        <v>168</v>
+      </c>
+      <c r="B2" s="128"/>
+      <c r="C2" s="144">
         <f>6219841.65-C5</f>
         <v>4906689.78</v>
       </c>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="202"/>
-      <c r="G2" s="202"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="194"/>
-      <c r="K2" s="194"/>
-      <c r="L2" s="194"/>
-      <c r="M2" s="194"/>
-      <c r="N2" s="194"/>
-      <c r="O2" s="194"/>
-      <c r="P2" s="195"/>
-      <c r="Q2" s="81"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="250"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="244"/>
+      <c r="K2" s="244"/>
+      <c r="L2" s="244"/>
+      <c r="M2" s="244"/>
+      <c r="N2" s="244"/>
+      <c r="O2" s="244"/>
+      <c r="P2" s="245"/>
+      <c r="Q2" s="62"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="151"/>
-      <c r="C3" s="170">
-        <v>0</v>
-      </c>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="194"/>
-      <c r="K3" s="194"/>
-      <c r="L3" s="194"/>
-      <c r="M3" s="194"/>
-      <c r="N3" s="194"/>
-      <c r="O3" s="194"/>
-      <c r="P3" s="195"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="51"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="144">
+        <v>0</v>
+      </c>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="244"/>
+      <c r="K3" s="244"/>
+      <c r="L3" s="244"/>
+      <c r="M3" s="244"/>
+      <c r="N3" s="244"/>
+      <c r="O3" s="244"/>
+      <c r="P3" s="245"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="40"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" s="151"/>
-      <c r="C4" s="170">
+        <v>174</v>
+      </c>
+      <c r="B4" s="128"/>
+      <c r="C4" s="144">
         <v>182823.01</v>
       </c>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="156"/>
-      <c r="G4" s="156"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="194"/>
-      <c r="K4" s="194"/>
-      <c r="L4" s="194"/>
-      <c r="M4" s="194"/>
-      <c r="N4" s="194"/>
-      <c r="O4" s="194"/>
-      <c r="P4" s="195"/>
-      <c r="Q4" s="81"/>
-      <c r="R4" s="51"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="M4" s="244"/>
+      <c r="N4" s="244"/>
+      <c r="O4" s="244"/>
+      <c r="P4" s="245"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="40"/>
     </row>
     <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="143" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="129"/>
+      <c r="C5" s="145">
+        <v>1313151.8700000001</v>
+      </c>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="M5" s="246"/>
+      <c r="N5" s="246"/>
+      <c r="O5" s="246"/>
+      <c r="P5" s="247"/>
+      <c r="Q5" s="62"/>
+    </row>
+    <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="217" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" s="218"/>
+      <c r="C6" s="219"/>
+      <c r="D6" s="219"/>
+      <c r="E6" s="219"/>
+      <c r="F6" s="219"/>
+      <c r="G6" s="219"/>
+      <c r="H6" s="219"/>
+      <c r="I6" s="219"/>
+      <c r="J6" s="219"/>
+      <c r="K6" s="219"/>
+      <c r="L6" s="219"/>
+      <c r="M6" s="219"/>
+      <c r="N6" s="219"/>
+      <c r="O6" s="219"/>
+      <c r="P6" s="220"/>
+      <c r="Q6" s="62"/>
+    </row>
+    <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="221"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="222"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="222"/>
+      <c r="F7" s="222"/>
+      <c r="G7" s="222"/>
+      <c r="H7" s="222"/>
+      <c r="I7" s="222"/>
+      <c r="J7" s="222"/>
+      <c r="K7" s="222"/>
+      <c r="L7" s="222"/>
+      <c r="M7" s="222"/>
+      <c r="N7" s="222"/>
+      <c r="O7" s="222"/>
+      <c r="P7" s="223"/>
+      <c r="Q7" s="62"/>
+    </row>
+    <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="221"/>
+      <c r="B8" s="222"/>
+      <c r="C8" s="222"/>
+      <c r="D8" s="222"/>
+      <c r="E8" s="222"/>
+      <c r="F8" s="222"/>
+      <c r="G8" s="222"/>
+      <c r="H8" s="222"/>
+      <c r="I8" s="222"/>
+      <c r="J8" s="222"/>
+      <c r="K8" s="222"/>
+      <c r="L8" s="222"/>
+      <c r="M8" s="222"/>
+      <c r="N8" s="222"/>
+      <c r="O8" s="222"/>
+      <c r="P8" s="223"/>
+      <c r="Q8" s="62"/>
+    </row>
+    <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="221"/>
+      <c r="B9" s="222"/>
+      <c r="C9" s="222"/>
+      <c r="D9" s="222"/>
+      <c r="E9" s="222"/>
+      <c r="F9" s="222"/>
+      <c r="G9" s="222"/>
+      <c r="H9" s="222"/>
+      <c r="I9" s="222"/>
+      <c r="J9" s="222"/>
+      <c r="K9" s="222"/>
+      <c r="L9" s="222"/>
+      <c r="M9" s="222"/>
+      <c r="N9" s="222"/>
+      <c r="O9" s="222"/>
+      <c r="P9" s="223"/>
+      <c r="Q9" s="62"/>
+    </row>
+    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="224"/>
+      <c r="B10" s="225"/>
+      <c r="C10" s="225"/>
+      <c r="D10" s="225"/>
+      <c r="E10" s="225"/>
+      <c r="F10" s="225"/>
+      <c r="G10" s="225"/>
+      <c r="H10" s="225"/>
+      <c r="I10" s="225"/>
+      <c r="J10" s="225"/>
+      <c r="K10" s="225"/>
+      <c r="L10" s="225"/>
+      <c r="M10" s="225"/>
+      <c r="N10" s="225"/>
+      <c r="O10" s="225"/>
+      <c r="P10" s="226"/>
+    </row>
+    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="235" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="236"/>
+      <c r="C11" s="236"/>
+      <c r="D11" s="236"/>
+      <c r="E11" s="236"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="236"/>
+      <c r="H11" s="236"/>
+      <c r="I11" s="236"/>
+      <c r="J11" s="236"/>
+      <c r="K11" s="236"/>
+      <c r="L11" s="236"/>
+      <c r="M11" s="236"/>
+      <c r="N11" s="236"/>
+      <c r="O11" s="236"/>
+      <c r="P11" s="237"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="227" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="240" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="229" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="229" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="229" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="231" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="229" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="233" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="231" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="231" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="231" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" s="240" t="s">
+        <v>173</v>
+      </c>
+      <c r="M12" s="231" t="s">
         <v>170</v>
       </c>
-      <c r="B5" s="152"/>
-      <c r="C5" s="171">
-        <v>1313151.8700000001</v>
-      </c>
-      <c r="D5" s="91"/>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="196"/>
-      <c r="K5" s="196"/>
-      <c r="L5" s="196"/>
-      <c r="M5" s="196"/>
-      <c r="N5" s="196"/>
-      <c r="O5" s="196"/>
-      <c r="P5" s="197"/>
-      <c r="Q5" s="81"/>
-    </row>
-    <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="204" t="s">
-        <v>172</v>
-      </c>
-      <c r="B6" s="205"/>
-      <c r="C6" s="206"/>
-      <c r="D6" s="206"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="206"/>
-      <c r="G6" s="206"/>
-      <c r="H6" s="206"/>
-      <c r="I6" s="206"/>
-      <c r="J6" s="206"/>
-      <c r="K6" s="206"/>
-      <c r="L6" s="206"/>
-      <c r="M6" s="206"/>
-      <c r="N6" s="206"/>
-      <c r="O6" s="206"/>
-      <c r="P6" s="207"/>
-      <c r="Q6" s="81"/>
-    </row>
-    <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="208"/>
-      <c r="B7" s="209"/>
-      <c r="C7" s="209"/>
-      <c r="D7" s="209"/>
-      <c r="E7" s="209"/>
-      <c r="F7" s="209"/>
-      <c r="G7" s="209"/>
-      <c r="H7" s="209"/>
-      <c r="I7" s="209"/>
-      <c r="J7" s="209"/>
-      <c r="K7" s="209"/>
-      <c r="L7" s="209"/>
-      <c r="M7" s="209"/>
-      <c r="N7" s="209"/>
-      <c r="O7" s="209"/>
-      <c r="P7" s="210"/>
-      <c r="Q7" s="81"/>
-    </row>
-    <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="208"/>
-      <c r="B8" s="209"/>
-      <c r="C8" s="209"/>
-      <c r="D8" s="209"/>
-      <c r="E8" s="209"/>
-      <c r="F8" s="209"/>
-      <c r="G8" s="209"/>
-      <c r="H8" s="209"/>
-      <c r="I8" s="209"/>
-      <c r="J8" s="209"/>
-      <c r="K8" s="209"/>
-      <c r="L8" s="209"/>
-      <c r="M8" s="209"/>
-      <c r="N8" s="209"/>
-      <c r="O8" s="209"/>
-      <c r="P8" s="210"/>
-      <c r="Q8" s="81"/>
-    </row>
-    <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="208"/>
-      <c r="B9" s="209"/>
-      <c r="C9" s="209"/>
-      <c r="D9" s="209"/>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="209"/>
-      <c r="H9" s="209"/>
-      <c r="I9" s="209"/>
-      <c r="J9" s="209"/>
-      <c r="K9" s="209"/>
-      <c r="L9" s="209"/>
-      <c r="M9" s="209"/>
-      <c r="N9" s="209"/>
-      <c r="O9" s="209"/>
-      <c r="P9" s="210"/>
-      <c r="Q9" s="81"/>
-    </row>
-    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="211"/>
-      <c r="B10" s="212"/>
-      <c r="C10" s="212"/>
-      <c r="D10" s="212"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="212"/>
-      <c r="H10" s="212"/>
-      <c r="I10" s="212"/>
-      <c r="J10" s="212"/>
-      <c r="K10" s="212"/>
-      <c r="L10" s="212"/>
-      <c r="M10" s="212"/>
-      <c r="N10" s="212"/>
-      <c r="O10" s="212"/>
-      <c r="P10" s="213"/>
-    </row>
-    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="220" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="221"/>
-      <c r="C11" s="221"/>
-      <c r="D11" s="221"/>
-      <c r="E11" s="221"/>
-      <c r="F11" s="221"/>
-      <c r="G11" s="221"/>
-      <c r="H11" s="221"/>
-      <c r="I11" s="221"/>
-      <c r="J11" s="221"/>
-      <c r="K11" s="221"/>
-      <c r="L11" s="221"/>
-      <c r="M11" s="221"/>
-      <c r="N11" s="221"/>
-      <c r="O11" s="221"/>
-      <c r="P11" s="222"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="214" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="225" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="216" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="216" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="216" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="198" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="216" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="218" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="198" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="198" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" s="198" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" s="225" t="s">
-        <v>174</v>
-      </c>
-      <c r="M12" s="198" t="s">
-        <v>171</v>
-      </c>
-      <c r="N12" s="223" t="s">
-        <v>51</v>
-      </c>
-      <c r="O12" s="115" t="s">
+      <c r="N12" s="238" t="s">
+        <v>215</v>
+      </c>
+      <c r="O12" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="200" t="s">
+      <c r="P12" s="248" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="215"/>
-      <c r="B13" s="226"/>
-      <c r="C13" s="217"/>
-      <c r="D13" s="217"/>
-      <c r="E13" s="217"/>
-      <c r="F13" s="199"/>
-      <c r="G13" s="217"/>
-      <c r="H13" s="219"/>
-      <c r="I13" s="199"/>
-      <c r="J13" s="199"/>
-      <c r="K13" s="199"/>
-      <c r="L13" s="226"/>
-      <c r="M13" s="199"/>
-      <c r="N13" s="224"/>
-      <c r="O13" s="116" t="str">
+    <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="228"/>
+      <c r="B13" s="241"/>
+      <c r="C13" s="230"/>
+      <c r="D13" s="230"/>
+      <c r="E13" s="230"/>
+      <c r="F13" s="232"/>
+      <c r="G13" s="230"/>
+      <c r="H13" s="234"/>
+      <c r="I13" s="232"/>
+      <c r="J13" s="232"/>
+      <c r="K13" s="232"/>
+      <c r="L13" s="241"/>
+      <c r="M13" s="232"/>
+      <c r="N13" s="239"/>
+      <c r="O13" s="94" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="P13" s="201"/>
+      <c r="P13" s="249"/>
     </row>
     <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="105">
+      <c r="A14" s="83">
         <v>1</v>
       </c>
-      <c r="B14" s="153" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="94" t="s">
-        <v>119</v>
-      </c>
-      <c r="D14" s="94"/>
-      <c r="E14" s="96">
+      <c r="B14" s="130" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="72" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="72"/>
+      <c r="E14" s="74">
         <v>5.22</v>
       </c>
-      <c r="F14" s="82">
+      <c r="F14" s="63">
         <v>388500.01</v>
       </c>
-      <c r="G14" s="234">
+      <c r="G14" s="63">
         <f>400155.01</f>
         <v>400155.01</v>
       </c>
-      <c r="H14" s="97">
+      <c r="H14" s="75">
         <f t="shared" ref="H14:H59" si="0">F14-G14</f>
         <v>-11655</v>
       </c>
-      <c r="I14" s="97">
+      <c r="I14" s="75">
         <f>IF(H14&gt;0,H14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="104">
+      <c r="J14" s="82">
         <f>C$2*E14/100</f>
         <v>256129.20651600001</v>
       </c>
-      <c r="K14" s="104">
+      <c r="K14" s="82">
         <f t="shared" ref="K14:K45" si="1">F$2*E14/100</f>
         <v>0</v>
       </c>
-      <c r="L14" s="104">
+      <c r="L14" s="82">
         <f>C$4*E14/100</f>
         <v>9543.3611220000003</v>
       </c>
-      <c r="M14" s="104">
+      <c r="M14" s="82">
         <f>C$5*E14/100</f>
         <v>68546.527614000006</v>
       </c>
-      <c r="N14" s="104"/>
-      <c r="O14" s="98">
+      <c r="N14" s="82"/>
+      <c r="O14" s="76">
         <f>ROUND(SUM(H14:N14),0) + Q14</f>
         <v>322564.01</v>
       </c>
-      <c r="P14" s="113">
+      <c r="P14" s="91">
         <f t="shared" ref="P14:P34" si="2">ROUND(O14*3%,0) + O14</f>
         <v>332241.01</v>
       </c>
-      <c r="Q14" s="51">
+      <c r="Q14" s="40">
         <v>0.01</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="105">
+      <c r="A15" s="83">
         <v>2</v>
       </c>
-      <c r="B15" s="153" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="D15" s="94" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" s="96">
+      <c r="B15" s="130" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" s="74">
         <v>3.4</v>
       </c>
-      <c r="F15" s="82">
+      <c r="F15" s="63">
         <v>257906.02</v>
       </c>
-      <c r="G15" s="234">
+      <c r="G15" s="63">
         <f>F15+204243.28-F41</f>
         <v>442321.02</v>
       </c>
-      <c r="H15" s="97">
+      <c r="H15" s="75">
         <f t="shared" si="0"/>
         <v>-184415.00000000003</v>
       </c>
-      <c r="I15" s="97">
+      <c r="I15" s="75">
         <f t="shared" ref="I15:I59" si="3">IF(H15&gt;0,H15*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="104">
+      <c r="J15" s="82">
         <f t="shared" ref="J15:J59" si="4">C$2*E15/100</f>
         <v>166827.45251999999</v>
       </c>
-      <c r="K15" s="104">
+      <c r="K15" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L15" s="104">
+      <c r="L15" s="82">
         <f t="shared" ref="L15:L59" si="5">C$4*E15/100</f>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M15" s="104">
+      <c r="M15" s="82">
         <f t="shared" ref="M15:M59" si="6">C$5*E15/100</f>
         <v>44647.16358</v>
       </c>
-      <c r="N15" s="104"/>
-      <c r="O15" s="98">
+      <c r="N15" s="82"/>
+      <c r="O15" s="76">
         <f t="shared" ref="O15:O59" si="7">ROUND(SUM(H15:N15),0) + Q15</f>
         <v>33276.019999999997</v>
       </c>
-      <c r="P15" s="113">
+      <c r="P15" s="91">
         <f t="shared" si="2"/>
         <v>34274.019999999997</v>
       </c>
-      <c r="Q15" s="51">
+      <c r="Q15" s="40">
         <f>Q14+0.01</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="105">
+      <c r="A16" s="83">
         <v>3</v>
       </c>
-      <c r="B16" s="153" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="94" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" s="94" t="s">
-        <v>161</v>
-      </c>
-      <c r="E16" s="96">
+      <c r="B16" s="130" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="72" t="s">
+        <v>160</v>
+      </c>
+      <c r="E16" s="74">
         <v>2.54</v>
       </c>
-      <c r="F16" s="82">
+      <c r="F16" s="63">
         <v>190304.03</v>
       </c>
-      <c r="G16" s="234">
+      <c r="G16" s="63">
         <v>192000</v>
       </c>
-      <c r="H16" s="97">
+      <c r="H16" s="75">
         <f t="shared" si="0"/>
         <v>-1695.9700000000012</v>
       </c>
-      <c r="I16" s="97">
+      <c r="I16" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J16" s="104">
+      <c r="J16" s="82">
         <f t="shared" si="4"/>
         <v>124629.92041200001</v>
       </c>
-      <c r="K16" s="104">
+      <c r="K16" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L16" s="104">
+      <c r="L16" s="82">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M16" s="104">
+      <c r="M16" s="82">
         <f t="shared" si="6"/>
         <v>33354.057498000002</v>
       </c>
-      <c r="N16" s="104"/>
-      <c r="O16" s="98">
+      <c r="N16" s="82"/>
+      <c r="O16" s="76">
         <f t="shared" si="7"/>
         <v>160932.03</v>
       </c>
-      <c r="P16" s="113">
+      <c r="P16" s="91">
         <f t="shared" si="2"/>
         <v>165760.03</v>
       </c>
-      <c r="Q16" s="51">
+      <c r="Q16" s="40">
         <f t="shared" ref="Q16:Q31" si="8">Q15+0.01</f>
         <v>0.03</v>
       </c>
       <c r="R16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="105">
+      <c r="A17" s="83">
         <v>4</v>
       </c>
-      <c r="B17" s="153" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="94" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="99" t="s">
-        <v>157</v>
-      </c>
-      <c r="E17" s="96">
+      <c r="B17" s="130" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="72" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" s="74">
         <v>5.19</v>
       </c>
-      <c r="F17" s="82">
+      <c r="F17" s="63">
         <v>384603.04</v>
       </c>
-      <c r="G17" s="234">
+      <c r="G17" s="63">
         <f>449413-G55-G44</f>
         <v>379957.27</v>
       </c>
-      <c r="H17" s="97">
+      <c r="H17" s="75">
         <f t="shared" si="0"/>
         <v>4645.7699999999604</v>
       </c>
-      <c r="I17" s="97">
+      <c r="I17" s="75">
         <f t="shared" si="3"/>
         <v>139.3730999999988</v>
       </c>
-      <c r="J17" s="104">
+      <c r="J17" s="82">
         <f t="shared" si="4"/>
         <v>254657.19958200003</v>
       </c>
-      <c r="K17" s="104">
+      <c r="K17" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L17" s="104">
+      <c r="L17" s="82">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M17" s="104">
+      <c r="M17" s="82">
         <f t="shared" si="6"/>
         <v>68152.58205300002</v>
       </c>
-      <c r="N17" s="104"/>
-      <c r="O17" s="98">
+      <c r="N17" s="82"/>
+      <c r="O17" s="76">
         <f t="shared" si="7"/>
         <v>337083.04</v>
       </c>
-      <c r="P17" s="113">
+      <c r="P17" s="91">
         <f t="shared" si="2"/>
         <v>347195.04</v>
       </c>
-      <c r="Q17" s="51">
+      <c r="Q17" s="40">
         <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
       <c r="R17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="105">
+      <c r="A18" s="83">
         <v>5</v>
       </c>
-      <c r="B18" s="153" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="94" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="99" t="s">
-        <v>153</v>
-      </c>
-      <c r="E18" s="96">
+      <c r="B18" s="130" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="72" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="77" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18" s="74">
         <v>3.4</v>
       </c>
-      <c r="F18" s="82">
+      <c r="F18" s="63">
         <v>255000.05</v>
       </c>
-      <c r="G18" s="234">
+      <c r="G18" s="63">
         <f>F18</f>
         <v>255000.05</v>
       </c>
-      <c r="H18" s="97">
+      <c r="H18" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="97">
+      <c r="I18" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J18" s="104">
+      <c r="J18" s="82">
         <f t="shared" si="4"/>
         <v>166827.45251999999</v>
       </c>
-      <c r="K18" s="104">
+      <c r="K18" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L18" s="104">
+      <c r="L18" s="82">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M18" s="104">
+      <c r="M18" s="82">
         <f t="shared" si="6"/>
         <v>44647.16358</v>
       </c>
-      <c r="N18" s="104"/>
-      <c r="O18" s="98">
+      <c r="N18" s="82"/>
+      <c r="O18" s="76">
         <f t="shared" si="7"/>
         <v>217691.05</v>
       </c>
-      <c r="P18" s="113">
+      <c r="P18" s="91">
         <f t="shared" si="2"/>
         <v>224222.05</v>
       </c>
-      <c r="Q18" s="51">
+      <c r="Q18" s="40">
         <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="105">
+      <c r="A19" s="83">
         <v>6</v>
       </c>
-      <c r="B19" s="153" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" s="94" t="s">
-        <v>205</v>
-      </c>
-      <c r="E19" s="96">
+      <c r="B19" s="130" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="72" t="s">
+        <v>204</v>
+      </c>
+      <c r="E19" s="74">
         <v>2.54</v>
       </c>
-      <c r="F19" s="82">
+      <c r="F19" s="63">
         <v>351985.06</v>
       </c>
-      <c r="G19" s="234">
+      <c r="G19" s="63">
         <f>156782+190500.06+4703</f>
         <v>351985.06</v>
       </c>
-      <c r="H19" s="97">
+      <c r="H19" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="97">
+      <c r="I19" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J19" s="104">
+      <c r="J19" s="82">
         <f t="shared" si="4"/>
         <v>124629.92041200001</v>
       </c>
-      <c r="K19" s="104">
+      <c r="K19" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L19" s="104">
+      <c r="L19" s="82">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M19" s="104">
+      <c r="M19" s="82">
         <f t="shared" si="6"/>
         <v>33354.057498000002</v>
       </c>
-      <c r="N19" s="104"/>
-      <c r="O19" s="98">
+      <c r="N19" s="82"/>
+      <c r="O19" s="76">
         <f t="shared" si="7"/>
         <v>162628.06</v>
       </c>
-      <c r="P19" s="113">
+      <c r="P19" s="91">
         <f t="shared" si="2"/>
         <v>167507.06</v>
       </c>
-      <c r="Q19" s="51">
+      <c r="Q19" s="40">
         <f t="shared" si="8"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="105">
+      <c r="A20" s="83">
         <v>7</v>
       </c>
-      <c r="B20" s="153" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="94" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="94"/>
-      <c r="E20" s="96">
+      <c r="B20" s="130" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="72" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="72"/>
+      <c r="E20" s="74">
         <v>5.19</v>
       </c>
-      <c r="F20" s="82">
+      <c r="F20" s="63">
         <v>389250.07</v>
       </c>
-      <c r="G20" s="234">
-        <f>F20</f>
+      <c r="G20" s="63">
+        <f t="shared" ref="G20:G25" si="9">F20</f>
         <v>389250.07</v>
       </c>
-      <c r="H20" s="97">
+      <c r="H20" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="97">
+      <c r="I20" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J20" s="104">
+      <c r="J20" s="82">
         <f t="shared" si="4"/>
         <v>254657.19958200003</v>
       </c>
-      <c r="K20" s="104">
+      <c r="K20" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L20" s="104">
+      <c r="L20" s="82">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M20" s="104">
+      <c r="M20" s="82">
         <f t="shared" si="6"/>
         <v>68152.58205300002</v>
       </c>
-      <c r="N20" s="104"/>
-      <c r="O20" s="98">
+      <c r="N20" s="82"/>
+      <c r="O20" s="76">
         <f t="shared" si="7"/>
         <v>332298.07</v>
       </c>
-      <c r="P20" s="113">
+      <c r="P20" s="91">
         <f t="shared" si="2"/>
         <v>342267.07</v>
       </c>
-      <c r="Q20" s="51">
+      <c r="Q20" s="40">
         <f t="shared" si="8"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="105">
+      <c r="A21" s="83">
         <v>8</v>
       </c>
-      <c r="B21" s="153" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="D21" s="99"/>
-      <c r="E21" s="96">
+      <c r="B21" s="130" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="77"/>
+      <c r="E21" s="74">
         <v>3.4</v>
       </c>
-      <c r="F21" s="82">
+      <c r="F21" s="63">
         <v>255000.08</v>
       </c>
-      <c r="G21" s="234">
-        <f>F21</f>
+      <c r="G21" s="63">
+        <f t="shared" si="9"/>
         <v>255000.08</v>
       </c>
-      <c r="H21" s="97">
+      <c r="H21" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21" s="97">
+      <c r="I21" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J21" s="104">
+      <c r="J21" s="82">
         <f t="shared" si="4"/>
         <v>166827.45251999999</v>
       </c>
-      <c r="K21" s="104">
+      <c r="K21" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L21" s="104">
+      <c r="L21" s="82">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M21" s="104">
+      <c r="M21" s="82">
         <f t="shared" si="6"/>
         <v>44647.16358</v>
       </c>
-      <c r="N21" s="104"/>
-      <c r="O21" s="98">
+      <c r="N21" s="82"/>
+      <c r="O21" s="76">
         <f t="shared" si="7"/>
         <v>217691.08</v>
       </c>
-      <c r="P21" s="113">
+      <c r="P21" s="91">
         <f t="shared" si="2"/>
         <v>224222.07999999999</v>
       </c>
-      <c r="Q21" s="51">
+      <c r="Q21" s="40">
         <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="105">
+      <c r="A22" s="83">
         <v>9</v>
       </c>
-      <c r="B22" s="153" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" s="99" t="s">
-        <v>156</v>
-      </c>
-      <c r="E22" s="96">
+      <c r="B22" s="130" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="77" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22" s="74">
         <v>2.54</v>
       </c>
-      <c r="F22" s="82">
+      <c r="F22" s="63">
         <v>190500.09</v>
       </c>
-      <c r="G22" s="234">
-        <f>F22</f>
+      <c r="G22" s="63">
+        <f t="shared" si="9"/>
         <v>190500.09</v>
       </c>
-      <c r="H22" s="97">
+      <c r="H22" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="97">
+      <c r="I22" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J22" s="104">
+      <c r="J22" s="82">
         <f t="shared" si="4"/>
         <v>124629.92041200001</v>
       </c>
-      <c r="K22" s="104">
+      <c r="K22" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L22" s="104">
+      <c r="L22" s="82">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M22" s="104">
+      <c r="M22" s="82">
         <f t="shared" si="6"/>
         <v>33354.057498000002</v>
       </c>
-      <c r="N22" s="104"/>
-      <c r="O22" s="98">
+      <c r="N22" s="82"/>
+      <c r="O22" s="76">
         <f t="shared" si="7"/>
         <v>162628.09</v>
       </c>
-      <c r="P22" s="113">
+      <c r="P22" s="91">
         <f t="shared" si="2"/>
         <v>167507.09</v>
       </c>
-      <c r="Q22" s="51">
+      <c r="Q22" s="40">
         <f t="shared" si="8"/>
         <v>0.09</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="105">
+      <c r="A23" s="83">
         <v>10</v>
       </c>
-      <c r="B23" s="153" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="94" t="s">
-        <v>126</v>
-      </c>
-      <c r="D23" s="99"/>
-      <c r="E23" s="96">
+      <c r="B23" s="130" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="72" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" s="77"/>
+      <c r="E23" s="74">
         <v>5.19</v>
       </c>
-      <c r="F23" s="82">
+      <c r="F23" s="63">
         <v>389250.1</v>
       </c>
-      <c r="G23" s="234">
-        <f>F23</f>
+      <c r="G23" s="63">
+        <f t="shared" si="9"/>
         <v>389250.1</v>
       </c>
-      <c r="H23" s="97">
+      <c r="H23" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I23" s="97">
+      <c r="I23" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J23" s="104">
+      <c r="J23" s="82">
         <f t="shared" si="4"/>
         <v>254657.19958200003</v>
       </c>
-      <c r="K23" s="104">
+      <c r="K23" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L23" s="104">
+      <c r="L23" s="82">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M23" s="104">
+      <c r="M23" s="82">
         <f t="shared" si="6"/>
         <v>68152.58205300002</v>
       </c>
-      <c r="N23" s="104"/>
-      <c r="O23" s="98">
+      <c r="N23" s="82"/>
+      <c r="O23" s="76">
         <f t="shared" si="7"/>
         <v>332298.09999999998</v>
       </c>
-      <c r="P23" s="113">
+      <c r="P23" s="91">
         <f t="shared" si="2"/>
         <v>342267.1</v>
       </c>
-      <c r="Q23" s="51">
+      <c r="Q23" s="40">
         <f t="shared" si="8"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="105">
+      <c r="A24" s="83">
         <v>11</v>
       </c>
-      <c r="B24" s="153" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="94" t="s">
-        <v>127</v>
-      </c>
-      <c r="D24" s="99" t="s">
-        <v>154</v>
-      </c>
-      <c r="E24" s="96">
+      <c r="B24" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24" s="77" t="s">
+        <v>153</v>
+      </c>
+      <c r="E24" s="74">
         <v>3.4</v>
       </c>
-      <c r="F24" s="82">
+      <c r="F24" s="63">
         <v>255000.11</v>
       </c>
-      <c r="G24" s="234">
-        <f>F24</f>
+      <c r="G24" s="63">
+        <f t="shared" si="9"/>
         <v>255000.11</v>
       </c>
-      <c r="H24" s="97">
+      <c r="H24" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I24" s="97">
+      <c r="I24" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="104">
+      <c r="J24" s="82">
         <f t="shared" si="4"/>
         <v>166827.45251999999</v>
       </c>
-      <c r="K24" s="104">
+      <c r="K24" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L24" s="104">
+      <c r="L24" s="82">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M24" s="104">
+      <c r="M24" s="82">
         <f t="shared" si="6"/>
         <v>44647.16358</v>
       </c>
-      <c r="N24" s="104"/>
-      <c r="O24" s="98">
+      <c r="N24" s="82"/>
+      <c r="O24" s="76">
         <f t="shared" si="7"/>
         <v>217691.11</v>
       </c>
-      <c r="P24" s="113">
+      <c r="P24" s="91">
         <f t="shared" si="2"/>
         <v>224222.11</v>
       </c>
-      <c r="Q24" s="51">
+      <c r="Q24" s="40">
         <f t="shared" si="8"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="105">
+      <c r="A25" s="83">
         <v>12</v>
       </c>
-      <c r="B25" s="153" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="94" t="s">
-        <v>128</v>
-      </c>
-      <c r="D25" s="99" t="s">
-        <v>158</v>
-      </c>
-      <c r="E25" s="96">
+      <c r="B25" s="130" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="72" t="s">
+        <v>127</v>
+      </c>
+      <c r="D25" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="E25" s="74">
         <v>2.54</v>
       </c>
-      <c r="F25" s="82">
+      <c r="F25" s="63">
         <v>190500.12</v>
       </c>
-      <c r="G25" s="234">
-        <f>F25</f>
+      <c r="G25" s="63">
+        <f t="shared" si="9"/>
         <v>190500.12</v>
       </c>
-      <c r="H25" s="97">
+      <c r="H25" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I25" s="97">
+      <c r="I25" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J25" s="104">
+      <c r="J25" s="82">
         <f t="shared" si="4"/>
         <v>124629.92041200001</v>
       </c>
-      <c r="K25" s="104">
+      <c r="K25" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L25" s="104">
+      <c r="L25" s="82">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M25" s="104">
+      <c r="M25" s="82">
         <f t="shared" si="6"/>
         <v>33354.057498000002</v>
       </c>
-      <c r="N25" s="104"/>
-      <c r="O25" s="98">
+      <c r="N25" s="82"/>
+      <c r="O25" s="76">
         <f t="shared" si="7"/>
         <v>162628.12</v>
       </c>
-      <c r="P25" s="113">
+      <c r="P25" s="91">
         <f t="shared" si="2"/>
         <v>167507.12</v>
       </c>
-      <c r="Q25" s="51">
+      <c r="Q25" s="40">
         <f t="shared" si="8"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="235">
+      <c r="A26" s="151">
         <v>13</v>
       </c>
-      <c r="B26" s="236" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="237" t="s">
-        <v>204</v>
-      </c>
-      <c r="D26" s="238"/>
-      <c r="E26" s="239">
+      <c r="B26" s="152" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="153" t="s">
+        <v>203</v>
+      </c>
+      <c r="D26" s="154"/>
+      <c r="E26" s="155">
         <v>5.19</v>
       </c>
-      <c r="F26" s="240">
+      <c r="F26" s="156">
         <v>389250.13</v>
       </c>
-      <c r="G26" s="234">
+      <c r="G26" s="156">
         <f>407108-G45</f>
         <v>401107.68</v>
       </c>
-      <c r="H26" s="241">
+      <c r="H26" s="157">
         <f t="shared" si="0"/>
         <v>-11857.549999999988</v>
       </c>
-      <c r="I26" s="241">
+      <c r="I26" s="157">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="242">
+      <c r="J26" s="158">
         <f t="shared" si="4"/>
         <v>254657.19958200003</v>
       </c>
-      <c r="K26" s="242">
+      <c r="K26" s="158">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L26" s="242">
+      <c r="L26" s="158">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M26" s="242">
+      <c r="M26" s="158">
         <f t="shared" si="6"/>
         <v>68152.58205300002</v>
       </c>
-      <c r="N26" s="242"/>
-      <c r="O26" s="243">
+      <c r="N26" s="158"/>
+      <c r="O26" s="159">
         <f t="shared" si="7"/>
         <v>320441.13</v>
       </c>
-      <c r="P26" s="244">
+      <c r="P26" s="160">
         <f t="shared" si="2"/>
         <v>330054.13</v>
       </c>
-      <c r="Q26" s="51">
+      <c r="Q26" s="40">
         <f t="shared" si="8"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="235">
+      <c r="A27" s="151">
         <v>14</v>
       </c>
-      <c r="B27" s="236" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="237" t="s">
-        <v>130</v>
-      </c>
-      <c r="D27" s="238"/>
-      <c r="E27" s="239">
+      <c r="B27" s="152" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="153" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="154"/>
+      <c r="E27" s="155">
         <v>3.4</v>
       </c>
-      <c r="F27" s="240">
+      <c r="F27" s="156">
         <v>255618.14</v>
       </c>
-      <c r="G27" s="234">
+      <c r="G27" s="156">
         <f>328368.22-G51</f>
         <v>255617.83999999997</v>
       </c>
-      <c r="H27" s="241">
+      <c r="H27" s="157">
         <f t="shared" si="0"/>
         <v>0.30000000004656613</v>
       </c>
-      <c r="I27" s="241">
+      <c r="I27" s="157">
         <f t="shared" si="3"/>
         <v>9.0000000013969843E-3</v>
       </c>
-      <c r="J27" s="242">
+      <c r="J27" s="158">
         <f t="shared" si="4"/>
         <v>166827.45251999999</v>
       </c>
-      <c r="K27" s="242">
+      <c r="K27" s="158">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L27" s="242">
+      <c r="L27" s="158">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M27" s="242">
+      <c r="M27" s="158">
         <f t="shared" si="6"/>
         <v>44647.16358</v>
       </c>
-      <c r="N27" s="242"/>
-      <c r="O27" s="243">
+      <c r="N27" s="158"/>
+      <c r="O27" s="159">
         <f t="shared" si="7"/>
         <v>217691.14</v>
       </c>
-      <c r="P27" s="244">
+      <c r="P27" s="160">
         <f t="shared" si="2"/>
         <v>224222.14</v>
       </c>
-      <c r="Q27" s="51">
+      <c r="Q27" s="40">
         <f t="shared" si="8"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="105">
+      <c r="A28" s="83">
         <v>15</v>
       </c>
-      <c r="B28" s="153" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="94" t="s">
-        <v>131</v>
-      </c>
-      <c r="D28" s="94" t="s">
-        <v>155</v>
-      </c>
-      <c r="E28" s="96">
+      <c r="B28" s="130" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="72" t="s">
+        <v>154</v>
+      </c>
+      <c r="E28" s="74">
         <v>2.54</v>
       </c>
-      <c r="F28" s="82">
+      <c r="F28" s="63">
         <v>225645.15</v>
       </c>
-      <c r="G28" s="234">
+      <c r="G28" s="63">
         <f>F28</f>
         <v>225645.15</v>
       </c>
-      <c r="H28" s="97">
+      <c r="H28" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I28" s="97">
+      <c r="I28" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J28" s="104">
+      <c r="J28" s="82">
         <f t="shared" si="4"/>
         <v>124629.92041200001</v>
       </c>
-      <c r="K28" s="104">
+      <c r="K28" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L28" s="104">
+      <c r="L28" s="82">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M28" s="104">
+      <c r="M28" s="82">
         <f t="shared" si="6"/>
         <v>33354.057498000002</v>
       </c>
-      <c r="N28" s="104"/>
-      <c r="O28" s="98">
+      <c r="N28" s="82"/>
+      <c r="O28" s="76">
         <f t="shared" si="7"/>
         <v>162628.15</v>
       </c>
-      <c r="P28" s="113">
+      <c r="P28" s="91">
         <f t="shared" si="2"/>
         <v>167507.15</v>
       </c>
-      <c r="Q28" s="51">
+      <c r="Q28" s="40">
         <f t="shared" si="8"/>
         <v>0.15</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="105">
+      <c r="A29" s="83">
         <v>16</v>
       </c>
-      <c r="B29" s="153" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="94" t="s">
-        <v>132</v>
-      </c>
-      <c r="D29" s="94"/>
-      <c r="E29" s="96">
+      <c r="B29" s="130" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="72" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" s="72"/>
+      <c r="E29" s="74">
         <v>5.19</v>
       </c>
-      <c r="F29" s="82">
+      <c r="F29" s="63">
         <v>389250.16</v>
       </c>
-      <c r="G29" s="234">
+      <c r="G29" s="63">
         <f>F29</f>
         <v>389250.16</v>
       </c>
-      <c r="H29" s="97">
+      <c r="H29" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I29" s="97">
+      <c r="I29" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="104">
+      <c r="J29" s="82">
         <f t="shared" si="4"/>
         <v>254657.19958200003</v>
       </c>
-      <c r="K29" s="104">
+      <c r="K29" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L29" s="104">
+      <c r="L29" s="82">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M29" s="104">
+      <c r="M29" s="82">
         <f t="shared" si="6"/>
         <v>68152.58205300002</v>
       </c>
-      <c r="N29" s="104"/>
-      <c r="O29" s="98">
+      <c r="N29" s="82"/>
+      <c r="O29" s="76">
         <f t="shared" si="7"/>
         <v>332298.15999999997</v>
       </c>
-      <c r="P29" s="113">
+      <c r="P29" s="91">
         <f t="shared" si="2"/>
         <v>342267.16</v>
       </c>
-      <c r="Q29" s="51">
+      <c r="Q29" s="40">
         <f t="shared" si="8"/>
         <v>0.16</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="105">
+      <c r="A30" s="83">
         <v>17</v>
       </c>
-      <c r="B30" s="153" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" s="94" t="s">
-        <v>133</v>
-      </c>
-      <c r="D30" s="99" t="s">
-        <v>173</v>
-      </c>
-      <c r="E30" s="96">
+      <c r="B30" s="130" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="E30" s="74">
         <v>3.4</v>
       </c>
-      <c r="F30" s="82">
+      <c r="F30" s="63">
         <v>269008.17</v>
       </c>
-      <c r="G30" s="234">
+      <c r="G30" s="63">
         <f>326761-G53</f>
         <v>269010.59999999998</v>
       </c>
-      <c r="H30" s="97">
+      <c r="H30" s="75">
         <f t="shared" si="0"/>
         <v>-2.4299999999930151</v>
       </c>
-      <c r="I30" s="97">
+      <c r="I30" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="104">
+      <c r="J30" s="82">
         <f t="shared" si="4"/>
         <v>166827.45251999999</v>
       </c>
-      <c r="K30" s="104">
+      <c r="K30" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L30" s="104">
+      <c r="L30" s="82">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M30" s="104">
+      <c r="M30" s="82">
         <f t="shared" si="6"/>
         <v>44647.16358</v>
       </c>
-      <c r="N30" s="104"/>
-      <c r="O30" s="98">
+      <c r="N30" s="82"/>
+      <c r="O30" s="76">
         <f t="shared" si="7"/>
         <v>217688.17</v>
       </c>
-      <c r="P30" s="113">
+      <c r="P30" s="91">
         <f t="shared" si="2"/>
         <v>224219.17</v>
       </c>
-      <c r="Q30" s="51">
+      <c r="Q30" s="40">
         <f t="shared" si="8"/>
         <v>0.17</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="105">
+      <c r="A31" s="83">
         <v>18</v>
       </c>
-      <c r="B31" s="153" t="s">
-        <v>90</v>
-      </c>
-      <c r="C31" s="94" t="s">
-        <v>134</v>
-      </c>
-      <c r="D31" s="95"/>
-      <c r="E31" s="96">
+      <c r="B31" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="72" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="73"/>
+      <c r="E31" s="74">
         <v>2.54</v>
       </c>
-      <c r="F31" s="82">
+      <c r="F31" s="63">
         <v>1410658.18</v>
       </c>
-      <c r="G31" s="82"/>
-      <c r="H31" s="97">
+      <c r="G31" s="63"/>
+      <c r="H31" s="75">
         <f t="shared" si="0"/>
         <v>1410658.18</v>
       </c>
-      <c r="I31" s="97">
+      <c r="I31" s="75">
         <f t="shared" si="3"/>
         <v>42319.7454</v>
       </c>
-      <c r="J31" s="104">
+      <c r="J31" s="82">
         <f t="shared" si="4"/>
         <v>124629.92041200001</v>
       </c>
-      <c r="K31" s="104">
+      <c r="K31" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L31" s="104">
+      <c r="L31" s="82">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M31" s="104">
+      <c r="M31" s="82">
         <f t="shared" si="6"/>
         <v>33354.057498000002</v>
       </c>
-      <c r="N31" s="104"/>
-      <c r="O31" s="98">
+      <c r="N31" s="82"/>
+      <c r="O31" s="76">
         <f t="shared" si="7"/>
         <v>1615606.18</v>
       </c>
-      <c r="P31" s="113">
+      <c r="P31" s="91">
         <f t="shared" si="2"/>
         <v>1664074.18</v>
       </c>
-      <c r="Q31" s="51">
+      <c r="Q31" s="40">
         <f t="shared" si="8"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="105">
+      <c r="A32" s="83">
         <v>19</v>
       </c>
-      <c r="B32" s="153" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" s="94" t="s">
-        <v>135</v>
-      </c>
-      <c r="D32" s="99"/>
-      <c r="E32" s="96">
+      <c r="B32" s="130" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" s="77"/>
+      <c r="E32" s="74">
         <v>5.19</v>
       </c>
-      <c r="F32" s="82">
+      <c r="F32" s="63">
         <v>745476.19</v>
       </c>
-      <c r="G32" s="82">
-        <v>0</v>
-      </c>
-      <c r="H32" s="97">
+      <c r="G32" s="63">
+        <v>0</v>
+      </c>
+      <c r="H32" s="75">
         <f t="shared" si="0"/>
         <v>745476.19</v>
       </c>
-      <c r="I32" s="97">
+      <c r="I32" s="75">
         <f t="shared" si="3"/>
         <v>22364.285699999997</v>
       </c>
-      <c r="J32" s="104">
+      <c r="J32" s="82">
         <f t="shared" si="4"/>
         <v>254657.19958200003</v>
       </c>
-      <c r="K32" s="104">
+      <c r="K32" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L32" s="104">
+      <c r="L32" s="82">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M32" s="104">
+      <c r="M32" s="82">
         <f t="shared" si="6"/>
         <v>68152.58205300002</v>
       </c>
-      <c r="N32" s="104"/>
-      <c r="O32" s="98">
+      <c r="N32" s="82">
+        <v>43500</v>
+      </c>
+      <c r="O32" s="76">
         <f t="shared" si="7"/>
-        <v>1100139.19</v>
-      </c>
-      <c r="P32" s="113">
+        <v>1143639.19</v>
+      </c>
+      <c r="P32" s="91">
         <f t="shared" si="2"/>
-        <v>1133143.19</v>
-      </c>
-      <c r="Q32" s="51">
+        <v>1177948.19</v>
+      </c>
+      <c r="Q32" s="40">
         <f>Q31+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="105">
+      <c r="A33" s="83">
         <v>20</v>
       </c>
-      <c r="B33" s="153" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" s="94" t="s">
-        <v>136</v>
-      </c>
-      <c r="D33" s="99"/>
-      <c r="E33" s="96">
+      <c r="B33" s="130" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="72" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="77"/>
+      <c r="E33" s="74">
         <v>3.4</v>
       </c>
-      <c r="F33" s="82">
+      <c r="F33" s="63">
         <v>255000.2</v>
       </c>
-      <c r="G33" s="234">
+      <c r="G33" s="63">
         <f>261000.54-G47</f>
         <v>255000.2</v>
       </c>
-      <c r="H33" s="97">
+      <c r="H33" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I33" s="97"/>
-      <c r="J33" s="104">
+      <c r="I33" s="75"/>
+      <c r="J33" s="82">
         <f t="shared" si="4"/>
         <v>166827.45251999999</v>
       </c>
-      <c r="K33" s="104">
+      <c r="K33" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L33" s="104">
+      <c r="L33" s="82">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M33" s="104">
+      <c r="M33" s="82">
         <f t="shared" si="6"/>
         <v>44647.16358</v>
       </c>
-      <c r="N33" s="104"/>
-      <c r="O33" s="98">
+      <c r="N33" s="82"/>
+      <c r="O33" s="76">
         <f t="shared" si="7"/>
         <v>217691.2</v>
       </c>
-      <c r="P33" s="113">
+      <c r="P33" s="91">
         <f t="shared" si="2"/>
         <v>224222.2</v>
       </c>
-      <c r="Q33" s="51">
-        <f t="shared" ref="Q33:Q59" si="9">Q32+0.01</f>
+      <c r="Q33" s="40">
+        <f t="shared" ref="Q33:Q59" si="10">Q32+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="105">
+      <c r="A34" s="83">
         <v>21</v>
       </c>
-      <c r="B34" s="153" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" s="100" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" s="99" t="s">
-        <v>152</v>
-      </c>
-      <c r="E34" s="96">
+      <c r="B34" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="78" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="77" t="s">
+        <v>151</v>
+      </c>
+      <c r="E34" s="74">
         <v>2.54</v>
       </c>
-      <c r="F34" s="82">
+      <c r="F34" s="63">
         <v>190500.21</v>
       </c>
-      <c r="G34" s="234">
+      <c r="G34" s="63">
         <f>F34</f>
         <v>190500.21</v>
       </c>
-      <c r="H34" s="97">
+      <c r="H34" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I34" s="97">
+      <c r="I34" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J34" s="104">
+      <c r="J34" s="82">
         <f t="shared" si="4"/>
         <v>124629.92041200001</v>
       </c>
-      <c r="K34" s="104">
+      <c r="K34" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L34" s="104">
+      <c r="L34" s="82">
         <f t="shared" si="5"/>
         <v>4643.7044540000006</v>
       </c>
-      <c r="M34" s="104">
+      <c r="M34" s="82">
         <f t="shared" si="6"/>
         <v>33354.057498000002</v>
       </c>
-      <c r="N34" s="104"/>
-      <c r="O34" s="98">
+      <c r="N34" s="82"/>
+      <c r="O34" s="76">
         <f t="shared" si="7"/>
         <v>162628.21</v>
       </c>
-      <c r="P34" s="113">
+      <c r="P34" s="91">
         <f t="shared" si="2"/>
         <v>167507.21</v>
       </c>
-      <c r="Q34" s="51">
-        <f t="shared" si="9"/>
+      <c r="Q34" s="40">
+        <f t="shared" si="10"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="105">
+      <c r="A35" s="83">
         <f>A34+1</f>
         <v>22</v>
       </c>
-      <c r="B35" s="153" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35" s="100" t="s">
-        <v>137</v>
-      </c>
-      <c r="D35" s="99" t="s">
-        <v>162</v>
-      </c>
-      <c r="E35" s="96">
+      <c r="B35" s="130" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" s="78" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" s="77" t="s">
+        <v>161</v>
+      </c>
+      <c r="E35" s="74">
         <v>4.9400000000000004</v>
       </c>
-      <c r="F35" s="82">
+      <c r="F35" s="63">
         <v>370500.22</v>
       </c>
-      <c r="G35" s="234">
+      <c r="G35" s="63">
         <f>F35</f>
         <v>370500.22</v>
       </c>
-      <c r="H35" s="97">
+      <c r="H35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I35" s="97">
+      <c r="I35" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="104">
+      <c r="J35" s="82">
         <f t="shared" si="4"/>
         <v>242390.47513200005</v>
       </c>
-      <c r="K35" s="104">
+      <c r="K35" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L35" s="104">
+      <c r="L35" s="82">
         <f t="shared" si="5"/>
         <v>9031.4566940000004</v>
       </c>
-      <c r="M35" s="104">
+      <c r="M35" s="82">
         <f t="shared" si="6"/>
         <v>64869.702378000009</v>
       </c>
-      <c r="N35" s="104"/>
-      <c r="O35" s="98">
+      <c r="N35" s="82"/>
+      <c r="O35" s="76">
         <f t="shared" si="7"/>
         <v>316292.21999999997</v>
       </c>
-      <c r="P35" s="113">
-        <f t="shared" ref="P35:P59" si="10">ROUND(O35*3%,0) + O35</f>
+      <c r="P35" s="91">
+        <f t="shared" ref="P35:P59" si="11">ROUND(O35*3%,0) + O35</f>
         <v>325781.21999999997</v>
       </c>
-      <c r="Q35" s="51">
-        <f t="shared" si="9"/>
+      <c r="Q35" s="40">
+        <f t="shared" si="10"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" s="105">
-        <f t="shared" ref="A36:A59" si="11">A35+1</f>
+      <c r="A36" s="83">
+        <f t="shared" ref="A36:A59" si="12">A35+1</f>
         <v>23</v>
       </c>
-      <c r="B36" s="153" t="s">
-        <v>95</v>
-      </c>
-      <c r="C36" s="100" t="s">
-        <v>138</v>
-      </c>
-      <c r="D36" s="99" t="s">
-        <v>160</v>
-      </c>
-      <c r="E36" s="96">
+      <c r="B36" s="130" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="77" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" s="74">
         <v>3.28</v>
       </c>
-      <c r="F36" s="82">
+      <c r="F36" s="63">
         <v>246844.23</v>
       </c>
-      <c r="G36" s="234">
+      <c r="G36" s="63">
         <v>246000</v>
       </c>
-      <c r="H36" s="97">
+      <c r="H36" s="75">
         <f t="shared" si="0"/>
         <v>844.23000000001048</v>
       </c>
-      <c r="I36" s="97">
+      <c r="I36" s="75">
         <f t="shared" si="3"/>
         <v>25.326900000000315</v>
       </c>
-      <c r="J36" s="104">
+      <c r="J36" s="82">
         <f t="shared" si="4"/>
         <v>160939.424784</v>
       </c>
-      <c r="K36" s="104">
+      <c r="K36" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L36" s="104">
+      <c r="L36" s="82">
         <f t="shared" si="5"/>
         <v>5996.594728</v>
       </c>
-      <c r="M36" s="104">
+      <c r="M36" s="82">
         <f t="shared" si="6"/>
         <v>43071.381336000006</v>
       </c>
-      <c r="N36" s="104"/>
-      <c r="O36" s="98">
+      <c r="N36" s="82"/>
+      <c r="O36" s="76">
         <f t="shared" si="7"/>
         <v>210877.23</v>
       </c>
-      <c r="P36" s="113">
+      <c r="P36" s="91">
+        <f t="shared" si="11"/>
+        <v>217203.23</v>
+      </c>
+      <c r="Q36" s="40">
         <f t="shared" si="10"/>
-        <v>217203.23</v>
-      </c>
-      <c r="Q36" s="51">
-        <f t="shared" si="9"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" s="105">
-        <f t="shared" si="11"/>
+      <c r="A37" s="83">
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
-      <c r="B37" s="153" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="100" t="s">
-        <v>139</v>
-      </c>
-      <c r="D37" s="99"/>
-      <c r="E37" s="96">
+      <c r="B37" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" s="78" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="77"/>
+      <c r="E37" s="74">
         <v>2.41</v>
       </c>
-      <c r="F37" s="82">
+      <c r="F37" s="63">
         <v>180750.24</v>
       </c>
-      <c r="G37" s="234">
+      <c r="G37" s="63">
         <f>F37</f>
         <v>180750.24</v>
       </c>
-      <c r="H37" s="97">
+      <c r="H37" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I37" s="97">
+      <c r="I37" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J37" s="104">
+      <c r="J37" s="82">
         <f t="shared" si="4"/>
         <v>118251.22369800002</v>
       </c>
-      <c r="K37" s="104">
+      <c r="K37" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L37" s="104">
+      <c r="L37" s="82">
         <f t="shared" si="5"/>
         <v>4406.034541</v>
       </c>
-      <c r="M37" s="104">
+      <c r="M37" s="82">
         <f t="shared" si="6"/>
         <v>31646.960067000004</v>
       </c>
-      <c r="N37" s="104"/>
-      <c r="O37" s="98">
+      <c r="N37" s="82"/>
+      <c r="O37" s="76">
         <f t="shared" si="7"/>
         <v>154304.24</v>
       </c>
-      <c r="P37" s="113">
+      <c r="P37" s="91">
+        <f t="shared" si="11"/>
+        <v>158933.24</v>
+      </c>
+      <c r="Q37" s="40">
         <f t="shared" si="10"/>
-        <v>158933.24</v>
-      </c>
-      <c r="Q37" s="51">
-        <f t="shared" si="9"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" s="105">
-        <f t="shared" si="11"/>
+      <c r="A38" s="83">
+        <f t="shared" si="12"/>
         <v>25</v>
       </c>
-      <c r="B38" s="153" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" s="100" t="s">
-        <v>138</v>
-      </c>
-      <c r="D38" s="99"/>
-      <c r="E38" s="96">
+      <c r="B38" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" s="77"/>
+      <c r="E38" s="74">
         <v>0.44</v>
       </c>
-      <c r="F38" s="82">
+      <c r="F38" s="63">
         <v>24889.25</v>
       </c>
-      <c r="G38" s="82">
-        <v>0</v>
-      </c>
-      <c r="H38" s="97">
+      <c r="G38" s="63">
+        <v>0</v>
+      </c>
+      <c r="H38" s="75">
         <f t="shared" si="0"/>
         <v>24889.25</v>
       </c>
-      <c r="I38" s="97">
+      <c r="I38" s="75">
         <f t="shared" si="3"/>
         <v>746.67750000000001</v>
       </c>
-      <c r="J38" s="104">
+      <c r="J38" s="82">
         <f t="shared" si="4"/>
         <v>21589.435032000001</v>
       </c>
-      <c r="K38" s="104">
+      <c r="K38" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L38" s="104">
+      <c r="L38" s="82">
         <f t="shared" si="5"/>
         <v>804.421244</v>
       </c>
-      <c r="M38" s="104">
+      <c r="M38" s="82">
         <f t="shared" si="6"/>
         <v>5777.8682280000012</v>
       </c>
-      <c r="N38" s="104"/>
-      <c r="O38" s="98">
+      <c r="N38" s="82"/>
+      <c r="O38" s="76">
         <f t="shared" si="7"/>
         <v>53808.25</v>
       </c>
-      <c r="P38" s="113">
+      <c r="P38" s="91">
+        <f t="shared" si="11"/>
+        <v>55422.25</v>
+      </c>
+      <c r="Q38" s="40">
         <f t="shared" si="10"/>
-        <v>55422.25</v>
-      </c>
-      <c r="Q38" s="51">
-        <f t="shared" si="9"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="R38" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" s="105">
-        <f t="shared" si="11"/>
+      <c r="A39" s="83">
+        <f t="shared" si="12"/>
         <v>26</v>
       </c>
-      <c r="B39" s="153" t="s">
-        <v>99</v>
-      </c>
-      <c r="C39" s="100" t="s">
-        <v>126</v>
-      </c>
-      <c r="D39" s="99"/>
-      <c r="E39" s="96">
+      <c r="B39" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="78" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" s="77"/>
+      <c r="E39" s="74">
         <v>0.55000000000000004</v>
       </c>
-      <c r="F39" s="82">
+      <c r="F39" s="63">
         <v>41250.26</v>
       </c>
-      <c r="G39" s="234">
+      <c r="G39" s="63">
         <f>F39</f>
         <v>41250.26</v>
       </c>
-      <c r="H39" s="97">
+      <c r="H39" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I39" s="97">
+      <c r="I39" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J39" s="104">
+      <c r="J39" s="82">
         <f t="shared" si="4"/>
         <v>26986.793790000003</v>
       </c>
-      <c r="K39" s="104">
+      <c r="K39" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L39" s="104">
+      <c r="L39" s="82">
         <f t="shared" si="5"/>
         <v>1005.526555</v>
       </c>
-      <c r="M39" s="104">
+      <c r="M39" s="82">
         <f t="shared" si="6"/>
         <v>7222.335285000001</v>
       </c>
-      <c r="N39" s="104"/>
-      <c r="O39" s="98">
+      <c r="N39" s="82"/>
+      <c r="O39" s="76">
         <f t="shared" si="7"/>
         <v>35215.26</v>
       </c>
-      <c r="P39" s="113">
+      <c r="P39" s="91">
+        <f t="shared" si="11"/>
+        <v>36271.26</v>
+      </c>
+      <c r="Q39" s="40">
         <f t="shared" si="10"/>
-        <v>36271.26</v>
-      </c>
-      <c r="Q39" s="51">
-        <f t="shared" si="9"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" s="105">
-        <f t="shared" si="11"/>
+      <c r="A40" s="83">
+        <f t="shared" si="12"/>
         <v>27</v>
       </c>
-      <c r="B40" s="153" t="s">
-        <v>98</v>
-      </c>
-      <c r="C40" s="100" t="s">
-        <v>126</v>
-      </c>
-      <c r="D40" s="99"/>
-      <c r="E40" s="96">
+      <c r="B40" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" s="78" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="77"/>
+      <c r="E40" s="74">
         <v>0.53</v>
       </c>
-      <c r="F40" s="82">
+      <c r="F40" s="63">
         <v>39750.269999999997</v>
       </c>
-      <c r="G40" s="234">
+      <c r="G40" s="63">
         <v>40943.269999999997</v>
       </c>
-      <c r="H40" s="97">
+      <c r="H40" s="75">
         <f t="shared" si="0"/>
         <v>-1193</v>
       </c>
-      <c r="I40" s="97">
+      <c r="I40" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J40" s="104">
+      <c r="J40" s="82">
         <f t="shared" si="4"/>
         <v>26005.455834000004</v>
       </c>
-      <c r="K40" s="104">
+      <c r="K40" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L40" s="104">
+      <c r="L40" s="82">
         <f t="shared" si="5"/>
         <v>968.96195300000011</v>
       </c>
-      <c r="M40" s="104">
+      <c r="M40" s="82">
         <f t="shared" si="6"/>
         <v>6959.7049110000007</v>
       </c>
-      <c r="N40" s="104"/>
-      <c r="O40" s="98">
+      <c r="N40" s="82"/>
+      <c r="O40" s="76">
         <f t="shared" si="7"/>
         <v>32741.27</v>
       </c>
-      <c r="P40" s="113">
+      <c r="P40" s="91">
+        <f t="shared" si="11"/>
+        <v>33723.270000000004</v>
+      </c>
+      <c r="Q40" s="40">
         <f t="shared" si="10"/>
-        <v>33723.270000000004</v>
-      </c>
-      <c r="Q40" s="51">
-        <f t="shared" si="9"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" s="105">
-        <f t="shared" si="11"/>
+      <c r="A41" s="83">
+        <f t="shared" si="12"/>
         <v>28</v>
       </c>
-      <c r="B41" s="153" t="s">
-        <v>100</v>
-      </c>
-      <c r="C41" s="100" t="s">
-        <v>140</v>
-      </c>
-      <c r="D41" s="94" t="s">
-        <v>159</v>
-      </c>
-      <c r="E41" s="96">
+      <c r="B41" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="78" t="s">
+        <v>139</v>
+      </c>
+      <c r="D41" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="E41" s="74">
         <v>0.28999999999999998</v>
       </c>
-      <c r="F41" s="82">
+      <c r="F41" s="63">
         <v>19828.28</v>
       </c>
-      <c r="G41" s="234">
+      <c r="G41" s="63">
         <f>F41</f>
         <v>19828.28</v>
       </c>
-      <c r="H41" s="97">
+      <c r="H41" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I41" s="97">
+      <c r="I41" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J41" s="104">
+      <c r="J41" s="82">
         <f t="shared" si="4"/>
         <v>14229.400362</v>
       </c>
-      <c r="K41" s="104">
+      <c r="K41" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L41" s="104">
+      <c r="L41" s="82">
         <f t="shared" si="5"/>
         <v>530.18672900000001</v>
       </c>
-      <c r="M41" s="104">
+      <c r="M41" s="82">
         <f t="shared" si="6"/>
         <v>3808.1404230000003</v>
       </c>
-      <c r="N41" s="104"/>
-      <c r="O41" s="98">
+      <c r="N41" s="82"/>
+      <c r="O41" s="76">
         <f t="shared" si="7"/>
         <v>18568.28</v>
       </c>
-      <c r="P41" s="113">
+      <c r="P41" s="91">
+        <f t="shared" si="11"/>
+        <v>19125.28</v>
+      </c>
+      <c r="Q41" s="40">
         <f t="shared" si="10"/>
-        <v>19125.28</v>
-      </c>
-      <c r="Q41" s="51">
-        <f t="shared" si="9"/>
         <v>0.28000000000000008</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" s="105">
-        <f t="shared" si="11"/>
+      <c r="A42" s="83">
+        <f t="shared" si="12"/>
         <v>29</v>
       </c>
-      <c r="B42" s="153" t="s">
-        <v>101</v>
-      </c>
-      <c r="C42" s="100" t="s">
-        <v>127</v>
-      </c>
-      <c r="D42" s="99" t="s">
-        <v>154</v>
-      </c>
-      <c r="E42" s="96">
+      <c r="B42" s="130" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="78" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42" s="77" t="s">
+        <v>153</v>
+      </c>
+      <c r="E42" s="74">
         <v>0.08</v>
       </c>
-      <c r="F42" s="82">
+      <c r="F42" s="63">
         <v>6000.29</v>
       </c>
-      <c r="G42" s="234">
+      <c r="G42" s="63">
         <f>F42</f>
         <v>6000.29</v>
       </c>
-      <c r="H42" s="97">
+      <c r="H42" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I42" s="97">
+      <c r="I42" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J42" s="104">
+      <c r="J42" s="82">
         <f t="shared" si="4"/>
         <v>3925.3518240000003</v>
       </c>
-      <c r="K42" s="104">
+      <c r="K42" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L42" s="104">
+      <c r="L42" s="82">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M42" s="104">
+      <c r="M42" s="82">
         <f t="shared" si="6"/>
         <v>1050.5214960000001</v>
       </c>
-      <c r="N42" s="104"/>
-      <c r="O42" s="98">
+      <c r="N42" s="82"/>
+      <c r="O42" s="76">
         <f t="shared" si="7"/>
         <v>5122.29</v>
       </c>
-      <c r="P42" s="113">
+      <c r="P42" s="91">
+        <f t="shared" si="11"/>
+        <v>5276.29</v>
+      </c>
+      <c r="Q42" s="40">
         <f t="shared" si="10"/>
-        <v>5276.29</v>
-      </c>
-      <c r="Q42" s="51">
-        <f t="shared" si="9"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" s="105">
-        <f t="shared" si="11"/>
+      <c r="A43" s="83">
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
-      <c r="B43" s="153" t="s">
-        <v>102</v>
-      </c>
-      <c r="C43" s="100" t="s">
-        <v>119</v>
-      </c>
-      <c r="D43" s="99"/>
-      <c r="E43" s="96">
+      <c r="B43" s="130" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="78" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="77"/>
+      <c r="E43" s="74">
         <v>0.08</v>
       </c>
-      <c r="F43" s="82">
+      <c r="F43" s="63">
         <v>6000.3</v>
       </c>
-      <c r="G43" s="234">
+      <c r="G43" s="63">
         <v>6180.3</v>
       </c>
-      <c r="H43" s="97">
+      <c r="H43" s="75">
         <f t="shared" si="0"/>
         <v>-180</v>
       </c>
-      <c r="I43" s="97">
+      <c r="I43" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J43" s="104">
+      <c r="J43" s="82">
         <f t="shared" si="4"/>
         <v>3925.3518240000003</v>
       </c>
-      <c r="K43" s="104">
+      <c r="K43" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L43" s="104">
+      <c r="L43" s="82">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M43" s="104">
+      <c r="M43" s="82">
         <f t="shared" si="6"/>
         <v>1050.5214960000001</v>
       </c>
-      <c r="N43" s="104"/>
-      <c r="O43" s="98">
+      <c r="N43" s="82"/>
+      <c r="O43" s="76">
         <f t="shared" si="7"/>
         <v>4942.3</v>
       </c>
-      <c r="P43" s="113">
+      <c r="P43" s="91">
+        <f t="shared" si="11"/>
+        <v>5090.3</v>
+      </c>
+      <c r="Q43" s="40">
         <f t="shared" si="10"/>
-        <v>5090.3</v>
-      </c>
-      <c r="Q43" s="51">
-        <f t="shared" si="9"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="105">
-        <f t="shared" si="11"/>
+      <c r="A44" s="83">
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
-      <c r="B44" s="153" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" s="100" t="s">
-        <v>122</v>
-      </c>
-      <c r="D44" s="99" t="s">
-        <v>157</v>
-      </c>
-      <c r="E44" s="96">
+      <c r="B44" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" s="78" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="E44" s="74">
         <v>0.08</v>
       </c>
-      <c r="F44" s="82">
+      <c r="F44" s="63">
         <v>11705.31</v>
       </c>
-      <c r="G44" s="234">
+      <c r="G44" s="63">
         <f>F44</f>
         <v>11705.31</v>
       </c>
-      <c r="H44" s="97">
+      <c r="H44" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I44" s="97">
+      <c r="I44" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J44" s="104">
+      <c r="J44" s="82">
         <f t="shared" si="4"/>
         <v>3925.3518240000003</v>
       </c>
-      <c r="K44" s="104">
+      <c r="K44" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L44" s="104">
+      <c r="L44" s="82">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M44" s="104">
+      <c r="M44" s="82">
         <f t="shared" si="6"/>
         <v>1050.5214960000001</v>
       </c>
-      <c r="N44" s="104"/>
-      <c r="O44" s="98">
+      <c r="N44" s="82"/>
+      <c r="O44" s="76">
         <f t="shared" si="7"/>
         <v>5122.3100000000004</v>
       </c>
-      <c r="P44" s="113">
+      <c r="P44" s="91">
+        <f t="shared" si="11"/>
+        <v>5276.31</v>
+      </c>
+      <c r="Q44" s="40">
         <f t="shared" si="10"/>
-        <v>5276.31</v>
-      </c>
-      <c r="Q44" s="51">
-        <f t="shared" si="9"/>
         <v>0.31000000000000011</v>
       </c>
       <c r="R44" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45" s="105">
-        <f t="shared" si="11"/>
+      <c r="A45" s="83">
+        <f t="shared" si="12"/>
         <v>32</v>
       </c>
-      <c r="B45" s="153" t="s">
-        <v>104</v>
-      </c>
-      <c r="C45" s="100" t="s">
-        <v>129</v>
-      </c>
-      <c r="D45" s="99"/>
-      <c r="E45" s="96">
+      <c r="B45" s="130" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="78" t="s">
+        <v>128</v>
+      </c>
+      <c r="D45" s="77"/>
+      <c r="E45" s="74">
         <v>0.08</v>
       </c>
-      <c r="F45" s="82">
+      <c r="F45" s="63">
         <v>6000.32</v>
       </c>
-      <c r="G45" s="234">
+      <c r="G45" s="63">
         <f>F45</f>
         <v>6000.32</v>
       </c>
-      <c r="H45" s="97">
+      <c r="H45" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I45" s="97">
+      <c r="I45" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J45" s="104">
+      <c r="J45" s="82">
         <f t="shared" si="4"/>
         <v>3925.3518240000003</v>
       </c>
-      <c r="K45" s="104">
+      <c r="K45" s="82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L45" s="104">
+      <c r="L45" s="82">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M45" s="104">
+      <c r="M45" s="82">
         <f t="shared" si="6"/>
         <v>1050.5214960000001</v>
       </c>
-      <c r="N45" s="104"/>
-      <c r="O45" s="98">
+      <c r="N45" s="82"/>
+      <c r="O45" s="76">
         <f t="shared" si="7"/>
         <v>5122.32</v>
       </c>
-      <c r="P45" s="113">
+      <c r="P45" s="91">
+        <f t="shared" si="11"/>
+        <v>5276.32</v>
+      </c>
+      <c r="Q45" s="40">
         <f t="shared" si="10"/>
-        <v>5276.32</v>
-      </c>
-      <c r="Q45" s="51">
-        <f t="shared" si="9"/>
         <v>0.32000000000000012</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46" s="105">
-        <f t="shared" si="11"/>
+      <c r="A46" s="83">
+        <f t="shared" si="12"/>
         <v>33</v>
       </c>
-      <c r="B46" s="153" t="s">
-        <v>105</v>
-      </c>
-      <c r="C46" s="100" t="s">
-        <v>141</v>
-      </c>
-      <c r="D46" s="99"/>
-      <c r="E46" s="96">
+      <c r="B46" s="130" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" s="78" t="s">
+        <v>140</v>
+      </c>
+      <c r="D46" s="77"/>
+      <c r="E46" s="74">
         <v>0.08</v>
       </c>
-      <c r="F46" s="82">
+      <c r="F46" s="63">
         <v>18312.330000000002</v>
       </c>
-      <c r="G46" s="82"/>
-      <c r="H46" s="97">
+      <c r="G46" s="63"/>
+      <c r="H46" s="75">
         <f t="shared" si="0"/>
         <v>18312.330000000002</v>
       </c>
-      <c r="I46" s="97"/>
-      <c r="J46" s="104">
+      <c r="I46" s="75"/>
+      <c r="J46" s="82">
         <f t="shared" si="4"/>
         <v>3925.3518240000003</v>
       </c>
-      <c r="K46" s="104">
-        <f t="shared" ref="K46:K59" si="12">F$2*E46/100</f>
-        <v>0</v>
-      </c>
-      <c r="L46" s="104">
+      <c r="K46" s="82">
+        <f t="shared" ref="K46:K59" si="13">F$2*E46/100</f>
+        <v>0</v>
+      </c>
+      <c r="L46" s="82">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M46" s="104">
+      <c r="M46" s="82">
         <f t="shared" si="6"/>
         <v>1050.5214960000001</v>
       </c>
-      <c r="N46" s="104"/>
-      <c r="O46" s="98">
+      <c r="N46" s="82"/>
+      <c r="O46" s="76">
         <f t="shared" si="7"/>
         <v>23434.33</v>
       </c>
-      <c r="P46" s="113">
+      <c r="P46" s="91">
+        <f t="shared" si="11"/>
+        <v>24137.33</v>
+      </c>
+      <c r="Q46" s="40">
         <f t="shared" si="10"/>
-        <v>24137.33</v>
-      </c>
-      <c r="Q46" s="51">
-        <f t="shared" si="9"/>
         <v>0.33000000000000013</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" s="105">
-        <f t="shared" si="11"/>
+      <c r="A47" s="83">
+        <f t="shared" si="12"/>
         <v>34</v>
       </c>
-      <c r="B47" s="153" t="s">
-        <v>106</v>
-      </c>
-      <c r="C47" s="100" t="s">
-        <v>136</v>
-      </c>
-      <c r="D47" s="99"/>
-      <c r="E47" s="96">
+      <c r="B47" s="130" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" s="77"/>
+      <c r="E47" s="74">
         <v>0.08</v>
       </c>
-      <c r="F47" s="82">
+      <c r="F47" s="63">
         <v>6000.34</v>
       </c>
-      <c r="G47" s="234">
+      <c r="G47" s="63">
         <f>F47</f>
         <v>6000.34</v>
       </c>
-      <c r="H47" s="97">
+      <c r="H47" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I47" s="97">
+      <c r="I47" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J47" s="104">
+      <c r="J47" s="82">
         <f t="shared" si="4"/>
         <v>3925.3518240000003</v>
       </c>
-      <c r="K47" s="104">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L47" s="104">
+      <c r="K47" s="82">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L47" s="82">
         <f t="shared" si="5"/>
         <v>146.25840800000003</v>
       </c>
-      <c r="M47" s="104">
+      <c r="M47" s="82">
         <f t="shared" si="6"/>
         <v>1050.5214960000001</v>
       </c>
-      <c r="N47" s="104"/>
-      <c r="O47" s="98">
+      <c r="N47" s="82"/>
+      <c r="O47" s="76">
         <f t="shared" si="7"/>
         <v>5122.34</v>
       </c>
-      <c r="P47" s="113">
+      <c r="P47" s="91">
+        <f t="shared" si="11"/>
+        <v>5276.34</v>
+      </c>
+      <c r="Q47" s="40">
         <f t="shared" si="10"/>
-        <v>5276.34</v>
-      </c>
-      <c r="Q47" s="51">
-        <f t="shared" si="9"/>
         <v>0.34000000000000014</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" s="144">
-        <f t="shared" si="11"/>
+      <c r="A48" s="121">
+        <f t="shared" si="12"/>
         <v>35</v>
       </c>
-      <c r="B48" s="153" t="s">
-        <v>107</v>
-      </c>
-      <c r="C48" s="145" t="s">
-        <v>142</v>
-      </c>
-      <c r="D48" s="146"/>
-      <c r="E48" s="147">
+      <c r="B48" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="122" t="s">
+        <v>141</v>
+      </c>
+      <c r="D48" s="123"/>
+      <c r="E48" s="124">
         <v>0.09</v>
       </c>
-      <c r="F48" s="82">
+      <c r="F48" s="63">
         <v>13563.35</v>
       </c>
-      <c r="G48" s="234">
+      <c r="G48" s="63">
         <v>13563.35</v>
       </c>
-      <c r="H48" s="148">
+      <c r="H48" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I48" s="148">
+      <c r="I48" s="125">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J48" s="104">
+      <c r="J48" s="82">
         <f t="shared" si="4"/>
         <v>4416.020802</v>
       </c>
-      <c r="K48" s="149">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L48" s="104">
+      <c r="K48" s="126">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="82">
         <f t="shared" si="5"/>
         <v>164.54070899999999</v>
       </c>
-      <c r="M48" s="104">
+      <c r="M48" s="82">
         <f t="shared" si="6"/>
         <v>1181.836683</v>
       </c>
-      <c r="N48" s="149"/>
-      <c r="O48" s="98">
+      <c r="N48" s="126"/>
+      <c r="O48" s="76">
         <f t="shared" si="7"/>
         <v>5762.35</v>
       </c>
-      <c r="P48" s="113">
+      <c r="P48" s="91">
+        <f t="shared" si="11"/>
+        <v>5935.35</v>
+      </c>
+      <c r="Q48" s="40">
         <f t="shared" si="10"/>
-        <v>5935.35</v>
-      </c>
-      <c r="Q48" s="51">
-        <f t="shared" si="9"/>
         <v>0.35000000000000014</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="105">
-        <f t="shared" si="11"/>
+      <c r="A49" s="83">
+        <f t="shared" si="12"/>
         <v>36</v>
       </c>
-      <c r="B49" s="153" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" s="99"/>
-      <c r="E49" s="96">
+      <c r="B49" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" s="78" t="s">
+        <v>131</v>
+      </c>
+      <c r="D49" s="77"/>
+      <c r="E49" s="74">
         <v>0.79</v>
       </c>
-      <c r="F49" s="82">
+      <c r="F49" s="63">
         <v>59250.36</v>
       </c>
-      <c r="G49" s="234">
+      <c r="G49" s="63">
         <f>F49</f>
         <v>59250.36</v>
       </c>
-      <c r="H49" s="97">
+      <c r="H49" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I49" s="97">
+      <c r="I49" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J49" s="104">
+      <c r="J49" s="82">
         <f t="shared" si="4"/>
         <v>38762.849262000003</v>
       </c>
-      <c r="K49" s="104">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L49" s="104">
+      <c r="K49" s="82">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L49" s="82">
         <f t="shared" si="5"/>
         <v>1444.3017790000001</v>
       </c>
-      <c r="M49" s="104">
+      <c r="M49" s="82">
         <f t="shared" si="6"/>
         <v>10373.899773000001</v>
       </c>
-      <c r="N49" s="104"/>
-      <c r="O49" s="98">
+      <c r="N49" s="82"/>
+      <c r="O49" s="76">
         <f t="shared" si="7"/>
         <v>50581.36</v>
       </c>
-      <c r="P49" s="113">
+      <c r="P49" s="91">
+        <f t="shared" si="11"/>
+        <v>52098.36</v>
+      </c>
+      <c r="Q49" s="40">
         <f t="shared" si="10"/>
-        <v>52098.36</v>
-      </c>
-      <c r="Q49" s="51">
-        <f t="shared" si="9"/>
         <v>0.36000000000000015</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="105">
-        <f t="shared" si="11"/>
+      <c r="A50" s="83">
+        <f t="shared" si="12"/>
         <v>37</v>
       </c>
-      <c r="B50" s="153" t="s">
-        <v>109</v>
-      </c>
-      <c r="C50" s="100" t="s">
-        <v>137</v>
-      </c>
-      <c r="D50" s="99"/>
-      <c r="E50" s="96">
+      <c r="B50" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="78" t="s">
+        <v>136</v>
+      </c>
+      <c r="D50" s="77"/>
+      <c r="E50" s="74">
         <v>1</v>
       </c>
-      <c r="F50" s="82">
+      <c r="F50" s="63">
         <v>233509.37</v>
       </c>
-      <c r="G50" s="82"/>
-      <c r="H50" s="97">
+      <c r="G50" s="63"/>
+      <c r="H50" s="75">
         <f t="shared" si="0"/>
         <v>233509.37</v>
       </c>
-      <c r="I50" s="97">
+      <c r="I50" s="75">
         <f t="shared" si="3"/>
         <v>7005.2810999999992</v>
       </c>
-      <c r="J50" s="104">
+      <c r="J50" s="82">
         <f t="shared" si="4"/>
         <v>49066.897800000006</v>
       </c>
-      <c r="K50" s="104">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L50" s="104">
+      <c r="K50" s="82">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="82">
         <f t="shared" si="5"/>
         <v>1828.2301</v>
       </c>
-      <c r="M50" s="104">
+      <c r="M50" s="82">
         <f t="shared" si="6"/>
         <v>13131.518700000001</v>
       </c>
-      <c r="N50" s="104"/>
-      <c r="O50" s="98">
+      <c r="N50" s="82"/>
+      <c r="O50" s="76">
         <f t="shared" si="7"/>
         <v>304541.37</v>
       </c>
-      <c r="P50" s="113">
+      <c r="P50" s="91">
+        <f t="shared" si="11"/>
+        <v>313677.37</v>
+      </c>
+      <c r="Q50" s="40">
         <f t="shared" si="10"/>
-        <v>313677.37</v>
-      </c>
-      <c r="Q50" s="51">
-        <f t="shared" si="9"/>
         <v>0.37000000000000016</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="105">
-        <f t="shared" si="11"/>
+      <c r="A51" s="83">
+        <f t="shared" si="12"/>
         <v>38</v>
       </c>
-      <c r="B51" s="153" t="s">
-        <v>110</v>
-      </c>
-      <c r="C51" s="100" t="s">
-        <v>130</v>
-      </c>
-      <c r="D51" s="99"/>
-      <c r="E51" s="96">
+      <c r="B51" s="130" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" s="78" t="s">
+        <v>129</v>
+      </c>
+      <c r="D51" s="77"/>
+      <c r="E51" s="74">
         <v>0.97</v>
       </c>
-      <c r="F51" s="82">
+      <c r="F51" s="63">
         <v>72750.38</v>
       </c>
-      <c r="G51" s="234">
+      <c r="G51" s="63">
         <f>F51</f>
         <v>72750.38</v>
       </c>
-      <c r="H51" s="97">
+      <c r="H51" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I51" s="97">
+      <c r="I51" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J51" s="104">
+      <c r="J51" s="82">
         <f t="shared" si="4"/>
         <v>47594.890866000002</v>
       </c>
-      <c r="K51" s="104">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L51" s="104">
+      <c r="K51" s="82">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L51" s="82">
         <f t="shared" si="5"/>
         <v>1773.3831969999999</v>
       </c>
-      <c r="M51" s="104">
+      <c r="M51" s="82">
         <f t="shared" si="6"/>
         <v>12737.573139000002</v>
       </c>
-      <c r="N51" s="104"/>
-      <c r="O51" s="98">
+      <c r="N51" s="82"/>
+      <c r="O51" s="76">
         <f t="shared" si="7"/>
         <v>62106.38</v>
       </c>
-      <c r="P51" s="113">
+      <c r="P51" s="91">
+        <f t="shared" si="11"/>
+        <v>63969.38</v>
+      </c>
+      <c r="Q51" s="40">
         <f t="shared" si="10"/>
-        <v>63969.38</v>
-      </c>
-      <c r="Q51" s="51">
-        <f t="shared" si="9"/>
         <v>0.38000000000000017</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="105">
-        <f t="shared" si="11"/>
+      <c r="A52" s="83">
+        <f t="shared" si="12"/>
         <v>39</v>
       </c>
-      <c r="B52" s="153" t="s">
-        <v>111</v>
-      </c>
-      <c r="C52" s="100" t="s">
-        <v>143</v>
-      </c>
-      <c r="D52" s="99"/>
-      <c r="E52" s="96">
+      <c r="B52" s="130" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="D52" s="77"/>
+      <c r="E52" s="74">
         <v>0.77</v>
       </c>
-      <c r="F52" s="82">
+      <c r="F52" s="63">
         <v>58231.39</v>
       </c>
-      <c r="G52" s="82">
-        <v>0</v>
-      </c>
-      <c r="H52" s="97">
+      <c r="G52" s="63">
+        <v>0</v>
+      </c>
+      <c r="H52" s="75">
         <f t="shared" si="0"/>
         <v>58231.39</v>
       </c>
-      <c r="I52" s="97">
+      <c r="I52" s="75">
         <f t="shared" si="3"/>
         <v>1746.9416999999999</v>
       </c>
-      <c r="J52" s="104">
+      <c r="J52" s="82">
         <f t="shared" si="4"/>
         <v>37781.511306</v>
       </c>
-      <c r="K52" s="104">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L52" s="104">
+      <c r="K52" s="82">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L52" s="82">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M52" s="104">
+      <c r="M52" s="82">
         <f t="shared" si="6"/>
         <v>10111.269399000001</v>
       </c>
-      <c r="N52" s="104"/>
-      <c r="O52" s="98">
+      <c r="N52" s="82"/>
+      <c r="O52" s="76">
         <f t="shared" si="7"/>
         <v>109279.39</v>
       </c>
-      <c r="P52" s="113">
+      <c r="P52" s="91">
+        <f t="shared" si="11"/>
+        <v>112557.39</v>
+      </c>
+      <c r="Q52" s="40">
         <f t="shared" si="10"/>
-        <v>112557.39</v>
-      </c>
-      <c r="Q52" s="51">
-        <f t="shared" si="9"/>
         <v>0.39000000000000018</v>
       </c>
       <c r="R52" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="105">
-        <f t="shared" si="11"/>
+      <c r="A53" s="83">
+        <f t="shared" si="12"/>
         <v>40</v>
       </c>
-      <c r="B53" s="153" t="s">
-        <v>112</v>
-      </c>
-      <c r="C53" s="100" t="s">
-        <v>144</v>
-      </c>
-      <c r="D53" s="99" t="s">
-        <v>173</v>
-      </c>
-      <c r="E53" s="96">
+      <c r="B53" s="130" t="s">
+        <v>111</v>
+      </c>
+      <c r="C53" s="78" t="s">
+        <v>143</v>
+      </c>
+      <c r="D53" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="E53" s="74">
         <v>0.77</v>
       </c>
-      <c r="F53" s="82">
+      <c r="F53" s="63">
         <v>57750.400000000001</v>
       </c>
-      <c r="G53" s="234">
+      <c r="G53" s="63">
         <f>F53</f>
         <v>57750.400000000001</v>
       </c>
-      <c r="H53" s="97">
+      <c r="H53" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I53" s="97">
+      <c r="I53" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J53" s="104">
+      <c r="J53" s="82">
         <f t="shared" si="4"/>
         <v>37781.511306</v>
       </c>
-      <c r="K53" s="104">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L53" s="104">
+      <c r="K53" s="82">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L53" s="82">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M53" s="104">
+      <c r="M53" s="82">
         <f t="shared" si="6"/>
         <v>10111.269399000001</v>
       </c>
-      <c r="N53" s="104"/>
-      <c r="O53" s="98">
+      <c r="N53" s="82"/>
+      <c r="O53" s="76">
         <f t="shared" si="7"/>
         <v>49301.4</v>
       </c>
-      <c r="P53" s="113">
+      <c r="P53" s="91">
+        <f t="shared" si="11"/>
+        <v>50780.4</v>
+      </c>
+      <c r="Q53" s="40">
         <f t="shared" si="10"/>
-        <v>50780.4</v>
-      </c>
-      <c r="Q53" s="51">
-        <f t="shared" si="9"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="105">
-        <f t="shared" si="11"/>
+      <c r="A54" s="83">
+        <f t="shared" si="12"/>
         <v>41</v>
       </c>
-      <c r="B54" s="153" t="s">
-        <v>113</v>
-      </c>
-      <c r="C54" s="100" t="s">
-        <v>123</v>
-      </c>
-      <c r="D54" s="99" t="s">
-        <v>153</v>
-      </c>
-      <c r="E54" s="96">
+      <c r="B54" s="130" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" s="78" t="s">
+        <v>122</v>
+      </c>
+      <c r="D54" s="77" t="s">
+        <v>152</v>
+      </c>
+      <c r="E54" s="74">
         <v>0.81</v>
       </c>
-      <c r="F54" s="82">
+      <c r="F54" s="63">
         <v>60750.41</v>
       </c>
-      <c r="G54" s="234">
+      <c r="G54" s="63">
         <f>F54</f>
         <v>60750.41</v>
       </c>
-      <c r="H54" s="97">
+      <c r="H54" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I54" s="97">
+      <c r="I54" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J54" s="104">
+      <c r="J54" s="82">
         <f t="shared" si="4"/>
         <v>39744.187218000006</v>
       </c>
-      <c r="K54" s="104">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L54" s="104">
+      <c r="K54" s="82">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L54" s="82">
         <f t="shared" si="5"/>
         <v>1480.866381</v>
       </c>
-      <c r="M54" s="104">
+      <c r="M54" s="82">
         <f t="shared" si="6"/>
         <v>10636.530147000001</v>
       </c>
-      <c r="N54" s="104"/>
-      <c r="O54" s="98">
+      <c r="N54" s="82"/>
+      <c r="O54" s="76">
         <f t="shared" si="7"/>
         <v>51862.41</v>
       </c>
-      <c r="P54" s="113">
+      <c r="P54" s="91">
+        <f t="shared" si="11"/>
+        <v>53418.41</v>
+      </c>
+      <c r="Q54" s="40">
         <f t="shared" si="10"/>
-        <v>53418.41</v>
-      </c>
-      <c r="Q54" s="51">
-        <f t="shared" si="9"/>
         <v>0.4100000000000002</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="105">
-        <f t="shared" si="11"/>
+      <c r="A55" s="83">
+        <f t="shared" si="12"/>
         <v>42</v>
       </c>
-      <c r="B55" s="153" t="s">
-        <v>114</v>
-      </c>
-      <c r="C55" s="100" t="s">
-        <v>144</v>
-      </c>
-      <c r="D55" s="99" t="s">
-        <v>157</v>
-      </c>
-      <c r="E55" s="96">
+      <c r="B55" s="130" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" s="78" t="s">
+        <v>143</v>
+      </c>
+      <c r="D55" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="E55" s="74">
         <v>0.77</v>
       </c>
-      <c r="F55" s="82">
+      <c r="F55" s="63">
         <v>57750.42</v>
       </c>
-      <c r="G55" s="234">
+      <c r="G55" s="63">
         <f>F55</f>
         <v>57750.42</v>
       </c>
-      <c r="H55" s="97">
+      <c r="H55" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I55" s="97"/>
-      <c r="J55" s="104">
+      <c r="I55" s="75"/>
+      <c r="J55" s="82">
         <f t="shared" si="4"/>
         <v>37781.511306</v>
       </c>
-      <c r="K55" s="104">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L55" s="104">
+      <c r="K55" s="82">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="82">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M55" s="104">
+      <c r="M55" s="82">
         <f t="shared" si="6"/>
         <v>10111.269399000001</v>
       </c>
-      <c r="N55" s="104"/>
-      <c r="O55" s="98">
+      <c r="N55" s="82"/>
+      <c r="O55" s="76">
         <f t="shared" si="7"/>
         <v>49301.42</v>
       </c>
-      <c r="P55" s="113">
+      <c r="P55" s="91">
+        <f t="shared" si="11"/>
+        <v>50780.42</v>
+      </c>
+      <c r="Q55" s="40">
         <f t="shared" si="10"/>
-        <v>50780.42</v>
-      </c>
-      <c r="Q55" s="51">
-        <f t="shared" si="9"/>
         <v>0.42000000000000021</v>
       </c>
       <c r="R55" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="105">
-        <f t="shared" si="11"/>
+      <c r="A56" s="83">
+        <f t="shared" si="12"/>
         <v>43</v>
       </c>
-      <c r="B56" s="153" t="s">
-        <v>115</v>
-      </c>
-      <c r="C56" s="100" t="s">
-        <v>137</v>
-      </c>
-      <c r="D56" s="99"/>
-      <c r="E56" s="96">
+      <c r="B56" s="130" t="s">
+        <v>114</v>
+      </c>
+      <c r="C56" s="78" t="s">
+        <v>136</v>
+      </c>
+      <c r="D56" s="77"/>
+      <c r="E56" s="74">
         <v>0.77</v>
       </c>
-      <c r="F56" s="82">
+      <c r="F56" s="63">
         <v>177845.43</v>
       </c>
-      <c r="G56" s="82"/>
-      <c r="H56" s="97">
+      <c r="G56" s="63"/>
+      <c r="H56" s="75">
         <f t="shared" si="0"/>
         <v>177845.43</v>
       </c>
-      <c r="I56" s="97">
+      <c r="I56" s="75">
         <f t="shared" si="3"/>
         <v>5335.3628999999992</v>
       </c>
-      <c r="J56" s="104">
+      <c r="J56" s="82">
         <f t="shared" si="4"/>
         <v>37781.511306</v>
       </c>
-      <c r="K56" s="104">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L56" s="104">
+      <c r="K56" s="82">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L56" s="82">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M56" s="104">
+      <c r="M56" s="82">
         <f t="shared" si="6"/>
         <v>10111.269399000001</v>
       </c>
-      <c r="N56" s="104"/>
-      <c r="O56" s="98">
+      <c r="N56" s="82"/>
+      <c r="O56" s="76">
         <f t="shared" si="7"/>
         <v>232481.43</v>
       </c>
-      <c r="P56" s="113">
+      <c r="P56" s="91">
+        <f t="shared" si="11"/>
+        <v>239455.43</v>
+      </c>
+      <c r="Q56" s="40">
         <f t="shared" si="10"/>
-        <v>239455.43</v>
-      </c>
-      <c r="Q56" s="51">
-        <f t="shared" si="9"/>
         <v>0.43000000000000022</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="105">
-        <f t="shared" si="11"/>
+      <c r="A57" s="83">
+        <f t="shared" si="12"/>
         <v>44</v>
       </c>
-      <c r="B57" s="153" t="s">
-        <v>116</v>
-      </c>
-      <c r="C57" s="100" t="s">
-        <v>131</v>
-      </c>
-      <c r="D57" s="99"/>
-      <c r="E57" s="96">
+      <c r="B57" s="130" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="78" t="s">
+        <v>130</v>
+      </c>
+      <c r="D57" s="77"/>
+      <c r="E57" s="74">
         <v>0.77</v>
       </c>
-      <c r="F57" s="82">
+      <c r="F57" s="63">
         <v>112564.44</v>
       </c>
-      <c r="G57" s="82"/>
-      <c r="H57" s="97">
+      <c r="G57" s="63"/>
+      <c r="H57" s="75">
         <f t="shared" si="0"/>
         <v>112564.44</v>
       </c>
-      <c r="I57" s="97">
+      <c r="I57" s="75">
         <f t="shared" si="3"/>
         <v>3376.9331999999999</v>
       </c>
-      <c r="J57" s="104">
+      <c r="J57" s="82">
         <f t="shared" si="4"/>
         <v>37781.511306</v>
       </c>
-      <c r="K57" s="104">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L57" s="104">
+      <c r="K57" s="82">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L57" s="82">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M57" s="104">
+      <c r="M57" s="82">
         <f t="shared" si="6"/>
         <v>10111.269399000001</v>
       </c>
-      <c r="N57" s="104"/>
-      <c r="O57" s="98">
+      <c r="N57" s="82"/>
+      <c r="O57" s="76">
         <f t="shared" si="7"/>
         <v>165242.44</v>
       </c>
-      <c r="P57" s="113">
+      <c r="P57" s="91">
+        <f t="shared" si="11"/>
+        <v>170199.44</v>
+      </c>
+      <c r="Q57" s="40">
         <f t="shared" si="10"/>
-        <v>170199.44</v>
-      </c>
-      <c r="Q57" s="51">
-        <f t="shared" si="9"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="105">
-        <f t="shared" si="11"/>
+      <c r="A58" s="83">
+        <f t="shared" si="12"/>
         <v>45</v>
       </c>
-      <c r="B58" s="153" t="s">
-        <v>117</v>
-      </c>
-      <c r="C58" s="100" t="s">
-        <v>123</v>
-      </c>
-      <c r="D58" s="99" t="s">
-        <v>152</v>
-      </c>
-      <c r="E58" s="96">
+      <c r="B58" s="130" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" s="78" t="s">
+        <v>122</v>
+      </c>
+      <c r="D58" s="77" t="s">
+        <v>151</v>
+      </c>
+      <c r="E58" s="74">
         <v>0.77</v>
       </c>
-      <c r="F58" s="82">
+      <c r="F58" s="63">
         <v>57750.45</v>
       </c>
-      <c r="G58" s="234">
+      <c r="G58" s="63">
         <f>F58</f>
         <v>57750.45</v>
       </c>
-      <c r="H58" s="97">
+      <c r="H58" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I58" s="97">
+      <c r="I58" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J58" s="104">
+      <c r="J58" s="82">
         <f t="shared" si="4"/>
         <v>37781.511306</v>
       </c>
-      <c r="K58" s="104">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L58" s="104">
+      <c r="K58" s="82">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L58" s="82">
         <f t="shared" si="5"/>
         <v>1407.737177</v>
       </c>
-      <c r="M58" s="104">
+      <c r="M58" s="82">
         <f t="shared" si="6"/>
         <v>10111.269399000001</v>
       </c>
-      <c r="N58" s="104"/>
-      <c r="O58" s="98">
+      <c r="N58" s="82"/>
+      <c r="O58" s="76">
         <f t="shared" si="7"/>
         <v>49301.45</v>
       </c>
-      <c r="P58" s="113">
+      <c r="P58" s="91">
+        <f t="shared" si="11"/>
+        <v>50780.45</v>
+      </c>
+      <c r="Q58" s="40">
         <f t="shared" si="10"/>
-        <v>50780.45</v>
-      </c>
-      <c r="Q58" s="51">
-        <f t="shared" si="9"/>
         <v>0.45000000000000023</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="105">
-        <f t="shared" si="11"/>
+      <c r="A59" s="83">
+        <f t="shared" si="12"/>
         <v>46</v>
       </c>
-      <c r="B59" s="153" t="s">
-        <v>118</v>
-      </c>
-      <c r="C59" s="100" t="s">
-        <v>123</v>
-      </c>
-      <c r="D59" s="99"/>
-      <c r="E59" s="96">
+      <c r="B59" s="130" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="78" t="s">
+        <v>122</v>
+      </c>
+      <c r="D59" s="77"/>
+      <c r="E59" s="74">
         <v>0.86</v>
       </c>
-      <c r="F59" s="82">
+      <c r="F59" s="63">
         <v>71628.460000000006</v>
       </c>
-      <c r="G59" s="82">
-        <v>0</v>
-      </c>
-      <c r="H59" s="97">
+      <c r="G59" s="63">
+        <v>0</v>
+      </c>
+      <c r="H59" s="75">
         <f t="shared" si="0"/>
         <v>71628.460000000006</v>
       </c>
-      <c r="I59" s="97">
+      <c r="I59" s="75">
         <f t="shared" si="3"/>
         <v>2148.8538000000003</v>
       </c>
-      <c r="J59" s="104">
+      <c r="J59" s="82">
         <f t="shared" si="4"/>
         <v>42197.532108000007</v>
       </c>
-      <c r="K59" s="104">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L59" s="104">
+      <c r="K59" s="82">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L59" s="82">
         <f t="shared" si="5"/>
         <v>1572.2778860000001</v>
       </c>
-      <c r="M59" s="104">
+      <c r="M59" s="82">
         <f t="shared" si="6"/>
         <v>11293.106082000002</v>
       </c>
-      <c r="N59" s="104"/>
-      <c r="O59" s="98">
+      <c r="N59" s="82"/>
+      <c r="O59" s="76">
         <f t="shared" si="7"/>
         <v>128840.46</v>
       </c>
-      <c r="P59" s="113">
+      <c r="P59" s="91">
+        <f t="shared" si="11"/>
+        <v>132705.46000000002</v>
+      </c>
+      <c r="Q59" s="40">
         <f t="shared" si="10"/>
-        <v>132705.46000000002</v>
-      </c>
-      <c r="Q59" s="51">
-        <f t="shared" si="9"/>
         <v>0.46000000000000024</v>
       </c>
       <c r="R59" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="105"/>
-      <c r="B60" s="153"/>
-      <c r="C60" s="94"/>
-      <c r="D60" s="99"/>
-      <c r="E60" s="96"/>
-      <c r="F60" s="82"/>
-      <c r="G60" s="82"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="104"/>
-      <c r="L60" s="104"/>
-      <c r="M60" s="104"/>
-      <c r="N60" s="104"/>
-      <c r="O60" s="98"/>
-      <c r="P60" s="113"/>
-      <c r="Q60" s="51"/>
+      <c r="A60" s="83"/>
+      <c r="B60" s="130"/>
+      <c r="C60" s="72"/>
+      <c r="D60" s="77"/>
+      <c r="E60" s="74"/>
+      <c r="F60" s="63"/>
+      <c r="G60" s="63"/>
+      <c r="H60" s="75"/>
+      <c r="I60" s="75"/>
+      <c r="J60" s="82"/>
+      <c r="K60" s="82"/>
+      <c r="L60" s="82"/>
+      <c r="M60" s="82"/>
+      <c r="N60" s="82"/>
+      <c r="O60" s="76"/>
+      <c r="P60" s="91"/>
+      <c r="Q60" s="40"/>
     </row>
     <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="106"/>
-      <c r="B61" s="154"/>
-      <c r="C61" s="107"/>
-      <c r="D61" s="107"/>
-      <c r="E61" s="108">
-        <f t="shared" ref="E61:M61" si="13">SUM(E14:E60)</f>
+      <c r="A61" s="84"/>
+      <c r="B61" s="131"/>
+      <c r="C61" s="85"/>
+      <c r="D61" s="85"/>
+      <c r="E61" s="86">
+        <f t="shared" ref="E61:M61" si="14">SUM(E14:E60)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F61" s="109">
-        <f t="shared" si="13"/>
+      <c r="F61" s="87">
+        <f t="shared" si="14"/>
         <v>9639381.8099999987</v>
       </c>
-      <c r="G61" s="110">
+      <c r="G61" s="88">
         <f>SUM(G14:G60)</f>
         <v>6991775.4199999999</v>
       </c>
-      <c r="H61" s="110">
-        <f t="shared" si="13"/>
+      <c r="H61" s="88">
+        <f t="shared" si="14"/>
         <v>2647606.39</v>
       </c>
-      <c r="I61" s="110">
-        <f t="shared" si="13"/>
+      <c r="I61" s="88">
+        <f t="shared" si="14"/>
         <v>85208.790299999979</v>
       </c>
-      <c r="J61" s="111">
-        <f t="shared" si="13"/>
+      <c r="J61" s="89">
+        <f t="shared" si="14"/>
         <v>4906689.7799999956</v>
       </c>
-      <c r="K61" s="111">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="L61" s="111">
-        <f t="shared" si="13"/>
+      <c r="K61" s="89">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L61" s="89">
+        <f t="shared" si="14"/>
         <v>182823.00999999992</v>
       </c>
-      <c r="M61" s="111">
-        <f t="shared" si="13"/>
+      <c r="M61" s="89">
+        <f t="shared" si="14"/>
         <v>1313151.8700000008</v>
       </c>
-      <c r="N61" s="112"/>
-      <c r="O61" s="117">
+      <c r="N61" s="90"/>
+      <c r="O61" s="95">
         <f>SUM(O14:O60)</f>
-        <v>9135494.8100000005</v>
-      </c>
-      <c r="P61" s="114">
+        <v>9178994.8100000005</v>
+      </c>
+      <c r="P61" s="92">
         <f>SUM(P14:P60)</f>
-        <v>9409558.8100000005</v>
+        <v>9454363.8100000005</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C62" s="83"/>
-      <c r="D62" s="83"/>
+      <c r="C62" s="64"/>
+      <c r="D62" s="64"/>
     </row>
     <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="203" t="s">
+      <c r="C64" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="203"/>
-      <c r="E64" s="203"/>
-      <c r="F64" s="203"/>
-      <c r="G64" s="203"/>
-      <c r="H64" s="203"/>
-      <c r="I64" s="203"/>
-      <c r="J64" s="203"/>
-      <c r="K64" s="203"/>
-      <c r="L64" s="203"/>
-      <c r="M64" s="203"/>
-      <c r="N64" s="203"/>
-      <c r="O64" s="203"/>
+      <c r="D64" s="216"/>
+      <c r="E64" s="216"/>
+      <c r="F64" s="216"/>
+      <c r="G64" s="216"/>
+      <c r="H64" s="216"/>
+      <c r="I64" s="216"/>
+      <c r="J64" s="216"/>
+      <c r="K64" s="216"/>
+      <c r="L64" s="216"/>
+      <c r="M64" s="216"/>
+      <c r="N64" s="216"/>
+      <c r="O64" s="216"/>
     </row>
     <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="203"/>
-      <c r="D65" s="203"/>
-      <c r="E65" s="203"/>
-      <c r="F65" s="203"/>
-      <c r="G65" s="203"/>
-      <c r="H65" s="203"/>
-      <c r="I65" s="203"/>
-      <c r="J65" s="203"/>
-      <c r="K65" s="203"/>
-      <c r="L65" s="203"/>
-      <c r="M65" s="203"/>
-      <c r="N65" s="203"/>
-      <c r="O65" s="203"/>
+      <c r="C65" s="216"/>
+      <c r="D65" s="216"/>
+      <c r="E65" s="216"/>
+      <c r="F65" s="216"/>
+      <c r="G65" s="216"/>
+      <c r="H65" s="216"/>
+      <c r="I65" s="216"/>
+      <c r="J65" s="216"/>
+      <c r="K65" s="216"/>
+      <c r="L65" s="216"/>
+      <c r="M65" s="216"/>
+      <c r="N65" s="216"/>
+      <c r="O65" s="216"/>
     </row>
     <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="203"/>
-      <c r="D66" s="203"/>
-      <c r="E66" s="203"/>
-      <c r="F66" s="203"/>
-      <c r="G66" s="203"/>
-      <c r="H66" s="203"/>
-      <c r="I66" s="203"/>
-      <c r="J66" s="203"/>
-      <c r="K66" s="203"/>
-      <c r="L66" s="203"/>
-      <c r="M66" s="203"/>
-      <c r="N66" s="203"/>
-      <c r="O66" s="203"/>
+      <c r="C66" s="216"/>
+      <c r="D66" s="216"/>
+      <c r="E66" s="216"/>
+      <c r="F66" s="216"/>
+      <c r="G66" s="216"/>
+      <c r="H66" s="216"/>
+      <c r="I66" s="216"/>
+      <c r="J66" s="216"/>
+      <c r="K66" s="216"/>
+      <c r="L66" s="216"/>
+      <c r="M66" s="216"/>
+      <c r="N66" s="216"/>
+      <c r="O66" s="216"/>
     </row>
     <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="203"/>
-      <c r="D67" s="203"/>
-      <c r="E67" s="203"/>
-      <c r="F67" s="203"/>
-      <c r="G67" s="203"/>
-      <c r="H67" s="203"/>
-      <c r="I67" s="203"/>
-      <c r="J67" s="203"/>
-      <c r="K67" s="203"/>
-      <c r="L67" s="203"/>
-      <c r="M67" s="203"/>
-      <c r="N67" s="203"/>
-      <c r="O67" s="203"/>
+      <c r="C67" s="216"/>
+      <c r="D67" s="216"/>
+      <c r="E67" s="216"/>
+      <c r="F67" s="216"/>
+      <c r="G67" s="216"/>
+      <c r="H67" s="216"/>
+      <c r="I67" s="216"/>
+      <c r="J67" s="216"/>
+      <c r="K67" s="216"/>
+      <c r="L67" s="216"/>
+      <c r="M67" s="216"/>
+      <c r="N67" s="216"/>
+      <c r="O67" s="216"/>
     </row>
     <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="203"/>
-      <c r="D68" s="203"/>
-      <c r="E68" s="203"/>
-      <c r="F68" s="203"/>
-      <c r="G68" s="203"/>
-      <c r="H68" s="203"/>
-      <c r="I68" s="203"/>
-      <c r="J68" s="203"/>
-      <c r="K68" s="203"/>
-      <c r="L68" s="203"/>
-      <c r="M68" s="203"/>
-      <c r="N68" s="203"/>
-      <c r="O68" s="203"/>
+      <c r="C68" s="216"/>
+      <c r="D68" s="216"/>
+      <c r="E68" s="216"/>
+      <c r="F68" s="216"/>
+      <c r="G68" s="216"/>
+      <c r="H68" s="216"/>
+      <c r="I68" s="216"/>
+      <c r="J68" s="216"/>
+      <c r="K68" s="216"/>
+      <c r="L68" s="216"/>
+      <c r="M68" s="216"/>
+      <c r="N68" s="216"/>
+      <c r="O68" s="216"/>
     </row>
     <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="203"/>
-      <c r="D69" s="203"/>
-      <c r="E69" s="203"/>
-      <c r="F69" s="203"/>
-      <c r="G69" s="203"/>
-      <c r="H69" s="203"/>
-      <c r="I69" s="203"/>
-      <c r="J69" s="203"/>
-      <c r="K69" s="203"/>
-      <c r="L69" s="203"/>
-      <c r="M69" s="203"/>
-      <c r="N69" s="203"/>
-      <c r="O69" s="203"/>
+      <c r="C69" s="216"/>
+      <c r="D69" s="216"/>
+      <c r="E69" s="216"/>
+      <c r="F69" s="216"/>
+      <c r="G69" s="216"/>
+      <c r="H69" s="216"/>
+      <c r="I69" s="216"/>
+      <c r="J69" s="216"/>
+      <c r="K69" s="216"/>
+      <c r="L69" s="216"/>
+      <c r="M69" s="216"/>
+      <c r="N69" s="216"/>
+      <c r="O69" s="216"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
     <mergeCell ref="J1:P5"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="P12:P13"/>
@@ -6769,6 +6899,10 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6786,182 +6920,182 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="21"/>
+      <c r="C3" s="20"/>
     </row>
     <row r="4" spans="3:13" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="138" t="s">
+      <c r="C4" s="116" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="117">
+        <v>1</v>
+      </c>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+    </row>
+    <row r="5" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="139">
-        <v>1</v>
-      </c>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="136"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-    </row>
-    <row r="5" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="140" t="s">
+      <c r="D5" s="119"/>
+      <c r="E5" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="141"/>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>55</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J5" s="115"/>
+      <c r="K5" s="150"/>
+      <c r="L5" s="20"/>
+    </row>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C6" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="H5" t="s">
-        <v>177</v>
-      </c>
-      <c r="J5" s="137"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="21"/>
-    </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C6" s="140" t="s">
+      <c r="D6" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="141" t="s">
+      <c r="E6" t="s">
         <v>58</v>
-      </c>
-      <c r="E6" t="s">
-        <v>59</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>176</v>
-      </c>
-      <c r="J6" s="137"/>
-      <c r="K6" s="233"/>
-      <c r="L6" s="21"/>
+        <v>175</v>
+      </c>
+      <c r="J6" s="115"/>
+      <c r="K6" s="150"/>
+      <c r="L6" s="20"/>
     </row>
     <row r="7" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="J7" s="137"/>
-      <c r="K7" s="233"/>
-      <c r="L7" s="21"/>
+      <c r="C7" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="115"/>
+      <c r="K7" s="150"/>
+      <c r="L7" s="20"/>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C8" s="227" t="s">
-        <v>178</v>
-      </c>
-      <c r="D8" s="228"/>
-      <c r="E8" s="228"/>
-      <c r="F8" s="228"/>
-      <c r="G8" s="228"/>
-      <c r="H8" s="228"/>
-      <c r="I8" s="228"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
+      <c r="C8" s="251" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="252"/>
+      <c r="E8" s="252"/>
+      <c r="F8" s="252"/>
+      <c r="G8" s="252"/>
+      <c r="H8" s="252"/>
+      <c r="I8" s="252"/>
+      <c r="J8" s="253"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
     </row>
     <row r="9" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="230"/>
-      <c r="D9" s="231"/>
-      <c r="E9" s="231"/>
-      <c r="F9" s="231"/>
-      <c r="G9" s="231"/>
-      <c r="H9" s="231"/>
-      <c r="I9" s="231"/>
-      <c r="J9" s="232"/>
+      <c r="C9" s="254"/>
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="256"/>
     </row>
     <row r="11" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="172" t="s">
+      <c r="C12" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="147">
+        <v>1</v>
+      </c>
+      <c r="E12" s="113"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="113"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="113"/>
+      <c r="J12" s="114"/>
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C13" s="148" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="173">
-        <v>1</v>
-      </c>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="135"/>
-      <c r="H12" s="135"/>
-      <c r="I12" s="135"/>
-      <c r="J12" s="136"/>
-    </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="174" t="s">
+      <c r="D13" s="149"/>
+      <c r="E13" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="175"/>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>55</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
+        <v>179</v>
+      </c>
+      <c r="J13" s="115"/>
+      <c r="K13" s="150"/>
+      <c r="L13" s="150"/>
+      <c r="M13" s="150"/>
+    </row>
+    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C14" s="148" t="s">
         <v>56</v>
       </c>
-      <c r="H13" t="s">
-        <v>180</v>
-      </c>
-      <c r="J13" s="137"/>
-      <c r="K13" s="233"/>
-      <c r="L13" s="233"/>
-      <c r="M13" s="233"/>
-    </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="174" t="s">
+      <c r="D14" s="149" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="175" t="s">
+      <c r="E14" t="s">
         <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>59</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
       </c>
       <c r="H14" t="s">
+        <v>180</v>
+      </c>
+      <c r="J14" s="115"/>
+      <c r="K14" s="150"/>
+      <c r="L14" s="150"/>
+      <c r="M14" s="150"/>
+    </row>
+    <row r="15" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="115"/>
+      <c r="K15" s="150"/>
+      <c r="L15" s="150"/>
+      <c r="M15" s="150"/>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C16" s="251" t="s">
         <v>181</v>
       </c>
-      <c r="J14" s="137"/>
-      <c r="K14" s="233"/>
-      <c r="L14" s="233"/>
-      <c r="M14" s="233"/>
-    </row>
-    <row r="15" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="J15" s="137"/>
-      <c r="K15" s="233"/>
-      <c r="L15" s="233"/>
-      <c r="M15" s="233"/>
-    </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="227" t="s">
-        <v>182</v>
-      </c>
-      <c r="D16" s="228"/>
-      <c r="E16" s="228"/>
-      <c r="F16" s="228"/>
-      <c r="G16" s="228"/>
-      <c r="H16" s="228"/>
-      <c r="I16" s="228"/>
-      <c r="J16" s="229"/>
-      <c r="K16" s="233"/>
-      <c r="L16" s="233"/>
-      <c r="M16" s="233"/>
+      <c r="D16" s="252"/>
+      <c r="E16" s="252"/>
+      <c r="F16" s="252"/>
+      <c r="G16" s="252"/>
+      <c r="H16" s="252"/>
+      <c r="I16" s="252"/>
+      <c r="J16" s="253"/>
+      <c r="K16" s="150"/>
+      <c r="L16" s="150"/>
+      <c r="M16" s="150"/>
     </row>
     <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="230"/>
-      <c r="D17" s="231"/>
-      <c r="E17" s="231"/>
-      <c r="F17" s="231"/>
-      <c r="G17" s="231"/>
-      <c r="H17" s="231"/>
-      <c r="I17" s="231"/>
-      <c r="J17" s="232"/>
+      <c r="C17" s="254"/>
+      <c r="D17" s="255"/>
+      <c r="E17" s="255"/>
+      <c r="F17" s="255"/>
+      <c r="G17" s="255"/>
+      <c r="H17" s="255"/>
+      <c r="I17" s="255"/>
+      <c r="J17" s="256"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/O HIGGINS 1157/Junio/Junio ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Junio/Junio ohiggins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3745DE5-2287-4812-AD76-97BD6F8CF30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9036379A-E821-4CB9-AF08-70D125706DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -147,10 +147,6 @@
     <t>Total 2do Vto</t>
   </si>
   <si>
-    <t xml:space="preserve">CONS. DE PROP. ITALIA 2156                                                                                                                                                                    
-</t>
-  </si>
-  <si>
     <t>IMPUESTOS</t>
   </si>
   <si>
@@ -691,6 +687,10 @@
   </si>
   <si>
     <t>Gasto particular / SUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONS. DE PROP. O HIGGINS 1157                                                                                                                                                        
+</t>
   </si>
 </sst>
 </file>
@@ -1831,6 +1831,39 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1876,12 +1909,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1908,33 +1935,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2376,7 +2376,7 @@
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="204" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C1" s="204"/>
       <c r="D1" s="204"/>
@@ -2385,7 +2385,7 @@
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -2394,7 +2394,7 @@
     <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="206" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C3" s="206"/>
       <c r="D3" s="206"/>
@@ -2413,10 +2413,10 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2426,18 +2426,18 @@
     </row>
     <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
-        <v>38</v>
+        <v>215</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" s="208" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C8" s="208"/>
     </row>
@@ -2452,7 +2452,7 @@
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="209" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B13" s="209"/>
       <c r="C13" s="209"/>
@@ -2496,7 +2496,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -2505,7 +2505,7 @@
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="210" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B22" s="211"/>
       <c r="C22" s="19"/>
@@ -2517,7 +2517,7 @@
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="200" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="201"/>
       <c r="C23" s="161"/>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="162" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26" s="162"/>
       <c r="C26" s="162"/>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="162"/>
       <c r="C31" s="162"/>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="161" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B32" s="164"/>
       <c r="C32" s="164"/>
@@ -2621,31 +2621,31 @@
         <v>589558.79</v>
       </c>
       <c r="E32" s="101" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F32" s="38"/>
       <c r="G32" s="48"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="161" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B33" s="161" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C33" s="164"/>
       <c r="D33" s="28">
         <v>182823.01</v>
       </c>
       <c r="E33" s="101" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F33" s="38"/>
       <c r="G33" s="48"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="161" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="164"/>
       <c r="C34" s="164"/>
@@ -2653,14 +2653,14 @@
         <v>53956.04</v>
       </c>
       <c r="E34" s="101" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F34" s="38"/>
       <c r="G34" s="48"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="161" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="164"/>
       <c r="C35" s="164"/>
@@ -2676,7 +2676,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="161" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="164"/>
       <c r="C36" s="164"/>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="162" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="162"/>
       <c r="C37" s="162"/>
@@ -2714,7 +2714,7 @@
     </row>
     <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="212" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B39" s="213"/>
       <c r="C39" s="165"/>
@@ -2722,13 +2722,13 @@
         <v>205033.71</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F39" s="38"/>
     </row>
     <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="212" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B40" s="213"/>
       <c r="C40" s="165"/>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="33"/>
@@ -2774,13 +2774,13 @@
         <v>1313151.8700000001</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F43" s="38"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B44" s="167"/>
       <c r="C44" s="33"/>
@@ -2792,7 +2792,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="212" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B45" s="213"/>
       <c r="C45" s="33"/>
@@ -2800,23 +2800,23 @@
         <v>511264.75</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F45" s="38"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="168" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B46" s="169" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C46" s="33"/>
       <c r="D46" s="134">
         <v>62785.37</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F46" s="38"/>
     </row>
@@ -2835,7 +2835,7 @@
     </row>
     <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B48" s="162"/>
       <c r="C48" s="162"/>
@@ -2845,7 +2845,7 @@
     </row>
     <row r="49" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="200" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B49" s="201"/>
       <c r="C49" s="33"/>
@@ -2857,7 +2857,7 @@
     </row>
     <row r="50" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="170" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B50" s="171"/>
       <c r="C50" s="161"/>
@@ -2865,13 +2865,13 @@
         <v>332362.82</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F50" s="138"/>
     </row>
     <row r="51" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="172" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B51" s="171"/>
       <c r="C51" s="161"/>
@@ -2879,13 +2879,13 @@
         <v>810000</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F51" s="138"/>
     </row>
     <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="214" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B52" s="215"/>
       <c r="C52" s="161"/>
@@ -2893,13 +2893,13 @@
         <v>180000</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F52" s="138"/>
     </row>
     <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="172" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B53" s="171"/>
       <c r="C53" s="161"/>
@@ -2907,13 +2907,13 @@
         <v>60000</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F53" s="38"/>
     </row>
     <row r="54" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="200" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B54" s="201"/>
       <c r="C54" s="161"/>
@@ -2921,13 +2921,13 @@
         <v>40000</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F54" s="38"/>
     </row>
     <row r="55" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="172" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B55" s="171"/>
       <c r="C55" s="161"/>
@@ -2935,7 +2935,7 @@
         <v>31000</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F55" s="138"/>
     </row>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="200" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B58" s="201"/>
       <c r="C58" s="161"/>
@@ -2976,10 +2976,10 @@
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="172" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B59" s="171" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C59" s="161"/>
       <c r="D59" s="133">
@@ -3013,7 +3013,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B62" s="174"/>
       <c r="C62" s="174"/>
@@ -3025,7 +3025,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B63" s="174"/>
       <c r="C63" s="174"/>
@@ -3141,7 +3141,7 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="188" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B75" s="189"/>
       <c r="C75" s="189"/>
@@ -3271,7 +3271,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="192" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B87" s="193">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="165" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B88" s="194">
         <v>6500000</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="90" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="195" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B90" s="196">
         <f>B88</f>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="93" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="192" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B93" s="193">
         <v>231400</v>
@@ -3344,7 +3344,7 @@
     </row>
     <row r="94" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="165" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B94" s="194">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="95" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="165" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B95" s="139"/>
       <c r="C95" s="38"/>
@@ -3366,7 +3366,7 @@
     </row>
     <row r="96" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="195" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B96" s="196">
         <f>SUM(B93:B95)</f>
@@ -3387,7 +3387,7 @@
     </row>
     <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="192" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B98" s="193">
         <v>64328</v>
@@ -3399,7 +3399,7 @@
     </row>
     <row r="99" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="165" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B99" s="194">
         <v>0</v>
@@ -3411,7 +3411,7 @@
     </row>
     <row r="100" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="165" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B100" s="139">
         <v>-5910</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="101" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="195" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B101" s="196">
         <f>SUM(B98:B100)</f>
@@ -3443,7 +3443,7 @@
     </row>
     <row r="103" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="112" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B103" s="51">
         <v>3986543.73</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B104" s="140">
         <f>-B82-B83</f>
@@ -3489,7 +3489,7 @@
     </row>
     <row r="107" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B107" s="96">
         <v>-6500000</v>
@@ -3500,7 +3500,7 @@
     </row>
     <row r="108" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B108" s="139">
         <v>2026301.37</v>
@@ -3511,7 +3511,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B109" s="96">
         <v>-4703</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="110" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B110" s="96">
         <v>-156782</v>
@@ -3533,7 +3533,7 @@
     </row>
     <row r="111" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B111" s="55">
         <f>SUM(B103:C110)</f>
@@ -3546,7 +3546,7 @@
     <row r="112" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="113" spans="1:13" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="141" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B113" s="142">
         <f>B111+B96</f>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="117" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="56" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B117" s="79">
         <v>160000</v>
@@ -3650,23 +3650,23 @@
       <c r="G1" s="127"/>
       <c r="H1" s="127"/>
       <c r="I1" s="127"/>
-      <c r="J1" s="242" t="str">
+      <c r="J1" s="216" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="242"/>
-      <c r="L1" s="242"/>
-      <c r="M1" s="242"/>
-      <c r="N1" s="242"/>
-      <c r="O1" s="242"/>
-      <c r="P1" s="243"/>
+      <c r="K1" s="216"/>
+      <c r="L1" s="216"/>
+      <c r="M1" s="216"/>
+      <c r="N1" s="216"/>
+      <c r="O1" s="216"/>
+      <c r="P1" s="217"/>
     </row>
     <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B2" s="128"/>
       <c r="C2" s="144">
@@ -3675,17 +3675,17 @@
       </c>
       <c r="D2" s="68"/>
       <c r="E2" s="68"/>
-      <c r="F2" s="250"/>
-      <c r="G2" s="250"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="226"/>
       <c r="H2" s="68"/>
       <c r="I2" s="68"/>
-      <c r="J2" s="244"/>
-      <c r="K2" s="244"/>
-      <c r="L2" s="244"/>
-      <c r="M2" s="244"/>
-      <c r="N2" s="244"/>
-      <c r="O2" s="244"/>
-      <c r="P2" s="245"/>
+      <c r="J2" s="218"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="218"/>
+      <c r="M2" s="218"/>
+      <c r="N2" s="218"/>
+      <c r="O2" s="218"/>
+      <c r="P2" s="219"/>
       <c r="Q2" s="62"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3702,19 +3702,19 @@
       <c r="G3" s="132"/>
       <c r="H3" s="68"/>
       <c r="I3" s="68"/>
-      <c r="J3" s="244"/>
-      <c r="K3" s="244"/>
-      <c r="L3" s="244"/>
-      <c r="M3" s="244"/>
-      <c r="N3" s="244"/>
-      <c r="O3" s="244"/>
-      <c r="P3" s="245"/>
+      <c r="J3" s="218"/>
+      <c r="K3" s="218"/>
+      <c r="L3" s="218"/>
+      <c r="M3" s="218"/>
+      <c r="N3" s="218"/>
+      <c r="O3" s="218"/>
+      <c r="P3" s="219"/>
       <c r="Q3" s="62"/>
       <c r="R3" s="40"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B4" s="128"/>
       <c r="C4" s="144">
@@ -3726,19 +3726,19 @@
       <c r="G4" s="132"/>
       <c r="H4" s="68"/>
       <c r="I4" s="68"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="M4" s="244"/>
-      <c r="N4" s="244"/>
-      <c r="O4" s="244"/>
-      <c r="P4" s="245"/>
+      <c r="J4" s="218"/>
+      <c r="K4" s="218"/>
+      <c r="L4" s="218"/>
+      <c r="M4" s="218"/>
+      <c r="N4" s="218"/>
+      <c r="O4" s="218"/>
+      <c r="P4" s="219"/>
       <c r="Q4" s="62"/>
       <c r="R4" s="40"/>
     </row>
     <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="143" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B5" s="129"/>
       <c r="C5" s="145">
@@ -3750,211 +3750,211 @@
       <c r="G5" s="70"/>
       <c r="H5" s="69"/>
       <c r="I5" s="69"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="M5" s="246"/>
-      <c r="N5" s="246"/>
-      <c r="O5" s="246"/>
-      <c r="P5" s="247"/>
+      <c r="J5" s="220"/>
+      <c r="K5" s="220"/>
+      <c r="L5" s="220"/>
+      <c r="M5" s="220"/>
+      <c r="N5" s="220"/>
+      <c r="O5" s="220"/>
+      <c r="P5" s="221"/>
       <c r="Q5" s="62"/>
     </row>
     <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="217" t="s">
-        <v>171</v>
-      </c>
-      <c r="B6" s="218"/>
-      <c r="C6" s="219"/>
-      <c r="D6" s="219"/>
-      <c r="E6" s="219"/>
-      <c r="F6" s="219"/>
-      <c r="G6" s="219"/>
-      <c r="H6" s="219"/>
-      <c r="I6" s="219"/>
-      <c r="J6" s="219"/>
-      <c r="K6" s="219"/>
-      <c r="L6" s="219"/>
-      <c r="M6" s="219"/>
-      <c r="N6" s="219"/>
-      <c r="O6" s="219"/>
-      <c r="P6" s="220"/>
+      <c r="A6" s="228" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="229"/>
+      <c r="C6" s="230"/>
+      <c r="D6" s="230"/>
+      <c r="E6" s="230"/>
+      <c r="F6" s="230"/>
+      <c r="G6" s="230"/>
+      <c r="H6" s="230"/>
+      <c r="I6" s="230"/>
+      <c r="J6" s="230"/>
+      <c r="K6" s="230"/>
+      <c r="L6" s="230"/>
+      <c r="M6" s="230"/>
+      <c r="N6" s="230"/>
+      <c r="O6" s="230"/>
+      <c r="P6" s="231"/>
       <c r="Q6" s="62"/>
     </row>
     <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="221"/>
-      <c r="B7" s="222"/>
-      <c r="C7" s="222"/>
-      <c r="D7" s="222"/>
-      <c r="E7" s="222"/>
-      <c r="F7" s="222"/>
-      <c r="G7" s="222"/>
-      <c r="H7" s="222"/>
-      <c r="I7" s="222"/>
-      <c r="J7" s="222"/>
-      <c r="K7" s="222"/>
-      <c r="L7" s="222"/>
-      <c r="M7" s="222"/>
-      <c r="N7" s="222"/>
-      <c r="O7" s="222"/>
-      <c r="P7" s="223"/>
+      <c r="A7" s="232"/>
+      <c r="B7" s="233"/>
+      <c r="C7" s="233"/>
+      <c r="D7" s="233"/>
+      <c r="E7" s="233"/>
+      <c r="F7" s="233"/>
+      <c r="G7" s="233"/>
+      <c r="H7" s="233"/>
+      <c r="I7" s="233"/>
+      <c r="J7" s="233"/>
+      <c r="K7" s="233"/>
+      <c r="L7" s="233"/>
+      <c r="M7" s="233"/>
+      <c r="N7" s="233"/>
+      <c r="O7" s="233"/>
+      <c r="P7" s="234"/>
       <c r="Q7" s="62"/>
     </row>
     <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="221"/>
-      <c r="B8" s="222"/>
-      <c r="C8" s="222"/>
-      <c r="D8" s="222"/>
-      <c r="E8" s="222"/>
-      <c r="F8" s="222"/>
-      <c r="G8" s="222"/>
-      <c r="H8" s="222"/>
-      <c r="I8" s="222"/>
-      <c r="J8" s="222"/>
-      <c r="K8" s="222"/>
-      <c r="L8" s="222"/>
-      <c r="M8" s="222"/>
-      <c r="N8" s="222"/>
-      <c r="O8" s="222"/>
-      <c r="P8" s="223"/>
+      <c r="A8" s="232"/>
+      <c r="B8" s="233"/>
+      <c r="C8" s="233"/>
+      <c r="D8" s="233"/>
+      <c r="E8" s="233"/>
+      <c r="F8" s="233"/>
+      <c r="G8" s="233"/>
+      <c r="H8" s="233"/>
+      <c r="I8" s="233"/>
+      <c r="J8" s="233"/>
+      <c r="K8" s="233"/>
+      <c r="L8" s="233"/>
+      <c r="M8" s="233"/>
+      <c r="N8" s="233"/>
+      <c r="O8" s="233"/>
+      <c r="P8" s="234"/>
       <c r="Q8" s="62"/>
     </row>
     <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="221"/>
-      <c r="B9" s="222"/>
-      <c r="C9" s="222"/>
-      <c r="D9" s="222"/>
-      <c r="E9" s="222"/>
-      <c r="F9" s="222"/>
-      <c r="G9" s="222"/>
-      <c r="H9" s="222"/>
-      <c r="I9" s="222"/>
-      <c r="J9" s="222"/>
-      <c r="K9" s="222"/>
-      <c r="L9" s="222"/>
-      <c r="M9" s="222"/>
-      <c r="N9" s="222"/>
-      <c r="O9" s="222"/>
-      <c r="P9" s="223"/>
+      <c r="A9" s="232"/>
+      <c r="B9" s="233"/>
+      <c r="C9" s="233"/>
+      <c r="D9" s="233"/>
+      <c r="E9" s="233"/>
+      <c r="F9" s="233"/>
+      <c r="G9" s="233"/>
+      <c r="H9" s="233"/>
+      <c r="I9" s="233"/>
+      <c r="J9" s="233"/>
+      <c r="K9" s="233"/>
+      <c r="L9" s="233"/>
+      <c r="M9" s="233"/>
+      <c r="N9" s="233"/>
+      <c r="O9" s="233"/>
+      <c r="P9" s="234"/>
       <c r="Q9" s="62"/>
     </row>
     <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="224"/>
-      <c r="B10" s="225"/>
-      <c r="C10" s="225"/>
-      <c r="D10" s="225"/>
-      <c r="E10" s="225"/>
-      <c r="F10" s="225"/>
-      <c r="G10" s="225"/>
-      <c r="H10" s="225"/>
-      <c r="I10" s="225"/>
-      <c r="J10" s="225"/>
-      <c r="K10" s="225"/>
-      <c r="L10" s="225"/>
-      <c r="M10" s="225"/>
-      <c r="N10" s="225"/>
-      <c r="O10" s="225"/>
-      <c r="P10" s="226"/>
+      <c r="A10" s="235"/>
+      <c r="B10" s="236"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="236"/>
+      <c r="E10" s="236"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="236"/>
+      <c r="H10" s="236"/>
+      <c r="I10" s="236"/>
+      <c r="J10" s="236"/>
+      <c r="K10" s="236"/>
+      <c r="L10" s="236"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="236"/>
+      <c r="O10" s="236"/>
+      <c r="P10" s="237"/>
     </row>
     <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="235" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="236"/>
-      <c r="C11" s="236"/>
-      <c r="D11" s="236"/>
-      <c r="E11" s="236"/>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="236"/>
-      <c r="I11" s="236"/>
-      <c r="J11" s="236"/>
-      <c r="K11" s="236"/>
-      <c r="L11" s="236"/>
-      <c r="M11" s="236"/>
-      <c r="N11" s="236"/>
-      <c r="O11" s="236"/>
-      <c r="P11" s="237"/>
+      <c r="A11" s="244" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="245"/>
+      <c r="C11" s="245"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
+      <c r="I11" s="245"/>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="245"/>
+      <c r="M11" s="245"/>
+      <c r="N11" s="245"/>
+      <c r="O11" s="245"/>
+      <c r="P11" s="246"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="227" t="s">
+      <c r="A12" s="238" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="240" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="229" t="s">
+      <c r="B12" s="249" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="240" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="229" t="s">
+      <c r="D12" s="240" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="229" t="s">
+      <c r="E12" s="240" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="231" t="s">
+      <c r="F12" s="222" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="229" t="s">
+      <c r="G12" s="240" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="233" t="s">
+      <c r="H12" s="242" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="231" t="s">
+      <c r="I12" s="222" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="231" t="s">
+      <c r="J12" s="222" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="231" t="s">
+      <c r="K12" s="222" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="240" t="s">
-        <v>173</v>
-      </c>
-      <c r="M12" s="231" t="s">
-        <v>170</v>
-      </c>
-      <c r="N12" s="238" t="s">
-        <v>215</v>
+      <c r="L12" s="249" t="s">
+        <v>172</v>
+      </c>
+      <c r="M12" s="222" t="s">
+        <v>169</v>
+      </c>
+      <c r="N12" s="247" t="s">
+        <v>214</v>
       </c>
       <c r="O12" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="248" t="s">
+      <c r="P12" s="224" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="228"/>
-      <c r="B13" s="241"/>
-      <c r="C13" s="230"/>
-      <c r="D13" s="230"/>
-      <c r="E13" s="230"/>
-      <c r="F13" s="232"/>
-      <c r="G13" s="230"/>
-      <c r="H13" s="234"/>
-      <c r="I13" s="232"/>
-      <c r="J13" s="232"/>
-      <c r="K13" s="232"/>
-      <c r="L13" s="241"/>
-      <c r="M13" s="232"/>
-      <c r="N13" s="239"/>
+      <c r="A13" s="239"/>
+      <c r="B13" s="250"/>
+      <c r="C13" s="241"/>
+      <c r="D13" s="241"/>
+      <c r="E13" s="241"/>
+      <c r="F13" s="223"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="243"/>
+      <c r="I13" s="223"/>
+      <c r="J13" s="223"/>
+      <c r="K13" s="223"/>
+      <c r="L13" s="250"/>
+      <c r="M13" s="223"/>
+      <c r="N13" s="248"/>
       <c r="O13" s="94" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="P13" s="249"/>
+      <c r="P13" s="225"/>
     </row>
     <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="83">
         <v>1</v>
       </c>
       <c r="B14" s="130" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C14" s="72" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D14" s="72"/>
       <c r="E14" s="74">
@@ -4009,13 +4009,13 @@
         <v>2</v>
       </c>
       <c r="B15" s="130" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D15" s="72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E15" s="74">
         <v>3.4</v>
@@ -4070,13 +4070,13 @@
         <v>3</v>
       </c>
       <c r="B16" s="130" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" s="72" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D16" s="72" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E16" s="74">
         <v>2.54</v>
@@ -4125,7 +4125,7 @@
         <v>0.03</v>
       </c>
       <c r="R16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4133,13 +4133,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="130" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="72" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D17" s="77" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E17" s="74">
         <v>5.19</v>
@@ -4189,7 +4189,7 @@
         <v>0.04</v>
       </c>
       <c r="R17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4197,13 +4197,13 @@
         <v>5</v>
       </c>
       <c r="B18" s="130" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" s="72" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D18" s="77" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E18" s="74">
         <v>3.4</v>
@@ -4258,13 +4258,13 @@
         <v>6</v>
       </c>
       <c r="B19" s="130" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D19" s="72" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E19" s="74">
         <v>2.54</v>
@@ -4319,10 +4319,10 @@
         <v>7</v>
       </c>
       <c r="B20" s="130" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C20" s="72" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D20" s="72"/>
       <c r="E20" s="74">
@@ -4378,10 +4378,10 @@
         <v>8</v>
       </c>
       <c r="B21" s="130" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" s="72" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D21" s="77"/>
       <c r="E21" s="74">
@@ -4437,13 +4437,13 @@
         <v>9</v>
       </c>
       <c r="B22" s="130" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C22" s="72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D22" s="77" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E22" s="74">
         <v>2.54</v>
@@ -4498,10 +4498,10 @@
         <v>10</v>
       </c>
       <c r="B23" s="130" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23" s="72" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D23" s="77"/>
       <c r="E23" s="74">
@@ -4557,13 +4557,13 @@
         <v>11</v>
       </c>
       <c r="B24" s="130" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C24" s="72" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D24" s="77" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E24" s="74">
         <v>3.4</v>
@@ -4618,13 +4618,13 @@
         <v>12</v>
       </c>
       <c r="B25" s="130" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C25" s="72" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D25" s="77" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E25" s="74">
         <v>2.54</v>
@@ -4679,10 +4679,10 @@
         <v>13</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D26" s="154"/>
       <c r="E26" s="155">
@@ -4738,10 +4738,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="152" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C27" s="153" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D27" s="154"/>
       <c r="E27" s="155">
@@ -4797,13 +4797,13 @@
         <v>15</v>
       </c>
       <c r="B28" s="130" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C28" s="72" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" s="72" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E28" s="74">
         <v>2.54</v>
@@ -4858,10 +4858,10 @@
         <v>16</v>
       </c>
       <c r="B29" s="130" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C29" s="72" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D29" s="72"/>
       <c r="E29" s="74">
@@ -4917,13 +4917,13 @@
         <v>17</v>
       </c>
       <c r="B30" s="130" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C30" s="72" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D30" s="77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E30" s="74">
         <v>3.4</v>
@@ -4978,10 +4978,10 @@
         <v>18</v>
       </c>
       <c r="B31" s="130" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C31" s="72" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D31" s="73"/>
       <c r="E31" s="74">
@@ -5034,10 +5034,10 @@
         <v>19</v>
       </c>
       <c r="B32" s="130" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C32" s="72" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D32" s="77"/>
       <c r="E32" s="74">
@@ -5094,10 +5094,10 @@
         <v>20</v>
       </c>
       <c r="B33" s="130" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C33" s="72" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D33" s="77"/>
       <c r="E33" s="74">
@@ -5150,13 +5150,13 @@
         <v>21</v>
       </c>
       <c r="B34" s="130" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C34" s="78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D34" s="77" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E34" s="74">
         <v>2.54</v>
@@ -5212,13 +5212,13 @@
         <v>22</v>
       </c>
       <c r="B35" s="130" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C35" s="78" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D35" s="77" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E35" s="74">
         <v>4.9400000000000004</v>
@@ -5274,13 +5274,13 @@
         <v>23</v>
       </c>
       <c r="B36" s="130" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C36" s="78" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D36" s="77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E36" s="74">
         <v>3.28</v>
@@ -5335,10 +5335,10 @@
         <v>24</v>
       </c>
       <c r="B37" s="130" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C37" s="78" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D37" s="77"/>
       <c r="E37" s="74">
@@ -5395,10 +5395,10 @@
         <v>25</v>
       </c>
       <c r="B38" s="130" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C38" s="78" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D38" s="77"/>
       <c r="E38" s="74">
@@ -5448,7 +5448,7 @@
         <v>0.25000000000000006</v>
       </c>
       <c r="R38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -5457,10 +5457,10 @@
         <v>26</v>
       </c>
       <c r="B39" s="130" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C39" s="78" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D39" s="77"/>
       <c r="E39" s="74">
@@ -5517,10 +5517,10 @@
         <v>27</v>
       </c>
       <c r="B40" s="130" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C40" s="78" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D40" s="77"/>
       <c r="E40" s="74">
@@ -5576,13 +5576,13 @@
         <v>28</v>
       </c>
       <c r="B41" s="130" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C41" s="78" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D41" s="72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E41" s="74">
         <v>0.28999999999999998</v>
@@ -5638,13 +5638,13 @@
         <v>29</v>
       </c>
       <c r="B42" s="130" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C42" s="78" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D42" s="77" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E42" s="74">
         <v>0.08</v>
@@ -5700,10 +5700,10 @@
         <v>30</v>
       </c>
       <c r="B43" s="130" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C43" s="78" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D43" s="77"/>
       <c r="E43" s="74">
@@ -5759,13 +5759,13 @@
         <v>31</v>
       </c>
       <c r="B44" s="130" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C44" s="78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D44" s="77" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E44" s="74">
         <v>0.08</v>
@@ -5815,7 +5815,7 @@
         <v>0.31000000000000011</v>
       </c>
       <c r="R44" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -5824,10 +5824,10 @@
         <v>32</v>
       </c>
       <c r="B45" s="130" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C45" s="78" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D45" s="77"/>
       <c r="E45" s="74">
@@ -5884,10 +5884,10 @@
         <v>33</v>
       </c>
       <c r="B46" s="130" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C46" s="78" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D46" s="77"/>
       <c r="E46" s="74">
@@ -5938,10 +5938,10 @@
         <v>34</v>
       </c>
       <c r="B47" s="130" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C47" s="78" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D47" s="77"/>
       <c r="E47" s="74">
@@ -5998,10 +5998,10 @@
         <v>35</v>
       </c>
       <c r="B48" s="130" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C48" s="122" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D48" s="123"/>
       <c r="E48" s="124">
@@ -6057,10 +6057,10 @@
         <v>36</v>
       </c>
       <c r="B49" s="130" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C49" s="78" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D49" s="77"/>
       <c r="E49" s="74">
@@ -6117,10 +6117,10 @@
         <v>37</v>
       </c>
       <c r="B50" s="130" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C50" s="78" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D50" s="77"/>
       <c r="E50" s="74">
@@ -6174,10 +6174,10 @@
         <v>38</v>
       </c>
       <c r="B51" s="130" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C51" s="78" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D51" s="77"/>
       <c r="E51" s="74">
@@ -6234,10 +6234,10 @@
         <v>39</v>
       </c>
       <c r="B52" s="130" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C52" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D52" s="77"/>
       <c r="E52" s="74">
@@ -6287,7 +6287,7 @@
         <v>0.39000000000000018</v>
       </c>
       <c r="R52" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
@@ -6296,13 +6296,13 @@
         <v>40</v>
       </c>
       <c r="B53" s="130" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C53" s="78" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D53" s="77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E53" s="74">
         <v>0.77</v>
@@ -6358,13 +6358,13 @@
         <v>41</v>
       </c>
       <c r="B54" s="130" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C54" s="78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D54" s="77" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E54" s="74">
         <v>0.81</v>
@@ -6420,13 +6420,13 @@
         <v>42</v>
       </c>
       <c r="B55" s="130" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C55" s="78" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D55" s="77" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E55" s="74">
         <v>0.77</v>
@@ -6473,7 +6473,7 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="R55" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
@@ -6482,10 +6482,10 @@
         <v>43</v>
       </c>
       <c r="B56" s="130" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C56" s="78" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D56" s="77"/>
       <c r="E56" s="74">
@@ -6539,10 +6539,10 @@
         <v>44</v>
       </c>
       <c r="B57" s="130" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C57" s="78" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D57" s="77"/>
       <c r="E57" s="74">
@@ -6596,13 +6596,13 @@
         <v>45</v>
       </c>
       <c r="B58" s="130" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C58" s="78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D58" s="77" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E58" s="74">
         <v>0.77</v>
@@ -6658,10 +6658,10 @@
         <v>46</v>
       </c>
       <c r="B59" s="130" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C59" s="78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D59" s="77"/>
       <c r="E59" s="74">
@@ -6711,7 +6711,7 @@
         <v>0.46000000000000024</v>
       </c>
       <c r="R59" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
@@ -6790,99 +6790,103 @@
     </row>
     <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="216" t="s">
+      <c r="C64" s="227" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="216"/>
-      <c r="E64" s="216"/>
-      <c r="F64" s="216"/>
-      <c r="G64" s="216"/>
-      <c r="H64" s="216"/>
-      <c r="I64" s="216"/>
-      <c r="J64" s="216"/>
-      <c r="K64" s="216"/>
-      <c r="L64" s="216"/>
-      <c r="M64" s="216"/>
-      <c r="N64" s="216"/>
-      <c r="O64" s="216"/>
+      <c r="D64" s="227"/>
+      <c r="E64" s="227"/>
+      <c r="F64" s="227"/>
+      <c r="G64" s="227"/>
+      <c r="H64" s="227"/>
+      <c r="I64" s="227"/>
+      <c r="J64" s="227"/>
+      <c r="K64" s="227"/>
+      <c r="L64" s="227"/>
+      <c r="M64" s="227"/>
+      <c r="N64" s="227"/>
+      <c r="O64" s="227"/>
     </row>
     <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="216"/>
-      <c r="D65" s="216"/>
-      <c r="E65" s="216"/>
-      <c r="F65" s="216"/>
-      <c r="G65" s="216"/>
-      <c r="H65" s="216"/>
-      <c r="I65" s="216"/>
-      <c r="J65" s="216"/>
-      <c r="K65" s="216"/>
-      <c r="L65" s="216"/>
-      <c r="M65" s="216"/>
-      <c r="N65" s="216"/>
-      <c r="O65" s="216"/>
+      <c r="C65" s="227"/>
+      <c r="D65" s="227"/>
+      <c r="E65" s="227"/>
+      <c r="F65" s="227"/>
+      <c r="G65" s="227"/>
+      <c r="H65" s="227"/>
+      <c r="I65" s="227"/>
+      <c r="J65" s="227"/>
+      <c r="K65" s="227"/>
+      <c r="L65" s="227"/>
+      <c r="M65" s="227"/>
+      <c r="N65" s="227"/>
+      <c r="O65" s="227"/>
     </row>
     <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="216"/>
-      <c r="D66" s="216"/>
-      <c r="E66" s="216"/>
-      <c r="F66" s="216"/>
-      <c r="G66" s="216"/>
-      <c r="H66" s="216"/>
-      <c r="I66" s="216"/>
-      <c r="J66" s="216"/>
-      <c r="K66" s="216"/>
-      <c r="L66" s="216"/>
-      <c r="M66" s="216"/>
-      <c r="N66" s="216"/>
-      <c r="O66" s="216"/>
+      <c r="C66" s="227"/>
+      <c r="D66" s="227"/>
+      <c r="E66" s="227"/>
+      <c r="F66" s="227"/>
+      <c r="G66" s="227"/>
+      <c r="H66" s="227"/>
+      <c r="I66" s="227"/>
+      <c r="J66" s="227"/>
+      <c r="K66" s="227"/>
+      <c r="L66" s="227"/>
+      <c r="M66" s="227"/>
+      <c r="N66" s="227"/>
+      <c r="O66" s="227"/>
     </row>
     <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="216"/>
-      <c r="D67" s="216"/>
-      <c r="E67" s="216"/>
-      <c r="F67" s="216"/>
-      <c r="G67" s="216"/>
-      <c r="H67" s="216"/>
-      <c r="I67" s="216"/>
-      <c r="J67" s="216"/>
-      <c r="K67" s="216"/>
-      <c r="L67" s="216"/>
-      <c r="M67" s="216"/>
-      <c r="N67" s="216"/>
-      <c r="O67" s="216"/>
+      <c r="C67" s="227"/>
+      <c r="D67" s="227"/>
+      <c r="E67" s="227"/>
+      <c r="F67" s="227"/>
+      <c r="G67" s="227"/>
+      <c r="H67" s="227"/>
+      <c r="I67" s="227"/>
+      <c r="J67" s="227"/>
+      <c r="K67" s="227"/>
+      <c r="L67" s="227"/>
+      <c r="M67" s="227"/>
+      <c r="N67" s="227"/>
+      <c r="O67" s="227"/>
     </row>
     <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="216"/>
-      <c r="D68" s="216"/>
-      <c r="E68" s="216"/>
-      <c r="F68" s="216"/>
-      <c r="G68" s="216"/>
-      <c r="H68" s="216"/>
-      <c r="I68" s="216"/>
-      <c r="J68" s="216"/>
-      <c r="K68" s="216"/>
-      <c r="L68" s="216"/>
-      <c r="M68" s="216"/>
-      <c r="N68" s="216"/>
-      <c r="O68" s="216"/>
+      <c r="C68" s="227"/>
+      <c r="D68" s="227"/>
+      <c r="E68" s="227"/>
+      <c r="F68" s="227"/>
+      <c r="G68" s="227"/>
+      <c r="H68" s="227"/>
+      <c r="I68" s="227"/>
+      <c r="J68" s="227"/>
+      <c r="K68" s="227"/>
+      <c r="L68" s="227"/>
+      <c r="M68" s="227"/>
+      <c r="N68" s="227"/>
+      <c r="O68" s="227"/>
     </row>
     <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="216"/>
-      <c r="D69" s="216"/>
-      <c r="E69" s="216"/>
-      <c r="F69" s="216"/>
-      <c r="G69" s="216"/>
-      <c r="H69" s="216"/>
-      <c r="I69" s="216"/>
-      <c r="J69" s="216"/>
-      <c r="K69" s="216"/>
-      <c r="L69" s="216"/>
-      <c r="M69" s="216"/>
-      <c r="N69" s="216"/>
-      <c r="O69" s="216"/>
+      <c r="C69" s="227"/>
+      <c r="D69" s="227"/>
+      <c r="E69" s="227"/>
+      <c r="F69" s="227"/>
+      <c r="G69" s="227"/>
+      <c r="H69" s="227"/>
+      <c r="I69" s="227"/>
+      <c r="J69" s="227"/>
+      <c r="K69" s="227"/>
+      <c r="L69" s="227"/>
+      <c r="M69" s="227"/>
+      <c r="N69" s="227"/>
+      <c r="O69" s="227"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="J1:P5"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="P12:P13"/>
@@ -6899,10 +6903,6 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6924,7 +6924,7 @@
     </row>
     <row r="4" spans="3:13" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="116" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" s="117">
         <v>1</v>
@@ -6940,17 +6940,17 @@
     </row>
     <row r="5" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="118" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" s="119"/>
       <c r="E5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
         <v>54</v>
       </c>
-      <c r="G5" t="s">
-        <v>55</v>
-      </c>
       <c r="H5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J5" s="115"/>
       <c r="K5" s="150"/>
@@ -6958,19 +6958,19 @@
     </row>
     <row r="6" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C6" s="118" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="119" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="119" t="s">
+      <c r="E6" t="s">
         <v>57</v>
-      </c>
-      <c r="E6" t="s">
-        <v>58</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J6" s="115"/>
       <c r="K6" s="150"/>
@@ -6978,7 +6978,7 @@
     </row>
     <row r="7" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J7" s="115"/>
       <c r="K7" s="150"/>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C8" s="251" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D8" s="252"/>
       <c r="E8" s="252"/>
@@ -7011,7 +7011,7 @@
     <row r="11" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C12" s="146" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="147">
         <v>1</v>
@@ -7025,17 +7025,17 @@
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C13" s="148" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="149"/>
       <c r="E13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" t="s">
         <v>54</v>
       </c>
-      <c r="G13" t="s">
-        <v>55</v>
-      </c>
       <c r="H13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J13" s="115"/>
       <c r="K13" s="150"/>
@@ -7044,19 +7044,19 @@
     </row>
     <row r="14" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C14" s="148" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="149" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="149" t="s">
+      <c r="E14" t="s">
         <v>57</v>
-      </c>
-      <c r="E14" t="s">
-        <v>58</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
       </c>
       <c r="H14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J14" s="115"/>
       <c r="K14" s="150"/>
@@ -7065,7 +7065,7 @@
     </row>
     <row r="15" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J15" s="115"/>
       <c r="K15" s="150"/>
@@ -7074,7 +7074,7 @@
     </row>
     <row r="16" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C16" s="251" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D16" s="252"/>
       <c r="E16" s="252"/>

--- a/2026/O HIGGINS 1157/Junio/Junio ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Junio/Junio ohiggins.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9036379A-E821-4CB9-AF08-70D125706DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED020C8F-2C32-473B-B92F-40333CE67632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -22,16 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$118</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="214">
   <si>
     <t>TOTAL</t>
   </si>
@@ -566,25 +561,10 @@
     <t>ARCA P. De pago:</t>
   </si>
   <si>
-    <t>2A , COCHERA 7 Y COCHERA 18</t>
-  </si>
-  <si>
     <t>Estudio M&amp;M</t>
   </si>
   <si>
-    <t>2A , COCHERA 7 Y COCHERA 18 TRANSFIRIO $449.413 EL DIA 04/06</t>
-  </si>
-  <si>
     <t>Myryam Martinez Del Valle</t>
-  </si>
-  <si>
-    <t>Federico Segura</t>
-  </si>
-  <si>
-    <t>1a y coch4</t>
-  </si>
-  <si>
-    <t>Dice que este mes se equivoco y transfirio $183.820 de mas</t>
   </si>
   <si>
     <t>VTO 17/07</t>
@@ -691,6 +671,15 @@
   <si>
     <t xml:space="preserve">CONS. DE PROP. O HIGGINS 1157                                                                                                                                                        
 </t>
+  </si>
+  <si>
+    <t>Cocheras  1, 15 y 22</t>
+  </si>
+  <si>
+    <t>Cocheras  1, 15 y 22 deposito $137.000 el 16/07</t>
+  </si>
+  <si>
+    <t>Pago 77.540,83 el 04/07 y deposito $140.500 el 16/07</t>
   </si>
 </sst>
 </file>
@@ -864,7 +853,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -945,13 +934,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="-0.249977111117893"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1458,7 +1453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1691,25 +1686,20 @@
     <xf numFmtId="44" fontId="1" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="15" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="15" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="15" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="15" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="14" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="14" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="14" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1780,6 +1770,12 @@
     <xf numFmtId="44" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1831,6 +1827,84 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1849,12 +1923,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1864,78 +1932,6 @@
     <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1954,6 +1950,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2037,9 +2040,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2077,9 +2080,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2112,26 +2115,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2164,26 +2150,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2358,31 +2327,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M119"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="204" t="s">
+      <c r="B1" s="203" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="205"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="204"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="10" t="s">
         <v>45</v>
@@ -2391,16 +2360,16 @@
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="56.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="206" t="s">
+      <c r="B3" s="205" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="206"/>
-      <c r="D3" s="206"/>
-      <c r="E3" s="207"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="205"/>
+      <c r="D3" s="205"/>
+      <c r="E3" s="206"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
@@ -2411,12 +2380,12 @@
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2424,9 +2393,9 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="65" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2435,57 +2404,57 @@
       </c>
       <c r="E6" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="208" t="s">
-        <v>181</v>
-      </c>
-      <c r="C8" s="208"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="208"/>
-      <c r="C9" s="208"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="208"/>
-      <c r="C10" s="208"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="209" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="207" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="207"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="207"/>
+      <c r="C9" s="207"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="207"/>
+      <c r="C10" s="207"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="208" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="209"/>
-      <c r="C13" s="209"/>
-      <c r="D13" s="209"/>
-      <c r="E13" s="209"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="209"/>
-      <c r="B14" s="209"/>
-      <c r="C14" s="209"/>
-      <c r="D14" s="209"/>
-      <c r="E14" s="209"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="209"/>
-      <c r="B15" s="209"/>
-      <c r="C15" s="209"/>
-      <c r="D15" s="209"/>
-      <c r="E15" s="209"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="209"/>
-      <c r="B16" s="209"/>
-      <c r="C16" s="209"/>
-      <c r="D16" s="209"/>
-      <c r="E16" s="209"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="208"/>
+      <c r="C13" s="208"/>
+      <c r="D13" s="208"/>
+      <c r="E13" s="208"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="208"/>
+      <c r="B14" s="208"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="208"/>
+      <c r="B15" s="208"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="208"/>
+      <c r="E15" s="208"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="208"/>
+      <c r="B16" s="208"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="208"/>
+      <c r="E16" s="208"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>7</v>
       </c>
@@ -2494,7 +2463,7 @@
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
         <v>61</v>
       </c>
@@ -2503,11 +2472,11 @@
       <c r="D21" s="81"/>
       <c r="E21" s="97"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="210" t="s">
-        <v>195</v>
-      </c>
-      <c r="B22" s="211"/>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="209" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" s="210"/>
       <c r="C22" s="19"/>
       <c r="D22" s="135">
         <v>1987270.86</v>
@@ -2515,12 +2484,12 @@
       <c r="E22" s="98"/>
       <c r="H22" s="20"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="200" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="199" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="201"/>
-      <c r="C23" s="161"/>
+      <c r="B23" s="200"/>
+      <c r="C23" s="156"/>
       <c r="D23" s="135">
         <v>-432231.42</v>
       </c>
@@ -2528,12 +2497,12 @@
       <c r="F23" s="38"/>
       <c r="H23" s="20"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="200" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="199" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="201"/>
-      <c r="C24" s="161"/>
+      <c r="B24" s="200"/>
+      <c r="C24" s="156"/>
       <c r="D24" s="136">
         <v>0.34</v>
       </c>
@@ -2541,12 +2510,12 @@
       <c r="F24" s="38"/>
       <c r="H24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="162" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="162"/>
-      <c r="C25" s="162"/>
+      <c r="B25" s="157"/>
+      <c r="C25" s="157"/>
       <c r="D25" s="22"/>
       <c r="E25" s="99">
         <f>SUM(D22:D24)</f>
@@ -2554,46 +2523,46 @@
       </c>
       <c r="F25" s="38"/>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="162" t="s">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="157" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="162"/>
-      <c r="C26" s="162"/>
+      <c r="B26" s="157"/>
+      <c r="C26" s="157"/>
       <c r="D26" s="22"/>
       <c r="E26" s="100"/>
       <c r="F26" s="38"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="161"/>
-      <c r="B27" s="161"/>
-      <c r="C27" s="161"/>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="156"/>
+      <c r="B27" s="156"/>
+      <c r="C27" s="156"/>
       <c r="D27" s="28"/>
       <c r="E27" s="111"/>
       <c r="F27" s="38"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="161"/>
-      <c r="B28" s="161"/>
-      <c r="C28" s="161"/>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="156"/>
+      <c r="B28" s="156"/>
+      <c r="C28" s="156"/>
       <c r="D28" s="28"/>
       <c r="E28" s="111"/>
       <c r="F28" s="38"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="161"/>
-      <c r="B29" s="161"/>
-      <c r="C29" s="161"/>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="156"/>
+      <c r="B29" s="156"/>
+      <c r="C29" s="156"/>
       <c r="D29" s="28"/>
       <c r="E29" s="111"/>
       <c r="F29" s="38"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="162" t="s">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="163"/>
-      <c r="C30" s="163"/>
+      <c r="B30" s="158"/>
+      <c r="C30" s="158"/>
       <c r="D30" s="71"/>
       <c r="E30" s="102">
         <f>SUM(D27:D29)</f>
@@ -2601,69 +2570,69 @@
       </c>
       <c r="F30" s="38"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="162"/>
-      <c r="C31" s="162"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="157"/>
       <c r="D31" s="22"/>
       <c r="E31" s="100"/>
       <c r="F31" s="38"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="161" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="156" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="164"/>
-      <c r="C32" s="164"/>
+      <c r="B32" s="159"/>
+      <c r="C32" s="159"/>
       <c r="D32" s="28">
         <v>589558.79</v>
       </c>
       <c r="E32" s="101" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F32" s="38"/>
       <c r="G32" s="48"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="161" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="156" t="s">
         <v>147</v>
       </c>
-      <c r="B33" s="161" t="s">
-        <v>192</v>
-      </c>
-      <c r="C33" s="164"/>
+      <c r="B33" s="156" t="s">
+        <v>187</v>
+      </c>
+      <c r="C33" s="159"/>
       <c r="D33" s="28">
         <v>182823.01</v>
       </c>
       <c r="E33" s="101" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F33" s="38"/>
       <c r="G33" s="48"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="161" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="156" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="164"/>
-      <c r="C34" s="164"/>
+      <c r="B34" s="159"/>
+      <c r="C34" s="159"/>
       <c r="D34" s="28">
         <v>53956.04</v>
       </c>
       <c r="E34" s="101" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F34" s="38"/>
       <c r="G34" s="48"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="161" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="156" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="164"/>
-      <c r="C35" s="164"/>
+      <c r="B35" s="159"/>
+      <c r="C35" s="159"/>
       <c r="D35" s="28">
         <v>5995.12</v>
       </c>
@@ -2674,12 +2643,12 @@
       <c r="F35" s="38"/>
       <c r="G35" s="40"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="161" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="156" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="164"/>
-      <c r="C36" s="164"/>
+      <c r="B36" s="159"/>
+      <c r="C36" s="159"/>
       <c r="D36" s="28">
         <v>97494.97</v>
       </c>
@@ -2689,12 +2658,12 @@
       </c>
       <c r="F36" s="38"/>
     </row>
-    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="162" t="s">
+    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="157" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="162"/>
-      <c r="C37" s="162"/>
+      <c r="B37" s="157"/>
+      <c r="C37" s="157"/>
       <c r="D37" s="22"/>
       <c r="E37" s="32">
         <f>SUM(D32:D36)</f>
@@ -2702,23 +2671,23 @@
       </c>
       <c r="F37" s="38"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="162"/>
-      <c r="C38" s="162"/>
+      <c r="B38" s="157"/>
+      <c r="C38" s="157"/>
       <c r="D38" s="23"/>
       <c r="E38" s="102"/>
       <c r="F38" s="38"/>
     </row>
-    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="212" t="s">
+    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="211" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="213"/>
-      <c r="C39" s="165"/>
-      <c r="D39" s="166">
+      <c r="B39" s="212"/>
+      <c r="C39" s="160"/>
+      <c r="D39" s="161">
         <v>205033.71</v>
       </c>
       <c r="E39" s="21" t="s">
@@ -2726,13 +2695,13 @@
       </c>
       <c r="F39" s="38"/>
     </row>
-    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="212" t="s">
+    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="211" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="213"/>
-      <c r="C40" s="165"/>
-      <c r="D40" s="166">
+      <c r="B40" s="212"/>
+      <c r="C40" s="160"/>
+      <c r="D40" s="161">
         <v>12020</v>
       </c>
       <c r="E40" s="21" t="str">
@@ -2741,12 +2710,12 @@
       </c>
       <c r="F40" s="38"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="162" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="157" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="162"/>
-      <c r="C41" s="162"/>
+      <c r="B41" s="157"/>
+      <c r="C41" s="157"/>
       <c r="D41" s="22"/>
       <c r="E41" s="32">
         <f>SUM(D39:D40)</f>
@@ -2754,17 +2723,17 @@
       </c>
       <c r="F41" s="38"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="163"/>
-      <c r="C42" s="163"/>
+      <c r="B42" s="158"/>
+      <c r="C42" s="158"/>
       <c r="D42" s="25"/>
       <c r="E42" s="103"/>
       <c r="F42" s="38"/>
     </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
         <v>145</v>
       </c>
@@ -2774,15 +2743,15 @@
         <v>1313151.8700000001</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F43" s="38"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B44" s="167"/>
+      <c r="B44" s="162"/>
       <c r="C44" s="33"/>
       <c r="D44" s="134">
         <v>0</v>
@@ -2790,42 +2759,42 @@
       <c r="E44" s="27"/>
       <c r="F44" s="38"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="212" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="211" t="s">
         <v>66</v>
       </c>
-      <c r="B45" s="213"/>
+      <c r="B45" s="212"/>
       <c r="C45" s="33"/>
       <c r="D45" s="134">
         <v>511264.75</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F45" s="38"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="168" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="163" t="s">
         <v>64</v>
       </c>
-      <c r="B46" s="169" t="s">
-        <v>190</v>
+      <c r="B46" s="164" t="s">
+        <v>185</v>
       </c>
       <c r="C46" s="33"/>
       <c r="D46" s="134">
         <v>62785.37</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F46" s="38"/>
     </row>
-    <row r="47" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="162" t="s">
+    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="157" t="s">
         <v>12</v>
       </c>
-      <c r="B47" s="162"/>
-      <c r="C47" s="162"/>
+      <c r="B47" s="157"/>
+      <c r="C47" s="157"/>
       <c r="D47" s="26"/>
       <c r="E47" s="104">
         <f>SUM(D43:D46)</f>
@@ -2833,21 +2802,21 @@
       </c>
       <c r="F47" s="38"/>
     </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="162"/>
-      <c r="C48" s="162"/>
+      <c r="B48" s="157"/>
+      <c r="C48" s="157"/>
       <c r="D48" s="22"/>
       <c r="E48" s="105"/>
       <c r="F48" s="38"/>
     </row>
-    <row r="49" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="200" t="s">
-        <v>196</v>
-      </c>
-      <c r="B49" s="201"/>
+    <row r="49" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="199" t="s">
+        <v>191</v>
+      </c>
+      <c r="B49" s="200"/>
       <c r="C49" s="33"/>
       <c r="D49" s="134">
         <v>0</v>
@@ -2855,92 +2824,92 @@
       <c r="E49" s="27"/>
       <c r="F49" s="38"/>
     </row>
-    <row r="50" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="170" t="s">
-        <v>183</v>
-      </c>
-      <c r="B50" s="171"/>
-      <c r="C50" s="161"/>
+    <row r="50" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="165" t="s">
+        <v>178</v>
+      </c>
+      <c r="B50" s="166"/>
+      <c r="C50" s="156"/>
       <c r="D50" s="134">
         <v>332362.82</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F50" s="138"/>
     </row>
-    <row r="51" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="172" t="s">
-        <v>185</v>
-      </c>
-      <c r="B51" s="171"/>
-      <c r="C51" s="161"/>
+    <row r="51" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="167" t="s">
+        <v>180</v>
+      </c>
+      <c r="B51" s="166"/>
+      <c r="C51" s="156"/>
       <c r="D51" s="134">
         <v>810000</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F51" s="138"/>
     </row>
-    <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="214" t="s">
-        <v>186</v>
-      </c>
-      <c r="B52" s="215"/>
-      <c r="C52" s="161"/>
+    <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="213" t="s">
+        <v>181</v>
+      </c>
+      <c r="B52" s="214"/>
+      <c r="C52" s="156"/>
       <c r="D52" s="134">
         <v>180000</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F52" s="138"/>
     </row>
-    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="172" t="s">
-        <v>187</v>
-      </c>
-      <c r="B53" s="171"/>
-      <c r="C53" s="161"/>
+    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="167" t="s">
+        <v>182</v>
+      </c>
+      <c r="B53" s="166"/>
+      <c r="C53" s="156"/>
       <c r="D53" s="134">
         <v>60000</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F53" s="38"/>
     </row>
-    <row r="54" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="200" t="s">
-        <v>212</v>
-      </c>
-      <c r="B54" s="201"/>
-      <c r="C54" s="161"/>
+    <row r="54" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="B54" s="200"/>
+      <c r="C54" s="156"/>
       <c r="D54" s="134">
         <v>40000</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F54" s="38"/>
     </row>
-    <row r="55" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="172" t="s">
+    <row r="55" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="167" t="s">
         <v>148</v>
       </c>
-      <c r="B55" s="171"/>
-      <c r="C55" s="161"/>
+      <c r="B55" s="166"/>
+      <c r="C55" s="156"/>
       <c r="D55" s="134">
         <v>31000</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F55" s="138"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="162" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="157" t="s">
         <v>0</v>
       </c>
       <c r="B56" s="29"/>
@@ -2952,7 +2921,7 @@
       </c>
       <c r="F56" s="38"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="29" t="s">
         <v>13</v>
       </c>
@@ -2962,38 +2931,38 @@
       <c r="E57" s="97"/>
       <c r="F57" s="38"/>
     </row>
-    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="200" t="s">
-        <v>197</v>
-      </c>
-      <c r="B58" s="201"/>
-      <c r="C58" s="161"/>
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="199" t="s">
+        <v>192</v>
+      </c>
+      <c r="B58" s="200"/>
+      <c r="C58" s="156"/>
       <c r="D58" s="137">
         <v>0</v>
       </c>
       <c r="E58" s="98"/>
       <c r="F58" s="38"/>
     </row>
-    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="172" t="s">
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="167" t="s">
         <v>149</v>
       </c>
-      <c r="B59" s="171" t="s">
-        <v>198</v>
-      </c>
-      <c r="C59" s="161"/>
+      <c r="B59" s="166" t="s">
+        <v>193</v>
+      </c>
+      <c r="C59" s="156"/>
       <c r="D59" s="133">
         <v>0</v>
       </c>
       <c r="E59" s="98"/>
       <c r="F59" s="38"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="162" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="B60" s="162"/>
-      <c r="C60" s="162"/>
+      <c r="B60" s="157"/>
+      <c r="C60" s="157"/>
       <c r="D60" s="22"/>
       <c r="E60" s="99">
         <f>SUM(D58:D59)</f>
@@ -3001,46 +2970,46 @@
       </c>
       <c r="F60" s="38"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B61" s="173"/>
-      <c r="C61" s="162"/>
+      <c r="B61" s="168"/>
+      <c r="C61" s="157"/>
       <c r="D61" s="30"/>
       <c r="E61" s="32"/>
       <c r="F61" s="38"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="B62" s="174"/>
-      <c r="C62" s="174"/>
-      <c r="D62" s="175">
+      <c r="B62" s="169"/>
+      <c r="C62" s="169"/>
+      <c r="D62" s="170">
         <v>69000</v>
       </c>
       <c r="E62" s="106"/>
       <c r="F62" s="38"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="B63" s="174"/>
-      <c r="C63" s="174"/>
-      <c r="D63" s="175">
+        <v>194</v>
+      </c>
+      <c r="B63" s="169"/>
+      <c r="C63" s="169"/>
+      <c r="D63" s="170">
         <v>109681.94</v>
       </c>
       <c r="E63" s="106"/>
       <c r="F63" s="38"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="176" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="171" t="s">
         <v>8</v>
       </c>
-      <c r="B64" s="176"/>
-      <c r="C64" s="176"/>
+      <c r="B64" s="171"/>
+      <c r="C64" s="171"/>
       <c r="D64" s="31"/>
       <c r="E64" s="32">
         <f>SUM(D62:D63)</f>
@@ -3048,7 +3017,7 @@
       </c>
       <c r="F64" s="38"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="33"/>
       <c r="B65" s="33"/>
       <c r="C65" s="33"/>
@@ -3056,39 +3025,39 @@
       <c r="E65" s="34"/>
       <c r="F65" s="38"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="177" t="s">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="172" t="s">
         <v>15</v>
       </c>
-      <c r="B66" s="177"/>
-      <c r="C66" s="177"/>
+      <c r="B66" s="172"/>
+      <c r="C66" s="172"/>
       <c r="D66" s="35"/>
       <c r="E66" s="36"/>
       <c r="F66" s="38"/>
     </row>
-    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="178"/>
+    <row r="67" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="173"/>
       <c r="B67" s="38"/>
       <c r="C67" s="38"/>
       <c r="D67" s="38"/>
       <c r="E67" s="39"/>
       <c r="F67" s="138"/>
     </row>
-    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="179" t="s">
+    <row r="68" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="174" t="s">
         <v>16</v>
       </c>
-      <c r="B68" s="180"/>
+      <c r="B68" s="175"/>
       <c r="C68" s="41"/>
       <c r="D68" s="41"/>
       <c r="E68" s="42">
         <f>(SUM(E21:E66))</f>
         <v>6221168.1700000009</v>
       </c>
-      <c r="F68" s="181"/>
+      <c r="F68" s="176"/>
       <c r="G68" s="40"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="38"/>
       <c r="B69" s="38"/>
       <c r="C69" s="38"/>
@@ -3096,7 +3065,7 @@
       <c r="E69" s="38"/>
       <c r="F69" s="38"/>
     </row>
-    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="38"/>
       <c r="B70" s="38"/>
       <c r="C70" s="38"/>
@@ -3105,25 +3074,25 @@
       <c r="F70" s="38"/>
       <c r="H70" s="44"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="182" t="s">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="177" t="s">
         <v>17</v>
       </c>
-      <c r="B71" s="183"/>
-      <c r="C71" s="184"/>
+      <c r="B71" s="178"/>
+      <c r="C71" s="179"/>
       <c r="D71" s="45"/>
       <c r="E71" s="46"/>
       <c r="F71" s="38"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="202"/>
-      <c r="B72" s="203"/>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="201"/>
+      <c r="B72" s="202"/>
       <c r="C72" s="33"/>
-      <c r="D72" s="185"/>
+      <c r="D72" s="180"/>
       <c r="E72" s="120"/>
       <c r="F72" s="38"/>
     </row>
-    <row r="73" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="38"/>
       <c r="B73" s="38"/>
       <c r="C73" s="38"/>
@@ -3131,20 +3100,20 @@
       <c r="E73" s="33"/>
       <c r="F73" s="38"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="186"/>
-      <c r="B74" s="187"/>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="181"/>
+      <c r="B74" s="182"/>
       <c r="C74" s="33"/>
       <c r="D74" s="28"/>
       <c r="E74" s="47"/>
       <c r="F74" s="38"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="188" t="s">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="183" t="s">
         <v>44</v>
       </c>
-      <c r="B75" s="189"/>
-      <c r="C75" s="189"/>
+      <c r="B75" s="184"/>
+      <c r="C75" s="184"/>
       <c r="D75" s="80"/>
       <c r="E75" s="107">
         <f>SUM(D72:D74)</f>
@@ -3152,7 +3121,7 @@
       </c>
       <c r="F75" s="38"/>
     </row>
-    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="38"/>
       <c r="B76" s="38"/>
       <c r="C76" s="38"/>
@@ -3160,19 +3129,19 @@
       <c r="E76" s="38"/>
       <c r="F76" s="38"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="177" t="s">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="172" t="s">
         <v>18</v>
       </c>
-      <c r="B77" s="177"/>
-      <c r="C77" s="177"/>
+      <c r="B77" s="172"/>
+      <c r="C77" s="172"/>
       <c r="D77" s="35"/>
       <c r="E77" s="110">
         <v>0</v>
       </c>
       <c r="F77" s="38"/>
     </row>
-    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="38"/>
       <c r="B78" s="38"/>
       <c r="C78" s="38"/>
@@ -3180,11 +3149,11 @@
       <c r="E78" s="38"/>
       <c r="F78" s="38"/>
     </row>
-    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="179" t="s">
+    <row r="79" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="174" t="s">
         <v>19</v>
       </c>
-      <c r="B79" s="180"/>
+      <c r="B79" s="175"/>
       <c r="C79" s="41"/>
       <c r="D79" s="41"/>
       <c r="E79" s="42">
@@ -3193,7 +3162,7 @@
       </c>
       <c r="F79" s="38"/>
     </row>
-    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="38"/>
       <c r="B80" s="38"/>
       <c r="C80" s="38"/>
@@ -3201,11 +3170,11 @@
       <c r="E80" s="38"/>
       <c r="F80" s="38"/>
     </row>
-    <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="190" t="s">
+    <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="185" t="s">
         <v>20</v>
       </c>
-      <c r="B81" s="191">
+      <c r="B81" s="186">
         <f>E68</f>
         <v>6221168.1700000009</v>
       </c>
@@ -3214,11 +3183,11 @@
       <c r="E81" s="38"/>
       <c r="F81" s="38"/>
     </row>
-    <row r="82" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="190" t="s">
+    <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="185" t="s">
         <v>21</v>
       </c>
-      <c r="B82" s="191">
+      <c r="B82" s="186">
         <f>E68-E66</f>
         <v>6221168.1700000009</v>
       </c>
@@ -3227,11 +3196,11 @@
       <c r="E82" s="38"/>
       <c r="F82" s="38"/>
     </row>
-    <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="190" t="s">
+    <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="185" t="s">
         <v>22</v>
       </c>
-      <c r="B83" s="191">
+      <c r="B83" s="186">
         <f>E79-E77</f>
         <v>0</v>
       </c>
@@ -3240,11 +3209,11 @@
       <c r="E83" s="38"/>
       <c r="F83" s="38"/>
     </row>
-    <row r="84" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="190" t="s">
+    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="185" t="s">
         <v>23</v>
       </c>
-      <c r="B84" s="191">
+      <c r="B84" s="186">
         <f>E79</f>
         <v>0</v>
       </c>
@@ -3253,7 +3222,7 @@
       <c r="E84" s="38"/>
       <c r="F84" s="38"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="38"/>
       <c r="B85" s="38"/>
       <c r="C85" s="38"/>
@@ -3261,7 +3230,7 @@
       <c r="E85" s="38"/>
       <c r="F85" s="38"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="38"/>
       <c r="B86" s="38"/>
       <c r="C86" s="38"/>
@@ -3269,11 +3238,11 @@
       <c r="E86" s="38"/>
       <c r="F86" s="38"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="192" t="s">
-        <v>209</v>
-      </c>
-      <c r="B87" s="193">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="187" t="s">
+        <v>204</v>
+      </c>
+      <c r="B87" s="188">
         <v>0</v>
       </c>
       <c r="C87" s="38"/>
@@ -3281,11 +3250,11 @@
       <c r="E87" s="38"/>
       <c r="F87" s="38"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="165" t="s">
-        <v>210</v>
-      </c>
-      <c r="B88" s="194">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="160" t="s">
+        <v>205</v>
+      </c>
+      <c r="B88" s="189">
         <v>6500000</v>
       </c>
       <c r="C88" s="38"/>
@@ -3293,19 +3262,19 @@
       <c r="E88" s="38"/>
       <c r="F88" s="38"/>
     </row>
-    <row r="89" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="165"/>
+    <row r="89" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="160"/>
       <c r="B89" s="139"/>
       <c r="C89" s="38"/>
       <c r="D89" s="38"/>
       <c r="E89" s="38"/>
       <c r="F89" s="38"/>
     </row>
-    <row r="90" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="195" t="s">
-        <v>201</v>
-      </c>
-      <c r="B90" s="196">
+    <row r="90" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="190" t="s">
+        <v>196</v>
+      </c>
+      <c r="B90" s="191">
         <f>B88</f>
         <v>6500000</v>
       </c>
@@ -3314,27 +3283,27 @@
       <c r="E90" s="38"/>
       <c r="F90" s="38"/>
     </row>
-    <row r="91" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="197"/>
-      <c r="B91" s="198"/>
+    <row r="91" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="192"/>
+      <c r="B91" s="193"/>
       <c r="C91" s="38"/>
       <c r="D91" s="38"/>
       <c r="E91" s="38"/>
       <c r="F91" s="38"/>
     </row>
-    <row r="92" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="197"/>
-      <c r="B92" s="198"/>
+    <row r="92" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="192"/>
+      <c r="B92" s="193"/>
       <c r="C92" s="38"/>
       <c r="D92" s="38"/>
       <c r="E92" s="38"/>
       <c r="F92" s="38"/>
     </row>
-    <row r="93" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="192" t="s">
+    <row r="93" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="187" t="s">
         <v>162</v>
       </c>
-      <c r="B93" s="193">
+      <c r="B93" s="188">
         <v>231400</v>
       </c>
       <c r="C93" s="38"/>
@@ -3342,11 +3311,11 @@
       <c r="E93" s="38"/>
       <c r="F93" s="38"/>
     </row>
-    <row r="94" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="165" t="s">
+    <row r="94" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="160" t="s">
         <v>163</v>
       </c>
-      <c r="B94" s="194">
+      <c r="B94" s="189">
         <v>0</v>
       </c>
       <c r="C94" s="38"/>
@@ -3354,8 +3323,8 @@
       <c r="E94" s="38"/>
       <c r="F94" s="38"/>
     </row>
-    <row r="95" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="165" t="s">
+    <row r="95" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="160" t="s">
         <v>164</v>
       </c>
       <c r="B95" s="139"/>
@@ -3364,11 +3333,11 @@
       <c r="E95" s="38"/>
       <c r="F95" s="38"/>
     </row>
-    <row r="96" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="195" t="s">
-        <v>201</v>
-      </c>
-      <c r="B96" s="196">
+    <row r="96" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="190" t="s">
+        <v>196</v>
+      </c>
+      <c r="B96" s="191">
         <f>SUM(B93:B95)</f>
         <v>231400</v>
       </c>
@@ -3377,19 +3346,19 @@
       <c r="E96" s="38"/>
       <c r="F96" s="38"/>
     </row>
-    <row r="97" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="197"/>
-      <c r="B97" s="198"/>
+    <row r="97" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="192"/>
+      <c r="B97" s="193"/>
       <c r="C97" s="38"/>
       <c r="D97" s="38"/>
       <c r="E97" s="38"/>
       <c r="F97" s="38"/>
     </row>
-    <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="192" t="s">
+    <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="187" t="s">
         <v>165</v>
       </c>
-      <c r="B98" s="193">
+      <c r="B98" s="188">
         <v>64328</v>
       </c>
       <c r="C98" s="38"/>
@@ -3397,11 +3366,11 @@
       <c r="E98" s="38"/>
       <c r="F98" s="38"/>
     </row>
-    <row r="99" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="165" t="s">
+    <row r="99" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="160" t="s">
         <v>163</v>
       </c>
-      <c r="B99" s="194">
+      <c r="B99" s="189">
         <v>0</v>
       </c>
       <c r="C99" s="38"/>
@@ -3409,9 +3378,9 @@
       <c r="E99" s="38"/>
       <c r="F99" s="38"/>
     </row>
-    <row r="100" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="165" t="s">
-        <v>211</v>
+    <row r="100" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="160" t="s">
+        <v>206</v>
       </c>
       <c r="B100" s="139">
         <v>-5910</v>
@@ -3421,11 +3390,11 @@
       <c r="E100" s="38"/>
       <c r="F100" s="38"/>
     </row>
-    <row r="101" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="195" t="s">
-        <v>201</v>
-      </c>
-      <c r="B101" s="196">
+    <row r="101" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="190" t="s">
+        <v>196</v>
+      </c>
+      <c r="B101" s="191">
         <f>SUM(B98:B100)</f>
         <v>58418</v>
       </c>
@@ -3434,16 +3403,16 @@
       <c r="E101" s="38"/>
       <c r="F101" s="38"/>
     </row>
-    <row r="102" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102"/>
       <c r="B102" s="48"/>
       <c r="C102" s="49"/>
       <c r="D102" s="108"/>
       <c r="E102" s="108"/>
     </row>
-    <row r="103" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="112" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B103" s="51">
         <v>3986543.73</v>
@@ -3452,7 +3421,7 @@
       <c r="D103" s="109"/>
       <c r="E103" s="109"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="24" t="s">
         <v>43</v>
       </c>
@@ -3463,7 +3432,7 @@
       <c r="D104" s="38"/>
       <c r="E104" s="38"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="24" t="s">
         <v>24</v>
       </c>
@@ -3475,7 +3444,7 @@
       <c r="E105" s="38"/>
       <c r="F105" s="48"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="24" t="s">
         <v>2</v>
       </c>
@@ -3487,9 +3456,9 @@
       <c r="E106" s="38"/>
       <c r="F106" s="48"/>
     </row>
-    <row r="107" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A107" s="24" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B107" s="96">
         <v>-6500000</v>
@@ -3498,9 +3467,9 @@
       <c r="E107" s="38"/>
       <c r="F107" s="48"/>
     </row>
-    <row r="108" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="24" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B108" s="139">
         <v>2026301.37</v>
@@ -3509,9 +3478,9 @@
       <c r="E108" s="38"/>
       <c r="F108" s="48"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="24" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B109" s="96">
         <v>-4703</v>
@@ -3520,9 +3489,9 @@
       <c r="E109" s="38"/>
       <c r="F109" s="48"/>
     </row>
-    <row r="110" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="24" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B110" s="96">
         <v>-156782</v>
@@ -3531,7 +3500,7 @@
       <c r="E110" s="38"/>
       <c r="F110" s="48"/>
     </row>
-    <row r="111" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="54" t="s">
         <v>47</v>
       </c>
@@ -3543,8 +3512,8 @@
       <c r="E111" s="40"/>
       <c r="F111" s="40"/>
     </row>
-    <row r="112" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="113" spans="1:13" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="113" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="141" t="s">
         <v>166</v>
       </c>
@@ -3555,22 +3524,22 @@
       <c r="D113" s="40"/>
       <c r="E113" s="40"/>
     </row>
-    <row r="114" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="199" t="s">
+    <row r="114" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A115" s="198" t="s">
         <v>25</v>
       </c>
-      <c r="B115" s="199"/>
-      <c r="C115" s="199"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="199"/>
-      <c r="B116" s="199"/>
-      <c r="C116" s="199"/>
-    </row>
-    <row r="117" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="198"/>
+      <c r="C115" s="198"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A116" s="198"/>
+      <c r="B116" s="198"/>
+      <c r="C116" s="198"/>
+    </row>
+    <row r="117" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="56" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B117" s="79">
         <v>160000</v>
@@ -3578,7 +3547,7 @@
       <c r="C117" s="57"/>
       <c r="D117" s="43"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="58" t="s">
         <v>0</v>
       </c>
@@ -3588,7 +3557,7 @@
       </c>
       <c r="C118" s="60"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M119" s="61"/>
     </row>
   </sheetData>
@@ -3619,28 +3588,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:R69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="13" width="14.42578125" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" customWidth="1"/>
-    <col min="17" max="17" width="8.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="13" width="14.44140625" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" customWidth="1"/>
+    <col min="17" max="17" width="8.5546875" customWidth="1"/>
     <col min="18" max="18" width="19" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="66"/>
       <c r="B1" s="127"/>
       <c r="C1" s="67"/>
@@ -3650,21 +3619,21 @@
       <c r="G1" s="127"/>
       <c r="H1" s="127"/>
       <c r="I1" s="127"/>
-      <c r="J1" s="216" t="str">
+      <c r="J1" s="241" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="216"/>
-      <c r="L1" s="216"/>
-      <c r="M1" s="216"/>
-      <c r="N1" s="216"/>
-      <c r="O1" s="216"/>
-      <c r="P1" s="217"/>
-    </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
+      <c r="P1" s="242"/>
+    </row>
+    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>167</v>
       </c>
@@ -3675,20 +3644,20 @@
       </c>
       <c r="D2" s="68"/>
       <c r="E2" s="68"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="226"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="249"/>
       <c r="H2" s="68"/>
       <c r="I2" s="68"/>
-      <c r="J2" s="218"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="218"/>
-      <c r="M2" s="218"/>
-      <c r="N2" s="218"/>
-      <c r="O2" s="218"/>
-      <c r="P2" s="219"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="M2" s="243"/>
+      <c r="N2" s="243"/>
+      <c r="O2" s="243"/>
+      <c r="P2" s="244"/>
       <c r="Q2" s="62"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
@@ -3702,17 +3671,17 @@
       <c r="G3" s="132"/>
       <c r="H3" s="68"/>
       <c r="I3" s="68"/>
-      <c r="J3" s="218"/>
-      <c r="K3" s="218"/>
-      <c r="L3" s="218"/>
-      <c r="M3" s="218"/>
-      <c r="N3" s="218"/>
-      <c r="O3" s="218"/>
-      <c r="P3" s="219"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
+      <c r="M3" s="243"/>
+      <c r="N3" s="243"/>
+      <c r="O3" s="243"/>
+      <c r="P3" s="244"/>
       <c r="Q3" s="62"/>
       <c r="R3" s="40"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>173</v>
       </c>
@@ -3726,17 +3695,17 @@
       <c r="G4" s="132"/>
       <c r="H4" s="68"/>
       <c r="I4" s="68"/>
-      <c r="J4" s="218"/>
-      <c r="K4" s="218"/>
-      <c r="L4" s="218"/>
-      <c r="M4" s="218"/>
-      <c r="N4" s="218"/>
-      <c r="O4" s="218"/>
-      <c r="P4" s="219"/>
+      <c r="J4" s="243"/>
+      <c r="K4" s="243"/>
+      <c r="L4" s="243"/>
+      <c r="M4" s="243"/>
+      <c r="N4" s="243"/>
+      <c r="O4" s="243"/>
+      <c r="P4" s="244"/>
       <c r="Q4" s="62"/>
       <c r="R4" s="40"/>
     </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="143" t="s">
         <v>168</v>
       </c>
@@ -3750,203 +3719,203 @@
       <c r="G5" s="70"/>
       <c r="H5" s="69"/>
       <c r="I5" s="69"/>
-      <c r="J5" s="220"/>
-      <c r="K5" s="220"/>
-      <c r="L5" s="220"/>
-      <c r="M5" s="220"/>
-      <c r="N5" s="220"/>
-      <c r="O5" s="220"/>
-      <c r="P5" s="221"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="M5" s="245"/>
+      <c r="N5" s="245"/>
+      <c r="O5" s="245"/>
+      <c r="P5" s="246"/>
       <c r="Q5" s="62"/>
     </row>
-    <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="228" t="s">
+    <row r="6" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="216" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="229"/>
-      <c r="C6" s="230"/>
-      <c r="D6" s="230"/>
-      <c r="E6" s="230"/>
-      <c r="F6" s="230"/>
-      <c r="G6" s="230"/>
-      <c r="H6" s="230"/>
-      <c r="I6" s="230"/>
-      <c r="J6" s="230"/>
-      <c r="K6" s="230"/>
-      <c r="L6" s="230"/>
-      <c r="M6" s="230"/>
-      <c r="N6" s="230"/>
-      <c r="O6" s="230"/>
-      <c r="P6" s="231"/>
+      <c r="B6" s="217"/>
+      <c r="C6" s="218"/>
+      <c r="D6" s="218"/>
+      <c r="E6" s="218"/>
+      <c r="F6" s="218"/>
+      <c r="G6" s="218"/>
+      <c r="H6" s="218"/>
+      <c r="I6" s="218"/>
+      <c r="J6" s="218"/>
+      <c r="K6" s="218"/>
+      <c r="L6" s="218"/>
+      <c r="M6" s="218"/>
+      <c r="N6" s="218"/>
+      <c r="O6" s="218"/>
+      <c r="P6" s="219"/>
       <c r="Q6" s="62"/>
     </row>
-    <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="232"/>
-      <c r="B7" s="233"/>
-      <c r="C7" s="233"/>
-      <c r="D7" s="233"/>
-      <c r="E7" s="233"/>
-      <c r="F7" s="233"/>
-      <c r="G7" s="233"/>
-      <c r="H7" s="233"/>
-      <c r="I7" s="233"/>
-      <c r="J7" s="233"/>
-      <c r="K7" s="233"/>
-      <c r="L7" s="233"/>
-      <c r="M7" s="233"/>
-      <c r="N7" s="233"/>
-      <c r="O7" s="233"/>
-      <c r="P7" s="234"/>
+    <row r="7" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="220"/>
+      <c r="B7" s="221"/>
+      <c r="C7" s="221"/>
+      <c r="D7" s="221"/>
+      <c r="E7" s="221"/>
+      <c r="F7" s="221"/>
+      <c r="G7" s="221"/>
+      <c r="H7" s="221"/>
+      <c r="I7" s="221"/>
+      <c r="J7" s="221"/>
+      <c r="K7" s="221"/>
+      <c r="L7" s="221"/>
+      <c r="M7" s="221"/>
+      <c r="N7" s="221"/>
+      <c r="O7" s="221"/>
+      <c r="P7" s="222"/>
       <c r="Q7" s="62"/>
     </row>
-    <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="232"/>
-      <c r="B8" s="233"/>
-      <c r="C8" s="233"/>
-      <c r="D8" s="233"/>
-      <c r="E8" s="233"/>
-      <c r="F8" s="233"/>
-      <c r="G8" s="233"/>
-      <c r="H8" s="233"/>
-      <c r="I8" s="233"/>
-      <c r="J8" s="233"/>
-      <c r="K8" s="233"/>
-      <c r="L8" s="233"/>
-      <c r="M8" s="233"/>
-      <c r="N8" s="233"/>
-      <c r="O8" s="233"/>
-      <c r="P8" s="234"/>
+    <row r="8" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="220"/>
+      <c r="B8" s="221"/>
+      <c r="C8" s="221"/>
+      <c r="D8" s="221"/>
+      <c r="E8" s="221"/>
+      <c r="F8" s="221"/>
+      <c r="G8" s="221"/>
+      <c r="H8" s="221"/>
+      <c r="I8" s="221"/>
+      <c r="J8" s="221"/>
+      <c r="K8" s="221"/>
+      <c r="L8" s="221"/>
+      <c r="M8" s="221"/>
+      <c r="N8" s="221"/>
+      <c r="O8" s="221"/>
+      <c r="P8" s="222"/>
       <c r="Q8" s="62"/>
     </row>
-    <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="232"/>
-      <c r="B9" s="233"/>
-      <c r="C9" s="233"/>
-      <c r="D9" s="233"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="233"/>
-      <c r="L9" s="233"/>
-      <c r="M9" s="233"/>
-      <c r="N9" s="233"/>
-      <c r="O9" s="233"/>
-      <c r="P9" s="234"/>
+    <row r="9" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="220"/>
+      <c r="B9" s="221"/>
+      <c r="C9" s="221"/>
+      <c r="D9" s="221"/>
+      <c r="E9" s="221"/>
+      <c r="F9" s="221"/>
+      <c r="G9" s="221"/>
+      <c r="H9" s="221"/>
+      <c r="I9" s="221"/>
+      <c r="J9" s="221"/>
+      <c r="K9" s="221"/>
+      <c r="L9" s="221"/>
+      <c r="M9" s="221"/>
+      <c r="N9" s="221"/>
+      <c r="O9" s="221"/>
+      <c r="P9" s="222"/>
       <c r="Q9" s="62"/>
     </row>
-    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="235"/>
-      <c r="B10" s="236"/>
-      <c r="C10" s="236"/>
-      <c r="D10" s="236"/>
-      <c r="E10" s="236"/>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="236"/>
-      <c r="J10" s="236"/>
-      <c r="K10" s="236"/>
-      <c r="L10" s="236"/>
-      <c r="M10" s="236"/>
-      <c r="N10" s="236"/>
-      <c r="O10" s="236"/>
-      <c r="P10" s="237"/>
-    </row>
-    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="244" t="s">
+    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="223"/>
+      <c r="B10" s="224"/>
+      <c r="C10" s="224"/>
+      <c r="D10" s="224"/>
+      <c r="E10" s="224"/>
+      <c r="F10" s="224"/>
+      <c r="G10" s="224"/>
+      <c r="H10" s="224"/>
+      <c r="I10" s="224"/>
+      <c r="J10" s="224"/>
+      <c r="K10" s="224"/>
+      <c r="L10" s="224"/>
+      <c r="M10" s="224"/>
+      <c r="N10" s="224"/>
+      <c r="O10" s="224"/>
+      <c r="P10" s="225"/>
+    </row>
+    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="234" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="245"/>
-      <c r="C11" s="245"/>
-      <c r="D11" s="245"/>
-      <c r="E11" s="245"/>
-      <c r="F11" s="245"/>
-      <c r="G11" s="245"/>
-      <c r="H11" s="245"/>
-      <c r="I11" s="245"/>
-      <c r="J11" s="245"/>
-      <c r="K11" s="245"/>
-      <c r="L11" s="245"/>
-      <c r="M11" s="245"/>
-      <c r="N11" s="245"/>
-      <c r="O11" s="245"/>
-      <c r="P11" s="246"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="238" t="s">
+      <c r="B11" s="235"/>
+      <c r="C11" s="235"/>
+      <c r="D11" s="235"/>
+      <c r="E11" s="235"/>
+      <c r="F11" s="235"/>
+      <c r="G11" s="235"/>
+      <c r="H11" s="235"/>
+      <c r="I11" s="235"/>
+      <c r="J11" s="235"/>
+      <c r="K11" s="235"/>
+      <c r="L11" s="235"/>
+      <c r="M11" s="235"/>
+      <c r="N11" s="235"/>
+      <c r="O11" s="235"/>
+      <c r="P11" s="236"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="226" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="249" t="s">
+      <c r="B12" s="239" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="240" t="s">
+      <c r="C12" s="228" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="240" t="s">
+      <c r="D12" s="228" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="240" t="s">
+      <c r="E12" s="228" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="222" t="s">
+      <c r="F12" s="230" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="240" t="s">
+      <c r="G12" s="228" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="242" t="s">
+      <c r="H12" s="232" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="222" t="s">
+      <c r="I12" s="230" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="222" t="s">
+      <c r="J12" s="230" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="222" t="s">
+      <c r="K12" s="230" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="249" t="s">
+      <c r="L12" s="239" t="s">
         <v>172</v>
       </c>
-      <c r="M12" s="222" t="s">
+      <c r="M12" s="230" t="s">
         <v>169</v>
       </c>
-      <c r="N12" s="247" t="s">
-        <v>214</v>
+      <c r="N12" s="237" t="s">
+        <v>209</v>
       </c>
       <c r="O12" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="224" t="s">
+      <c r="P12" s="247" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="239"/>
-      <c r="B13" s="250"/>
-      <c r="C13" s="241"/>
-      <c r="D13" s="241"/>
-      <c r="E13" s="241"/>
-      <c r="F13" s="223"/>
-      <c r="G13" s="241"/>
-      <c r="H13" s="243"/>
-      <c r="I13" s="223"/>
-      <c r="J13" s="223"/>
-      <c r="K13" s="223"/>
-      <c r="L13" s="250"/>
-      <c r="M13" s="223"/>
-      <c r="N13" s="248"/>
+    <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="227"/>
+      <c r="B13" s="240"/>
+      <c r="C13" s="229"/>
+      <c r="D13" s="229"/>
+      <c r="E13" s="229"/>
+      <c r="F13" s="231"/>
+      <c r="G13" s="229"/>
+      <c r="H13" s="233"/>
+      <c r="I13" s="231"/>
+      <c r="J13" s="231"/>
+      <c r="K13" s="231"/>
+      <c r="L13" s="240"/>
+      <c r="M13" s="231"/>
+      <c r="N13" s="238"/>
       <c r="O13" s="94" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="P13" s="225"/>
-    </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P13" s="248"/>
+    </row>
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="83">
         <v>1</v>
       </c>
@@ -4004,7 +3973,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="83">
         <v>2</v>
       </c>
@@ -4065,7 +4034,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="83">
         <v>3</v>
       </c>
@@ -4125,10 +4094,10 @@
         <v>0.03</v>
       </c>
       <c r="R16" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="83">
         <v>4</v>
       </c>
@@ -4189,17 +4158,17 @@
         <v>0.04</v>
       </c>
       <c r="R17" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="83">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="256">
         <v>5</v>
       </c>
-      <c r="B18" s="130" t="s">
+      <c r="B18" s="257" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="72" t="s">
+      <c r="C18" s="258" t="s">
         <v>121</v>
       </c>
       <c r="D18" s="77" t="s">
@@ -4253,7 +4222,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="83">
         <v>6</v>
       </c>
@@ -4264,7 +4233,7 @@
         <v>118</v>
       </c>
       <c r="D19" s="72" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E19" s="74">
         <v>2.54</v>
@@ -4314,7 +4283,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="83">
         <v>7</v>
       </c>
@@ -4373,7 +4342,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="83">
         <v>8</v>
       </c>
@@ -4432,7 +4401,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="83">
         <v>9</v>
       </c>
@@ -4493,7 +4462,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="83">
         <v>10</v>
       </c>
@@ -4552,7 +4521,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="83">
         <v>11</v>
       </c>
@@ -4613,7 +4582,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="83">
         <v>12</v>
       </c>
@@ -4674,57 +4643,57 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="151">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="146">
         <v>13</v>
       </c>
-      <c r="B26" s="152" t="s">
+      <c r="B26" s="147" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="153" t="s">
-        <v>202</v>
-      </c>
-      <c r="D26" s="154"/>
-      <c r="E26" s="155">
+      <c r="C26" s="148" t="s">
+        <v>197</v>
+      </c>
+      <c r="D26" s="149"/>
+      <c r="E26" s="150">
         <v>5.19</v>
       </c>
-      <c r="F26" s="156">
+      <c r="F26" s="151">
         <v>389250.13</v>
       </c>
-      <c r="G26" s="156">
+      <c r="G26" s="151">
         <f>407108-G45</f>
         <v>401107.68</v>
       </c>
-      <c r="H26" s="157">
+      <c r="H26" s="152">
         <f t="shared" si="0"/>
         <v>-11857.549999999988</v>
       </c>
-      <c r="I26" s="157">
+      <c r="I26" s="152">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="158">
+      <c r="J26" s="153">
         <f t="shared" si="4"/>
         <v>254657.19958200003</v>
       </c>
-      <c r="K26" s="158">
+      <c r="K26" s="153">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L26" s="158">
+      <c r="L26" s="153">
         <f t="shared" si="5"/>
         <v>9488.5142190000006</v>
       </c>
-      <c r="M26" s="158">
+      <c r="M26" s="153">
         <f t="shared" si="6"/>
         <v>68152.58205300002</v>
       </c>
-      <c r="N26" s="158"/>
-      <c r="O26" s="159">
+      <c r="N26" s="153"/>
+      <c r="O26" s="154">
         <f t="shared" si="7"/>
         <v>320441.13</v>
       </c>
-      <c r="P26" s="160">
+      <c r="P26" s="155">
         <f t="shared" si="2"/>
         <v>330054.13</v>
       </c>
@@ -4733,57 +4702,57 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="151">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
         <v>14</v>
       </c>
-      <c r="B27" s="152" t="s">
+      <c r="B27" s="147" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="153" t="s">
+      <c r="C27" s="148" t="s">
         <v>128</v>
       </c>
-      <c r="D27" s="154"/>
-      <c r="E27" s="155">
+      <c r="D27" s="149"/>
+      <c r="E27" s="150">
         <v>3.4</v>
       </c>
-      <c r="F27" s="156">
+      <c r="F27" s="151">
         <v>255618.14</v>
       </c>
-      <c r="G27" s="156">
+      <c r="G27" s="151">
         <f>328368.22-G51</f>
         <v>255617.83999999997</v>
       </c>
-      <c r="H27" s="157">
+      <c r="H27" s="152">
         <f t="shared" si="0"/>
         <v>0.30000000004656613</v>
       </c>
-      <c r="I27" s="157">
+      <c r="I27" s="152">
         <f t="shared" si="3"/>
         <v>9.0000000013969843E-3</v>
       </c>
-      <c r="J27" s="158">
+      <c r="J27" s="153">
         <f t="shared" si="4"/>
         <v>166827.45251999999</v>
       </c>
-      <c r="K27" s="158">
+      <c r="K27" s="153">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L27" s="158">
+      <c r="L27" s="153">
         <f t="shared" si="5"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M27" s="158">
+      <c r="M27" s="153">
         <f t="shared" si="6"/>
         <v>44647.16358</v>
       </c>
-      <c r="N27" s="158"/>
-      <c r="O27" s="159">
+      <c r="N27" s="153"/>
+      <c r="O27" s="154">
         <f t="shared" si="7"/>
         <v>217691.14</v>
       </c>
-      <c r="P27" s="160">
+      <c r="P27" s="155">
         <f t="shared" si="2"/>
         <v>224222.14</v>
       </c>
@@ -4792,7 +4761,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="83">
         <v>15</v>
       </c>
@@ -4853,7 +4822,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="83">
         <v>16</v>
       </c>
@@ -4912,7 +4881,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="83">
         <v>17</v>
       </c>
@@ -4973,7 +4942,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="83">
         <v>18</v>
       </c>
@@ -5029,7 +4998,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="83">
         <v>19</v>
       </c>
@@ -5089,7 +5058,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="83">
         <v>20</v>
       </c>
@@ -5145,7 +5114,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="83">
         <v>21</v>
       </c>
@@ -5206,7 +5175,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="83">
         <f>A34+1</f>
         <v>22</v>
@@ -5268,7 +5237,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="83">
         <f t="shared" ref="A36:A59" si="12">A35+1</f>
         <v>23</v>
@@ -5329,7 +5298,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="83">
         <f t="shared" si="12"/>
         <v>24</v>
@@ -5389,15 +5358,15 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" s="83">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A38" s="195">
         <f t="shared" si="12"/>
         <v>25</v>
       </c>
-      <c r="B38" s="130" t="s">
+      <c r="B38" s="196" t="s">
         <v>95</v>
       </c>
-      <c r="C38" s="78" t="s">
+      <c r="C38" s="197" t="s">
         <v>136</v>
       </c>
       <c r="D38" s="77"/>
@@ -5451,7 +5420,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="83">
         <f t="shared" si="12"/>
         <v>26</v>
@@ -5511,7 +5480,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="83">
         <f t="shared" si="12"/>
         <v>27</v>
@@ -5570,7 +5539,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="83">
         <f t="shared" si="12"/>
         <v>28</v>
@@ -5632,7 +5601,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="83">
         <f t="shared" si="12"/>
         <v>29</v>
@@ -5694,7 +5663,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="83">
         <f t="shared" si="12"/>
         <v>30</v>
@@ -5753,7 +5722,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="83">
         <f t="shared" si="12"/>
         <v>31</v>
@@ -5815,10 +5784,10 @@
         <v>0.31000000000000011</v>
       </c>
       <c r="R44" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="83">
         <f t="shared" si="12"/>
         <v>32</v>
@@ -5878,7 +5847,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="83">
         <f t="shared" si="12"/>
         <v>33</v>
@@ -5932,7 +5901,7 @@
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="83">
         <f t="shared" si="12"/>
         <v>34</v>
@@ -5992,7 +5961,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="121">
         <f t="shared" si="12"/>
         <v>35</v>
@@ -6051,7 +6020,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="83">
         <f t="shared" si="12"/>
         <v>36</v>
@@ -6111,7 +6080,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="83">
         <f t="shared" si="12"/>
         <v>37</v>
@@ -6168,7 +6137,7 @@
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="83">
         <f t="shared" si="12"/>
         <v>38</v>
@@ -6228,7 +6197,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="83">
         <f t="shared" si="12"/>
         <v>39</v>
@@ -6290,7 +6259,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="83">
         <f t="shared" si="12"/>
         <v>40</v>
@@ -6352,7 +6321,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="83">
         <f t="shared" si="12"/>
         <v>41</v>
@@ -6414,7 +6383,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="83">
         <f t="shared" si="12"/>
         <v>42</v>
@@ -6473,10 +6442,10 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="R55" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="83">
         <f t="shared" si="12"/>
         <v>43</v>
@@ -6533,7 +6502,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="83">
         <f t="shared" si="12"/>
         <v>44</v>
@@ -6590,7 +6559,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="83">
         <f t="shared" si="12"/>
         <v>45</v>
@@ -6652,7 +6621,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="83">
         <f t="shared" si="12"/>
         <v>46</v>
@@ -6714,7 +6683,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="83"/>
       <c r="B60" s="130"/>
       <c r="C60" s="72"/>
@@ -6733,7 +6702,7 @@
       <c r="P60" s="91"/>
       <c r="Q60" s="40"/>
     </row>
-    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="84"/>
       <c r="B61" s="131"/>
       <c r="C61" s="85"/>
@@ -6784,109 +6753,105 @@
         <v>9454363.8100000005</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="64"/>
       <c r="D62" s="64"/>
     </row>
-    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="227" t="s">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C64" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="227"/>
-      <c r="E64" s="227"/>
-      <c r="F64" s="227"/>
-      <c r="G64" s="227"/>
-      <c r="H64" s="227"/>
-      <c r="I64" s="227"/>
-      <c r="J64" s="227"/>
-      <c r="K64" s="227"/>
-      <c r="L64" s="227"/>
-      <c r="M64" s="227"/>
-      <c r="N64" s="227"/>
-      <c r="O64" s="227"/>
-    </row>
-    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="227"/>
-      <c r="D65" s="227"/>
-      <c r="E65" s="227"/>
-      <c r="F65" s="227"/>
-      <c r="G65" s="227"/>
-      <c r="H65" s="227"/>
-      <c r="I65" s="227"/>
-      <c r="J65" s="227"/>
-      <c r="K65" s="227"/>
-      <c r="L65" s="227"/>
-      <c r="M65" s="227"/>
-      <c r="N65" s="227"/>
-      <c r="O65" s="227"/>
-    </row>
-    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="227"/>
-      <c r="D66" s="227"/>
-      <c r="E66" s="227"/>
-      <c r="F66" s="227"/>
-      <c r="G66" s="227"/>
-      <c r="H66" s="227"/>
-      <c r="I66" s="227"/>
-      <c r="J66" s="227"/>
-      <c r="K66" s="227"/>
-      <c r="L66" s="227"/>
-      <c r="M66" s="227"/>
-      <c r="N66" s="227"/>
-      <c r="O66" s="227"/>
-    </row>
-    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="227"/>
-      <c r="D67" s="227"/>
-      <c r="E67" s="227"/>
-      <c r="F67" s="227"/>
-      <c r="G67" s="227"/>
-      <c r="H67" s="227"/>
-      <c r="I67" s="227"/>
-      <c r="J67" s="227"/>
-      <c r="K67" s="227"/>
-      <c r="L67" s="227"/>
-      <c r="M67" s="227"/>
-      <c r="N67" s="227"/>
-      <c r="O67" s="227"/>
-    </row>
-    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="227"/>
-      <c r="D68" s="227"/>
-      <c r="E68" s="227"/>
-      <c r="F68" s="227"/>
-      <c r="G68" s="227"/>
-      <c r="H68" s="227"/>
-      <c r="I68" s="227"/>
-      <c r="J68" s="227"/>
-      <c r="K68" s="227"/>
-      <c r="L68" s="227"/>
-      <c r="M68" s="227"/>
-      <c r="N68" s="227"/>
-      <c r="O68" s="227"/>
-    </row>
-    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="227"/>
-      <c r="D69" s="227"/>
-      <c r="E69" s="227"/>
-      <c r="F69" s="227"/>
-      <c r="G69" s="227"/>
-      <c r="H69" s="227"/>
-      <c r="I69" s="227"/>
-      <c r="J69" s="227"/>
-      <c r="K69" s="227"/>
-      <c r="L69" s="227"/>
-      <c r="M69" s="227"/>
-      <c r="N69" s="227"/>
-      <c r="O69" s="227"/>
+      <c r="D64" s="215"/>
+      <c r="E64" s="215"/>
+      <c r="F64" s="215"/>
+      <c r="G64" s="215"/>
+      <c r="H64" s="215"/>
+      <c r="I64" s="215"/>
+      <c r="J64" s="215"/>
+      <c r="K64" s="215"/>
+      <c r="L64" s="215"/>
+      <c r="M64" s="215"/>
+      <c r="N64" s="215"/>
+      <c r="O64" s="215"/>
+    </row>
+    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C65" s="215"/>
+      <c r="D65" s="215"/>
+      <c r="E65" s="215"/>
+      <c r="F65" s="215"/>
+      <c r="G65" s="215"/>
+      <c r="H65" s="215"/>
+      <c r="I65" s="215"/>
+      <c r="J65" s="215"/>
+      <c r="K65" s="215"/>
+      <c r="L65" s="215"/>
+      <c r="M65" s="215"/>
+      <c r="N65" s="215"/>
+      <c r="O65" s="215"/>
+    </row>
+    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C66" s="215"/>
+      <c r="D66" s="215"/>
+      <c r="E66" s="215"/>
+      <c r="F66" s="215"/>
+      <c r="G66" s="215"/>
+      <c r="H66" s="215"/>
+      <c r="I66" s="215"/>
+      <c r="J66" s="215"/>
+      <c r="K66" s="215"/>
+      <c r="L66" s="215"/>
+      <c r="M66" s="215"/>
+      <c r="N66" s="215"/>
+      <c r="O66" s="215"/>
+    </row>
+    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C67" s="215"/>
+      <c r="D67" s="215"/>
+      <c r="E67" s="215"/>
+      <c r="F67" s="215"/>
+      <c r="G67" s="215"/>
+      <c r="H67" s="215"/>
+      <c r="I67" s="215"/>
+      <c r="J67" s="215"/>
+      <c r="K67" s="215"/>
+      <c r="L67" s="215"/>
+      <c r="M67" s="215"/>
+      <c r="N67" s="215"/>
+      <c r="O67" s="215"/>
+    </row>
+    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C68" s="215"/>
+      <c r="D68" s="215"/>
+      <c r="E68" s="215"/>
+      <c r="F68" s="215"/>
+      <c r="G68" s="215"/>
+      <c r="H68" s="215"/>
+      <c r="I68" s="215"/>
+      <c r="J68" s="215"/>
+      <c r="K68" s="215"/>
+      <c r="L68" s="215"/>
+      <c r="M68" s="215"/>
+      <c r="N68" s="215"/>
+      <c r="O68" s="215"/>
+    </row>
+    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C69" s="215"/>
+      <c r="D69" s="215"/>
+      <c r="E69" s="215"/>
+      <c r="F69" s="215"/>
+      <c r="G69" s="215"/>
+      <c r="H69" s="215"/>
+      <c r="I69" s="215"/>
+      <c r="J69" s="215"/>
+      <c r="K69" s="215"/>
+      <c r="L69" s="215"/>
+      <c r="M69" s="215"/>
+      <c r="N69" s="215"/>
+      <c r="O69" s="215"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
     <mergeCell ref="J1:P5"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="P12:P13"/>
@@ -6903,6 +6868,10 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6912,17 +6881,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="C3:M17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C3:L17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="20"/>
     </row>
-    <row r="4" spans="3:13" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="116" t="s">
         <v>51</v>
       </c>
@@ -6938,7 +6907,7 @@
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
     </row>
-    <row r="5" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="118" t="s">
         <v>52</v>
       </c>
@@ -6949,14 +6918,11 @@
       <c r="G5" t="s">
         <v>54</v>
       </c>
-      <c r="H5" t="s">
-        <v>175</v>
-      </c>
       <c r="J5" s="115"/>
-      <c r="K5" s="150"/>
+      <c r="K5" s="194"/>
       <c r="L5" s="20"/>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C6" s="118" t="s">
         <v>55</v>
       </c>
@@ -6970,50 +6936,51 @@
         <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="J6" s="115"/>
-      <c r="K6" s="150"/>
+      <c r="K6" s="194"/>
       <c r="L6" s="20"/>
     </row>
-    <row r="7" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C7" s="37" t="s">
         <v>58</v>
       </c>
       <c r="J7" s="115"/>
-      <c r="K7" s="150"/>
+      <c r="K7" s="194"/>
       <c r="L7" s="20"/>
     </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C8" s="251" t="s">
-        <v>176</v>
-      </c>
-      <c r="D8" s="252"/>
-      <c r="E8" s="252"/>
-      <c r="F8" s="252"/>
-      <c r="G8" s="252"/>
-      <c r="H8" s="252"/>
-      <c r="I8" s="252"/>
-      <c r="J8" s="253"/>
-      <c r="K8" s="20"/>
+    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C8" s="250" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" s="251"/>
+      <c r="E8" s="251"/>
+      <c r="F8" s="251"/>
+      <c r="G8" s="251"/>
+      <c r="H8" s="251"/>
+      <c r="I8" s="251"/>
+      <c r="J8" s="252"/>
+      <c r="K8" s="194"/>
       <c r="L8" s="20"/>
     </row>
-    <row r="9" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="254"/>
-      <c r="D9" s="255"/>
-      <c r="E9" s="255"/>
-      <c r="F9" s="255"/>
-      <c r="G9" s="255"/>
-      <c r="H9" s="255"/>
-      <c r="I9" s="255"/>
-      <c r="J9" s="256"/>
-    </row>
-    <row r="11" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="146" t="s">
+    <row r="9" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C9" s="253"/>
+      <c r="D9" s="254"/>
+      <c r="E9" s="254"/>
+      <c r="F9" s="254"/>
+      <c r="G9" s="254"/>
+      <c r="H9" s="254"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="194"/>
+    </row>
+    <row r="11" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C12" s="259" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="147">
+      <c r="D12" s="260">
         <v>1</v>
       </c>
       <c r="E12" s="113"/>
@@ -7023,30 +6990,24 @@
       <c r="I12" s="113"/>
       <c r="J12" s="114"/>
     </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="148" t="s">
+    <row r="13" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C13" s="261" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="149"/>
+      <c r="D13" s="262"/>
       <c r="E13" t="s">
         <v>53</v>
       </c>
       <c r="G13" t="s">
         <v>54</v>
       </c>
-      <c r="H13" t="s">
-        <v>178</v>
-      </c>
       <c r="J13" s="115"/>
-      <c r="K13" s="150"/>
-      <c r="L13" s="150"/>
-      <c r="M13" s="150"/>
-    </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="148" t="s">
+    </row>
+    <row r="14" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C14" s="261" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="149" t="s">
+      <c r="D14" s="262" t="s">
         <v>56</v>
       </c>
       <c r="E14" t="s">
@@ -7056,46 +7017,37 @@
         <v>28</v>
       </c>
       <c r="H14" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="J14" s="115"/>
-      <c r="K14" s="150"/>
-      <c r="L14" s="150"/>
-      <c r="M14" s="150"/>
-    </row>
-    <row r="15" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="37" t="s">
         <v>58</v>
       </c>
       <c r="J15" s="115"/>
-      <c r="K15" s="150"/>
-      <c r="L15" s="150"/>
-      <c r="M15" s="150"/>
-    </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="251" t="s">
-        <v>180</v>
-      </c>
-      <c r="D16" s="252"/>
-      <c r="E16" s="252"/>
-      <c r="F16" s="252"/>
-      <c r="G16" s="252"/>
-      <c r="H16" s="252"/>
-      <c r="I16" s="252"/>
-      <c r="J16" s="253"/>
-      <c r="K16" s="150"/>
-      <c r="L16" s="150"/>
-      <c r="M16" s="150"/>
-    </row>
-    <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="254"/>
-      <c r="D17" s="255"/>
-      <c r="E17" s="255"/>
-      <c r="F17" s="255"/>
-      <c r="G17" s="255"/>
-      <c r="H17" s="255"/>
-      <c r="I17" s="255"/>
-      <c r="J17" s="256"/>
+    </row>
+    <row r="16" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C16" s="250" t="s">
+        <v>213</v>
+      </c>
+      <c r="D16" s="251"/>
+      <c r="E16" s="251"/>
+      <c r="F16" s="251"/>
+      <c r="G16" s="251"/>
+      <c r="H16" s="251"/>
+      <c r="I16" s="251"/>
+      <c r="J16" s="252"/>
+    </row>
+    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="253"/>
+      <c r="D17" s="254"/>
+      <c r="E17" s="254"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="254"/>
+      <c r="J17" s="255"/>
     </row>
   </sheetData>
   <mergeCells count="2">
